--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -10118,7 +10118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16285,6 +16285,218 @@
           <t>https://github.com/gasharper/PyramidFlow</t>
         </is>
       </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>Zoom In, Reason Out: Efficient Far-field Anomaly Detection in Expressway Surveillance Vide</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Xiaowei Mao, Bowen Sui, Weijie Zhang, Yawen Yang, Shengnan Guo, Shilong Zhao, Jiaqi Lin, Tingrui Wu</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="21" t="n"/>
+      <c r="J83" s="21" t="n"/>
+      <c r="K83" s="21" t="n"/>
+      <c r="L83" s="21" t="n"/>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N83" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.23724</t>
+        </is>
+      </c>
+      <c r="O83" s="23" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>Learning to Identify Out-of-Distribution Objects for 3D LiDAR Anomaly Segmentation</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>Simone Mosco, Daniel Fusaro, Alberto Pretto</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="21" t="n"/>
+      <c r="J84" s="21" t="n"/>
+      <c r="K84" s="21" t="n"/>
+      <c r="L84" s="21" t="n"/>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N84" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.23604</t>
+        </is>
+      </c>
+      <c r="O84" s="23" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>Self Knowledge Re-expression: A Fully Local Method for Adapting LLMs to Tasks Using Intrin</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>Mengyu Wang, Xiaoying Zhi, Zhiyi Li, Robin Schmucker, Shay B. Cohen, Tiejun Ma, Fran Silavong</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H85" s="21" t="n"/>
+      <c r="I85" s="21" t="n"/>
+      <c r="J85" s="21" t="n"/>
+      <c r="K85" s="21" t="n"/>
+      <c r="L85" s="21" t="n"/>
+      <c r="M85" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N85" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.22939</t>
+        </is>
+      </c>
+      <c r="O85" s="23" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anatomy-Aware Unsupervised Detection and Localization of Retinal Abnormalities in Optical </t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>Tania Haghighi, Sina Gholami, Hamed Tabkhi, Minhaj Nur Alam</t>
+        </is>
+      </c>
+      <c r="E86" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G86" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H86" s="21" t="n"/>
+      <c r="I86" s="21" t="n"/>
+      <c r="J86" s="21" t="n"/>
+      <c r="K86" s="21" t="n"/>
+      <c r="L86" s="21" t="n"/>
+      <c r="M86" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-04); 待人工核對指標 [基於重構 (Reconstruction)]</t>
+        </is>
+      </c>
+      <c r="N86" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.22139</t>
+        </is>
+      </c>
+      <c r="O86" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -25512,7 +25724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -26536,6 +26748,59 @@
           <t>https://github.com/amazon-science/patchcore-inspection</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Text-Guided Multimodal Unified Industrial Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Zewen Li, Shuo Ye, Zitong Yu, Weicheng Xie, Linlin Shen</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.22899</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -10118,7 +10118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16285,218 +16285,6 @@
           <t>https://github.com/gasharper/PyramidFlow</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B83" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="inlineStr">
-        <is>
-          <t>Zoom In, Reason Out: Efficient Far-field Anomaly Detection in Expressway Surveillance Vide</t>
-        </is>
-      </c>
-      <c r="D83" s="21" t="inlineStr">
-        <is>
-          <t>Xiaowei Mao, Bowen Sui, Weijie Zhang, Yawen Yang, Shengnan Guo, Shilong Zhao, Jiaqi Lin, Tingrui Wu</t>
-        </is>
-      </c>
-      <c r="E83" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G83" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="21" t="n"/>
-      <c r="J83" s="21" t="n"/>
-      <c r="K83" s="21" t="n"/>
-      <c r="L83" s="21" t="n"/>
-      <c r="M83" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
-        </is>
-      </c>
-      <c r="N83" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23724</t>
-        </is>
-      </c>
-      <c r="O83" s="23" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="inlineStr">
-        <is>
-          <t>Learning to Identify Out-of-Distribution Objects for 3D LiDAR Anomaly Segmentation</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>Simone Mosco, Daniel Fusaro, Alberto Pretto</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G84" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H84" s="21" t="n"/>
-      <c r="I84" s="21" t="n"/>
-      <c r="J84" s="21" t="n"/>
-      <c r="K84" s="21" t="n"/>
-      <c r="L84" s="21" t="n"/>
-      <c r="M84" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
-        </is>
-      </c>
-      <c r="N84" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23604</t>
-        </is>
-      </c>
-      <c r="O84" s="23" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B85" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>Self Knowledge Re-expression: A Fully Local Method for Adapting LLMs to Tasks Using Intrin</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>Mengyu Wang, Xiaoying Zhi, Zhiyi Li, Robin Schmucker, Shay B. Cohen, Tiejun Ma, Fran Silavong</t>
-        </is>
-      </c>
-      <c r="E85" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G85" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H85" s="21" t="n"/>
-      <c r="I85" s="21" t="n"/>
-      <c r="J85" s="21" t="n"/>
-      <c r="K85" s="21" t="n"/>
-      <c r="L85" s="21" t="n"/>
-      <c r="M85" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
-        </is>
-      </c>
-      <c r="N85" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22939</t>
-        </is>
-      </c>
-      <c r="O85" s="23" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B86" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anatomy-Aware Unsupervised Detection and Localization of Retinal Abnormalities in Optical </t>
-        </is>
-      </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>Tania Haghighi, Sina Gholami, Hamed Tabkhi, Minhaj Nur Alam</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G86" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="21" t="n"/>
-      <c r="J86" s="21" t="n"/>
-      <c r="K86" s="21" t="n"/>
-      <c r="L86" s="21" t="n"/>
-      <c r="M86" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-04); 待人工核對指標 [基於重構 (Reconstruction)]</t>
-        </is>
-      </c>
-      <c r="N86" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22139</t>
-        </is>
-      </c>
-      <c r="O86" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -17499,7 +17499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18373,6 +18373,59 @@
           <t>https://github.com/DonaldRR/SimpleNet</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>SuperADD: Training-free Class-agnostic Anomaly Segmentation -- CVPR 2026 VAND 4.0 Workshop</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Lukas Roming, Felix Lehnerer, Jonas V. Funk, Andreas Michel, Georg Maier, Thomas Längle, Jürgen Beyerer</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.14808</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -9906,6 +9906,1659 @@
       <c r="O114" s="20" t="inlineStr">
         <is>
           <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="18" t="n"/>
+      <c r="L115" s="18" t="n"/>
+      <c r="M115" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O115" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wavelet and Prototype Augmented Query-based Transformer for </t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+      <c r="J116" s="18" t="n"/>
+      <c r="K116" s="18" t="n"/>
+      <c r="L116" s="18" t="n"/>
+      <c r="M116" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Wavelet and Prototype Augmented Query-based Transformer for Pixel-level Surface Defect Detection</t>
+        </is>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yan_Wavelet_and_Prototype_Augmented_Query-based_Transformer_for_Pixel-level_Surface_Defect_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O116" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+      <c r="J117" s="18" t="n"/>
+      <c r="K117" s="18" t="n"/>
+      <c r="L117" s="18" t="n"/>
+      <c r="M117" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-set Supervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O117" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
+      <c r="L118" s="18" t="n"/>
+      <c r="M118" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Anomaly Detection Dataset for Tiny Objects</t>
+        </is>
+      </c>
+      <c r="N118" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O118" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>Real-IAD D3</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="n"/>
+      <c r="I119" s="18" t="n"/>
+      <c r="J119" s="18" t="n"/>
+      <c r="K119" s="18" t="n"/>
+      <c r="L119" s="18" t="n"/>
+      <c r="M119" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset for Industrial Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>Odd-One-Out</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+      <c r="J120" s="18" t="n"/>
+      <c r="K120" s="18" t="n"/>
+      <c r="L120" s="18" t="n"/>
+      <c r="M120" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Neighbors</t>
+        </is>
+      </c>
+      <c r="N120" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O120" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B121" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H121" s="18" t="n"/>
+      <c r="I121" s="18" t="n"/>
+      <c r="J121" s="18" t="n"/>
+      <c r="K121" s="18" t="n"/>
+      <c r="L121" s="18" t="n"/>
+      <c r="M121" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning with Multimodal Large Language Models</t>
+        </is>
+      </c>
+      <c r="N121" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O121" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+      <c r="J122" s="18" t="n"/>
+      <c r="K122" s="18" t="n"/>
+      <c r="L122" s="18" t="n"/>
+      <c r="M122" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly Detection through Visual Prototype and Harmonization</t>
+        </is>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O122" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B123" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exploring Intrinsic Normal Prototypes within a Single Image </t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+      <c r="J123" s="18" t="n"/>
+      <c r="K123" s="18" t="n"/>
+      <c r="L123" s="18" t="n"/>
+      <c r="M123" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Single Image for Universal Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N123" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O123" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>PatchGuard</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+      <c r="J124" s="18" t="n"/>
+      <c r="K124" s="18" t="n"/>
+      <c r="L124" s="18" t="n"/>
+      <c r="M124" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PatchGuard: Adversarially Robust Anomaly Detection and Localization through Vision Transformers and Pseudo Anomalies</t>
+        </is>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O124" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B125" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="n"/>
+      <c r="I125" s="18" t="n"/>
+      <c r="J125" s="18" t="n"/>
+      <c r="K125" s="18" t="n"/>
+      <c r="L125" s="18" t="n"/>
+      <c r="M125" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying Appearance, Geometry, and Internal Properties</t>
+        </is>
+      </c>
+      <c r="N125" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O125" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+      <c r="J126" s="18" t="n"/>
+      <c r="K126" s="18" t="n"/>
+      <c r="L126" s="18" t="n"/>
+      <c r="M126" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real-World Physical Dynamics: Physics-Grounded Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O126" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+      <c r="J127" s="18" t="n"/>
+      <c r="K127" s="18" t="n"/>
+      <c r="L127" s="18" t="n"/>
+      <c r="M127" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision and Language Foundation Models</t>
+        </is>
+      </c>
+      <c r="N127" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O127" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="n"/>
+      <c r="I128" s="18" t="n"/>
+      <c r="J128" s="18" t="n"/>
+      <c r="K128" s="18" t="n"/>
+      <c r="L128" s="18" t="n"/>
+      <c r="M128" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O128" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>Correcting Deviations from Normality</t>
+        </is>
+      </c>
+      <c r="D129" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H129" s="18" t="n"/>
+      <c r="I129" s="18" t="n"/>
+      <c r="J129" s="18" t="n"/>
+      <c r="K129" s="18" t="n"/>
+      <c r="L129" s="18" t="n"/>
+      <c r="M129" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Correcting Deviations from Normality: A Reformulated Diffusion Model for Multi-Class Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O129" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>TailedCore</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="n"/>
+      <c r="I130" s="18" t="n"/>
+      <c r="J130" s="18" t="n"/>
+      <c r="K130" s="18" t="n"/>
+      <c r="L130" s="18" t="n"/>
+      <c r="M130" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long-Tail Noisy Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O130" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>A Unified Latent Schrodinger Bridge Diffusion Model for Unsu</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+      <c r="J131" s="18" t="n"/>
+      <c r="K131" s="18" t="n"/>
+      <c r="L131" s="18" t="n"/>
+      <c r="M131" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Unified Latent Schrodinger Bridge Diffusion Model for Unsupervised Anomaly Detection and Localization</t>
+        </is>
+      </c>
+      <c r="N131" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O131" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
+      <c r="J132" s="18" t="n"/>
+      <c r="K132" s="18" t="n"/>
+      <c r="L132" s="18" t="n"/>
+      <c r="M132" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion Models with Dynamic Transformer UNet</t>
+        </is>
+      </c>
+      <c r="N132" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O132" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>Towards Accurate Unified Anomaly Segmentation</t>
+        </is>
+      </c>
+      <c r="D133" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="n"/>
+      <c r="I133" s="18" t="n"/>
+      <c r="J133" s="18" t="n"/>
+      <c r="K133" s="18" t="n"/>
+      <c r="L133" s="18" t="n"/>
+      <c r="M133" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Accurate Unified Anomaly Segmentation</t>
+        </is>
+      </c>
+      <c r="N133" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O133" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removing Geometric Bias in One-Class Anomaly Detection with </t>
+        </is>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="n"/>
+      <c r="I134" s="18" t="n"/>
+      <c r="J134" s="18" t="n"/>
+      <c r="K134" s="18" t="n"/>
+      <c r="L134" s="18" t="n"/>
+      <c r="M134" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detection with Adaptive Feature Perturbation</t>
+        </is>
+      </c>
+      <c r="N134" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O134" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>Anomaly Detection for People with Visual Impairments using a</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="n"/>
+      <c r="I135" s="18" t="n"/>
+      <c r="J135" s="18" t="n"/>
+      <c r="K135" s="18" t="n"/>
+      <c r="L135" s="18" t="n"/>
+      <c r="M135" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Anomaly Detection for People with Visual Impairments using an Egocentric 360-Degree Camera</t>
+        </is>
+      </c>
+      <c r="N135" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Song_Anomaly_Detection_for_People_with_Visual_Impairments_using_an_Egocentric_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O135" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="n"/>
+      <c r="I136" s="18" t="n"/>
+      <c r="J136" s="18" t="n"/>
+      <c r="K136" s="18" t="n"/>
+      <c r="L136" s="18" t="n"/>
+      <c r="M136" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SPACE: SPAtial-Aware Consistency rEgularization for Anomaly Detection in Industrial Applications</t>
+        </is>
+      </c>
+      <c r="N136" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O136" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>Looking at Model Debiasing through the Lens of Anomaly Detec</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="n"/>
+      <c r="I137" s="18" t="n"/>
+      <c r="J137" s="18" t="n"/>
+      <c r="K137" s="18" t="n"/>
+      <c r="L137" s="18" t="n"/>
+      <c r="M137" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Looking at Model Debiasing through the Lens of Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N137" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Pastore_Looking_at_Model_Debiasing_through_the_Lens_of_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O137" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>PV-VTT</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="n"/>
+      <c r="I138" s="18" t="n"/>
+      <c r="J138" s="18" t="n"/>
+      <c r="K138" s="18" t="n"/>
+      <c r="L138" s="18" t="n"/>
+      <c r="M138" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PV-VTT: A Privacy-Centric Dataset for Mission-Specific Anomaly Detection and Natural Language Interpretation</t>
+        </is>
+      </c>
+      <c r="N138" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Masukawa_PV-VTT_A_Privacy-Centric_Dataset_for_Mission-Specific_Anomaly_Detection_and_Natural_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O138" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+        </is>
+      </c>
+      <c r="D139" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H139" s="18" t="n"/>
+      <c r="I139" s="18" t="n"/>
+      <c r="J139" s="18" t="n"/>
+      <c r="K139" s="18" t="n"/>
+      <c r="L139" s="18" t="n"/>
+      <c r="M139" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Detection with Data Contamination</t>
+        </is>
+      </c>
+      <c r="N139" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O139" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="n"/>
+      <c r="I140" s="18" t="n"/>
+      <c r="J140" s="18" t="n"/>
+      <c r="K140" s="18" t="n"/>
+      <c r="L140" s="18" t="n"/>
+      <c r="M140" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions for Texture Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N140" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O140" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>FUN-AD</t>
+        </is>
+      </c>
+      <c r="D141" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="n"/>
+      <c r="I141" s="18" t="n"/>
+      <c r="J141" s="18" t="n"/>
+      <c r="K141" s="18" t="n"/>
+      <c r="L141" s="18" t="n"/>
+      <c r="M141" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FUN-AD: Fully Unsupervised Learning for Anomaly Detection with Noisy Training Data</t>
+        </is>
+      </c>
+      <c r="N141" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O141" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="n"/>
+      <c r="I142" s="18" t="n"/>
+      <c r="J142" s="18" t="n"/>
+      <c r="K142" s="18" t="n"/>
+      <c r="L142" s="18" t="n"/>
+      <c r="M142" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N142" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O142" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>ROADS</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
+      <c r="J143" s="18" t="n"/>
+      <c r="K143" s="18" t="n"/>
+      <c r="L143" s="18" t="n"/>
+      <c r="M143" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Detection under Domain Shift</t>
+        </is>
+      </c>
+      <c r="N143" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O143" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -10710,7 +10710,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B129" s="18" t="inlineStr">
@@ -10720,12 +10720,12 @@
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>Correcting Deviations from Normality</t>
+          <t>DeCo-Diff</t>
         </is>
       </c>
       <c r="D129" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Farzad Beizaee, et al.</t>
         </is>
       </c>
       <c r="E129" s="18" t="inlineStr">
@@ -10743,14 +10743,22 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H129" s="18" t="n"/>
-      <c r="I129" s="18" t="n"/>
-      <c r="J129" s="18" t="n"/>
-      <c r="K129" s="18" t="n"/>
+      <c r="H129" s="18" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I129" s="18" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J129" s="18" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K129" s="18" t="n">
+        <v>94.90000000000001</v>
+      </c>
       <c r="L129" s="18" t="n"/>
       <c r="M129" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Correcting Deviations from Normality: A Reformulated Diffusion Model for Multi-Class Unsupervised Anomaly Detection</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -10760,7 +10768,7 @@
       </c>
       <c r="O129" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/farzad-bz/DeCo-Diff</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11402,7 @@
     <row r="141">
       <c r="A141" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B141" s="18" t="inlineStr">
@@ -11409,7 +11417,7 @@
       </c>
       <c r="D141" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jiin Im, et al.</t>
         </is>
       </c>
       <c r="E141" s="18" t="inlineStr">
@@ -11427,14 +11435,18 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H141" s="18" t="n"/>
-      <c r="I141" s="18" t="n"/>
+      <c r="H141" s="18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I141" s="18" t="n">
+        <v>98.59999999999999</v>
+      </c>
       <c r="J141" s="18" t="n"/>
       <c r="K141" s="18" t="n"/>
       <c r="L141" s="18" t="n"/>
       <c r="M141" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。FUN-AD: Fully Unsupervised Learning for Anomaly Detection with Noisy Training Data</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -11444,7 +11456,7 @@
       </c>
       <c r="O141" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -17936,6 +17948,132 @@
       <c r="O82" s="23" t="inlineStr">
         <is>
           <t>https://github.com/gasharper/PyramidFlow</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>DeCo-Diff</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Farzad Beizaee, et al.</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I83" s="21" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J83" s="21" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K83" s="21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L83" s="21" t="n"/>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N83" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O83" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/farzad-bz/DeCo-Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>FUN-AD</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>Jiin Im, et al.</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I84" s="21" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J84" s="21" t="n"/>
+      <c r="K84" s="21" t="n"/>
+      <c r="L84" s="21" t="n"/>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N84" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O84" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
         </is>
       </c>
     </row>
@@ -20116,7 +20254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24824,6 +24962,132 @@
       <c r="O63" s="14" t="inlineStr">
         <is>
           <t>https://github.com/zqhang/WinCLIP-pytorch</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>DeCo-Diff</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Farzad Beizaee, et al.</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N64" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O64" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/farzad-bz/DeCo-Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>FUN-AD</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Jiin Im, et al.</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N65" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -10832,7 +10832,7 @@
     <row r="131">
       <c r="A131" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B131" s="18" t="inlineStr">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>A Unified Latent Schrodinger Bridge Diffusion Model for Unsu</t>
+          <t>LASB</t>
         </is>
       </c>
       <c r="D131" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Akshay Kulkarni, et al.</t>
         </is>
       </c>
       <c r="E131" s="18" t="inlineStr">
@@ -10865,14 +10865,18 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
+      <c r="H131" s="18" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="I131" s="18" t="n">
+        <v>99.15000000000001</v>
+      </c>
       <c r="J131" s="18" t="n"/>
       <c r="K131" s="18" t="n"/>
       <c r="L131" s="18" t="n"/>
       <c r="M131" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。A Unified Latent Schrodinger Bridge Diffusion Model for Unsupervised Anomaly Detection and Localization</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Latent Schrödinger Bridge 擴散模型；class-based 設定 (Table 1) [基於擴散]</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -10946,22 +10950,22 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B133" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
         <is>
-          <t>Towards Accurate Unified Anomaly Segmentation</t>
+          <t>UniAS</t>
         </is>
       </c>
       <c r="D133" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wenxuan Ma, et al.</t>
         </is>
       </c>
       <c r="E133" s="18" t="inlineStr">
@@ -10980,13 +10984,17 @@
         </is>
       </c>
       <c r="H133" s="18" t="n"/>
-      <c r="I133" s="18" t="n"/>
-      <c r="J133" s="18" t="n"/>
+      <c r="I133" s="18" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="J133" s="18" t="n">
+        <v>65.12</v>
+      </c>
       <c r="K133" s="18" t="n"/>
       <c r="L133" s="18" t="n"/>
       <c r="M133" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Accurate Unified Anomaly Segmentation</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：One-for-All 多類別異常分割；論文主打 pixel-AUROC / pAP / DSC,未報告 image-AUROC [基於重構]</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -11783,7 +11791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18074,6 +18082,128 @@
       <c r="O84" s="23" t="inlineStr">
         <is>
           <t>https://github.com/HY-Vision-Lab/FUNAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>UniAS</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>Wenxuan Ma, et al.</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H85" s="21" t="n"/>
+      <c r="I85" s="21" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="J85" s="21" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="K85" s="21" t="n"/>
+      <c r="L85" s="21" t="n"/>
+      <c r="M85" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：One-for-All 多類別異常分割；論文主打 pixel-AUROC / pAP / DSC,未報告 image-AUROC [基於重構]</t>
+        </is>
+      </c>
+      <c r="N85" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O85" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t>LASB</t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>Akshay Kulkarni, et al.</t>
+        </is>
+      </c>
+      <c r="E86" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G86" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H86" s="21" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="I86" s="21" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="J86" s="21" t="n"/>
+      <c r="K86" s="21" t="n"/>
+      <c r="L86" s="21" t="n"/>
+      <c r="M86" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Latent Schrödinger Bridge 擴散模型；class-based 設定 (Table 1) [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N86" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O86" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20254,7 +20384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25088,6 +25218,128 @@
       <c r="O65" s="14" t="inlineStr">
         <is>
           <t>https://github.com/HY-Vision-Lab/FUNAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>UniAS</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Wenxuan Ma, et al.</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="n"/>
+      <c r="I66" s="12" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="12" t="n"/>
+      <c r="M66" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：One-for-All 多類別異常分割；論文主打 pixel-AUROC / pAP / DSC,未報告 image-AUROC [基於重構]</t>
+        </is>
+      </c>
+      <c r="N66" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O66" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>LASB</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Akshay Kulkarni, et al.</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Latent Schrödinger Bridge 擴散模型；class-based 設定 (Table 1) [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N67" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O67" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -10425,7 +10425,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B124" s="18" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="D124" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E124" s="18" t="inlineStr">
@@ -10458,14 +10458,18 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H124" s="18" t="n"/>
-      <c r="I124" s="18" t="n"/>
+      <c r="H124" s="18" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="I124" s="18" t="n">
+        <v>92.7</v>
+      </c>
       <c r="J124" s="18" t="n"/>
       <c r="K124" s="18" t="n"/>
       <c r="L124" s="18" t="n"/>
       <c r="M124" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。PatchGuard: Adversarially Robust Anomaly Detection and Localization through Vision Transformers and Pseudo Anomalies</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -11125,12 +11129,12 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B136" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
@@ -11140,7 +11144,7 @@
       </c>
       <c r="D136" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Daehwan Kim, et al.</t>
         </is>
       </c>
       <c r="E136" s="18" t="inlineStr">
@@ -11158,14 +11162,18 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H136" s="18" t="n"/>
-      <c r="I136" s="18" t="n"/>
+      <c r="H136" s="18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I136" s="18" t="n">
+        <v>98.8</v>
+      </c>
       <c r="J136" s="18" t="n"/>
       <c r="K136" s="18" t="n"/>
       <c r="L136" s="18" t="n"/>
       <c r="M136" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SPACE: SPAtial-Aware Consistency rEgularization for Anomaly Detection in Industrial Applications</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -11791,7 +11799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18202,6 +18210,128 @@
         </is>
       </c>
       <c r="O86" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>PatchGuard</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Mojtaba Nafez, et al.</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H87" s="21" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="I87" s="21" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="J87" s="21" t="n"/>
+      <c r="K87" s="21" t="n"/>
+      <c r="L87" s="21" t="n"/>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N87" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O87" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C88" s="21" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D88" s="21" t="inlineStr">
+        <is>
+          <t>Daehwan Kim, et al.</t>
+        </is>
+      </c>
+      <c r="E88" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F88" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G88" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H88" s="21" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I88" s="21" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="J88" s="21" t="n"/>
+      <c r="K88" s="21" t="n"/>
+      <c r="L88" s="21" t="n"/>
+      <c r="M88" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N88" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O88" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18358,7 +18488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -19380,6 +19510,65 @@
       <c r="O15" s="14" t="inlineStr">
         <is>
           <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Daehwan Kim, et al.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25338,6 +25527,128 @@
         </is>
       </c>
       <c r="O67" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>PatchGuard</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Mojtaba Nafez, et al.</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N68" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Daehwan Kim, et al.</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N69" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25458,7 +25769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -26391,6 +26702,67 @@
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>PatchGuard</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Mojtaba Nafez, et al.</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26432,7 +26804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27685,6 +28057,67 @@
       <c r="O18" s="23" t="inlineStr">
         <is>
           <t>https://github.com/gudovskiy/cflow-ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>PatchGuard</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Mojtaba Nafez, et al.</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -646,7 +646,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" style="27" min="1" max="1"/>
     <col width="90" customWidth="1" style="27" min="2" max="2"/>
@@ -1134,7 +1134,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O143"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -11799,8 +11799,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -18332,6 +18332,2343 @@
         </is>
       </c>
       <c r="O88" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>CFM (Crossmodal Feature Mapping)</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>Alex Costanzino, Pierluigi Zama Ramirez, Giuseppe Lisanti, Luigi Di Stefano</t>
+        </is>
+      </c>
+      <c r="E89" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2024 / arXiv 2312.04521</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
+      <c r="J89" s="21" t="n"/>
+      <c r="K89" s="21" t="n"/>
+      <c r="L89" s="21" t="n"/>
+      <c r="M89" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RGB-3D 跨模態特徵映射；以 RGB→3D 與 3D→RGB 雙向蒸餾學異常；MVTec 3D-AD SOTA I=98.5 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N89" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.04521</t>
+        </is>
+      </c>
+      <c r="O89" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/CVLAB-Unibo/crossmodal-feature-mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="inlineStr">
+        <is>
+          <t>CSAD (Component Segmentation AD)</t>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>Yu-Hsuan Hsieh, Shang-Hong Lai (National Tsing Hua University)</t>
+        </is>
+      </c>
+      <c r="E90" s="21" t="inlineStr">
+        <is>
+          <t>BMVC 2024 / arXiv 2408.15628</t>
+        </is>
+      </c>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G90" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+      <c r="J90" s="21" t="n"/>
+      <c r="K90" s="21" t="n"/>
+      <c r="L90" s="21" t="n"/>
+      <c r="M90" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec LOCO 為主：I-AUROC 95.3 (logical 96.7 / structural 94.0)；latency 8.9ms / 321.</t>
+        </is>
+      </c>
+      <c r="N90" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.15628</t>
+        </is>
+      </c>
+      <c r="O90" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/Tokichan/CSAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>M3DM-NR (Noisy-Resistant)</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>Chengjie Wang, Haokun Zhu, Jinlong Peng, Yue Wang, Ran Yi, Yunsheng Wu, Lizhuang Ma, Jiangning Zhang</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024 / 2406.02263</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="21" t="n"/>
+      <c r="J91" s="21" t="n"/>
+      <c r="K91" s="21" t="n"/>
+      <c r="L91" s="21" t="n"/>
+      <c r="M91" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：M3DM 雜訊穩健版：以多模態去雜訊處理 noisy 訓練集 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N91" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.02263</t>
+        </is>
+      </c>
+      <c r="O91" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="inlineStr">
+        <is>
+          <t>M3DM (Multimodal Hybrid Fusion)</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>Yue Wang, Jinlong Peng, Jiangning Zhang, Ran Yi, Yabiao Wang, Chengjie Wang</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2023 / arXiv 2303.00601</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
+      <c r="J92" s="21" t="n"/>
+      <c r="K92" s="21" t="n"/>
+      <c r="L92" s="21" t="n"/>
+      <c r="M92" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-modal Memory Bank + 點雲對齊 + Patch-wise 對比學習；RGB-3D 異常檢測 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N92" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.00601</t>
+        </is>
+      </c>
+      <c r="O92" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/nomewang/M3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>VT-ADL</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
+        <is>
+          <t>ISIE 2021 / arXiv 2104.10036</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="21" t="n"/>
+      <c r="J93" s="21" t="n"/>
+      <c r="K93" s="21" t="n"/>
+      <c r="L93" s="21" t="n"/>
+      <c r="M93" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N93" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2104.10036</t>
+        </is>
+      </c>
+      <c r="O93" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/pankajmishra000/VT-ADL</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B94" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C94" s="21" t="inlineStr">
+        <is>
+          <t>AST (Asymmetric Student-Teacher)</t>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
+        <is>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+        </is>
+      </c>
+      <c r="E94" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2023</t>
+        </is>
+      </c>
+      <c r="F94" s="21" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="G94" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="21" t="n"/>
+      <c r="J94" s="21" t="n"/>
+      <c r="K94" s="21" t="n"/>
+      <c r="L94" s="21" t="n"/>
+      <c r="M94" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：非對稱 S-T (NF teacher + FFN student)；MVTec 3D-AD RGB-only 設定 SOTA [基於重構]</t>
+        </is>
+      </c>
+      <c r="N94" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2210.07829</t>
+        </is>
+      </c>
+      <c r="O94" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/marco-rudolph/AST</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>EasyNet</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>Ruitao Chen, Guoyang Xie, Jiaqi Liu, Jinbao Wang, Ziqi Luo, Jinfan Wang, Feng Zheng</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="inlineStr">
+        <is>
+          <t>ACM MM 2023 / arXiv 2307.13925</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+      <c r="J95" s="21" t="n"/>
+      <c r="K95" s="21" t="n"/>
+      <c r="L95" s="21" t="n"/>
+      <c r="M95" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：輕量易部署網路：無需 pretrained / memory bank；多模態異常分割；快速推論 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N95" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2307.13925</t>
+        </is>
+      </c>
+      <c r="O95" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/sukanyapatra1997/ULSAD-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>PSAD (Few-Shot Part Segmentation)</t>
+        </is>
+      </c>
+      <c r="D96" s="21" t="inlineStr">
+        <is>
+          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="inlineStr">
+        <is>
+          <t>AAAI 2024 / arXiv 2312.13783</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+      <c r="J96" s="21" t="n"/>
+      <c r="K96" s="21" t="n"/>
+      <c r="L96" s="21" t="n"/>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
+        </is>
+      </c>
+      <c r="N96" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.13783</t>
+        </is>
+      </c>
+      <c r="O96" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/kaist-cvml-lab/PSAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>Multi-Flow (Multi-View NF)</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>Mathis Kruse, Bodo Rosenhahn</t>
+        </is>
+      </c>
+      <c r="E97" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="21" t="n"/>
+      <c r="J97" s="21" t="n"/>
+      <c r="K97" s="21" t="n"/>
+      <c r="L97" s="21" t="n"/>
+      <c r="M97" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+        </is>
+      </c>
+      <c r="N97" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.03306</t>
+        </is>
+      </c>
+      <c r="O97" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="inlineStr">
+        <is>
+          <t>LogicQA (VLM Logical AD)</t>
+        </is>
+      </c>
+      <c r="D98" s="21" t="inlineStr">
+        <is>
+          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
+        </is>
+      </c>
+      <c r="E98" s="21" t="inlineStr">
+        <is>
+          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G98" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+      <c r="J98" s="21" t="n"/>
+      <c r="K98" s="21" t="n"/>
+      <c r="L98" s="21" t="n"/>
+      <c r="M98" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N98" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.20252</t>
+        </is>
+      </c>
+      <c r="O98" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>SINBAD (Set Features)</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="inlineStr">
+        <is>
+          <t>ICML 2024 / arXiv 2311.14773</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="21" t="n"/>
+      <c r="K99" s="21" t="n"/>
+      <c r="L99" s="21" t="n"/>
+      <c r="M99" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N99" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2311.14773</t>
+        </is>
+      </c>
+      <c r="O99" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/NivC/SINBAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B100" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C100" s="21" t="inlineStr">
+        <is>
+          <t>BTF (Back to the Feature)</t>
+        </is>
+      </c>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>Eliahu Horwitz, Yedid Hoshen</t>
+        </is>
+      </c>
+      <c r="E100" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="G100" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="21" t="n"/>
+      <c r="J100" s="21" t="n"/>
+      <c r="K100" s="21" t="n"/>
+      <c r="L100" s="21" t="n"/>
+      <c r="M100" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+        </is>
+      </c>
+      <c r="N100" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2203.05550</t>
+        </is>
+      </c>
+      <c r="O100" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B101" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>RoBiS (VAND 2025 第二名)</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
+      <c r="K101" s="21" t="n"/>
+      <c r="L101" s="21" t="n"/>
+      <c r="M101" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+        </is>
+      </c>
+      <c r="N101" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.21152</t>
+        </is>
+      </c>
+      <c r="O101" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/xrli-U/RoBiS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B102" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C102" s="21" t="inlineStr">
+        <is>
+          <t>SuperAD (Training-free DINOv2)</t>
+        </is>
+      </c>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G102" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="21" t="n"/>
+      <c r="K102" s="21" t="n"/>
+      <c r="L102" s="21" t="n"/>
+      <c r="M102" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+        </is>
+      </c>
+      <c r="N102" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.19750</t>
+        </is>
+      </c>
+      <c r="O102" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B103" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>ISVL (VAND 2025 第一名)</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+        </is>
+      </c>
+      <c r="E103" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H103" s="21" t="n"/>
+      <c r="I103" s="21" t="n"/>
+      <c r="J103" s="21" t="n"/>
+      <c r="K103" s="21" t="n"/>
+      <c r="L103" s="21" t="n"/>
+      <c r="M103" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+        </is>
+      </c>
+      <c r="N103" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.17615</t>
+        </is>
+      </c>
+      <c r="O103" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B104" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C104" s="21" t="inlineStr">
+        <is>
+          <t>INP-Former (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D104" s="21" t="inlineStr">
+        <is>
+          <t>Wei Luo, Yunkang Cao, Haiming Yao, Xiaotian Zhang, Jianan Lou, Yuqi Cheng, Weiming Shen, Wenyong Yu</t>
+        </is>
+      </c>
+      <c r="E104" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 / arXiv 2503.02424</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G104" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+      <c r="J104" s="21" t="n"/>
+      <c r="K104" s="21" t="n"/>
+      <c r="L104" s="21" t="n"/>
+      <c r="M104" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：INP-Former 在 MVTec AD 2 SegF1 priv 21.8 (RoBiS baseline 起點，後續被 RoBiS+SAM 拉到 51.0</t>
+        </is>
+      </c>
+      <c r="N104" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.02424</t>
+        </is>
+      </c>
+      <c r="O104" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/luow23/INP-Former</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B105" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>PatchCore (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+        </is>
+      </c>
+      <c r="E105" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="21" t="n"/>
+      <c r="K105" s="21" t="n"/>
+      <c r="L105" s="21" t="n"/>
+      <c r="M105" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N105" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O105" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B106" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C106" s="21" t="inlineStr">
+        <is>
+          <t>EfficientAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D106" s="21" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E106" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G106" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H106" s="21" t="n"/>
+      <c r="I106" s="21" t="n"/>
+      <c r="J106" s="21" t="n"/>
+      <c r="K106" s="21" t="n"/>
+      <c r="L106" s="21" t="n"/>
+      <c r="M106" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N106" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O106" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>DRAEM (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
+        <is>
+          <t>ICCV 2021 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+      <c r="J107" s="21" t="n"/>
+      <c r="K107" s="21" t="n"/>
+      <c r="L107" s="21" t="n"/>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N107" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O107" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B108" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C108" s="21" t="inlineStr">
+        <is>
+          <t>RD4AD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>Hanqiu Deng, Xingyu Li</t>
+        </is>
+      </c>
+      <c r="E108" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G108" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="21" t="n"/>
+      <c r="J108" s="21" t="n"/>
+      <c r="K108" s="21" t="n"/>
+      <c r="L108" s="21" t="n"/>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+        </is>
+      </c>
+      <c r="N108" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O108" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
+        <is>
+          <t>SimpleNet (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+        </is>
+      </c>
+      <c r="E109" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2023 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="21" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="21" t="n"/>
+      <c r="M109" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N109" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O109" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B110" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C110" s="21" t="inlineStr">
+        <is>
+          <t>DDAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D110" s="21" t="inlineStr">
+        <is>
+          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+        </is>
+      </c>
+      <c r="E110" s="21" t="inlineStr">
+        <is>
+          <t>BMVC 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G110" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H110" s="21" t="n"/>
+      <c r="I110" s="21" t="n"/>
+      <c r="J110" s="21" t="n"/>
+      <c r="K110" s="21" t="n"/>
+      <c r="L110" s="21" t="n"/>
+      <c r="M110" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N110" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O110" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B111" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+      <c r="D111" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="21" t="n"/>
+      <c r="J111" s="21" t="n"/>
+      <c r="K111" s="21" t="n"/>
+      <c r="L111" s="21" t="n"/>
+      <c r="M111" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="N111" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O111" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B112" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C112" s="21" t="inlineStr">
+        <is>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G112" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+      <c r="J112" s="21" t="n"/>
+      <c r="K112" s="21" t="n"/>
+      <c r="L112" s="21" t="n"/>
+      <c r="M112" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+        </is>
+      </c>
+      <c r="N112" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O112" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D113" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
+      <c r="J113" s="21" t="n"/>
+      <c r="K113" s="21" t="n"/>
+      <c r="L113" s="21" t="n"/>
+      <c r="M113" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+        </is>
+      </c>
+      <c r="N113" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O113" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B114" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C114" s="21" t="inlineStr">
+        <is>
+          <t>Real-IAD D3</t>
+        </is>
+      </c>
+      <c r="D114" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F114" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G114" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="21" t="n"/>
+      <c r="J114" s="21" t="n"/>
+      <c r="K114" s="21" t="n"/>
+      <c r="L114" s="21" t="n"/>
+      <c r="M114" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+        </is>
+      </c>
+      <c r="N114" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O114" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>Odd-One-Out</t>
+        </is>
+      </c>
+      <c r="D115" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H115" s="21" t="n"/>
+      <c r="I115" s="21" t="n"/>
+      <c r="J115" s="21" t="n"/>
+      <c r="K115" s="21" t="n"/>
+      <c r="L115" s="21" t="n"/>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+        </is>
+      </c>
+      <c r="N115" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O115" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C116" s="21" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+      <c r="J116" s="21" t="n"/>
+      <c r="K116" s="21" t="n"/>
+      <c r="L116" s="21" t="n"/>
+      <c r="M116" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+        </is>
+      </c>
+      <c r="N116" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O116" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D117" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G117" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+      <c r="J117" s="21" t="n"/>
+      <c r="K117" s="21" t="n"/>
+      <c r="L117" s="21" t="n"/>
+      <c r="M117" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+        </is>
+      </c>
+      <c r="N117" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O117" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B118" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C118" s="21" t="inlineStr">
+        <is>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G118" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H118" s="21" t="n"/>
+      <c r="I118" s="21" t="n"/>
+      <c r="J118" s="21" t="n"/>
+      <c r="K118" s="21" t="n"/>
+      <c r="L118" s="21" t="n"/>
+      <c r="M118" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+        </is>
+      </c>
+      <c r="N118" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O118" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D119" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G119" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H119" s="21" t="n"/>
+      <c r="I119" s="21" t="n"/>
+      <c r="J119" s="21" t="n"/>
+      <c r="K119" s="21" t="n"/>
+      <c r="L119" s="21" t="n"/>
+      <c r="M119" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N119" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O119" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B120" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D120" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F120" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+      <c r="J120" s="21" t="n"/>
+      <c r="K120" s="21" t="n"/>
+      <c r="L120" s="21" t="n"/>
+      <c r="M120" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N120" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O120" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+        </is>
+      </c>
+      <c r="D121" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="21" t="n"/>
+      <c r="J121" s="21" t="n"/>
+      <c r="K121" s="21" t="n"/>
+      <c r="L121" s="21" t="n"/>
+      <c r="M121" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+        </is>
+      </c>
+      <c r="N121" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O121" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B122" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C122" s="21" t="inlineStr">
+        <is>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+        </is>
+      </c>
+      <c r="D122" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H122" s="21" t="n"/>
+      <c r="I122" s="21" t="n"/>
+      <c r="J122" s="21" t="n"/>
+      <c r="K122" s="21" t="n"/>
+      <c r="L122" s="21" t="n"/>
+      <c r="M122" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+        </is>
+      </c>
+      <c r="N122" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O122" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>TailedCore</t>
+        </is>
+      </c>
+      <c r="D123" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G123" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+      <c r="J123" s="21" t="n"/>
+      <c r="K123" s="21" t="n"/>
+      <c r="L123" s="21" t="n"/>
+      <c r="M123" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+        </is>
+      </c>
+      <c r="N123" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O123" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B124" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C124" s="21" t="inlineStr">
+        <is>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+        </is>
+      </c>
+      <c r="D124" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G124" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H124" s="21" t="n"/>
+      <c r="I124" s="21" t="n"/>
+      <c r="J124" s="21" t="n"/>
+      <c r="K124" s="21" t="n"/>
+      <c r="L124" s="21" t="n"/>
+      <c r="M124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
+        </is>
+      </c>
+      <c r="N124" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O124" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
+        </is>
+      </c>
+      <c r="D125" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H125" s="21" t="n"/>
+      <c r="I125" s="21" t="n"/>
+      <c r="J125" s="21" t="n"/>
+      <c r="K125" s="21" t="n"/>
+      <c r="L125" s="21" t="n"/>
+      <c r="M125" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="N125" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O125" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B126" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C126" s="21" t="inlineStr">
+        <is>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+        </is>
+      </c>
+      <c r="D126" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="21" t="n"/>
+      <c r="J126" s="21" t="n"/>
+      <c r="K126" s="21" t="n"/>
+      <c r="L126" s="21" t="n"/>
+      <c r="M126" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+        </is>
+      </c>
+      <c r="N126" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O126" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
+        </is>
+      </c>
+      <c r="D127" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="21" t="n"/>
+      <c r="J127" s="21" t="n"/>
+      <c r="K127" s="21" t="n"/>
+      <c r="L127" s="21" t="n"/>
+      <c r="M127" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
+        </is>
+      </c>
+      <c r="N127" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O127" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B128" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C128" s="21" t="inlineStr">
+        <is>
+          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="D128" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G128" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+      <c r="J128" s="21" t="n"/>
+      <c r="K128" s="21" t="n"/>
+      <c r="L128" s="21" t="n"/>
+      <c r="M128" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
+        </is>
+      </c>
+      <c r="N128" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O128" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>ROADS</t>
+        </is>
+      </c>
+      <c r="D129" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G129" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H129" s="21" t="n"/>
+      <c r="I129" s="21" t="n"/>
+      <c r="J129" s="21" t="n"/>
+      <c r="K129" s="21" t="n"/>
+      <c r="L129" s="21" t="n"/>
+      <c r="M129" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Det</t>
+        </is>
+      </c>
+      <c r="N129" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O129" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18488,8 +20825,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -19567,6 +21904,1260 @@
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Generalist Multi-Class AD (Dual-Student)</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Hangil Park, Sunghyun Cho, Jiwoong Choi, et al.</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：雙學生 (Encoder-Decoder + Encoder-Encoder) + DINOv2 知識蒸餾；Noisy-OR 聯合學習 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.24448</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>ReContrast</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>NeurIPS 2023</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.02602</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/guojiajeremy/ReContrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>AnomalyXFusion (Multi-modal Diffusion)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2404.19444)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MIF 多模態融合 + DDF 動態擴散；多源 X-embedding 增強合成 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.19444</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>RD++</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2304.02216</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>InvAD (Feature Inversion)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+        </is>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.10760</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/zhangzjn/ADer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>TFA-Net (Template-based Feature Aggregation)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2603.22874)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：模板特徵聚合網路；以多模板做特徵級重構，I-AUROC 98.7%、P-AUROC 98.3% [基於重構]</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22874</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Triad (LMM-Aided AD)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.13184</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/tzjtatata/Triad</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>PromptAD</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2024</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot prompt learning；MVTec/VisA 12 個少樣本中 11 項第一；4-shot MVTec 96.6 / 96.5 [基於</t>
+        </is>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.05231</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/FuNz-0/PromptAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Flow (Multi-View NF)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Mathis Kruse, Bodo Rosenhahn</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+        </is>
+      </c>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.03306</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>ISVL (VAND 2025 第一名)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.17615</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>PatchCore (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>EfficientAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>DRAEM (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2021 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>RD4AD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Hanqiu Deng, Xingyu Li</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>SimpleNet (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>DDAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BMVC 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N32" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+        </is>
+      </c>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
+        </is>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19610,7 +23201,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -20573,8 +24164,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -25649,6 +29240,1716 @@
         </is>
       </c>
       <c r="O69" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>VQ-Flow</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Yu Wang, Shiwei Chen</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024 / IEEE 投稿中</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n"/>
+      <c r="I70" s="12" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="12" t="n"/>
+      <c r="M70" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：階層式向量量化 + Conditional NF；多類異常 SOTA 99.5%/98.3% [基於 NF]</t>
+        </is>
+      </c>
+      <c r="N70" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2409.00942</t>
+        </is>
+      </c>
+      <c r="O70" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/cool-xuan/vqflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>RD++</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="n"/>
+      <c r="I71" s="12" t="n"/>
+      <c r="J71" s="12" t="n"/>
+      <c r="K71" s="12" t="n"/>
+      <c r="L71" s="12" t="n"/>
+      <c r="M71" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N71" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2304.02216</t>
+        </is>
+      </c>
+      <c r="O71" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>CSAD (Component Segmentation AD)</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Yu-Hsuan Hsieh, Shang-Hong Lai (National Tsing Hua University)</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>BMVC 2024 / arXiv 2408.15628</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec LOCO 為主：I-AUROC 95.3 (logical 96.7 / structural 94.0)；latency 8.9ms / 321.</t>
+        </is>
+      </c>
+      <c r="N72" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.15628</t>
+        </is>
+      </c>
+      <c r="O72" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/Tokichan/CSAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Flow (Multi-View NF)</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Mathis Kruse, Bodo Rosenhahn</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="12" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="12" t="n"/>
+      <c r="M73" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+        </is>
+      </c>
+      <c r="N73" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.03306</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>April-GAN (CLIP-AD)</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="12" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="12" t="n"/>
+      <c r="M74" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N74" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2305.17382</t>
+        </is>
+      </c>
+      <c r="O74" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>SAA+ (Segment Any Anomaly)</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>IEEE TCYB 2025 / arXiv 2023</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
+        </is>
+      </c>
+      <c r="N75" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2305.10724</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>SuperAD (Training-free DINOv2)</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+        </is>
+      </c>
+      <c r="N76" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.19750</t>
+        </is>
+      </c>
+      <c r="O76" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>ISVL (VAND 2025 第一名)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+        </is>
+      </c>
+      <c r="N77" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.17615</t>
+        </is>
+      </c>
+      <c r="O77" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>INP-Former (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Wei Luo, Yunkang Cao, Haiming Yao, Xiaotian Zhang, Jianan Lou, Yuqi Cheng, Weiming Shen, Wenyong Yu</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 / arXiv 2503.02424</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="12" t="n"/>
+      <c r="M78" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：INP-Former 在 MVTec AD 2 SegF1 priv 21.8 (RoBiS baseline 起點，後續被 RoBiS+SAM 拉到 51.0</t>
+        </is>
+      </c>
+      <c r="N78" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.02424</t>
+        </is>
+      </c>
+      <c r="O78" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/luow23/INP-Former</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>PatchCore (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N79" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>EfficientAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N80" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O80" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>DRAEM (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2021 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="12" t="n"/>
+      <c r="M81" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N81" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>RD4AD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Hanqiu Deng, Xingyu Li</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+        </is>
+      </c>
+      <c r="N82" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O82" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>SimpleNet (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="n"/>
+      <c r="I83" s="12" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="12" t="n"/>
+      <c r="M83" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N83" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>DDAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>BMVC 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="12" t="n"/>
+      <c r="M84" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N84" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O84" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n"/>
+      <c r="I85" s="12" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="12" t="n"/>
+      <c r="M85" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="N85" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O85" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="n"/>
+      <c r="I86" s="12" t="n"/>
+      <c r="J86" s="12" t="n"/>
+      <c r="K86" s="12" t="n"/>
+      <c r="L86" s="12" t="n"/>
+      <c r="M86" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+        </is>
+      </c>
+      <c r="N86" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O86" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Real-IAD D3</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="n"/>
+      <c r="I87" s="12" t="n"/>
+      <c r="J87" s="12" t="n"/>
+      <c r="K87" s="12" t="n"/>
+      <c r="L87" s="12" t="n"/>
+      <c r="M87" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+        </is>
+      </c>
+      <c r="N87" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O87" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Odd-One-Out</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="n"/>
+      <c r="I88" s="12" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="12" t="n"/>
+      <c r="M88" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+        </is>
+      </c>
+      <c r="N88" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O88" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="n"/>
+      <c r="I89" s="12" t="n"/>
+      <c r="J89" s="12" t="n"/>
+      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="12" t="n"/>
+      <c r="M89" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+        </is>
+      </c>
+      <c r="N89" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O89" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="n"/>
+      <c r="I90" s="12" t="n"/>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="12" t="n"/>
+      <c r="M90" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+        </is>
+      </c>
+      <c r="N90" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O90" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="n"/>
+      <c r="I91" s="12" t="n"/>
+      <c r="J91" s="12" t="n"/>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="12" t="n"/>
+      <c r="M91" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+        </is>
+      </c>
+      <c r="N91" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O91" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N92" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O92" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n"/>
+      <c r="I93" s="12" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="12" t="n"/>
+      <c r="M93" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N93" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O93" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n"/>
+      <c r="I94" s="12" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="12" t="n"/>
+      <c r="M94" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+        </is>
+      </c>
+      <c r="N94" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O94" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="n"/>
+      <c r="M95" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+        </is>
+      </c>
+      <c r="N95" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O95" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>TailedCore</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n"/>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="12" t="n"/>
+      <c r="M96" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+        </is>
+      </c>
+      <c r="N96" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O96" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n"/>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="n"/>
+      <c r="M97" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+        </is>
+      </c>
+      <c r="N97" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O97" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="n"/>
+      <c r="I98" s="12" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="12" t="n"/>
+      <c r="M98" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
+        </is>
+      </c>
+      <c r="N98" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O98" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>ROADS</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n"/>
+      <c r="I99" s="12" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="12" t="n"/>
+      <c r="M99" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Det</t>
+        </is>
+      </c>
+      <c r="N99" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O99" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25769,8 +31070,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -26763,6 +32064,747 @@
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Dinomaly</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Jia Guo, Shuai Lu, Weihang Zhang, Huiqi Li, et al.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.14325</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/guojiajeremy/Dinomaly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>GLAD</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Hang Yao, Ming Liu, Haolin Wang, Zhicun Yin, Zifei Yan, Xiaopeng Hong, Wangmeng Zuo</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Global+Local 自適應擴散；每樣本預測去噪步驟、空間自適應特徵融合 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.07487</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/hyao1/GLAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>InvAD-Diff (Inversion-based Diffusion)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Shunsuke Sakai, et al.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint / CVPR 2026 投稿中</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Reconstruction-Free：在 latent space 直接以 likelihood 評分；無需顯式重構 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.05662</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>PromptAD</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2024</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot prompt learning；MVTec/VisA 12 個少樣本中 11 項第一；4-shot MVTec 96.6 / 96.5 [基於</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.05231</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/FuNz-0/PromptAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>PatchEAD</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2509.25856)</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.25856</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.06661</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>MultiADS (Multi-Type Zero-Shot AD)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Bosch Research / Ehsan Bayat et al.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2504.06740</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Bosch Research；多類型 zero-shot AD：依異常類型分支 prompt + 多任務分割 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.06740</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/boschresearch/MultiADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>AnomalyCLIP</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>ICLR 2024</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Object-agnostic prompt learning；學習通用異常 prompts；零樣本 MVTec I=91.5 P=91.1 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2310.18961</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+        </is>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+        </is>
+      </c>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26804,8 +32846,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -28116,6 +34158,1032 @@
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Dinomaly2 (Dinomaly Extended)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Jia Guo, Shuai Lu, Lei Fan, Zelin Li, Donglin Di, Yang Song, Weihang Zhang, Wenbing Zhu, Hong Yan, Fang Chen, Huiqi Li, Hongen Liao</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="21" t="n"/>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dinomaly 強化版：DINOv2 ViT-S/B/L Encoder + ViT decoder 重構；MVTec/VisA/MPDD 同時 SOTA；V</t>
+        </is>
+      </c>
+      <c r="N20" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2510.17611</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/guojiajeremy/Dinomaly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>STAGE (Graded Diffusion + Mask Alignment)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2509.06693)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Segmentation-oriented 工業異常合成；分級擴散 + explicit mask 對齊 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N21" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.06693</t>
+        </is>
+      </c>
+      <c r="O21" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="21" t="n"/>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：多尺度原型殘差 + 多尺度自注意力；利用合成異常監督 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N22" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2212.02031</t>
+        </is>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/xiahaifeng1995/PRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>AMI-Net</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>IEEE TASE 2024</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N23" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.11802</t>
+        </is>
+      </c>
+      <c r="O23" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/luow23/AMI-Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>InvAD (Feature Inversion)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.10760</t>
+        </is>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/zhangzjn/ADer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Adversarially Robust Diffusion AD</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2408.04839)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N25" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.04839</t>
+        </is>
+      </c>
+      <c r="O25" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>U-Flow</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>JMIV 2024 / arXiv 2211.12353</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
+        </is>
+      </c>
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2211.12353</t>
+        </is>
+      </c>
+      <c r="O26" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/mtailanian/uflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>MuSc</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>ICLR 2024</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="21" t="n"/>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot 互評分機制；未標註測試集內相互打分 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2401.16753</t>
+        </is>
+      </c>
+      <c r="O27" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/xrli-U/MuSc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>PatchEAD</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2509.25856)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="21" t="n"/>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.25856</t>
+        </is>
+      </c>
+      <c r="O28" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="21" t="n"/>
+      <c r="M29" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.06661</t>
+        </is>
+      </c>
+      <c r="O29" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>AnomalyCLIP</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>ICLR 2024</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="21" t="n"/>
+      <c r="L30" s="21" t="n"/>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Object-agnostic prompt learning；學習通用異常 prompts；零樣本 MVTec I=91.5 P=91.1 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2310.18961</t>
+        </is>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>MANTA</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="21" t="n"/>
+      <c r="L31" s="21" t="n"/>
+      <c r="M31" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O31" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="21" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="21" t="n"/>
+      <c r="L32" s="21" t="n"/>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+        </is>
+      </c>
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O32" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="21" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="21" t="n"/>
+      <c r="L33" s="21" t="n"/>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+        </is>
+      </c>
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O33" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="21" t="n"/>
+      <c r="J34" s="21" t="n"/>
+      <c r="K34" s="21" t="n"/>
+      <c r="L34" s="21" t="n"/>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N34" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O34" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="21" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="21" t="n"/>
+      <c r="L35" s="21" t="n"/>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N35" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O35" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="21" t="n"/>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="21" t="n"/>
+      <c r="L36" s="21" t="n"/>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+        </is>
+      </c>
+      <c r="N36" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O36" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="21" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="21" t="n"/>
+      <c r="L37" s="21" t="n"/>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O37" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -28167,8 +35235,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -29244,6 +36312,1260 @@
         </is>
       </c>
       <c r="O16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>UniMMAD (MoE Multi-Modal AD)</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Yuanzhao team (GitHub: yuanzhao-CVLAB)</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MoE Feature Decompression；統一 9 個資料集 / 12 模態 / 66 類別 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.25934</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/yuanzhao-CVLAB/UniMMAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>RD++</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2304.02216</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>SNARM (Self-Navigated Residual Mamba)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2508.01591)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-Navigated 殘差 Mamba：以 inter/intra-residual 自參考學習；MVTec AD/3D/VisA SOTA [基於重構</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.01591</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>EfficientAD</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2024</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch Description Network + S-T + AE；2ms 低延遲、614 FPS [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.14535</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>InvAD (Feature Inversion)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+        </is>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.10760</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/zhangzjn/ADer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>MambaAD</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>NeurIPS 2024</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：首個將 Mamba State Space Model 應用於多類異常檢測；LSS 模組+HSS block 八向掃描 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.06564</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/lewandofskee/MambaAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>DiAD</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>AAAI 2024</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.06607</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/lewandofskee/DiAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Flow (Multi-View NF)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Mathis Kruse, Bodo Rosenhahn</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+        </is>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.03306</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>ISVL (VAND 2025 第一名)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+        </is>
+      </c>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.17615</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>PatchCore (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>EfficientAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>WACV 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>DRAEM (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2021 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>RD4AD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Hanqiu Deng, Xingyu Li</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>SimpleNet (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>DDAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>BMVC 2024 (AD2 paper baseline)</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.21622</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="N32" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Real-IAD D3</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+        </is>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Odd-One-Out</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+        </is>
+      </c>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Beyond Single-Modal Boundary</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Sensor Object Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+        </is>
+      </c>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+        </is>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -646,7 +646,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="38" customWidth="1" style="27" min="1" max="1"/>
     <col width="90" customWidth="1" style="27" min="2" max="2"/>
@@ -1134,7 +1134,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O143"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -11536,12 +11536,12 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MVTec AD</t>
         </is>
       </c>
       <c r="B143" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D143" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E143" s="18" t="inlineStr">
@@ -11569,14 +11569,18 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H143" s="18" t="n"/>
-      <c r="I143" s="18" t="n"/>
+      <c r="H143" s="18" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I143" s="18" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J143" s="18" t="n"/>
       <c r="K143" s="18" t="n"/>
       <c r="L143" s="18" t="n"/>
       <c r="M143" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Detection under Domain Shift</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -11800,7 +11804,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -20625,7 +20629,7 @@
       </c>
       <c r="B129" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C129" s="21" t="inlineStr">
@@ -20635,7 +20639,7 @@
       </c>
       <c r="D129" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -20653,14 +20657,18 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H129" s="21" t="n"/>
-      <c r="I129" s="21" t="n"/>
+      <c r="H129" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I129" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J129" s="21" t="n"/>
       <c r="K129" s="21" t="n"/>
       <c r="L129" s="21" t="n"/>
       <c r="M129" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Det</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N129" s="23" t="inlineStr">
@@ -20826,7 +20834,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -23201,7 +23209,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -24165,7 +24173,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O99"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -30906,7 +30914,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -30916,7 +30924,7 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -30934,14 +30942,18 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H99" s="12" t="n"/>
+      <c r="H99" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I99" s="12" t="n"/>
       <c r="J99" s="12" t="n"/>
-      <c r="K99" s="12" t="n"/>
+      <c r="K99" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L99" s="12" t="n"/>
       <c r="M99" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ROADS: Robust Prompt-Driven Multi-Class Anomaly Det</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N99" s="14" t="inlineStr">
@@ -31071,7 +31083,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -32847,7 +32859,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>
@@ -35236,7 +35248,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="24" customWidth="1" style="27" min="2" max="2"/>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -11803,7 +11803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O129"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>PIAD</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
@@ -19638,12 +19638,12 @@
       <c r="L111" s="21" t="n"/>
       <c r="M111" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N111" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O111" s="23" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D112" s="21" t="inlineStr">
@@ -19695,12 +19695,12 @@
       <c r="L112" s="21" t="n"/>
       <c r="M112" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N112" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O112" s="23" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>MANTA</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D113" s="21" t="inlineStr">
@@ -19752,12 +19752,12 @@
       <c r="L113" s="21" t="n"/>
       <c r="M113" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N113" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O113" s="23" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>Real-IAD D3</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D114" s="21" t="inlineStr">
@@ -19809,12 +19809,12 @@
       <c r="L114" s="21" t="n"/>
       <c r="M114" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N114" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O114" s="23" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>Odd-One-Out</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D115" s="21" t="inlineStr">
@@ -19866,12 +19866,12 @@
       <c r="L115" s="21" t="n"/>
       <c r="M115" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N115" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O115" s="23" t="inlineStr">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D116" s="21" t="inlineStr">
@@ -19923,12 +19923,12 @@
       <c r="L116" s="21" t="n"/>
       <c r="M116" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N116" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O116" s="23" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D117" s="21" t="inlineStr">
@@ -19980,12 +19980,12 @@
       <c r="L117" s="21" t="n"/>
       <c r="M117" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N117" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O117" s="23" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D118" s="21" t="inlineStr">
@@ -20037,12 +20037,12 @@
       <c r="L118" s="21" t="n"/>
       <c r="M118" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N118" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O118" s="23" t="inlineStr">
@@ -20059,12 +20059,12 @@
       </c>
       <c r="B119" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C119" s="21" t="inlineStr">
         <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D119" s="21" t="inlineStr">
@@ -20074,12 +20074,12 @@
       </c>
       <c r="E119" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F119" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G119" s="21" t="inlineStr">
@@ -20094,12 +20094,12 @@
       <c r="L119" s="21" t="n"/>
       <c r="M119" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N119" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O119" s="23" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="C120" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D120" s="21" t="inlineStr">
@@ -20131,12 +20131,12 @@
       </c>
       <c r="E120" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F120" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G120" s="21" t="inlineStr">
@@ -20151,12 +20151,12 @@
       <c r="L120" s="21" t="n"/>
       <c r="M120" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N120" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O120" s="23" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D121" s="21" t="inlineStr">
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E121" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F121" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G121" s="21" t="inlineStr">
@@ -20208,12 +20208,12 @@
       <c r="L121" s="21" t="n"/>
       <c r="M121" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N121" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O121" s="23" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D122" s="21" t="inlineStr">
@@ -20245,12 +20245,12 @@
       </c>
       <c r="E122" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F122" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G122" s="21" t="inlineStr">
@@ -20265,12 +20265,12 @@
       <c r="L122" s="21" t="n"/>
       <c r="M122" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N122" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O122" s="23" t="inlineStr">
@@ -20287,27 +20287,27 @@
       </c>
       <c r="B123" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D123" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F123" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G123" s="21" t="inlineStr">
@@ -20315,368 +20315,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
+      <c r="H123" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I123" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J123" s="21" t="n"/>
       <c r="K123" s="21" t="n"/>
       <c r="L123" s="21" t="n"/>
       <c r="M123" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N123" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O123" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B124" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C124" s="21" t="inlineStr">
-        <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
-        </is>
-      </c>
-      <c r="D124" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E124" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F124" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G124" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-      <c r="J124" s="21" t="n"/>
-      <c r="K124" s="21" t="n"/>
-      <c r="L124" s="21" t="n"/>
-      <c r="M124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
-        </is>
-      </c>
-      <c r="N124" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O124" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B125" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C125" s="21" t="inlineStr">
-        <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
-        </is>
-      </c>
-      <c r="D125" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E125" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F125" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G125" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H125" s="21" t="n"/>
-      <c r="I125" s="21" t="n"/>
-      <c r="J125" s="21" t="n"/>
-      <c r="K125" s="21" t="n"/>
-      <c r="L125" s="21" t="n"/>
-      <c r="M125" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="N125" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O125" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B126" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C126" s="21" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D126" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E126" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F126" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G126" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H126" s="21" t="n"/>
-      <c r="I126" s="21" t="n"/>
-      <c r="J126" s="21" t="n"/>
-      <c r="K126" s="21" t="n"/>
-      <c r="L126" s="21" t="n"/>
-      <c r="M126" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N126" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O126" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B127" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="inlineStr">
-        <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
-        </is>
-      </c>
-      <c r="D127" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E127" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F127" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G127" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H127" s="21" t="n"/>
-      <c r="I127" s="21" t="n"/>
-      <c r="J127" s="21" t="n"/>
-      <c r="K127" s="21" t="n"/>
-      <c r="L127" s="21" t="n"/>
-      <c r="M127" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
-        </is>
-      </c>
-      <c r="N127" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O127" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B128" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="inlineStr">
-        <is>
-          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="D128" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E128" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F128" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G128" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H128" s="21" t="n"/>
-      <c r="I128" s="21" t="n"/>
-      <c r="J128" s="21" t="n"/>
-      <c r="K128" s="21" t="n"/>
-      <c r="L128" s="21" t="n"/>
-      <c r="M128" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
-        </is>
-      </c>
-      <c r="N128" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O128" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B129" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C129" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D129" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E129" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F129" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G129" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H129" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I129" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J129" s="21" t="n"/>
-      <c r="K129" s="21" t="n"/>
-      <c r="L129" s="21" t="n"/>
-      <c r="M129" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N129" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O129" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20833,7 +20491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22842,7 +22500,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>PIAD</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -22872,12 +22530,12 @@
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O33" s="14" t="inlineStr">
@@ -22899,7 +22557,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>MANTA</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -22929,243 +22587,15 @@
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O36" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24172,7 +23602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -30121,7 +29551,7 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>PIAD</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -30151,12 +29581,12 @@
       <c r="L85" s="12" t="n"/>
       <c r="M85" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O85" s="14" t="inlineStr">
@@ -30178,7 +29608,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>MANTA</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -30208,12 +29638,12 @@
       <c r="L86" s="12" t="n"/>
       <c r="M86" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N86" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O86" s="14" t="inlineStr">
@@ -30235,7 +29665,7 @@
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Real-IAD D3</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -30265,12 +29695,12 @@
       <c r="L87" s="12" t="n"/>
       <c r="M87" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N87" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O87" s="14" t="inlineStr">
@@ -30292,7 +29722,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Odd-One-Out</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -30322,12 +29752,12 @@
       <c r="L88" s="12" t="n"/>
       <c r="M88" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N88" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O88" s="14" t="inlineStr">
@@ -30349,7 +29779,7 @@
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -30379,12 +29809,12 @@
       <c r="L89" s="12" t="n"/>
       <c r="M89" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N89" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O89" s="14" t="inlineStr">
@@ -30406,7 +29836,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -30436,12 +29866,12 @@
       <c r="L90" s="12" t="n"/>
       <c r="M90" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N90" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O90" s="14" t="inlineStr">
@@ -30463,7 +29893,7 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -30493,12 +29923,12 @@
       <c r="L91" s="12" t="n"/>
       <c r="M91" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N91" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O91" s="14" t="inlineStr">
@@ -30520,7 +29950,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -30530,12 +29960,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -30550,12 +29980,12 @@
       <c r="L92" s="12" t="n"/>
       <c r="M92" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N92" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O92" s="14" t="inlineStr">
@@ -30572,27 +30002,27 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -30600,368 +30030,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H93" s="12" t="n"/>
+      <c r="H93" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I93" s="12" t="n"/>
       <c r="J93" s="12" t="n"/>
-      <c r="K93" s="12" t="n"/>
+      <c r="K93" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L93" s="12" t="n"/>
       <c r="M93" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N93" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O93" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F94" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G94" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="n"/>
-      <c r="I94" s="12" t="n"/>
-      <c r="J94" s="12" t="n"/>
-      <c r="K94" s="12" t="n"/>
-      <c r="L94" s="12" t="n"/>
-      <c r="M94" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N94" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O94" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F95" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G95" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H95" s="12" t="n"/>
-      <c r="I95" s="12" t="n"/>
-      <c r="J95" s="12" t="n"/>
-      <c r="K95" s="12" t="n"/>
-      <c r="L95" s="12" t="n"/>
-      <c r="M95" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N95" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O95" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>TailedCore</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F96" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G96" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n"/>
-      <c r="I96" s="12" t="n"/>
-      <c r="J96" s="12" t="n"/>
-      <c r="K96" s="12" t="n"/>
-      <c r="L96" s="12" t="n"/>
-      <c r="M96" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
-        </is>
-      </c>
-      <c r="N96" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O96" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="n"/>
-      <c r="I97" s="12" t="n"/>
-      <c r="J97" s="12" t="n"/>
-      <c r="K97" s="12" t="n"/>
-      <c r="L97" s="12" t="n"/>
-      <c r="M97" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N97" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O97" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F98" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="n"/>
-      <c r="I98" s="12" t="n"/>
-      <c r="J98" s="12" t="n"/>
-      <c r="K98" s="12" t="n"/>
-      <c r="L98" s="12" t="n"/>
-      <c r="M98" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
-        </is>
-      </c>
-      <c r="N98" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O98" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F99" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I99" s="12" t="n"/>
-      <c r="J99" s="12" t="n"/>
-      <c r="K99" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L99" s="12" t="n"/>
-      <c r="M99" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N99" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O99" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -31082,7 +30170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32550,7 +31638,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>MANTA</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -32580,12 +31668,12 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -32607,7 +31695,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -32637,12 +31725,12 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -32664,7 +31752,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -32694,129 +31782,15 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -32858,7 +31832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34815,7 +33789,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>MANTA</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -34845,12 +33819,12 @@
       <c r="L31" s="21" t="n"/>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MANTA: A Large-Scale Multi-View and Visual-Text Ano</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Fan_MANTA_A_Large-Scale_Multi-View_and_Visual-Text_Anomaly_Detection_Dataset_for_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -34872,7 +33846,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -34902,12 +33876,12 @@
       <c r="L32" s="21" t="n"/>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O32" s="23" t="inlineStr">
@@ -34929,7 +33903,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -34959,12 +33933,12 @@
       <c r="L33" s="21" t="n"/>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -34986,7 +33960,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -35016,186 +33990,15 @@
       <c r="L34" s="21" t="n"/>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N34" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O34" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N35" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O35" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N36" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O36" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>Heterogeneous Datasets for Unsupervised Image Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="n"/>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="n"/>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Heterogeneous Datasets for Unsupervised Image Anoma</t>
-        </is>
-      </c>
-      <c r="N37" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lagos_Heterogeneous_Datasets_for_Unsupervised_Image_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O37" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -35247,7 +34050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -37193,7 +35996,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>PIAD</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -37223,12 +36026,12 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PIAD: Pose and Illumination agnostic Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yang_PIAD_Pose_and_Illumination_agnostic_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O32" s="14" t="inlineStr">
@@ -37250,7 +36053,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Real-IAD D3</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -37280,12 +36083,12 @@
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Real-IAD D3: A Real-World 2D/Pseudo-3D/3D Dataset f</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Real-IAD_D3_A_Real-World_2DPseudo-3D3D_Dataset_for_Industrial_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O33" s="14" t="inlineStr">
@@ -37307,7 +36110,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Odd-One-Out</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -37337,243 +36140,15 @@
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Odd-One-Out: Anomaly Detection by Comparing with Ne</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhunia_Odd-One-Out_Anomaly_Detection_by_Comparing_with_Neighbors_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
-        </is>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O36" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Multi-Sensor Object Anomaly Detection</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Multi-Sensor Object Anomaly Detection: Unifying App</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Multi-Sensor_Object_Anomaly_Detection_Unifying_Appearance_Geometry_and_Internal_Properties_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -11803,7 +11803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>INP-Former (AD2 baseline)</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
         <is>
-          <t>Wei Luo, Yunkang Cao, Haiming Yao, Xiaotian Zhang, Jianan Lou, Yuqi Cheng, Weiming Shen, Wenyong Yu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 / arXiv 2503.02424</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F104" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G104" s="21" t="inlineStr">
@@ -19239,17 +19239,17 @@
       <c r="L104" s="21" t="n"/>
       <c r="M104" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：INP-Former 在 MVTec AD 2 SegF1 priv 21.8 (RoBiS baseline 起點，後續被 RoBiS+SAM 拉到 51.0</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N104" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.02424</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O104" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/luow23/INP-Former</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19266,22 +19266,22 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>PatchCore (AD2 baseline)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G105" s="21" t="inlineStr">
@@ -19296,17 +19296,17 @@
       <c r="L105" s="21" t="n"/>
       <c r="M105" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N105" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O105" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19323,22 +19323,22 @@
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>EfficientAD (AD2 baseline)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>WACV 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
@@ -19353,17 +19353,17 @@
       <c r="L106" s="21" t="n"/>
       <c r="M106" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N106" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O106" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19375,27 +19375,27 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>DRAEM (AD2 baseline)</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D107" s="21" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E107" s="21" t="inlineStr">
         <is>
-          <t>ICCV 2021 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F107" s="21" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G107" s="21" t="inlineStr">
@@ -19410,17 +19410,17 @@
       <c r="L107" s="21" t="n"/>
       <c r="M107" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N107" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O107" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/vitjanz/draem</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19432,27 +19432,27 @@
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>RD4AD (AD2 baseline)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
         <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
@@ -19467,17 +19467,17 @@
       <c r="L108" s="21" t="n"/>
       <c r="M108" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N108" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O108" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19494,22 +19494,22 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>SimpleNet (AD2 baseline)</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
         <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E109" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G109" s="21" t="inlineStr">
@@ -19524,17 +19524,17 @@
       <c r="L109" s="21" t="n"/>
       <c r="M109" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N109" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O109" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19546,27 +19546,27 @@
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>DDAD (AD2 baseline)</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
         <is>
-          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E110" s="21" t="inlineStr">
         <is>
-          <t>BMVC 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F110" s="21" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G110" s="21" t="inlineStr">
@@ -19581,17 +19581,17 @@
       <c r="L110" s="21" t="n"/>
       <c r="M110" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N110" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O110" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/arimousa/DDAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
@@ -19638,12 +19638,12 @@
       <c r="L111" s="21" t="n"/>
       <c r="M111" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N111" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O111" s="23" t="inlineStr">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D112" s="21" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E112" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F112" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G112" s="21" t="inlineStr">
@@ -19695,12 +19695,12 @@
       <c r="L112" s="21" t="n"/>
       <c r="M112" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N112" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O112" s="23" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D113" s="21" t="inlineStr">
@@ -19732,12 +19732,12 @@
       </c>
       <c r="E113" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F113" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G113" s="21" t="inlineStr">
@@ -19752,12 +19752,12 @@
       <c r="L113" s="21" t="n"/>
       <c r="M113" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N113" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O113" s="23" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D114" s="21" t="inlineStr">
@@ -19789,12 +19789,12 @@
       </c>
       <c r="E114" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F114" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G114" s="21" t="inlineStr">
@@ -19809,12 +19809,12 @@
       <c r="L114" s="21" t="n"/>
       <c r="M114" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N114" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O114" s="23" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D115" s="21" t="inlineStr">
@@ -19846,12 +19846,12 @@
       </c>
       <c r="E115" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F115" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G115" s="21" t="inlineStr">
@@ -19866,12 +19866,12 @@
       <c r="L115" s="21" t="n"/>
       <c r="M115" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N115" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O115" s="23" t="inlineStr">
@@ -19888,27 +19888,27 @@
       </c>
       <c r="B116" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D116" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E116" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F116" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G116" s="21" t="inlineStr">
@@ -19916,425 +19916,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
+      <c r="H116" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I116" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J116" s="21" t="n"/>
       <c r="K116" s="21" t="n"/>
       <c r="L116" s="21" t="n"/>
       <c r="M116" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N116" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O116" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B117" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C117" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D117" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F117" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G117" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-      <c r="J117" s="21" t="n"/>
-      <c r="K117" s="21" t="n"/>
-      <c r="L117" s="21" t="n"/>
-      <c r="M117" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N117" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O117" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B118" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C118" s="21" t="inlineStr">
-        <is>
-          <t>TailedCore</t>
-        </is>
-      </c>
-      <c r="D118" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E118" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F118" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G118" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H118" s="21" t="n"/>
-      <c r="I118" s="21" t="n"/>
-      <c r="J118" s="21" t="n"/>
-      <c r="K118" s="21" t="n"/>
-      <c r="L118" s="21" t="n"/>
-      <c r="M118" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
-        </is>
-      </c>
-      <c r="N118" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O118" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B119" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
-        </is>
-      </c>
-      <c r="D119" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F119" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G119" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H119" s="21" t="n"/>
-      <c r="I119" s="21" t="n"/>
-      <c r="J119" s="21" t="n"/>
-      <c r="K119" s="21" t="n"/>
-      <c r="L119" s="21" t="n"/>
-      <c r="M119" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
-        </is>
-      </c>
-      <c r="N119" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O119" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B120" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
-        </is>
-      </c>
-      <c r="D120" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E120" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F120" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G120" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-      <c r="J120" s="21" t="n"/>
-      <c r="K120" s="21" t="n"/>
-      <c r="L120" s="21" t="n"/>
-      <c r="M120" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="N120" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O120" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B121" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C121" s="21" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D121" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E121" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F121" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G121" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="21" t="n"/>
-      <c r="K121" s="21" t="n"/>
-      <c r="L121" s="21" t="n"/>
-      <c r="M121" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N121" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O121" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B122" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C122" s="21" t="inlineStr">
-        <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
-        </is>
-      </c>
-      <c r="D122" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E122" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F122" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G122" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H122" s="21" t="n"/>
-      <c r="I122" s="21" t="n"/>
-      <c r="J122" s="21" t="n"/>
-      <c r="K122" s="21" t="n"/>
-      <c r="L122" s="21" t="n"/>
-      <c r="M122" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
-        </is>
-      </c>
-      <c r="N122" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O122" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B123" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C123" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D123" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E123" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F123" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G123" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H123" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I123" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J123" s="21" t="n"/>
-      <c r="K123" s="21" t="n"/>
-      <c r="L123" s="21" t="n"/>
-      <c r="M123" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N123" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O123" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20491,7 +20092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22005,19 +21606,27 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="G24" s="12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot prompt learning；MVTec/VisA 12 個少樣本中 11 項第一；4-shot MVTec 96.6 / 96.5 [基於</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
@@ -22158,22 +21767,22 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>PatchCore (AD2 baseline)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -22188,17 +21797,17 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22215,22 +21824,22 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>EfficientAD (AD2 baseline)</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>WACV 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -22245,357 +21854,15 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>DRAEM (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>ICCV 2021 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/vitjanz/draem</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>RD4AD (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
-        </is>
-      </c>
-      <c r="N30" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>SimpleNet (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2023 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>DDAD (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BMVC 2024 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
-        </is>
-      </c>
-      <c r="N32" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O32" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/arimousa/DDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23602,7 +22869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29152,22 +28419,22 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>INP-Former (AD2 baseline)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Wei Luo, Yunkang Cao, Haiming Yao, Xiaotian Zhang, Jianan Lou, Yuqi Cheng, Weiming Shen, Wenyong Yu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 / arXiv 2503.02424</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -29182,17 +28449,17 @@
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：INP-Former 在 MVTec AD 2 SegF1 priv 21.8 (RoBiS baseline 起點，後續被 RoBiS+SAM 拉到 51.0</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.02424</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/luow23/INP-Former</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29209,22 +28476,22 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>PatchCore (AD2 baseline)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -29239,17 +28506,17 @@
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O79" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29266,22 +28533,22 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>EfficientAD (AD2 baseline)</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>WACV 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -29296,17 +28563,17 @@
       <c r="L80" s="12" t="n"/>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O80" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29318,27 +28585,27 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>DRAEM (AD2 baseline)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2021 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -29353,17 +28620,17 @@
       <c r="L81" s="12" t="n"/>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N81" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O81" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/vitjanz/draem</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29375,27 +28642,27 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>RD4AD (AD2 baseline)</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -29410,17 +28677,17 @@
       <c r="L82" s="12" t="n"/>
       <c r="M82" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N82" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O82" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29437,22 +28704,22 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SimpleNet (AD2 baseline)</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -29467,17 +28734,17 @@
       <c r="L83" s="12" t="n"/>
       <c r="M83" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N83" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O83" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29489,27 +28756,27 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>DDAD (AD2 baseline)</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>BMVC 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -29524,17 +28791,17 @@
       <c r="L84" s="12" t="n"/>
       <c r="M84" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N84" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O84" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/arimousa/DDAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29551,7 +28818,7 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -29561,12 +28828,12 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -29581,12 +28848,12 @@
       <c r="L85" s="12" t="n"/>
       <c r="M85" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O85" s="14" t="inlineStr">
@@ -29603,27 +28870,27 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -29631,425 +28898,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H86" s="12" t="n"/>
+      <c r="H86" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
-      <c r="K86" s="12" t="n"/>
+      <c r="K86" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L86" s="12" t="n"/>
       <c r="M86" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N86" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O86" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H87" s="12" t="n"/>
-      <c r="I87" s="12" t="n"/>
-      <c r="J87" s="12" t="n"/>
-      <c r="K87" s="12" t="n"/>
-      <c r="L87" s="12" t="n"/>
-      <c r="M87" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
-        </is>
-      </c>
-      <c r="N87" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O87" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n"/>
-      <c r="I88" s="12" t="n"/>
-      <c r="J88" s="12" t="n"/>
-      <c r="K88" s="12" t="n"/>
-      <c r="L88" s="12" t="n"/>
-      <c r="M88" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N88" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O88" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G89" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H89" s="12" t="n"/>
-      <c r="I89" s="12" t="n"/>
-      <c r="J89" s="12" t="n"/>
-      <c r="K89" s="12" t="n"/>
-      <c r="L89" s="12" t="n"/>
-      <c r="M89" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N89" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O89" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="n"/>
-      <c r="I90" s="12" t="n"/>
-      <c r="J90" s="12" t="n"/>
-      <c r="K90" s="12" t="n"/>
-      <c r="L90" s="12" t="n"/>
-      <c r="M90" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N90" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O90" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>TailedCore</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G91" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="n"/>
-      <c r="I91" s="12" t="n"/>
-      <c r="J91" s="12" t="n"/>
-      <c r="K91" s="12" t="n"/>
-      <c r="L91" s="12" t="n"/>
-      <c r="M91" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
-        </is>
-      </c>
-      <c r="N91" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O91" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="n"/>
-      <c r="I92" s="12" t="n"/>
-      <c r="J92" s="12" t="n"/>
-      <c r="K92" s="12" t="n"/>
-      <c r="L92" s="12" t="n"/>
-      <c r="M92" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N92" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O92" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G93" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I93" s="12" t="n"/>
-      <c r="J93" s="12" t="n"/>
-      <c r="K93" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L93" s="12" t="n"/>
-      <c r="M93" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N93" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O93" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -31200,19 +30068,23 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="G16" s="12" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>96.59999999999999</v>
+      </c>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
+          <t>✅ 已驗證 (Dinomaly Table A11 multi-class)：DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -31371,19 +30243,27 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="G19" s="12" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot prompt learning；MVTec/VisA 12 個少樣本中 11 項第一；4-shot MVTec 96.6 / 96.5 [基於</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；ViT-B/16+ CLIP backbone [基於 VLM]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -31599,19 +30479,25 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
+      <c r="G23" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>88.7</v>
+      </c>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Object-agnostic prompt learning；學習通用異常 prompts；零樣本 MVTec I=91.5 P=91.1 [基於表徵]</t>
+          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本通用異常 prompts [基於 VLM]</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
@@ -33180,19 +32066,23 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
+      <c r="G20" s="21" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>79.8</v>
+      </c>
       <c r="K20" s="21" t="n"/>
       <c r="L20" s="21" t="n"/>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dinomaly 強化版：DINOv2 ViT-S/B/L Encoder + ViT decoder 重構；MVTec/VisA/MPDD 同時 SOTA；V</t>
+          <t>✅ 已驗證 (Dinomaly2 Table 2, Dinomaly2-L multi-class)：DINOv2 ViT-L Encoder + ViT decoder；BTAD 多類別 SOTA [基於重構]</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
@@ -33579,19 +32469,27 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
+      <c r="G27" s="21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K27" s="21" t="n"/>
       <c r="L27" s="21" t="n"/>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot 互評分機制；未標註測試集內相互打分 [基於表徵]</t>
+          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
@@ -33750,19 +32648,25 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
+      <c r="G30" s="21" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="n">
+        <v>74.8</v>
+      </c>
       <c r="K30" s="21" t="n"/>
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Object-agnostic prompt learning；學習通用異常 prompts；零樣本 MVTec I=91.5 P=91.1 [基於表徵]</t>
+          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -34050,7 +32954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -35307,27 +34211,27 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>EfficientAD</t>
+          <t>InvAD (Feature Inversion)</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>WACV 2024</t>
+          <t>arXiv preprint 2024</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -35342,17 +34246,17 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch Description Network + S-T + AE；2ms 低延遲、614 FPS [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.14535</t>
+          <t>https://arxiv.org/abs/2404.10760</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
+          <t>https://github.com/zhangzjn/ADer</t>
         </is>
       </c>
     </row>
@@ -35369,17 +34273,17 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>MambaAD</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>NeurIPS 2024</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -35387,29 +34291,33 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="G21" s="12" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>93.59999999999999</v>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>✅ 已驗證 (MambaAD Table A5/A6 multi-class)：Mamba SSM 多類別異常偵測；Hilbert Hybrid Scanning [基於 SSM]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
+          <t>https://arxiv.org/abs/2404.06564</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/zhangzjn/ADer</t>
+          <t>https://github.com/lewandofskee/MambaAD</t>
         </is>
       </c>
     </row>
@@ -35421,27 +34329,27 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>MambaAD</t>
+          <t>DiAD</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
+          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2024</t>
+          <t>AAAI 2024</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -35456,17 +34364,17 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：首個將 Mamba State Space Model 應用於多類異常檢測；LSS 模組+HSS block 八向掃描 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.06564</t>
+          <t>https://arxiv.org/abs/2312.06607</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/lewandofskee/MambaAD</t>
+          <t>https://github.com/lewandofskee/DiAD</t>
         </is>
       </c>
     </row>
@@ -35478,27 +34386,27 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>DiAD</t>
+          <t>Multi-Flow (Multi-View NF)</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
+          <t>Mathis Kruse, Bodo Rosenhahn</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>AAAI 2024</t>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -35513,17 +34421,17 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.06607</t>
+          <t>https://arxiv.org/abs/2504.03306</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/lewandofskee/DiAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -35535,27 +34443,27 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Multi-Flow (Multi-View NF)</t>
+          <t>ISVL (VAND 2025 第一名)</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Mathis Kruse, Bodo Rosenhahn</t>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -35570,12 +34478,12 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03306</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -35597,17 +34505,17 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -35627,12 +34535,12 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -35654,22 +34562,22 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>PatchCore (AD2 baseline)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -35684,17 +34592,17 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -35711,22 +34619,22 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>EfficientAD (AD2 baseline)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>WACV 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -35741,414 +34649,15 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>DRAEM (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>ICCV 2021 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/vitjanz/draem</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>RD4AD (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>SimpleNet (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2023 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]</t>
-        </is>
-      </c>
-      <c r="N30" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>DDAD (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>BMVC 2024 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/arimousa/DDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
-        </is>
-      </c>
-      <c r="N32" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O32" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -11803,7 +11803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18805,27 +18805,27 @@
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>Multi-Flow (Multi-View NF)</t>
+          <t>LogicQA (VLM Logical AD)</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>Mathis Kruse, Bodo Rosenhahn</t>
+          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G97" s="21" t="inlineStr">
@@ -18840,12 +18840,12 @@
       <c r="L97" s="21" t="n"/>
       <c r="M97" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
         </is>
       </c>
       <c r="N97" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03306</t>
+          <t>https://arxiv.org/abs/2503.20252</t>
         </is>
       </c>
       <c r="O97" s="23" t="inlineStr">
@@ -18862,27 +18862,27 @@
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>LogicQA (VLM Logical AD)</t>
+          <t>SINBAD (Set Features)</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
+          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
+          <t>ICML 2024 / arXiv 2311.14773</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
@@ -18897,17 +18897,17 @@
       <c r="L98" s="21" t="n"/>
       <c r="M98" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
         </is>
       </c>
       <c r="N98" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.20252</t>
+          <t>https://arxiv.org/abs/2311.14773</t>
         </is>
       </c>
       <c r="O98" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/NivC/SINBAD</t>
         </is>
       </c>
     </row>
@@ -18919,27 +18919,27 @@
       </c>
       <c r="B99" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>SINBAD (Set Features)</t>
+          <t>BTF (Back to the Feature)</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+          <t>Eliahu Horwitz, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>ICML 2024 / arXiv 2311.14773</t>
+          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="G99" s="21" t="inlineStr">
@@ -18954,17 +18954,17 @@
       <c r="L99" s="21" t="n"/>
       <c r="M99" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
         </is>
       </c>
       <c r="N99" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.14773</t>
+          <t>https://arxiv.org/abs/2203.05550</t>
         </is>
       </c>
       <c r="O99" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/NivC/SINBAD</t>
+          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
         </is>
       </c>
     </row>
@@ -18981,22 +18981,22 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>BTF (Back to the Feature)</t>
+          <t>RoBiS (VAND 2025 第二名)</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
         <is>
-          <t>Eliahu Horwitz, Yedid Hoshen</t>
+          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
         </is>
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
@@ -19011,17 +19011,17 @@
       <c r="L100" s="21" t="n"/>
       <c r="M100" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
         </is>
       </c>
       <c r="N100" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.05550</t>
+          <t>https://arxiv.org/abs/2505.21152</t>
         </is>
       </c>
       <c r="O100" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+          <t>https://github.com/xrli-U/RoBiS</t>
         </is>
       </c>
     </row>
@@ -19038,17 +19038,17 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>RoBiS (VAND 2025 第二名)</t>
+          <t>SuperAD (Training-free DINOv2)</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
         </is>
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
         </is>
       </c>
       <c r="F101" s="21" t="inlineStr">
@@ -19068,17 +19068,17 @@
       <c r="L101" s="21" t="n"/>
       <c r="M101" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
         </is>
       </c>
       <c r="N101" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.21152</t>
+          <t>https://arxiv.org/abs/2505.19750</t>
         </is>
       </c>
       <c r="O101" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/RoBiS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19095,22 +19095,22 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>SuperAD (Training-free DINOv2)</t>
+          <t>ISVL (VAND 2025 第一名)</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
         <is>
-          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
         </is>
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G102" s="21" t="inlineStr">
@@ -19125,12 +19125,12 @@
       <c r="L102" s="21" t="n"/>
       <c r="M102" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
         </is>
       </c>
       <c r="N102" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.19750</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O102" s="23" t="inlineStr">
@@ -19152,17 +19152,17 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E103" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
@@ -19182,12 +19182,12 @@
       <c r="L103" s="21" t="n"/>
       <c r="M103" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N103" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O103" s="23" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -19239,12 +19239,12 @@
       <c r="L104" s="21" t="n"/>
       <c r="M104" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N104" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O104" s="23" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
@@ -19296,12 +19296,12 @@
       <c r="L105" s="21" t="n"/>
       <c r="M105" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N105" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O105" s="23" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
@@ -19353,12 +19353,12 @@
       <c r="L106" s="21" t="n"/>
       <c r="M106" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N106" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O106" s="23" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D107" s="21" t="inlineStr">
@@ -19410,12 +19410,12 @@
       <c r="L107" s="21" t="n"/>
       <c r="M107" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N107" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O107" s="23" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
@@ -19467,12 +19467,12 @@
       <c r="L108" s="21" t="n"/>
       <c r="M108" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N108" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O108" s="23" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
@@ -19524,12 +19524,12 @@
       <c r="L109" s="21" t="n"/>
       <c r="M109" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N109" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O109" s="23" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
@@ -19581,12 +19581,12 @@
       <c r="L110" s="21" t="n"/>
       <c r="M110" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N110" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O110" s="23" t="inlineStr">
@@ -19603,12 +19603,12 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E111" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F111" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G111" s="21" t="inlineStr">
@@ -19638,12 +19638,12 @@
       <c r="L111" s="21" t="n"/>
       <c r="M111" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N111" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O111" s="23" t="inlineStr">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D112" s="21" t="inlineStr">
@@ -19695,12 +19695,12 @@
       <c r="L112" s="21" t="n"/>
       <c r="M112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N112" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O112" s="23" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D113" s="21" t="inlineStr">
@@ -19752,12 +19752,12 @@
       <c r="L113" s="21" t="n"/>
       <c r="M113" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N113" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O113" s="23" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D114" s="21" t="inlineStr">
@@ -19809,12 +19809,12 @@
       <c r="L114" s="21" t="n"/>
       <c r="M114" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N114" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O114" s="23" t="inlineStr">
@@ -19831,17 +19831,17 @@
       </c>
       <c r="B115" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D115" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -19859,83 +19859,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H115" s="21" t="n"/>
-      <c r="I115" s="21" t="n"/>
+      <c r="H115" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I115" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J115" s="21" t="n"/>
       <c r="K115" s="21" t="n"/>
       <c r="L115" s="21" t="n"/>
       <c r="M115" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N115" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O115" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B116" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C116" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D116" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E116" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F116" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G116" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H116" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I116" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J116" s="21" t="n"/>
-      <c r="K116" s="21" t="n"/>
-      <c r="L116" s="21" t="n"/>
-      <c r="M116" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N116" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O116" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20092,7 +20035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -21417,22 +21360,22 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>TFA-Net (Template-based Feature Aggregation)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Anonymous (arXiv 2603.22874)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -21447,17 +21390,17 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：模板特徵聚合網路；以多模板做特徵級重構，I-AUROC 98.7%、P-AUROC 98.3% [基於重構]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
+          <t>https://arxiv.org/abs/2603.22874</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/zhangzjn/ADer</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21469,27 +21412,27 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>TFA-Net (Template-based Feature Aggregation)</t>
+          <t>Triad (LMM-Aided AD)</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2603.22874)</t>
+          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -21504,17 +21447,17 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：模板特徵聚合網路；以多模板做特徵級重構，I-AUROC 98.7%、P-AUROC 98.3% [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2603.22874</t>
+          <t>https://arxiv.org/abs/2503.13184</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/tzjtatata/Triad</t>
         </is>
       </c>
     </row>
@@ -21531,47 +21474,55 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Triad (LMM-Aided AD)</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13184</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tzjtatata/Triad</t>
+          <t>https://github.com/FuNz-0/PromptAD</t>
         </is>
       </c>
     </row>
@@ -21588,55 +21539,47 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>PromptAD</t>
+          <t>ISVL (VAND 2025 第一名)</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21648,27 +21591,27 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Multi-Flow (Multi-View NF)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Mathis Kruse, Bodo Rosenhahn</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -21683,12 +21626,12 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03306</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -21710,17 +21653,17 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -21740,129 +21683,15 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22869,7 +22698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28129,27 +27958,27 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Multi-Flow (Multi-View NF)</t>
+          <t>April-GAN (CLIP-AD)</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Mathis Kruse, Bodo Rosenhahn</t>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -28164,17 +27993,17 @@
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03306</t>
+          <t>https://arxiv.org/abs/2305.17382</t>
         </is>
       </c>
       <c r="O73" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
         </is>
       </c>
     </row>
@@ -28191,17 +28020,17 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>April-GAN (CLIP-AD)</t>
+          <t>SAA+ (Segment Any Anomaly)</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+          <t>IEEE TCYB 2025 / arXiv 2023</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -28221,17 +28050,17 @@
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.17382</t>
+          <t>https://arxiv.org/abs/2305.10724</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
+          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
         </is>
       </c>
     </row>
@@ -28248,22 +28077,22 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SAA+ (Segment Any Anomaly)</t>
+          <t>SuperAD (Training-free DINOv2)</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
+          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>IEEE TCYB 2025 / arXiv 2023</t>
+          <t>CVPR 2025 VAND 3.0 Workshop</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -28278,17 +28107,17 @@
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.10724</t>
+          <t>https://arxiv.org/abs/2505.19750</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28305,22 +28134,22 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SuperAD (Training-free DINOv2)</t>
+          <t>ISVL (VAND 2025 第一名)</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -28335,12 +28164,12 @@
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.19750</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
@@ -28362,17 +28191,17 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -28392,12 +28221,12 @@
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
@@ -28419,7 +28248,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -28449,12 +28278,12 @@
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -28476,7 +28305,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -28506,12 +28335,12 @@
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O79" s="14" t="inlineStr">
@@ -28533,7 +28362,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -28563,12 +28392,12 @@
       <c r="L80" s="12" t="n"/>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O80" s="14" t="inlineStr">
@@ -28590,7 +28419,7 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -28620,12 +28449,12 @@
       <c r="L81" s="12" t="n"/>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
         </is>
       </c>
       <c r="N81" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O81" s="14" t="inlineStr">
@@ -28647,7 +28476,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -28677,12 +28506,12 @@
       <c r="L82" s="12" t="n"/>
       <c r="M82" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N82" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O82" s="14" t="inlineStr">
@@ -28704,7 +28533,7 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -28734,12 +28563,12 @@
       <c r="L83" s="12" t="n"/>
       <c r="M83" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N83" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O83" s="14" t="inlineStr">
@@ -28761,7 +28590,7 @@
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -28771,12 +28600,12 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -28791,12 +28620,12 @@
       <c r="L84" s="12" t="n"/>
       <c r="M84" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N84" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O84" s="14" t="inlineStr">
@@ -28813,17 +28642,17 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -28841,83 +28670,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H85" s="12" t="n"/>
+      <c r="H85" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n"/>
+      <c r="K85" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L85" s="12" t="n"/>
       <c r="M85" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O85" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I86" s="12" t="n"/>
-      <c r="J86" s="12" t="n"/>
-      <c r="K86" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L86" s="12" t="n"/>
-      <c r="M86" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N86" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O86" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -30308,19 +30080,23 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
+      <c r="G20" s="12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>89.59999999999999</v>
+      </c>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；DINOv2 ViT-B/14 backbone [零樣本 Foundation Model]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
@@ -30365,19 +30141,27 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="G21" s="12" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP 兩階段 prompt+residual adapter；零樣本/few-shot 通用 [基於 VLM]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -30718,7 +30502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32275,17 +32059,17 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>Adversarially Robust Diffusion AD</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Anonymous (arXiv 2408.04839)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -32295,7 +32079,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -32310,17 +32094,17 @@
       <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
+          <t>https://arxiv.org/abs/2408.04839</t>
         </is>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/zhangzjn/ADer</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32332,27 +32116,27 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Adversarially Robust Diffusion AD</t>
+          <t>U-Flow</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2408.04839)</t>
+          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>JMIV 2024 / arXiv 2211.12353</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -32367,17 +32151,17 @@
       <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2408.04839</t>
+          <t>https://arxiv.org/abs/2211.12353</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/mtailanian/uflow</t>
         </is>
       </c>
     </row>
@@ -32389,52 +32173,60 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>U-Flow</t>
+          <t>MuSc</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>JMIV 2024 / arXiv 2211.12353</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K26" s="21" t="n"/>
       <c r="L26" s="21" t="n"/>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
+          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12353</t>
+          <t>https://arxiv.org/abs/2401.16753</t>
         </is>
       </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/mtailanian/uflow</t>
+          <t>https://github.com/xrli-U/MuSc</t>
         </is>
       </c>
     </row>
@@ -32451,55 +32243,51 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>MuSc</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G27" s="21" t="n">
-        <v>94.8</v>
+        <v>91.2</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>80</v>
       </c>
       <c r="K27" s="21" t="n"/>
       <c r="L27" s="21" t="n"/>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
+          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.16753</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/MuSc</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32516,47 +32304,55 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>PatchEAD</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>97</v>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K28" s="21" t="n"/>
       <c r="L28" s="21" t="n"/>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
         </is>
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -32573,47 +32369,53 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>74.8</v>
+      </c>
       <c r="K29" s="21" t="n"/>
       <c r="L29" s="21" t="n"/>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
         </is>
       </c>
     </row>
@@ -32630,53 +32432,47 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>AnomalyCLIP</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="21" t="n">
-        <v>74.8</v>
-      </c>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="21" t="n"/>
       <c r="K30" s="21" t="n"/>
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32693,7 +32489,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -32723,12 +32519,12 @@
       <c r="L31" s="21" t="n"/>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -32750,7 +32546,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -32780,12 +32576,12 @@
       <c r="L32" s="21" t="n"/>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O32" s="23" t="inlineStr">
@@ -32807,7 +32603,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -32837,72 +32633,15 @@
       <c r="L33" s="21" t="n"/>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N34" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O34" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -32954,7 +32693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34234,19 +33973,23 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
+      <c r="G20" s="12" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>94.7</v>
+      </c>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>✅ 已驗證 (InvAD Appendix Table A2, MUAD)：Feature Inversion 多類別異常偵測；MVTec 3D AD I=86.1, P=98.8 [基於重構]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
@@ -34386,27 +34129,27 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Multi-Flow (Multi-View NF)</t>
+          <t>ISVL (VAND 2025 第一名)</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Mathis Kruse, Bodo Rosenhahn</t>
+          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -34421,12 +34164,12 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-IAD 多視角 NF：sample-wise 95.85 / image 90.27 / pixel 96.47 / AUPRO 87.91；MVTe</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03306</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -34448,17 +34191,17 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -34478,12 +34221,12 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -34505,7 +34248,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -34535,12 +34278,12 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -34562,7 +34305,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -34592,72 +34335,15 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -11803,7 +11803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -13473,25 +13473,17 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
+      <c r="G24" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>96.09999999999999</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -13505,7 +13497,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>多尺度原型殘差 + 多尺度自注意力；利用合成異常監督 [基於資料擴增]</t>
+          <t>✅ 已驗證 (PRN CVPR2023 Table 1+2 average)：Prototypical Residual Network；多尺度殘差表徵+異常生成 [監督式異常定位]</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -18411,22 +18403,22 @@
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>CSAD (Component Segmentation AD)</t>
+          <t>M3DM-NR (Noisy-Resistant)</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>Yu-Hsuan Hsieh, Shang-Hong Lai (National Tsing Hua University)</t>
+          <t>Chengjie Wang, Haokun Zhu, Jinlong Peng, Yue Wang, Ran Yi, Yunsheng Wu, Lizhuang Ma, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>BMVC 2024 / arXiv 2408.15628</t>
+          <t>arXiv preprint 2024 / 2406.02263</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -18441,17 +18433,17 @@
       <c r="L90" s="21" t="n"/>
       <c r="M90" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec LOCO 為主：I-AUROC 95.3 (logical 96.7 / structural 94.0)；latency 8.9ms / 321.</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：M3DM 雜訊穩健版：以多模態去雜訊處理 noisy 訓練集 [基於表徵]</t>
         </is>
       </c>
       <c r="N90" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2408.15628</t>
+          <t>https://arxiv.org/abs/2406.02263</t>
         </is>
       </c>
       <c r="O90" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/Tokichan/CSAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18468,22 +18460,22 @@
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>M3DM-NR (Noisy-Resistant)</t>
+          <t>M3DM (Multimodal Hybrid Fusion)</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Chengjie Wang, Haokun Zhu, Jinlong Peng, Yue Wang, Ran Yi, Yunsheng Wu, Lizhuang Ma, Jiangning Zhang</t>
+          <t>Yue Wang, Jinlong Peng, Jiangning Zhang, Ran Yi, Yabiao Wang, Chengjie Wang</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024 / 2406.02263</t>
+          <t>CVPR 2023 / arXiv 2303.00601</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
@@ -18498,17 +18490,17 @@
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：M3DM 雜訊穩健版：以多模態去雜訊處理 noisy 訓練集 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-modal Memory Bank + 點雲對齊 + Patch-wise 對比學習；RGB-3D 異常檢測 [基於表徵]</t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2406.02263</t>
+          <t>https://arxiv.org/abs/2303.00601</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/nomewang/M3DM</t>
         </is>
       </c>
     </row>
@@ -18520,27 +18512,27 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>M3DM (Multimodal Hybrid Fusion)</t>
+          <t>VT-ADL</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Yue Wang, Jinlong Peng, Jiangning Zhang, Ran Yi, Yabiao Wang, Chengjie Wang</t>
+          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 / arXiv 2303.00601</t>
+          <t>ISIE 2021 / arXiv 2104.10036</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -18555,17 +18547,17 @@
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-modal Memory Bank + 點雲對齊 + Patch-wise 對比學習；RGB-3D 異常檢測 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.00601</t>
+          <t>https://arxiv.org/abs/2104.10036</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/nomewang/M3DM</t>
+          <t>https://github.com/pankajmishra000/VT-ADL</t>
         </is>
       </c>
     </row>
@@ -18582,22 +18574,22 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>VT-ADL</t>
+          <t>AST (Asymmetric Student-Teacher)</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>ISIE 2021 / arXiv 2104.10036</t>
+          <t>WACV 2023</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -18612,17 +18604,17 @@
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：非對稱 S-T (NF teacher + FFN student)；MVTec 3D-AD RGB-only 設定 SOTA [基於重構]</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2104.10036</t>
+          <t>https://arxiv.org/abs/2210.07829</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/pankajmishra000/VT-ADL</t>
+          <t>https://github.com/marco-rudolph/AST</t>
         </is>
       </c>
     </row>
@@ -18639,22 +18631,22 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>AST (Asymmetric Student-Teacher)</t>
+          <t>EasyNet</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+          <t>Ruitao Chen, Guoyang Xie, Jiaqi Liu, Jinbao Wang, Ziqi Luo, Jinfan Wang, Feng Zheng</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>WACV 2023</t>
+          <t>ACM MM 2023 / arXiv 2307.13925</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
@@ -18669,17 +18661,17 @@
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：非對稱 S-T (NF teacher + FFN student)；MVTec 3D-AD RGB-only 設定 SOTA [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：輕量易部署網路：無需 pretrained / memory bank；多模態異常分割；快速推論 [基於重構]</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2210.07829</t>
+          <t>https://arxiv.org/abs/2307.13925</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/marco-rudolph/AST</t>
+          <t>https://github.com/sukanyapatra1997/ULSAD-2024</t>
         </is>
       </c>
     </row>
@@ -18691,27 +18683,27 @@
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>EasyNet</t>
+          <t>PSAD (Few-Shot Part Segmentation)</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Ruitao Chen, Guoyang Xie, Jiaqi Liu, Jinbao Wang, Ziqi Luo, Jinfan Wang, Feng Zheng</t>
+          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>ACM MM 2023 / arXiv 2307.13925</t>
+          <t>AAAI 2024 / arXiv 2312.13783</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
@@ -18726,17 +18718,17 @@
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：輕量易部署網路：無需 pretrained / memory bank；多模態異常分割；快速推論 [基於重構]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2307.13925</t>
+          <t>https://arxiv.org/abs/2312.13783</t>
         </is>
       </c>
       <c r="O95" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/sukanyapatra1997/ULSAD-2024</t>
+          <t>https://github.com/kaist-cvml-lab/PSAD</t>
         </is>
       </c>
     </row>
@@ -18753,22 +18745,22 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>PSAD (Few-Shot Part Segmentation)</t>
+          <t>LogicQA (VLM Logical AD)</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
+          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
         </is>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>AAAI 2024 / arXiv 2312.13783</t>
+          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
@@ -18783,17 +18775,17 @@
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.13783</t>
+          <t>https://arxiv.org/abs/2503.20252</t>
         </is>
       </c>
       <c r="O96" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/kaist-cvml-lab/PSAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18805,27 +18797,27 @@
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>LogicQA (VLM Logical AD)</t>
+          <t>SINBAD (Set Features)</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
+          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
+          <t>ICML 2024 / arXiv 2311.14773</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="G97" s="21" t="inlineStr">
@@ -18840,17 +18832,17 @@
       <c r="L97" s="21" t="n"/>
       <c r="M97" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
         </is>
       </c>
       <c r="N97" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.20252</t>
+          <t>https://arxiv.org/abs/2311.14773</t>
         </is>
       </c>
       <c r="O97" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/NivC/SINBAD</t>
         </is>
       </c>
     </row>
@@ -18862,27 +18854,27 @@
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>SINBAD (Set Features)</t>
+          <t>BTF (Back to the Feature)</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+          <t>Eliahu Horwitz, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>ICML 2024 / arXiv 2311.14773</t>
+          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
@@ -18897,17 +18889,17 @@
       <c r="L98" s="21" t="n"/>
       <c r="M98" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
         </is>
       </c>
       <c r="N98" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.14773</t>
+          <t>https://arxiv.org/abs/2203.05550</t>
         </is>
       </c>
       <c r="O98" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/NivC/SINBAD</t>
+          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
         </is>
       </c>
     </row>
@@ -18924,22 +18916,22 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>BTF (Back to the Feature)</t>
+          <t>RoBiS (VAND 2025 第二名)</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>Eliahu Horwitz, Yedid Hoshen</t>
+          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G99" s="21" t="inlineStr">
@@ -18954,17 +18946,17 @@
       <c r="L99" s="21" t="n"/>
       <c r="M99" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
         </is>
       </c>
       <c r="N99" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.05550</t>
+          <t>https://arxiv.org/abs/2505.21152</t>
         </is>
       </c>
       <c r="O99" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+          <t>https://github.com/xrli-U/RoBiS</t>
         </is>
       </c>
     </row>
@@ -18981,22 +18973,22 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>RoBiS (VAND 2025 第二名)</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
@@ -19011,17 +19003,17 @@
       <c r="L100" s="21" t="n"/>
       <c r="M100" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N100" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.21152</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O100" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/RoBiS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19038,42 +19030,52 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>SuperAD (Training-free DINOv2)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F101" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="G101" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G101" s="21" t="n">
+        <v>94</v>
+      </c>
+      <c r="H101" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J101" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K101" s="21" t="n"/>
       <c r="L101" s="21" t="n"/>
       <c r="M101" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
         </is>
       </c>
       <c r="N101" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.19750</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O101" s="23" t="inlineStr">
@@ -19095,17 +19097,17 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr">
@@ -19113,24 +19115,32 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G102" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
-      <c r="J102" s="21" t="n"/>
+      <c r="G102" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H102" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I102" s="21" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J102" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K102" s="21" t="n"/>
       <c r="L102" s="21" t="n"/>
       <c r="M102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N102" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O102" s="23" t="inlineStr">
@@ -19152,7 +19162,7 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -19170,24 +19180,28 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G103" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="21" t="n"/>
+      <c r="G103" s="21" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H103" s="21" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I103" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="J103" s="21" t="n">
+        <v>94.90000000000001</v>
+      </c>
       <c r="K103" s="21" t="n"/>
       <c r="L103" s="21" t="n"/>
       <c r="M103" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
         </is>
       </c>
       <c r="N103" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O103" s="23" t="inlineStr">
@@ -19209,7 +19223,7 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -19239,12 +19253,12 @@
       <c r="L104" s="21" t="n"/>
       <c r="M104" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N104" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O104" s="23" t="inlineStr">
@@ -19266,7 +19280,7 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
@@ -19284,24 +19298,30 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G105" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
+      <c r="G105" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H105" s="21" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I105" s="21" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J105" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K105" s="21" t="n"/>
       <c r="L105" s="21" t="n"/>
       <c r="M105" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
         </is>
       </c>
       <c r="N105" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O105" s="23" t="inlineStr">
@@ -19323,7 +19343,7 @@
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
@@ -19353,12 +19373,12 @@
       <c r="L106" s="21" t="n"/>
       <c r="M106" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N106" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O106" s="23" t="inlineStr">
@@ -19375,12 +19395,12 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D107" s="21" t="inlineStr">
@@ -19390,12 +19410,12 @@
       </c>
       <c r="E107" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F107" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G107" s="21" t="inlineStr">
@@ -19410,12 +19430,12 @@
       <c r="L107" s="21" t="n"/>
       <c r="M107" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N107" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O107" s="23" t="inlineStr">
@@ -19437,7 +19457,7 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
@@ -19447,12 +19467,12 @@
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
@@ -19467,12 +19487,12 @@
       <c r="L108" s="21" t="n"/>
       <c r="M108" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N108" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O108" s="23" t="inlineStr">
@@ -19494,7 +19514,7 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
@@ -19504,12 +19524,12 @@
       </c>
       <c r="E109" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G109" s="21" t="inlineStr">
@@ -19524,12 +19544,12 @@
       <c r="L109" s="21" t="n"/>
       <c r="M109" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N109" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O109" s="23" t="inlineStr">
@@ -19551,7 +19571,7 @@
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
@@ -19561,12 +19581,12 @@
       </c>
       <c r="E110" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F110" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G110" s="21" t="inlineStr">
@@ -19581,12 +19601,12 @@
       <c r="L110" s="21" t="n"/>
       <c r="M110" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N110" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O110" s="23" t="inlineStr">
@@ -19603,17 +19623,17 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E111" s="21" t="inlineStr">
@@ -19631,254 +19651,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="21" t="n"/>
+      <c r="H111" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I111" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J111" s="21" t="n"/>
       <c r="K111" s="21" t="n"/>
       <c r="L111" s="21" t="n"/>
       <c r="M111" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N111" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O111" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B112" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C112" s="21" t="inlineStr">
-        <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E112" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G112" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H112" s="21" t="n"/>
-      <c r="I112" s="21" t="n"/>
-      <c r="J112" s="21" t="n"/>
-      <c r="K112" s="21" t="n"/>
-      <c r="L112" s="21" t="n"/>
-      <c r="M112" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="N112" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O112" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B113" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C113" s="21" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D113" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E113" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F113" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G113" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
-      <c r="K113" s="21" t="n"/>
-      <c r="L113" s="21" t="n"/>
-      <c r="M113" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N113" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O113" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B114" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C114" s="21" t="inlineStr">
-        <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
-        </is>
-      </c>
-      <c r="D114" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E114" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F114" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G114" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H114" s="21" t="n"/>
-      <c r="I114" s="21" t="n"/>
-      <c r="J114" s="21" t="n"/>
-      <c r="K114" s="21" t="n"/>
-      <c r="L114" s="21" t="n"/>
-      <c r="M114" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
-        </is>
-      </c>
-      <c r="N114" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O114" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B115" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C115" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D115" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E115" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F115" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G115" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H115" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I115" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J115" s="21" t="n"/>
-      <c r="K115" s="21" t="n"/>
-      <c r="L115" s="21" t="n"/>
-      <c r="M115" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N115" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O115" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20035,7 +19827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -21539,17 +21331,17 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -21569,12 +21361,12 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -21596,7 +21388,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -21614,84 +21406,37 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
+      <c r="G25" s="12" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
-        </is>
-      </c>
-      <c r="N26" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22698,7 +22443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27906,22 +27651,22 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>CSAD (Component Segmentation AD)</t>
+          <t>April-GAN (CLIP-AD)</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Yu-Hsuan Hsieh, Shang-Hong Lai (National Tsing Hua University)</t>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>BMVC 2024 / arXiv 2408.15628</t>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -27936,17 +27681,17 @@
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MVTec LOCO 為主：I-AUROC 95.3 (logical 96.7 / structural 94.0)；latency 8.9ms / 321.</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2408.15628</t>
+          <t>https://arxiv.org/abs/2305.17382</t>
         </is>
       </c>
       <c r="O72" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/Tokichan/CSAD</t>
+          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
         </is>
       </c>
     </row>
@@ -27963,17 +27708,17 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>April-GAN (CLIP-AD)</t>
+          <t>SAA+ (Segment Any Anomaly)</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+          <t>IEEE TCYB 2025 / arXiv 2023</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -27993,17 +27738,17 @@
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.17382</t>
+          <t>https://arxiv.org/abs/2305.10724</t>
         </is>
       </c>
       <c r="O73" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
+          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
         </is>
       </c>
     </row>
@@ -28020,47 +27765,57 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SAA+ (Segment Any Anomaly)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>IEEE TCYB 2025 / arXiv 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="n"/>
-      <c r="I74" s="12" t="n"/>
-      <c r="J74" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K74" s="12" t="n"/>
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.10724</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28077,42 +27832,50 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SuperAD (Training-free DINOv2)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n"/>
-      <c r="I75" s="12" t="n"/>
-      <c r="J75" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.19750</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
@@ -28134,17 +27897,17 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -28152,24 +27915,28 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n"/>
-      <c r="I76" s="12" t="n"/>
-      <c r="J76" s="12" t="n"/>
+      <c r="G76" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>94.40000000000001</v>
+      </c>
       <c r="K76" s="12" t="n"/>
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
@@ -28191,7 +27958,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -28221,12 +27988,12 @@
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
@@ -28248,7 +28015,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -28266,24 +28033,30 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n"/>
-      <c r="I78" s="12" t="n"/>
-      <c r="J78" s="12" t="n"/>
+      <c r="G78" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K78" s="12" t="n"/>
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -28305,7 +28078,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -28335,12 +28108,12 @@
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Exploring Intrinsic Normal Prototypes within a Sing</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O79" s="14" t="inlineStr">
@@ -28362,7 +28135,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -28372,12 +28145,12 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -28392,12 +28165,12 @@
       <c r="L80" s="12" t="n"/>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O80" s="14" t="inlineStr">
@@ -28414,27 +28187,27 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -28442,254 +28215,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n"/>
+      <c r="H81" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n"/>
+      <c r="K81" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L81" s="12" t="n"/>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Training-free Anomaly Detection with Vision</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N81" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O81" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n"/>
-      <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="12" t="n"/>
-      <c r="M82" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
-        </is>
-      </c>
-      <c r="N82" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O82" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>TailedCore</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="n"/>
-      <c r="I83" s="12" t="n"/>
-      <c r="J83" s="12" t="n"/>
-      <c r="K83" s="12" t="n"/>
-      <c r="L83" s="12" t="n"/>
-      <c r="M83" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
-        </is>
-      </c>
-      <c r="N83" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O83" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G84" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H84" s="12" t="n"/>
-      <c r="I84" s="12" t="n"/>
-      <c r="J84" s="12" t="n"/>
-      <c r="K84" s="12" t="n"/>
-      <c r="L84" s="12" t="n"/>
-      <c r="M84" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N84" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O84" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I85" s="12" t="n"/>
-      <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L85" s="12" t="n"/>
-      <c r="M85" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N85" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O85" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -30326,19 +29871,29 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="G24" s="12" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
@@ -30383,19 +29938,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
+      <c r="G25" s="12" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
@@ -31968,19 +31531,23 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
+      <c r="G22" s="21" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>78</v>
+      </c>
       <c r="K22" s="21" t="n"/>
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：多尺度原型殘差 + 多尺度自注意力；利用合成異常監督 [基於資料擴增]</t>
+          <t>✅ 已驗證 (PRN CVPR2023 Table 8)：Prototypical Residual Network；BTAD I=94.7 P=97.1 [監督式]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -32450,19 +32017,29 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
+      <c r="G30" s="21" t="n">
+        <v>89</v>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K30" s="21" t="n"/>
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -32507,19 +32084,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
+      <c r="G31" s="21" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K31" s="21" t="n"/>
       <c r="L31" s="21" t="n"/>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -32621,19 +32206,25 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
+      <c r="G33" s="21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K33" s="21" t="n"/>
       <c r="L33" s="21" t="n"/>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bayesian Prompt Flow Learning for Zero-Shot Anomaly</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
@@ -32693,7 +32284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34134,17 +33725,17 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ISVL (VAND 2025 第一名)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -34152,24 +33743,32 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
+      <c r="G23" s="12" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO </t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.17615</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -34191,7 +33790,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -34221,129 +33820,15 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Zero-Shot Anomaly Detection and Reasoning w</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Beyond Single-Modal Boundary: Cross-Modal Anomaly D</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N26" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -11803,7 +11803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -13396,19 +13396,15 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
+      <c r="G23" s="21" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>98.3</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -13428,7 +13424,7 @@
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>階層式向量量化 + Conditional NF；多類異常 SOTA 99.5%/98.3% [基於 NF]</t>
+          <t>✅ 已驗證 (VQ-Flow Table I multi-class avg, ConvNeXt)：Hierarchical Vector Quantization Flow；99.5/98.3 @ 33 FPS [基於 NF]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -18341,27 +18337,27 @@
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>CFM (Crossmodal Feature Mapping)</t>
+          <t>VT-ADL</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>Alex Costanzino, Pierluigi Zama Ramirez, Giuseppe Lisanti, Luigi Di Stefano</t>
+          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2024 / arXiv 2312.04521</t>
+          <t>ISIE 2021 / arXiv 2104.10036</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="G89" s="21" t="inlineStr">
@@ -18376,17 +18372,17 @@
       <c r="L89" s="21" t="n"/>
       <c r="M89" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RGB-3D 跨模態特徵映射；以 RGB→3D 與 3D→RGB 雙向蒸餾學異常；MVTec 3D-AD SOTA I=98.5 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
         </is>
       </c>
       <c r="N89" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.04521</t>
+          <t>https://arxiv.org/abs/2104.10036</t>
         </is>
       </c>
       <c r="O89" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/CVLAB-Unibo/crossmodal-feature-mapping</t>
+          <t>https://github.com/pankajmishra000/VT-ADL</t>
         </is>
       </c>
     </row>
@@ -18398,52 +18394,60 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>M3DM-NR (Noisy-Resistant)</t>
+          <t>AST (Asymmetric Student-Teacher)</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>Chengjie Wang, Haokun Zhu, Jinlong Peng, Yue Wang, Ran Yi, Yunsheng Wu, Lizhuang Ma, Jiangning Zhang</t>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024 / 2406.02263</t>
+          <t>WACV 2023</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="G90" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="G90" s="21" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H90" s="21" t="n">
+        <v>95</v>
+      </c>
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K90" s="21" t="n"/>
       <c r="L90" s="21" t="n"/>
       <c r="M90" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：M3DM 雜訊穩健版：以多模態去雜訊處理 noisy 訓練集 [基於表徵]</t>
+          <t>✅ 已驗證 (AST WACV23 Table 2+4)：Asymmetric Student-Teacher (RGB+3D NF teacher)；MVTec AD I=99.2 P=95.0 [Student-Teacher]</t>
         </is>
       </c>
       <c r="N90" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2406.02263</t>
+          <t>https://arxiv.org/abs/2210.07829</t>
         </is>
       </c>
       <c r="O90" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/marco-rudolph/AST</t>
         </is>
       </c>
     </row>
@@ -18460,22 +18464,22 @@
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>M3DM (Multimodal Hybrid Fusion)</t>
+          <t>PSAD (Few-Shot Part Segmentation)</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Yue Wang, Jinlong Peng, Jiangning Zhang, Ran Yi, Yabiao Wang, Chengjie Wang</t>
+          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 / arXiv 2303.00601</t>
+          <t>AAAI 2024 / arXiv 2312.13783</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
@@ -18490,17 +18494,17 @@
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-modal Memory Bank + 點雲對齊 + Patch-wise 對比學習；RGB-3D 異常檢測 [基於表徵]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.00601</t>
+          <t>https://arxiv.org/abs/2312.13783</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/nomewang/M3DM</t>
+          <t>https://github.com/kaist-cvml-lab/PSAD</t>
         </is>
       </c>
     </row>
@@ -18512,27 +18516,27 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>VT-ADL</t>
+          <t>LogicQA (VLM Logical AD)</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
+          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>ISIE 2021 / arXiv 2104.10036</t>
+          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -18547,17 +18551,17 @@
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2104.10036</t>
+          <t>https://arxiv.org/abs/2503.20252</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/pankajmishra000/VT-ADL</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18574,22 +18578,22 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>AST (Asymmetric Student-Teacher)</t>
+          <t>SINBAD (Set Features)</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>WACV 2023</t>
+          <t>ICML 2024 / arXiv 2311.14773</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -18604,17 +18608,17 @@
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：非對稱 S-T (NF teacher + FFN student)；MVTec 3D-AD RGB-only 設定 SOTA [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2210.07829</t>
+          <t>https://arxiv.org/abs/2311.14773</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/marco-rudolph/AST</t>
+          <t>https://github.com/NivC/SINBAD</t>
         </is>
       </c>
     </row>
@@ -18626,27 +18630,27 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>EasyNet</t>
+          <t>BTF (Back to the Feature)</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>Ruitao Chen, Guoyang Xie, Jiaqi Liu, Jinbao Wang, Ziqi Luo, Jinfan Wang, Feng Zheng</t>
+          <t>Eliahu Horwitz, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>ACM MM 2023 / arXiv 2307.13925</t>
+          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
@@ -18661,17 +18665,17 @@
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：輕量易部署網路：無需 pretrained / memory bank；多模態異常分割；快速推論 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2307.13925</t>
+          <t>https://arxiv.org/abs/2203.05550</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/sukanyapatra1997/ULSAD-2024</t>
+          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
         </is>
       </c>
     </row>
@@ -18688,22 +18692,22 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>PSAD (Few-Shot Part Segmentation)</t>
+          <t>RoBiS (VAND 2025 第二名)</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
+          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>AAAI 2024 / arXiv 2312.13783</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
@@ -18718,17 +18722,17 @@
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.13783</t>
+          <t>https://arxiv.org/abs/2505.21152</t>
         </is>
       </c>
       <c r="O95" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/kaist-cvml-lab/PSAD</t>
+          <t>https://github.com/xrli-U/RoBiS</t>
         </is>
       </c>
     </row>
@@ -18745,22 +18749,22 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>LogicQA (VLM Logical AD)</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
@@ -18775,12 +18779,12 @@
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.20252</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O96" s="23" t="inlineStr">
@@ -18797,52 +18801,62 @@
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>SINBAD (Set Features)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>ICML 2024 / arXiv 2311.14773</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="G97" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H97" s="21" t="n"/>
-      <c r="I97" s="21" t="n"/>
-      <c r="J97" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="n">
+        <v>94</v>
+      </c>
+      <c r="H97" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J97" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K97" s="21" t="n"/>
       <c r="L97" s="21" t="n"/>
       <c r="M97" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
         </is>
       </c>
       <c r="N97" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.14773</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O97" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/NivC/SINBAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18859,47 +18873,55 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>BTF (Back to the Feature)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>Eliahu Horwitz, Yedid Hoshen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="G98" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-      <c r="J98" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G98" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H98" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J98" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K98" s="21" t="n"/>
       <c r="L98" s="21" t="n"/>
       <c r="M98" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N98" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.05550</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O98" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18916,47 +18938,51 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>RoBiS (VAND 2025 第二名)</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="G99" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H99" s="21" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I99" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="J99" s="21" t="n">
+        <v>94.90000000000001</v>
+      </c>
       <c r="K99" s="21" t="n"/>
       <c r="L99" s="21" t="n"/>
       <c r="M99" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
         </is>
       </c>
       <c r="N99" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.21152</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O99" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/RoBiS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18999,7 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -18991,24 +19017,30 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G100" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
+      <c r="G100" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H100" s="21" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I100" s="21" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J100" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K100" s="21" t="n"/>
       <c r="L100" s="21" t="n"/>
       <c r="M100" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
         </is>
       </c>
       <c r="N100" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O100" s="23" t="inlineStr">
@@ -19030,7 +19062,7 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
@@ -19048,34 +19080,24 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G101" s="21" t="n">
-        <v>94</v>
-      </c>
-      <c r="H101" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I101" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J101" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
       <c r="K101" s="21" t="n"/>
       <c r="L101" s="21" t="n"/>
       <c r="M101" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N101" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O101" s="23" t="inlineStr">
@@ -19092,12 +19114,12 @@
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -19107,40 +19129,32 @@
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G102" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="H102" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I102" s="21" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="J102" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G102" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="21" t="n"/>
       <c r="K102" s="21" t="n"/>
       <c r="L102" s="21" t="n"/>
       <c r="M102" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N102" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O102" s="23" t="inlineStr">
@@ -19162,7 +19176,7 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -19172,36 +19186,32 @@
       </c>
       <c r="E103" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G103" s="21" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="H103" s="21" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="I103" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="J103" s="21" t="n">
-        <v>94.90000000000001</v>
-      </c>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H103" s="21" t="n"/>
+      <c r="I103" s="21" t="n"/>
+      <c r="J103" s="21" t="n"/>
       <c r="K103" s="21" t="n"/>
       <c r="L103" s="21" t="n"/>
       <c r="M103" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N103" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O103" s="23" t="inlineStr">
@@ -19223,7 +19233,7 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -19233,12 +19243,12 @@
       </c>
       <c r="E104" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F104" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G104" s="21" t="inlineStr">
@@ -19253,12 +19263,12 @@
       <c r="L104" s="21" t="n"/>
       <c r="M104" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N104" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O104" s="23" t="inlineStr">
@@ -19280,7 +19290,7 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
@@ -19290,38 +19300,32 @@
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G105" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="H105" s="21" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I105" s="21" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J105" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="21" t="n"/>
       <c r="K105" s="21" t="n"/>
       <c r="L105" s="21" t="n"/>
       <c r="M105" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N105" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O105" s="23" t="inlineStr">
@@ -19338,27 +19342,27 @@
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
@@ -19366,311 +19370,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H106" s="21" t="n"/>
-      <c r="I106" s="21" t="n"/>
+      <c r="H106" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I106" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J106" s="21" t="n"/>
       <c r="K106" s="21" t="n"/>
       <c r="L106" s="21" t="n"/>
       <c r="M106" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N106" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O106" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B107" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
-        </is>
-      </c>
-      <c r="D107" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="21" t="n"/>
-      <c r="J107" s="21" t="n"/>
-      <c r="K107" s="21" t="n"/>
-      <c r="L107" s="21" t="n"/>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
-        </is>
-      </c>
-      <c r="N107" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O107" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B108" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C108" s="21" t="inlineStr">
-        <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
-        </is>
-      </c>
-      <c r="D108" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E108" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G108" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-      <c r="J108" s="21" t="n"/>
-      <c r="K108" s="21" t="n"/>
-      <c r="L108" s="21" t="n"/>
-      <c r="M108" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="N108" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O108" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B109" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C109" s="21" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E109" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G109" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H109" s="21" t="n"/>
-      <c r="I109" s="21" t="n"/>
-      <c r="J109" s="21" t="n"/>
-      <c r="K109" s="21" t="n"/>
-      <c r="L109" s="21" t="n"/>
-      <c r="M109" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N109" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O109" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B110" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C110" s="21" t="inlineStr">
-        <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
-        </is>
-      </c>
-      <c r="D110" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E110" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F110" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G110" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H110" s="21" t="n"/>
-      <c r="I110" s="21" t="n"/>
-      <c r="J110" s="21" t="n"/>
-      <c r="K110" s="21" t="n"/>
-      <c r="L110" s="21" t="n"/>
-      <c r="M110" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
-        </is>
-      </c>
-      <c r="N110" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O110" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B111" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C111" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D111" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E111" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F111" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G111" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H111" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I111" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J111" s="21" t="n"/>
-      <c r="K111" s="21" t="n"/>
-      <c r="L111" s="21" t="n"/>
-      <c r="M111" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N111" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O111" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19827,7 +19546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -20999,19 +20718,29 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="G18" s="12" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+          <t>✅ 已驗證 (ReContrast NeurIPS23 Table A7)：Mean I-AUROC=82.1 (struct 90.7 + logic 73.4)；非專為 LOCO 設計但優於多 baseline [Student-Teacher 對比]</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -21331,7 +21060,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -21349,94 +21078,37 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="G24" s="12" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22443,7 +22115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27555,19 +27227,27 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n"/>
-      <c r="I70" s="12" t="n"/>
-      <c r="J70" s="12" t="n"/>
+      <c r="G70" s="12" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K70" s="12" t="n"/>
       <c r="L70" s="12" t="n"/>
       <c r="M70" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：階層式向量量化 + Conditional NF；多類異常 SOTA 99.5%/98.3% [基於 NF]</t>
+          <t>✅ 已驗證 (VQ-Flow Table IV multi-class)：VisA I=95.9 P=98.9 [基於 NF]</t>
         </is>
       </c>
       <c r="N70" s="14" t="inlineStr">
@@ -27958,7 +27638,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -27976,24 +27656,30 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="n"/>
-      <c r="I77" s="12" t="n"/>
-      <c r="J77" s="12" t="n"/>
+      <c r="G77" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K77" s="12" t="n"/>
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
@@ -28015,7 +27701,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -28033,30 +27719,24 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G78" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="J78" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
       <c r="K78" s="12" t="n"/>
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -28078,7 +27758,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -28088,12 +27768,12 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -28108,12 +27788,12 @@
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O79" s="14" t="inlineStr">
@@ -28130,17 +27810,17 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -28158,83 +27838,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H80" s="12" t="n"/>
+      <c r="H80" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
+      <c r="K80" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L80" s="12" t="n"/>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O80" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I81" s="12" t="n"/>
-      <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L81" s="12" t="n"/>
-      <c r="M81" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N81" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -28355,7 +27978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29967,63 +29590,6 @@
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N26" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -30065,7 +29631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32131,7 +31697,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -32149,90 +31715,33 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
+      <c r="G32" s="21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K32" s="21" t="n"/>
       <c r="L32" s="21" t="n"/>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O32" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="H33" s="21" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I33" s="21" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N33" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O33" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -32284,7 +31793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -33772,63 +33281,6 @@
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Towards Visual Discrimination and Reasoning of Real-World Ph</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards Visual Discrimination and Reasoning of Real</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_Visual_Discrimination_and_Reasoning_of_Real-World_Physical_Dynamics_Physics-Grounded_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -19546,7 +19546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -20876,27 +20876,27 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>TFA-Net (Template-based Feature Aggregation)</t>
+          <t>Triad (LMM-Aided AD)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2603.22874)</t>
+          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -20911,17 +20911,17 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：模板特徵聚合網路；以多模板做特徵級重構，I-AUROC 98.7%、P-AUROC 98.3% [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2603.22874</t>
+          <t>https://arxiv.org/abs/2503.13184</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/tzjtatata/Triad</t>
         </is>
       </c>
     </row>
@@ -20938,47 +20938,55 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Triad (LMM-Aided AD)</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13184</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tzjtatata/Triad</t>
+          <t>https://github.com/FuNz-0/PromptAD</t>
         </is>
       </c>
     </row>
@@ -20995,29 +21003,31 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>PromptAD</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>74.5</v>
+        <v>90.2</v>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
@@ -21033,82 +21043,15 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
+          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -27349,19 +27292,25 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="n"/>
-      <c r="I72" s="12" t="n"/>
-      <c r="J72" s="12" t="n"/>
+      <c r="G72" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>86.8</v>
+      </c>
       <c r="K72" s="12" t="n"/>
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
+          <t>✅ 已驗證 (April-GAN VAND2023 Table 4 zero-shot)：CLIP-AD with linear projection adapters；VAND 2023 Challenge zero-shot 第一名 [基於 VLM]</t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
@@ -29069,19 +29018,27 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="G17" s="12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Global+Local 自適應擴散；每樣本預測去噪步驟、空間自適應特徵融合 [基於擴散]</t>
+          <t>✅ 已驗證 (GLAD ECCV24 Table 2 average)：Global-Local Anomaly Detection；LDM + DINO fine-tuned；MPDD I=97.5 P=98.7 [基於擴散]</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -11589,6 +11589,1659 @@
         </is>
       </c>
       <c r="O143" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>PO3AD</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="n"/>
+      <c r="I144" s="18" t="n"/>
+      <c r="J144" s="18" t="n"/>
+      <c r="K144" s="18" t="n"/>
+      <c r="L144" s="18" t="n"/>
+      <c r="M144" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PO3AD: Predicting Point Offsets toward Better 3D Point Cloud Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N144" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Ye_PO3AD_Predicting_Point_Offsets_toward_Better_3D_Point_Cloud_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O144" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>Correcting Deviations from Normality</t>
+        </is>
+      </c>
+      <c r="D145" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="n"/>
+      <c r="I145" s="18" t="n"/>
+      <c r="J145" s="18" t="n"/>
+      <c r="K145" s="18" t="n"/>
+      <c r="L145" s="18" t="n"/>
+      <c r="M145" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Correcting Deviations from Normality: A Reformulated Diffusion Model for Multi-Class Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N145" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O145" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>A Unified Latent Schrodinger Bridge Diffusion Model for Unsu</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="n"/>
+      <c r="I146" s="18" t="n"/>
+      <c r="J146" s="18" t="n"/>
+      <c r="K146" s="18" t="n"/>
+      <c r="L146" s="18" t="n"/>
+      <c r="M146" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Unified Latent Schrodinger Bridge Diffusion Model for Unsupervised Anomaly Detection and Localization</t>
+        </is>
+      </c>
+      <c r="N146" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O146" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anomaly Detection of Integrated Circuits Package Substrates </t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="n"/>
+      <c r="I147" s="18" t="n"/>
+      <c r="J147" s="18" t="n"/>
+      <c r="K147" s="18" t="n"/>
+      <c r="L147" s="18" t="n"/>
+      <c r="M147" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Anomaly Detection of Integrated Circuits Package Substrates Using the Large Vision Model SAIC: Dataset Construction, Methodology, and Application</t>
+        </is>
+      </c>
+      <c r="N147" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yu_Anomaly_Detection_of_Integrated_Circuits_Package_Substrates_Using_the_Large_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O147" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>Toward Long-Tailed Online Anomaly Detection through Class-Ag</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="n"/>
+      <c r="I148" s="18" t="n"/>
+      <c r="J148" s="18" t="n"/>
+      <c r="K148" s="18" t="n"/>
+      <c r="L148" s="18" t="n"/>
+      <c r="M148" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Toward Long-Tailed Online Anomaly Detection through Class-Agnostic Concepts</t>
+        </is>
+      </c>
+      <c r="N148" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_Toward_Long-Tailed_Online_Anomaly_Detection_through_Class-Agnostic_Concepts_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O148" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>G2SF</t>
+        </is>
+      </c>
+      <c r="D149" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="n"/>
+      <c r="I149" s="18" t="n"/>
+      <c r="J149" s="18" t="n"/>
+      <c r="K149" s="18" t="n"/>
+      <c r="L149" s="18" t="n"/>
+      <c r="M149" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。G2SF: Geometry-Guided Score Fusion for Multimodal Industrial Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N149" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Tao_G2SF_Geometry-Guided_Score_Fusion_for_Multimodal_Industrial_Anomaly_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O149" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>ReMP-AD</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="n"/>
+      <c r="I150" s="18" t="n"/>
+      <c r="J150" s="18" t="n"/>
+      <c r="K150" s="18" t="n"/>
+      <c r="L150" s="18" t="n"/>
+      <c r="M150" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ReMP-AD: Retrieval-enhanced Multi-modal Prompt Fusion for Few-Shot Industrial Visual Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N150" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Ma_ReMP-AD_Retrieval-enhanced_Multi-modal_Prompt_Fusion_for_Few-Shot_Industrial_Visual_Anomaly_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O150" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>SiM3D</t>
+        </is>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="n"/>
+      <c r="I151" s="18" t="n"/>
+      <c r="J151" s="18" t="n"/>
+      <c r="K151" s="18" t="n"/>
+      <c r="L151" s="18" t="n"/>
+      <c r="M151" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SiM3D: Single-instance Multiview Multimodal and Multisetup 3D Anomaly Detection Benchmark</t>
+        </is>
+      </c>
+      <c r="N151" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Costanzino_SiM3D_Single-instance_Multiview_Multimodal_and_Multisetup_3D_Anomaly_Detection_Benchmark_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O151" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>DecAD</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="n"/>
+      <c r="I152" s="18" t="n"/>
+      <c r="J152" s="18" t="n"/>
+      <c r="K152" s="18" t="n"/>
+      <c r="L152" s="18" t="n"/>
+      <c r="M152" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DecAD: Decoupling Anomalies in Latent Space for Multi-Class Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N152" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DecAD_Decoupling_Anomalies_in_Latent_Space_for_Multi-Class_Unsupervised_Anomaly_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O152" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>Kaputt</t>
+        </is>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="n"/>
+      <c r="I153" s="18" t="n"/>
+      <c r="J153" s="18" t="n"/>
+      <c r="K153" s="18" t="n"/>
+      <c r="L153" s="18" t="n"/>
+      <c r="M153" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Kaputt: A Large-Scale Dataset for Visual Defect Detection</t>
+        </is>
+      </c>
+      <c r="N153" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Hofer_Kaputt_A_Large-Scale_Dataset_for_Visual_Defect_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O153" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>Wave-MambaAD</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="n"/>
+      <c r="I154" s="18" t="n"/>
+      <c r="J154" s="18" t="n"/>
+      <c r="K154" s="18" t="n"/>
+      <c r="L154" s="18" t="n"/>
+      <c r="M154" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Wave-MambaAD: Wavelet-driven State Space Model for Multi-class Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N154" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhang_Wave-MambaAD_Wavelet-driven_State_Space_Model_for_Multi-class_Unsupervised_Anomaly_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O154" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="inlineStr">
+        <is>
+          <t>FE-CLIP</t>
+        </is>
+      </c>
+      <c r="D155" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="n"/>
+      <c r="I155" s="18" t="n"/>
+      <c r="J155" s="18" t="n"/>
+      <c r="K155" s="18" t="n"/>
+      <c r="L155" s="18" t="n"/>
+      <c r="M155" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FE-CLIP: Frequency Enhanced CLIP Model for Zero-Shot Anomaly Detection and Segmentation</t>
+        </is>
+      </c>
+      <c r="N155" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Gong_FE-CLIP_Frequency_Enhanced_CLIP_Model_for_Zero-Shot_Anomaly_Detection_and_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O155" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>DADet</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="n"/>
+      <c r="I156" s="18" t="n"/>
+      <c r="J156" s="18" t="n"/>
+      <c r="K156" s="18" t="n"/>
+      <c r="L156" s="18" t="n"/>
+      <c r="M156" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DADet: Safeguarding Image Conditional Diffusion Models against Adversarial and Backdoor Attacks via Diffusion Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N156" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yu_DADet_Safeguarding_Image_Conditional_Diffusion_Models_against_Adversarial_and_Backdoor_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O156" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>Salvaging the Overlooked</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="n"/>
+      <c r="I157" s="18" t="n"/>
+      <c r="J157" s="18" t="n"/>
+      <c r="K157" s="18" t="n"/>
+      <c r="L157" s="18" t="n"/>
+      <c r="M157" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Salvaging the Overlooked: Leveraging Class-Aware Contrastive Learning for Multi-Class Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N157" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Fan_Salvaging_the_Overlooked_Leveraging_Class-Aware_Contrastive_Learning_for_Multi-Class_Anomaly_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O157" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>DictAS</t>
+        </is>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="n"/>
+      <c r="I158" s="18" t="n"/>
+      <c r="J158" s="18" t="n"/>
+      <c r="K158" s="18" t="n"/>
+      <c r="L158" s="18" t="n"/>
+      <c r="M158" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DictAS: A Framework for Class-Generalizable Few-Shot Anomaly Segmentation via Dictionary Lookup</t>
+        </is>
+      </c>
+      <c r="N158" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Qu_DictAS_A_Framework_for_Class-Generalizable_Few-Shot_Anomaly_Segmentation_via_Dictionary_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O158" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>Towards Real Unsupervised Anomaly Detection Via Confident Me</t>
+        </is>
+      </c>
+      <c r="D159" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="n"/>
+      <c r="I159" s="18" t="n"/>
+      <c r="J159" s="18" t="n"/>
+      <c r="K159" s="18" t="n"/>
+      <c r="L159" s="18" t="n"/>
+      <c r="M159" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Real Unsupervised Anomaly Detection Via Confident Meta-Learning</t>
+        </is>
+      </c>
+      <c r="N159" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Aqeel_Towards_Real_Unsupervised_Anomaly_Detection_Via_Confident_Meta-Learning_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O159" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>Fine-grained Abnormality Prompt Learning for Zero-shot Anoma</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="n"/>
+      <c r="I160" s="18" t="n"/>
+      <c r="J160" s="18" t="n"/>
+      <c r="K160" s="18" t="n"/>
+      <c r="L160" s="18" t="n"/>
+      <c r="M160" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Fine-grained Abnormality Prompt Learning for Zero-shot Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N160" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhu_Fine-grained_Abnormality_Prompt_Learning_for_Zero-shot_Anomaly_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O160" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>SeaS</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="n"/>
+      <c r="I161" s="18" t="n"/>
+      <c r="J161" s="18" t="n"/>
+      <c r="K161" s="18" t="n"/>
+      <c r="L161" s="18" t="n"/>
+      <c r="M161" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SeaS: Few-shot Industrial Anomaly Image Generation with Separation and Sharing Fine-tuning</t>
+        </is>
+      </c>
+      <c r="N161" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Dai_SeaS_Few-shot_Industrial_Anomaly_Image_Generation_with_Separation_and_Sharing_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O161" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>Debiasing Trace Guidance</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="n"/>
+      <c r="I162" s="18" t="n"/>
+      <c r="J162" s="18" t="n"/>
+      <c r="K162" s="18" t="n"/>
+      <c r="L162" s="18" t="n"/>
+      <c r="M162" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Debiasing Trace Guidance: Top-down Trace Distillation and Bottom-up Velocity Alignment for Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N162" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_Debiasing_Trace_Guidance_Top-down_Trace_Distillation_and_Bottom-up_Velocity_Alignment_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O162" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>Normal and Abnormal Pathology Knowledge-Augmented Vision-Lan</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H163" s="18" t="n"/>
+      <c r="I163" s="18" t="n"/>
+      <c r="J163" s="18" t="n"/>
+      <c r="K163" s="18" t="n"/>
+      <c r="L163" s="18" t="n"/>
+      <c r="M163" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Normal and Abnormal Pathology Knowledge-Augmented Vision-Language Model for Anomaly Detection in Pathology Images</t>
+        </is>
+      </c>
+      <c r="N163" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Song_Normal_and_Abnormal_Pathology_Knowledge-Augmented_Vision-Language_Model_for_Anomaly_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O163" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>SALAD -- Semantics-Aware Logical Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H164" s="18" t="n"/>
+      <c r="I164" s="18" t="n"/>
+      <c r="J164" s="18" t="n"/>
+      <c r="K164" s="18" t="n"/>
+      <c r="L164" s="18" t="n"/>
+      <c r="M164" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SALAD -- Semantics-Aware Logical Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N164" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Fucka_SALAD_--_Semantics-Aware_Logical_Anomaly_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O164" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>Towards Accurate Unified Anomaly Segmentation</t>
+        </is>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H165" s="18" t="n"/>
+      <c r="I165" s="18" t="n"/>
+      <c r="J165" s="18" t="n"/>
+      <c r="K165" s="18" t="n"/>
+      <c r="L165" s="18" t="n"/>
+      <c r="M165" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Accurate Unified Anomaly Segmentation</t>
+        </is>
+      </c>
+      <c r="N165" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O165" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t>ObjectCore - Efficient Few-shot Logical Anomaly Detection us</t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="n"/>
+      <c r="I166" s="18" t="n"/>
+      <c r="J166" s="18" t="n"/>
+      <c r="K166" s="18" t="n"/>
+      <c r="L166" s="18" t="n"/>
+      <c r="M166" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ObjectCore - Efficient Few-shot Logical Anomaly Detection using Object Representations</t>
+        </is>
+      </c>
+      <c r="N166" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Fucka_ObjectCore_-_Efficient_Few-shot_Logical_Anomaly_Detection_using_Object_Representations_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O166" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B167" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>Sea-CLIP</t>
+        </is>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="n"/>
+      <c r="I167" s="18" t="n"/>
+      <c r="J167" s="18" t="n"/>
+      <c r="K167" s="18" t="n"/>
+      <c r="L167" s="18" t="n"/>
+      <c r="M167" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Sea-CLIP: Mining Semantic-Aware Representations for Few-Shot Anomaly Detection with CLIP</t>
+        </is>
+      </c>
+      <c r="N167" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Guo_Sea-CLIP_Mining_Semantic-Aware_Representations_for_Few-Shot_Anomaly_Detection_with_CLIP_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O167" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>Enhancing Reverse Distillation with Core Exemplar Learning f</t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H168" s="18" t="n"/>
+      <c r="I168" s="18" t="n"/>
+      <c r="J168" s="18" t="n"/>
+      <c r="K168" s="18" t="n"/>
+      <c r="L168" s="18" t="n"/>
+      <c r="M168" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Reverse Distillation with Core Exemplar Learning for Unified Multi-Class Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N168" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lim_Enhancing_Reverse_Distillation_with_Core_Exemplar_Learning_for_Unified_Multi-Class_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O168" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>A Multi-Agent Diffusion Approach for MRI Anomaly Segmentatio</t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H169" s="18" t="n"/>
+      <c r="I169" s="18" t="n"/>
+      <c r="J169" s="18" t="n"/>
+      <c r="K169" s="18" t="n"/>
+      <c r="L169" s="18" t="n"/>
+      <c r="M169" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Multi-Agent Diffusion Approach for MRI Anomaly Segmentation via Modality-Specific LoRA Specialization</t>
+        </is>
+      </c>
+      <c r="N169" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Al_Ghallabi_A_Multi-Agent_Diffusion_Approach_for_MRI_Anomaly_Segmentation_via_Modality-Specific_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O169" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B170" s="18" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>FlowCLAS</t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="n"/>
+      <c r="I170" s="18" t="n"/>
+      <c r="J170" s="18" t="n"/>
+      <c r="K170" s="18" t="n"/>
+      <c r="L170" s="18" t="n"/>
+      <c r="M170" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FlowCLAS: Enhancing Normalizing Flow-Based Anomaly Segmentation Via Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="N170" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lee_FlowCLAS_Enhancing_Normalizing_Flow-Based_Anomaly_Segmentation_Via_Contrastive_Learning_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O170" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B171" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>VLMDiff</t>
+        </is>
+      </c>
+      <c r="D171" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H171" s="18" t="n"/>
+      <c r="I171" s="18" t="n"/>
+      <c r="J171" s="18" t="n"/>
+      <c r="K171" s="18" t="n"/>
+      <c r="L171" s="18" t="n"/>
+      <c r="M171" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。VLMDiff: Leveraging Vision-Language Models for Multi-Class Anomaly Detection with Diffusion</t>
+        </is>
+      </c>
+      <c r="N171" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Hicsonmez_VLMDiff_Leveraging_Vision-Language_Models_for_Multi-Class_Anomaly_Detection_with_Diffusion_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O171" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>DMS2F-HAD</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="n"/>
+      <c r="I172" s="18" t="n"/>
+      <c r="J172" s="18" t="n"/>
+      <c r="K172" s="18" t="n"/>
+      <c r="L172" s="18" t="n"/>
+      <c r="M172" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DMS2F-HAD: A Dual-branch Mamba-based Spatial-Spectral Fusion Network for Hyperspectral Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N172" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Pant_DMS2F-HAD_A_Dual-branch_Mamba-based_Spatial-Spectral_Fusion_Network_for_Hyperspectral_Anomaly_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O172" s="20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11803,7 +13456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -19394,6 +21047,59 @@
           <t>N/A</t>
         </is>
       </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+      <c r="J107" s="21" t="n"/>
+      <c r="K107" s="21" t="n"/>
+      <c r="L107" s="21" t="n"/>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N107" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.20682</t>
+        </is>
+      </c>
+      <c r="O107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -13456,7 +13456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -20112,27 +20112,27 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>PSAD (Few-Shot Part Segmentation)</t>
+          <t>SINBAD (Set Features)</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Soopil Kim, Sion An, Philip Chikontwe, Myeongkyun Kang, Ehsan Adeli, Kilian M. Pohl, Sang Hyun Park</t>
+          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>AAAI 2024 / arXiv 2312.13783</t>
+          <t>ICML 2024 / arXiv 2311.14773</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
@@ -20147,17 +20147,17 @@
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.13783</t>
+          <t>https://arxiv.org/abs/2311.14773</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/kaist-cvml-lab/PSAD</t>
+          <t>https://github.com/NivC/SINBAD</t>
         </is>
       </c>
     </row>
@@ -20174,22 +20174,22 @@
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>LogicQA (VLM Logical AD)</t>
+          <t>BTF (Back to the Feature)</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Yejin Kwon, Daeun Moon, Youngje Oh, Hyunsoo Yoon</t>
+          <t>Eliahu Horwitz, Yedid Hoshen</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>ACL 2025 Industry Track / arXiv 2503.20252</t>
+          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -20204,17 +20204,17 @@
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.20252</t>
+          <t>https://arxiv.org/abs/2203.05550</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
         </is>
       </c>
     </row>
@@ -20226,27 +20226,27 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>SINBAD (Set Features)</t>
+          <t>RoBiS (VAND 2025 第二名)</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>ICML 2024 / arXiv 2311.14773</t>
+          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -20261,17 +20261,17 @@
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.14773</t>
+          <t>https://arxiv.org/abs/2505.21152</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/NivC/SINBAD</t>
+          <t>https://github.com/xrli-U/RoBiS</t>
         </is>
       </c>
     </row>
@@ -20288,22 +20288,22 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>BTF (Back to the Feature)</t>
+          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>Eliahu Horwitz, Yedid Hoshen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
@@ -20318,17 +20318,17 @@
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.05550</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20345,47 +20345,57 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>RoBiS (VAND 2025 第二名)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="G95" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="n">
+        <v>94</v>
+      </c>
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K95" s="21" t="n"/>
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.21152</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O95" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/RoBiS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20412,7 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
@@ -20420,24 +20430,32 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G96" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
+      <c r="G96" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K96" s="21" t="n"/>
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O96" s="23" t="inlineStr">
@@ -20459,7 +20477,7 @@
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
@@ -20478,33 +20496,27 @@
         </is>
       </c>
       <c r="G97" s="21" t="n">
-        <v>94</v>
-      </c>
-      <c r="H97" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I97" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J97" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>99.7</v>
+      </c>
+      <c r="H97" s="21" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I97" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="J97" s="21" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="K97" s="21" t="n"/>
       <c r="L97" s="21" t="n"/>
       <c r="M97" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
         </is>
       </c>
       <c r="N97" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O97" s="23" t="inlineStr">
@@ -20526,7 +20538,7 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
@@ -20547,13 +20559,11 @@
       <c r="G98" s="21" t="n">
         <v>92.3</v>
       </c>
-      <c r="H98" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H98" s="21" t="n">
+        <v>91.8</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>96.3</v>
+        <v>48.3</v>
       </c>
       <c r="J98" s="21" t="inlineStr">
         <is>
@@ -20564,12 +20574,12 @@
       <c r="L98" s="21" t="n"/>
       <c r="M98" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
         </is>
       </c>
       <c r="N98" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O98" s="23" t="inlineStr">
@@ -20591,7 +20601,7 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
@@ -20609,28 +20619,24 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G99" s="21" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="H99" s="21" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="I99" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="J99" s="21" t="n">
-        <v>94.90000000000001</v>
-      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="21" t="n"/>
       <c r="K99" s="21" t="n"/>
       <c r="L99" s="21" t="n"/>
       <c r="M99" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N99" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O99" s="23" t="inlineStr">
@@ -20647,12 +20653,12 @@
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -20662,38 +20668,32 @@
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G100" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="H100" s="21" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I100" s="21" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J100" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G100" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="21" t="n"/>
+      <c r="J100" s="21" t="n"/>
       <c r="K100" s="21" t="n"/>
       <c r="L100" s="21" t="n"/>
       <c r="M100" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
         </is>
       </c>
       <c r="N100" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O100" s="23" t="inlineStr">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F101" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G101" s="21" t="inlineStr">
@@ -20745,12 +20745,12 @@
       <c r="L101" s="21" t="n"/>
       <c r="M101" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
         </is>
       </c>
       <c r="N101" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O101" s="23" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -20802,12 +20802,12 @@
       <c r="L102" s="21" t="n"/>
       <c r="M102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N102" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O102" s="23" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
+          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -20859,12 +20859,12 @@
       <c r="L103" s="21" t="n"/>
       <c r="M103" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
         </is>
       </c>
       <c r="N103" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O103" s="23" t="inlineStr">
@@ -20881,17 +20881,17 @@
       </c>
       <c r="B104" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E104" s="21" t="inlineStr">
@@ -20909,19 +20909,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
+      <c r="H104" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I104" s="21" t="n">
+        <v>98.36</v>
+      </c>
       <c r="J104" s="21" t="n"/>
       <c r="K104" s="21" t="n"/>
       <c r="L104" s="21" t="n"/>
       <c r="M104" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N104" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O104" s="23" t="inlineStr">
@@ -20943,22 +20947,22 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
+          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
         </is>
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>arXiv preprint</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G105" s="21" t="inlineStr">
@@ -20973,133 +20977,15 @@
       <c r="L105" s="21" t="n"/>
       <c r="M105" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
         </is>
       </c>
       <c r="N105" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O105" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B106" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C106" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D106" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H106" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I106" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J106" s="21" t="n"/>
-      <c r="K106" s="21" t="n"/>
-      <c r="L106" s="21" t="n"/>
-      <c r="M106" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N106" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O106" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B107" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
-        </is>
-      </c>
-      <c r="D107" s="21" t="inlineStr">
-        <is>
-          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
-        </is>
-      </c>
-      <c r="E107" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="21" t="n"/>
-      <c r="J107" s="21" t="n"/>
-      <c r="K107" s="21" t="n"/>
-      <c r="L107" s="21" t="n"/>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
-        </is>
-      </c>
-      <c r="N107" s="23" t="inlineStr">
-        <is>
           <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
-      <c r="O107" s="23" t="n"/>
+      <c r="O105" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21252,7 +21138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22367,19 +22253,29 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="G17" s="12" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：雙學生 (Encoder-Decoder + Encoder-Encoder) + DINOv2 知識蒸餾；Noisy-OR 聯合學習 [基於重構]</t>
+          <t>✅ 已驗證 (Generalist Multi-Class AD arXiv25 Table 1, multi-class)：Dual-Student ensemble；MVTec-LOCO I=86.1 (image-AUROC) [Student-Teacher 雙學生]</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
@@ -22468,27 +22364,27 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>AnomalyXFusion (Multi-modal Diffusion)</t>
+          <t>Triad (LMM-Aided AD)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2404.19444)</t>
+          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -22503,17 +22399,17 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MIF 多模態融合 + DDF 動態擴散；多源 X-embedding 增強合成 [基於擴散]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.19444</t>
+          <t>https://arxiv.org/abs/2503.13184</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/tzjtatata/Triad</t>
         </is>
       </c>
     </row>
@@ -22525,52 +22421,60 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>RD++</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.02216</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+          <t>https://github.com/FuNz-0/PromptAD</t>
         </is>
       </c>
     </row>
@@ -22587,177 +22491,55 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Triad (LMM-Aided AD)</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13184</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/tzjtatata/Triad</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>PromptAD</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2024</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23764,7 +23546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28918,52 +28700,58 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>RD++</t>
+          <t>April-GAN (CLIP-AD)</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="n"/>
-      <c r="I71" s="12" t="n"/>
-      <c r="J71" s="12" t="n"/>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>86.8</v>
+      </c>
       <c r="K71" s="12" t="n"/>
       <c r="L71" s="12" t="n"/>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+          <t>✅ 已驗證 (April-GAN VAND2023 Table 4 zero-shot)：CLIP-AD with linear projection adapters；VAND 2023 Challenge zero-shot 第一名 [基於 VLM]</t>
         </is>
       </c>
       <c r="N71" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.02216</t>
+          <t>https://arxiv.org/abs/2305.17382</t>
         </is>
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
         </is>
       </c>
     </row>
@@ -28980,17 +28768,17 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>April-GAN (CLIP-AD)</t>
+          <t>SAA+ (Segment Any Anomaly)</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+          <t>IEEE TCYB 2025 / arXiv 2023</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -28998,35 +28786,29 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="G72" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>86.8</v>
-      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
       <c r="K72" s="12" t="n"/>
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (April-GAN VAND2023 Table 4 zero-shot)：CLIP-AD with linear projection adapters；VAND 2023 Challenge zero-shot 第一名 [基於 VLM]</t>
+          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.17382</t>
+          <t>https://arxiv.org/abs/2305.10724</t>
         </is>
       </c>
       <c r="O72" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
+          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
         </is>
       </c>
     </row>
@@ -29043,47 +28825,57 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SAA+ (Segment Any Anomaly)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>IEEE TCYB 2025 / arXiv 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n"/>
-      <c r="I73" s="12" t="n"/>
-      <c r="J73" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K73" s="12" t="n"/>
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.10724</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O73" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -29100,7 +28892,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -29119,17 +28911,15 @@
         </is>
       </c>
       <c r="G74" s="12" t="n">
-        <v>91.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I74" s="12" t="n">
+        <v>89.3</v>
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
@@ -29140,12 +28930,12 @@
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
@@ -29167,7 +28957,7 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -29186,31 +28976,27 @@
         </is>
       </c>
       <c r="G75" s="12" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="J75" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>51.2</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
@@ -29232,7 +29018,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -29251,27 +29037,29 @@
         </is>
       </c>
       <c r="G76" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>29.8</v>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K76" s="12" t="n"/>
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
@@ -29293,7 +29081,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>TailedCore</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -29311,30 +29099,24 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G77" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="J77" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
       <c r="K77" s="12" t="n"/>
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
@@ -29356,7 +29138,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -29366,12 +29148,12 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -29386,12 +29168,12 @@
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -29408,17 +29190,17 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -29436,83 +29218,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H79" s="12" t="n"/>
+      <c r="H79" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n"/>
+      <c r="K79" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O79" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I80" s="12" t="n"/>
-      <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L80" s="12" t="n"/>
-      <c r="M80" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N80" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O80" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -31037,19 +30762,25 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="G22" s="12" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>89.7</v>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Bosch Research；多類型 zero-shot AD：依異常類型分支 prompt + 多任務分割 [基於表徵]</t>
+          <t>✅ 已驗證 (MultiADS Table 4, ZSAD)：Multi-type Zero-Shot AD；MPDD I=78.3 P=95.8 PRO=89.7 [基於 VLM 多缺陷類型 prompt]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -31294,7 +31025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32685,47 +32416,51 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>STAGE (Graded Diffusion + Mask Alignment)</t>
+          <t>PRN</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.06693)</t>
+          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>78</v>
+      </c>
       <c r="K21" s="21" t="n"/>
       <c r="L21" s="21" t="n"/>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Segmentation-oriented 工業異常合成；分級擴散 + explicit mask 對齊 [基於資料擴增]</t>
+          <t>✅ 已驗證 (PRN CVPR2023 Table 8)：Prototypical Residual Network；BTAD I=94.7 P=97.1 [監督式]</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.06693</t>
+          <t>https://arxiv.org/abs/2212.02031</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/xiahaifeng1995/PRN</t>
         </is>
       </c>
     </row>
@@ -32737,56 +32472,52 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>PRN</t>
+          <t>AMI-Net</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
+          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>IEEE TASE 2024</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>78</v>
-      </c>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
       <c r="K22" s="21" t="n"/>
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PRN CVPR2023 Table 8)：Prototypical Residual Network；BTAD I=94.7 P=97.1 [監督式]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.02031</t>
+          <t>https://arxiv.org/abs/2412.11802</t>
         </is>
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xiahaifeng1995/PRN</t>
+          <t>https://github.com/luow23/AMI-Net</t>
         </is>
       </c>
     </row>
@@ -32798,27 +32529,27 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>AMI-Net</t>
+          <t>U-Flow</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
+          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>IEEE TASE 2024</t>
+          <t>JMIV 2024 / arXiv 2211.12353</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -32833,17 +32564,17 @@
       <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.11802</t>
+          <t>https://arxiv.org/abs/2211.12353</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/luow23/AMI-Net</t>
+          <t>https://github.com/mtailanian/uflow</t>
         </is>
       </c>
     </row>
@@ -32855,52 +32586,60 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Adversarially Robust Diffusion AD</t>
+          <t>MuSc</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2408.04839)</t>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K24" s="21" t="n"/>
       <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
+          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2408.04839</t>
+          <t>https://arxiv.org/abs/2401.16753</t>
         </is>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/xrli-U/MuSc</t>
         </is>
       </c>
     </row>
@@ -32912,52 +32651,56 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>U-Flow</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>JMIV 2024 / arXiv 2211.12353</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>97</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>80</v>
+      </c>
       <c r="K25" s="21" t="n"/>
       <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
+          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12353</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/mtailanian/uflow</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32974,29 +32717,29 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>MuSc</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G26" s="21" t="n">
         <v>94.8</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
@@ -33012,17 +32755,17 @@
       <c r="L26" s="21" t="n"/>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
+          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.16753</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/MuSc</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -33039,51 +32782,53 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>PatchEAD</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G27" s="21" t="n">
-        <v>91.2</v>
+        <v>88.3</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>97</v>
-      </c>
-      <c r="I27" s="21" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="J27" s="21" t="n">
-        <v>80</v>
+        <v>74.8</v>
       </c>
       <c r="K27" s="21" t="n"/>
       <c r="L27" s="21" t="n"/>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
+          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
         </is>
       </c>
     </row>
@@ -33100,29 +32845,31 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>97</v>
+        <v>89</v>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
         <is>
@@ -33138,17 +32885,17 @@
       <c r="L28" s="21" t="n"/>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -33165,53 +32912,55 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>AnomalyCLIP</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G29" s="21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="H29" s="21" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="n">
-        <v>74.8</v>
+        <v>97.5</v>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K29" s="21" t="n"/>
       <c r="L29" s="21" t="n"/>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -33228,7 +32977,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -33247,17 +32996,13 @@
         </is>
       </c>
       <c r="G30" s="21" t="n">
-        <v>89</v>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>93.2</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>47.1</v>
       </c>
       <c r="J30" s="21" t="inlineStr">
         <is>
@@ -33268,143 +33013,15 @@
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
-        </is>
-      </c>
-      <c r="N31" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O31" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N32" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O32" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -33456,7 +33073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34604,47 +34221,51 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>RD++</t>
+          <t>SNARM (Self-Navigated Residual Mamba)</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+          <t>Anonymous (arXiv 2508.01591)</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>97.40000000000001</v>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+          <t>✅ 已驗證 (SNARM arXiv25 Table 1, multi-class, T=10^5)：Self-Navigated Residual Mamba；I=93.9 P=99.2 AP=63.6 PRO=97.4 [基於 Mamba SSM]</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.02216</t>
+          <t>https://arxiv.org/abs/2508.01591</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -34661,47 +34282,51 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SNARM (Self-Navigated Residual Mamba)</t>
+          <t>InvAD (Feature Inversion)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2508.01591)</t>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>arXiv preprint 2024</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>94.7</v>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-Navigated 殘差 Mamba：以 inter/intra-residual 自參考學習；MVTec AD/3D/VisA SOTA [基於重構</t>
+          <t>✅ 已驗證 (InvAD Appendix Table A2, MUAD)：Feature Inversion 多類別異常偵測；MVTec 3D AD I=86.1, P=98.8 [基於重構]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.01591</t>
+          <t>https://arxiv.org/abs/2404.10760</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/zhangzjn/ADer</t>
         </is>
       </c>
     </row>
@@ -34718,17 +34343,17 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>MambaAD</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>NeurIPS 2024</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -34737,32 +34362,32 @@
         </is>
       </c>
       <c r="G20" s="12" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>94.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (InvAD Appendix Table A2, MUAD)：Feature Inversion 多類別異常偵測；MVTec 3D AD I=86.1, P=98.8 [基於重構]</t>
+          <t>✅ 已驗證 (MambaAD Table A5/A6 multi-class)：Mamba SSM 多類別異常偵測；Hilbert Hybrid Scanning [基於 SSM]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
+          <t>https://arxiv.org/abs/2404.06564</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/zhangzjn/ADer</t>
+          <t>https://github.com/lewandofskee/MambaAD</t>
         </is>
       </c>
     </row>
@@ -34774,56 +34399,52 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>MambaAD</t>
+          <t>DiAD</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
+          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2024</t>
+          <t>AAAI 2024</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>93.59999999999999</v>
-      </c>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MambaAD Table A5/A6 multi-class)：Mamba SSM 多類別異常偵測；Hilbert Hybrid Scanning [基於 SSM]</t>
+          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.06564</t>
+          <t>https://arxiv.org/abs/2312.06607</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/lewandofskee/MambaAD</t>
+          <t>https://github.com/lewandofskee/DiAD</t>
         </is>
       </c>
     </row>
@@ -34835,115 +34456,58 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>DiAD</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>AAAI 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.06607</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/lewandofskee/DiAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>MVTec 3D</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -13456,7 +13456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -19459,79 +19459,79 @@
       </c>
     </row>
     <row r="81" ht="38.25" customHeight="1" s="27">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>MVTec AD</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>SAA+ (Segment Any Anomaly)</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>IEEE TCYB 2025 / arXiv 2023</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>PyramidFlow</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
+        </is>
+      </c>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
         <is>
           <t>已發表</t>
         </is>
       </c>
-      <c r="H81" s="12" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="I81" s="12" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="J81" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="L81" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr">
-        <is>
-          <t>Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA zero-shot [基於表徵]</t>
-        </is>
-      </c>
-      <c r="N81" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2305.10724</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="21" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="J81" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K81" s="21" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
+        </is>
+      </c>
+      <c r="N81" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.02595</t>
+        </is>
+      </c>
+      <c r="O81" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/gasharper/PyramidFlow</t>
         </is>
       </c>
     </row>
@@ -19543,27 +19543,27 @@
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>PyramidFlow</t>
+          <t>DeCo-Diff</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
         <is>
-          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
+          <t>Farzad Beizaee, et al.</t>
         </is>
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G82" s="21" t="inlineStr">
@@ -19571,44 +19571,32 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H82" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I82" s="21" t="inlineStr">
-        <is>
-          <t>97.1</t>
-        </is>
-      </c>
-      <c r="J82" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K82" s="21" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="L82" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H82" s="21" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I82" s="21" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J82" s="21" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K82" s="21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L82" s="21" t="n"/>
       <c r="M82" s="22" t="inlineStr">
         <is>
-          <t>金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
         </is>
       </c>
       <c r="N82" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.02595</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O82" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/gasharper/PyramidFlow</t>
+          <t>https://github.com/farzad-bz/DeCo-Diff</t>
         </is>
       </c>
     </row>
@@ -19620,27 +19608,27 @@
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>DeCo-Diff</t>
+          <t>FUN-AD</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>Farzad Beizaee, et al.</t>
+          <t>Jiin Im, et al.</t>
         </is>
       </c>
       <c r="E83" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G83" s="21" t="inlineStr">
@@ -19649,31 +19637,27 @@
         </is>
       </c>
       <c r="H83" s="21" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="J83" s="21" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="K83" s="21" t="n">
-        <v>94.90000000000001</v>
-      </c>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J83" s="21" t="n"/>
+      <c r="K83" s="21" t="n"/>
       <c r="L83" s="21" t="n"/>
       <c r="M83" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
         </is>
       </c>
       <c r="N83" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O83" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/farzad-bz/DeCo-Diff</t>
+          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
         </is>
       </c>
     </row>
@@ -19685,17 +19669,17 @@
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>FUN-AD</t>
+          <t>UniAS</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
         <is>
-          <t>Jiin Im, et al.</t>
+          <t>Wenxuan Ma, et al.</t>
         </is>
       </c>
       <c r="E84" s="21" t="inlineStr">
@@ -19713,28 +19697,28 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H84" s="21" t="n">
-        <v>99.2</v>
-      </c>
+      <c r="H84" s="21" t="n"/>
       <c r="I84" s="21" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="J84" s="21" t="n"/>
+        <v>98.22</v>
+      </c>
+      <c r="J84" s="21" t="n">
+        <v>65.12</v>
+      </c>
       <c r="K84" s="21" t="n"/>
       <c r="L84" s="21" t="n"/>
       <c r="M84" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：One-for-All 多類別異常分割；論文主打 pixel-AUROC / pAP / DSC,未報告 image-AUROC [基於重構]</t>
         </is>
       </c>
       <c r="N84" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O84" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19746,27 +19730,27 @@
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>UniAS</t>
+          <t>LASB</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>Wenxuan Ma, et al.</t>
+          <t>Akshay Kulkarni, et al.</t>
         </is>
       </c>
       <c r="E85" s="21" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G85" s="21" t="inlineStr">
@@ -19774,23 +19758,23 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H85" s="21" t="n"/>
+      <c r="H85" s="21" t="n">
+        <v>99.66</v>
+      </c>
       <c r="I85" s="21" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="J85" s="21" t="n">
-        <v>65.12</v>
-      </c>
+        <v>99.15000000000001</v>
+      </c>
+      <c r="J85" s="21" t="n"/>
       <c r="K85" s="21" t="n"/>
       <c r="L85" s="21" t="n"/>
       <c r="M85" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：One-for-All 多類別異常分割；論文主打 pixel-AUROC / pAP / DSC,未報告 image-AUROC [基於重構]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Latent Schrödinger Bridge 擴散模型；class-based 設定 (Table 1) [基於擴散]</t>
         </is>
       </c>
       <c r="N85" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O85" s="23" t="inlineStr">
@@ -19807,17 +19791,17 @@
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>LASB</t>
+          <t>PatchGuard</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>Akshay Kulkarni, et al.</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E86" s="21" t="inlineStr">
@@ -19836,22 +19820,22 @@
         </is>
       </c>
       <c r="H86" s="21" t="n">
-        <v>99.66</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>99.15000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="J86" s="21" t="n"/>
       <c r="K86" s="21" t="n"/>
       <c r="L86" s="21" t="n"/>
       <c r="M86" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Latent Schrödinger Bridge 擴散模型；class-based 設定 (Table 1) [基於擴散]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N86" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O86" s="23" t="inlineStr">
@@ -19873,22 +19857,22 @@
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>PatchGuard</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D87" s="21" t="inlineStr">
         <is>
-          <t>Mojtaba Nafez, et al.</t>
+          <t>Daehwan Kim, et al.</t>
         </is>
       </c>
       <c r="E87" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F87" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
@@ -19897,22 +19881,22 @@
         </is>
       </c>
       <c r="H87" s="21" t="n">
-        <v>88.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>92.7</v>
+        <v>98.8</v>
       </c>
       <c r="J87" s="21" t="n"/>
       <c r="K87" s="21" t="n"/>
       <c r="L87" s="21" t="n"/>
       <c r="M87" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
         </is>
       </c>
       <c r="N87" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O87" s="23" t="inlineStr">
@@ -19929,56 +19913,60 @@
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>AST (Asymmetric Student-Teacher)</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
         <is>
-          <t>Daehwan Kim, et al.</t>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
         </is>
       </c>
       <c r="E88" s="21" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>WACV 2023</t>
         </is>
       </c>
       <c r="F88" s="21" t="inlineStr">
         <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G88" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="G88" s="21" t="n">
+        <v>99.2</v>
       </c>
       <c r="H88" s="21" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I88" s="21" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="J88" s="21" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="I88" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J88" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K88" s="21" t="n"/>
       <c r="L88" s="21" t="n"/>
       <c r="M88" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+          <t>✅ 已驗證 (AST WACV23 Table 2+4)：Asymmetric Student-Teacher (RGB+3D NF teacher)；MVTec AD I=99.2 P=95.0 [Student-Teacher]</t>
         </is>
       </c>
       <c r="N88" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2210.07829</t>
         </is>
       </c>
       <c r="O88" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/marco-rudolph/AST</t>
         </is>
       </c>
     </row>
@@ -19990,52 +19978,62 @@
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>VT-ADL</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>ISIE 2021 / arXiv 2104.10036</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="G89" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G89" s="21" t="n">
+        <v>94</v>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I89" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J89" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K89" s="21" t="n"/>
       <c r="L89" s="21" t="n"/>
       <c r="M89" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
         </is>
       </c>
       <c r="N89" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2104.10036</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O89" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/pankajmishra000/VT-ADL</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20047,39 +20045,39 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>AST (Asymmetric Student-Teacher)</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>WACV 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G90" s="21" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="H90" s="21" t="n">
-        <v>95</v>
-      </c>
-      <c r="I90" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>92.3</v>
+      </c>
+      <c r="H90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="21" t="n">
+        <v>96.3</v>
       </c>
       <c r="J90" s="21" t="inlineStr">
         <is>
@@ -20090,17 +20088,17 @@
       <c r="L90" s="21" t="n"/>
       <c r="M90" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AST WACV23 Table 2+4)：Asymmetric Student-Teacher (RGB+3D NF teacher)；MVTec AD I=99.2 P=95.0 [Student-Teacher]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N90" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2210.07829</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O90" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/marco-rudolph/AST</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20112,52 +20110,56 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>SINBAD (Set Features)</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Niv Cohen, Issar Tzachor, Yedid Hoshen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>ICML 2024 / arXiv 2311.14773</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="G91" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H91" s="21" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I91" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="J91" s="21" t="n">
+        <v>94.90000000000001</v>
+      </c>
       <c r="K91" s="21" t="n"/>
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.14773</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/NivC/SINBAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20174,47 +20176,53 @@
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>BTF (Back to the Feature)</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Eliahu Horwitz, Yedid Hoshen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 Workshop / arXiv 2203.05550</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="G92" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="J92" s="21" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H92" s="21" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I92" s="21" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J92" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K92" s="21" t="n"/>
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOT</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.05550</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/eliahuhorwitz/3D-ADS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20226,52 +20234,62 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>RoBiS (VAND 2025 第二名)</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Zhongsheng Jiang, Tingxuan Ai, Yu Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="G93" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="21" t="n"/>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I93" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J93" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K93" s="21" t="n"/>
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 /</t>
+          <t>✅ 已驗證 (SSASDM WACV25 Table 2)：DTU-Net 自監督擴散+動態 Transformer UNet；MVTec AD 15-class avg AUROC 99.17 [基於擴散自監督]</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.21152</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/RoBiS</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20288,7 +20306,7 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Distribution Prototype Diffusion Learning for Open-set Super</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
@@ -20298,32 +20316,42 @@
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G94" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="21" t="n"/>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G94" s="21" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="H94" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K94" s="21" t="n"/>
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Distribution Prototype Diffusion Learning for Open-</t>
+          <t>✅ 已驗證 (ADL WACV25 Table 1, 10% contamination)：Adaptive Deviation Learning under contaminated data；MVTec AD avg AUROC 0.924 [基於監督式 + Noisy normal]</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Distribution_Prototype_Diffusion_Learning_for_Open-set_Supervised_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
@@ -20340,57 +20368,51 @@
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G95" s="21" t="n">
-        <v>94</v>
-      </c>
-      <c r="H95" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I95" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J95" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H95" s="21" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="I95" s="21" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="J95" s="21" t="n"/>
       <c r="K95" s="21" t="n"/>
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD；Look-Twice Feature Matching [基於 MLLM]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O95" s="23" t="inlineStr">
@@ -20412,580 +20434,45 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
         </is>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv preprint</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G96" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I96" s="21" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="J96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+      <c r="J96" s="21" t="n"/>
       <c r="K96" s="21" t="n"/>
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 Transferable Visual Prototype；MVTec/VisA/BTAD/MPDD/3D 通用 [跨模態 ZSAD]</t>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O96" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B97" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C97" s="21" t="inlineStr">
-        <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
-        </is>
-      </c>
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E97" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F97" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G97" s="21" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="H97" s="21" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="I97" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="J97" s="21" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K97" s="21" t="n"/>
-      <c r="L97" s="21" t="n"/>
-      <c r="M97" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N97" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O97" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B98" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F98" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G98" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="H98" s="21" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I98" s="21" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J98" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K98" s="21" t="n"/>
-      <c r="L98" s="21" t="n"/>
-      <c r="M98" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N98" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O98" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C99" s="21" t="inlineStr">
-        <is>
-          <t>TailedCore</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E99" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F99" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G99" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="21" t="n"/>
-      <c r="K99" s="21" t="n"/>
-      <c r="L99" s="21" t="n"/>
-      <c r="M99" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
-        </is>
-      </c>
-      <c r="N99" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O99" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B100" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C100" s="21" t="inlineStr">
-        <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
-        </is>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F100" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G100" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
-      <c r="K100" s="21" t="n"/>
-      <c r="L100" s="21" t="n"/>
-      <c r="M100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Self-Supervised Anomaly Segmentation via Diffusion </t>
-        </is>
-      </c>
-      <c r="N100" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O100" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B101" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C101" s="21" t="inlineStr">
-        <is>
-          <t>Removing Geometric Bias in One-Class Anomaly Detection with</t>
-        </is>
-      </c>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E101" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F101" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G101" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="21" t="n"/>
-      <c r="M101" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Removing Geometric Bias in One-Class Anomaly Detect</t>
-        </is>
-      </c>
-      <c r="N101" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hermary_Removing_Geometric_Bias_in_One-Class_Anomaly_Detection_with_Adaptive_Feature_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O101" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B102" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C102" s="21" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D102" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E102" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F102" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G102" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
-      <c r="J102" s="21" t="n"/>
-      <c r="K102" s="21" t="n"/>
-      <c r="L102" s="21" t="n"/>
-      <c r="M102" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N102" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O102" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B103" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C103" s="21" t="inlineStr">
-        <is>
-          <t>Single-Layer Distillation with Fourier Convolutions for Text</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E103" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G103" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="21" t="n"/>
-      <c r="K103" s="21" t="n"/>
-      <c r="L103" s="21" t="n"/>
-      <c r="M103" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Single-Layer Distillation with Fourier Convolutions</t>
-        </is>
-      </c>
-      <c r="N103" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Thomine_Single-Layer_Distillation_with_Fourier_Convolutions_for_Texture_Anomaly_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O103" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B104" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C104" s="21" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G104" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H104" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I104" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J104" s="21" t="n"/>
-      <c r="K104" s="21" t="n"/>
-      <c r="L104" s="21" t="n"/>
-      <c r="M104" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N104" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O104" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B105" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C105" s="21" t="inlineStr">
-        <is>
-          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
-        </is>
-      </c>
-      <c r="E105" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="G105" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
-      <c r="K105" s="21" t="n"/>
-      <c r="L105" s="21" t="n"/>
-      <c r="M105" s="22" t="inlineStr">
-        <is>
-          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
-        </is>
-      </c>
-      <c r="N105" s="23" t="inlineStr">
-        <is>
           <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
-      <c r="O105" s="23" t="n"/>
+      <c r="O96" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21123,10 +20610,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21138,7 +20623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22369,47 +21854,55 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Triad (LMM-Aided AD)</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13184</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/tzjtatata/Triad</t>
+          <t>https://github.com/FuNz-0/PromptAD</t>
         </is>
       </c>
     </row>
@@ -22426,29 +21919,31 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>PromptAD</t>
+          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G20" s="12" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>74.5</v>
+        <v>90.2</v>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -22464,82 +21959,15 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
+          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>MVTec LOCO</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Towards Training-free Anomaly Detection with Vision and Lang</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (LogSAD CVPR25 Table 1, full-data)：Multi-granularity (patch + interest + composition) training-free VLM AD；MVTec LOCO full-data I=90.2 [基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N21" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Towards_Training-free_Anomaly_Detection_with_Vision_and_Language_Foundation_Models_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23546,7 +22974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28768,47 +28196,57 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SAA+ (Segment Any Anomaly)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Yunkang Cao, Xiaohao Xu, Chen Sun, Yuqi Cheng, Zongwei Du, Liang Gao, Weiming Shen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>IEEE TCYB 2025 / arXiv 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="n"/>
-      <c r="I72" s="12" t="n"/>
-      <c r="J72" s="12" t="n"/>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K72" s="12" t="n"/>
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Zero-shot SAM-based；Hybrid Prompt Regularization 結合專家知識；訓練-free MVTec/VisA SOTA </t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.10724</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O72" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/caoyunkang/Segment-Any-Anomaly</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28825,7 +28263,7 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -28844,17 +28282,15 @@
         </is>
       </c>
       <c r="G73" s="12" t="n">
-        <v>91.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I73" s="12" t="n">
+        <v>89.3</v>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
@@ -28865,12 +28301,12 @@
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O73" s="14" t="inlineStr">
@@ -28892,7 +28328,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -28911,31 +28347,27 @@
         </is>
       </c>
       <c r="G74" s="12" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="J74" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>51.2</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="K74" s="12" t="n"/>
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
+          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
@@ -28957,7 +28389,7 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -28976,27 +28408,29 @@
         </is>
       </c>
       <c r="G75" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>29.8</v>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
@@ -29018,7 +28452,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -29028,22 +28462,26 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G76" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>29.8</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
@@ -29054,12 +28492,12 @@
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>✅ 已驗證 (ADL WACV25 Table 1 VisA, 10% contamination)：Adaptive Deviation Learning under contaminated data；VisA avg AUROC 0.844 [基於監督式 + Noisy normal]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
@@ -29076,27 +28514,27 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>TailedCore</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -29104,140 +28542,26 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H77" s="12" t="n"/>
+      <c r="H77" s="12" t="n">
+        <v>95.42</v>
+      </c>
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
+      <c r="K77" s="12" t="n">
+        <v>92.27</v>
+      </c>
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。TailedCore: Few-Shot Sampling for Unsupervised Long</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jung_TailedCore_Few-Shot_Sampling_for_Unsupervised_Long-Tail_Noisy_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n"/>
-      <c r="I78" s="12" t="n"/>
-      <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
-      <c r="L78" s="12" t="n"/>
-      <c r="M78" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Adaptive Deviation Learning for Visual Anomaly Dete</t>
-        </is>
-      </c>
-      <c r="N78" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O78" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I79" s="12" t="n"/>
-      <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L79" s="12" t="n"/>
-      <c r="M79" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N79" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O79" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -30514,19 +29838,23 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="G18" s="12" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>91.2</v>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Reconstruction-Free：在 latent space 直接以 likelihood 評分；無需顯式重構 [基於擴散]</t>
+          <t>✅ 已驗證 (InvAD-Diff CVPR26投 Table 3 single-class)：Inversion-based Diffusion；MPDD I=96.5 P=98.3 AP=40.1 PRO=91.2 [基於擴散+重構]</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -31025,7 +30353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32495,19 +31823,27 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
+      <c r="G22" s="21" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K22" s="21" t="n"/>
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
+          <t>✅ 已驗證 (AMI-Net IEEE TASE24 Table II)：Adaptive Masked Inpainting；BTAD Average I=95.1 P=97.1 [基於重構]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -32529,52 +31865,60 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>U-Flow</t>
+          <t>MuSc</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>JMIV 2024 / arXiv 2211.12353</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K23" s="21" t="n"/>
       <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
+          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12353</t>
+          <t>https://arxiv.org/abs/2401.16753</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/mtailanian/uflow</t>
+          <t>https://github.com/xrli-U/MuSc</t>
         </is>
       </c>
     </row>
@@ -32591,55 +31935,51 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>MuSc</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G24" s="21" t="n">
-        <v>94.8</v>
+        <v>91.2</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>80</v>
       </c>
       <c r="K24" s="21" t="n"/>
       <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
+          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.16753</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/MuSc</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32656,51 +31996,55 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>PatchEAD</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G25" s="21" t="n">
-        <v>91.2</v>
+        <v>94.8</v>
       </c>
       <c r="H25" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="I25" s="21" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="J25" s="21" t="n">
-        <v>80</v>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K25" s="21" t="n"/>
       <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
+          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -32717,55 +32061,53 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G26" s="21" t="n">
-        <v>94.8</v>
+        <v>88.3</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>97</v>
+        <v>94.2</v>
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J26" s="21" t="n">
+        <v>74.8</v>
       </c>
       <c r="K26" s="21" t="n"/>
       <c r="L26" s="21" t="n"/>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
+          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
         </is>
       </c>
     </row>
@@ -32782,53 +32124,57 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>AnomalyCLIP</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G27" s="21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="H27" s="21" t="n">
-        <v>94.2</v>
+        <v>89</v>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J27" s="21" t="n">
-        <v>74.8</v>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K27" s="21" t="n"/>
       <c r="L27" s="21" t="n"/>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32845,7 +32191,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -32864,17 +32210,15 @@
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>89</v>
+        <v>97.5</v>
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I28" s="21" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
@@ -32885,12 +32229,12 @@
       <c r="L28" s="21" t="n"/>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O28" s="23" t="inlineStr">
@@ -32912,7 +32256,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -32931,15 +32275,13 @@
         </is>
       </c>
       <c r="G29" s="21" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>93.2</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>93.90000000000001</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>98.90000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
@@ -32950,78 +32292,15 @@
       <c r="L29" s="21" t="n"/>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I30" s="21" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J30" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
-        </is>
-      </c>
-      <c r="N30" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -34182,19 +33461,23 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="G17" s="12" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：MoE Feature Decompression；統一 9 個資料集 / 12 模態 / 66 類別 [基於表徵]</t>
+          <t>✅ 已驗證 (UniMMAD arXiv25 Tables 14+15)：MoE Multi-Modal AD；MVTec 3D I=92.5 P=99.0 AP=44.1 PRO=95.9 [多模態 MoE]</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
@@ -34422,19 +33705,23 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="G21" s="12" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>87.8</v>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable D</t>
+          <t>✅ 已驗證 (DiAD AAAI24 Table 5)：Diffusion-based multi-class AD；MVTec 3D I=84.6 P=96.4 AP=25.3 PRO=87.8 [基於擴散]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15049,16 +15049,16 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="n">
         <v>99.5</v>
       </c>
-      <c r="H23" s="21" t="n">
+      <c r="I23" s="21" t="n">
         <v>98.3</v>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
@@ -15122,22 +15122,22 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="I24" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="J24" s="9" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="K24" s="9" t="n">
         <v>96.09999999999999</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
@@ -19936,23 +19936,27 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="G88" s="21" t="n">
+      <c r="G88" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H88" s="21" t="n">
         <v>99.2</v>
       </c>
-      <c r="H88" s="21" t="n">
+      <c r="I88" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="I88" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J88" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K88" s="21" t="n"/>
+      <c r="K88" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L88" s="21" t="n"/>
       <c r="M88" s="22" t="inlineStr">
         <is>
@@ -20001,14 +20005,14 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G89" s="21" t="n">
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="n">
         <v>94</v>
       </c>
-      <c r="H89" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -20019,7 +20023,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K89" s="21" t="n"/>
+      <c r="K89" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L89" s="21" t="n"/>
       <c r="M89" s="22" t="inlineStr">
         <is>
@@ -20068,23 +20076,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G90" s="21" t="n">
+      <c r="G90" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H90" s="21" t="n">
         <v>92.3</v>
       </c>
-      <c r="H90" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I90" s="21" t="n">
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J90" s="21" t="n">
         <v>96.3</v>
       </c>
-      <c r="J90" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K90" s="21" t="n"/>
+      <c r="K90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L90" s="21" t="n"/>
       <c r="M90" s="22" t="inlineStr">
         <is>
@@ -20133,19 +20145,23 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G91" s="21" t="n">
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H91" s="21" t="n">
         <v>99.7</v>
       </c>
-      <c r="H91" s="21" t="n">
+      <c r="I91" s="21" t="n">
         <v>98.5</v>
       </c>
-      <c r="I91" s="21" t="n">
+      <c r="J91" s="21" t="n">
         <v>71</v>
       </c>
-      <c r="J91" s="21" t="n">
+      <c r="K91" s="21" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="K91" s="21" t="n"/>
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
@@ -20194,21 +20210,25 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G92" s="21" t="n">
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="n">
         <v>92.3</v>
       </c>
-      <c r="H92" s="21" t="n">
+      <c r="I92" s="21" t="n">
         <v>91.8</v>
       </c>
-      <c r="I92" s="21" t="n">
+      <c r="J92" s="21" t="n">
         <v>48.3</v>
       </c>
-      <c r="J92" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K92" s="21" t="n"/>
+      <c r="K92" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
@@ -20257,14 +20277,14 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="G93" s="21" t="n">
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="n">
         <v>99.17</v>
       </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -20275,7 +20295,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K93" s="21" t="n"/>
+      <c r="K93" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
@@ -20324,14 +20348,14 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="G94" s="21" t="n">
+      <c r="G94" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H94" s="21" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="H94" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I94" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -20342,7 +20366,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K94" s="21" t="n"/>
+      <c r="K94" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
@@ -21738,14 +21766,14 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -21756,7 +21784,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" s="12" t="n"/>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -21805,14 +21837,14 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -21823,7 +21855,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K18" s="12" t="n"/>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
@@ -21872,23 +21908,27 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>73.5</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>74.5</v>
       </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K19" s="12" t="n"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -21937,14 +21977,14 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>90.2</v>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -21955,7 +21995,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K20" s="12" t="n"/>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
@@ -28086,23 +28130,27 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="G70" s="12" t="n">
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="I70" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K70" s="12" t="n"/>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L70" s="12" t="n"/>
       <c r="M70" s="13" t="inlineStr">
         <is>
@@ -28151,21 +28199,25 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="G71" s="12" t="n">
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H71" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>94.2</v>
       </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J71" s="12" t="n">
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>86.8</v>
       </c>
-      <c r="K71" s="12" t="n"/>
       <c r="L71" s="12" t="n"/>
       <c r="M71" s="13" t="inlineStr">
         <is>
@@ -28214,14 +28266,14 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G72" s="12" t="n">
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -28232,7 +28284,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K72" s="12" t="n"/>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="inlineStr">
         <is>
@@ -28281,23 +28337,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G73" s="12" t="n">
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>86.8</v>
       </c>
-      <c r="H73" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="n">
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="n">
         <v>89.3</v>
       </c>
-      <c r="J73" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K73" s="12" t="n"/>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="inlineStr">
         <is>
@@ -28346,19 +28406,23 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G74" s="12" t="n">
-        <v>98.90000000000001</v>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
       </c>
       <c r="H74" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="I74" s="12" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>51.2</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="K74" s="12" t="n"/>
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
@@ -28407,21 +28471,25 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G75" s="12" t="n">
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="I75" s="12" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="I75" s="12" t="n">
+      <c r="J75" s="12" t="n">
         <v>29.8</v>
       </c>
-      <c r="J75" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" s="12" t="n"/>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
@@ -28470,14 +28538,14 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="G76" s="12" t="n">
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -28488,7 +28556,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K76" s="12" t="n"/>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
@@ -29712,19 +29784,23 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>97.2</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>59.5</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
@@ -29773,23 +29849,27 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>97.5</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>98.7</v>
       </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" s="12" t="n"/>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -29838,19 +29918,23 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>98.3</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>40.1</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>91.2</v>
       </c>
-      <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
@@ -29899,23 +29983,27 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>87.2</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>97.3</v>
       </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K19" s="12" t="n"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -29964,19 +30052,23 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>71.8</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
@@ -30025,23 +30117,27 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>96.7</v>
       </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K21" s="12" t="n"/>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
@@ -30090,21 +30186,25 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>78.3</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>95.8</v>
       </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="n">
         <v>89.7</v>
       </c>
-      <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
@@ -30153,21 +30253,25 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>88.7</v>
       </c>
-      <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
@@ -30216,14 +30320,14 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>81.7</v>
       </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -30234,7 +30338,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K24" s="12" t="n"/>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="inlineStr">
         <is>
@@ -30283,23 +30391,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>72.8</v>
       </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>79.7</v>
       </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="n"/>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="inlineStr">
         <is>
@@ -31701,19 +31813,23 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="n">
         <v>97.5</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="I20" s="21" t="n">
         <v>98.2</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="J20" s="21" t="n">
         <v>73.8</v>
       </c>
-      <c r="J20" s="21" t="n">
+      <c r="K20" s="21" t="n">
         <v>79.8</v>
       </c>
-      <c r="K20" s="21" t="n"/>
       <c r="L20" s="21" t="n"/>
       <c r="M20" s="22" t="inlineStr">
         <is>
@@ -31762,19 +31878,23 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="n">
         <v>94.7</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="I21" s="21" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="J21" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="J21" s="21" t="n">
+      <c r="K21" s="21" t="n">
         <v>78</v>
       </c>
-      <c r="K21" s="21" t="n"/>
       <c r="L21" s="21" t="n"/>
       <c r="M21" s="22" t="inlineStr">
         <is>
@@ -31823,23 +31943,27 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="I22" s="21" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" s="21" t="n"/>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
@@ -31888,23 +32012,27 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="n">
         <v>94.8</v>
       </c>
-      <c r="H23" s="21" t="n">
+      <c r="I23" s="21" t="n">
         <v>97.3</v>
       </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K23" s="21" t="n"/>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
@@ -31953,19 +32081,23 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="n">
         <v>91.2</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="I24" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="J24" s="21" t="n">
         <v>94.3</v>
       </c>
-      <c r="J24" s="21" t="n">
+      <c r="K24" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="K24" s="21" t="n"/>
       <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="inlineStr">
         <is>
@@ -32014,23 +32146,27 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="n">
         <v>94.8</v>
       </c>
-      <c r="H25" s="21" t="n">
+      <c r="I25" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K25" s="21" t="n"/>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="inlineStr">
         <is>
@@ -32079,21 +32215,25 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="n">
         <v>88.3</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="I26" s="21" t="n">
         <v>94.2</v>
       </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="n">
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="n">
         <v>74.8</v>
       </c>
-      <c r="K26" s="21" t="n"/>
       <c r="L26" s="21" t="n"/>
       <c r="M26" s="22" t="inlineStr">
         <is>
@@ -32142,14 +32282,14 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="n">
         <v>89</v>
       </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -32160,7 +32300,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K27" s="21" t="n"/>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L27" s="21" t="n"/>
       <c r="M27" s="22" t="inlineStr">
         <is>
@@ -32209,23 +32353,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="n">
         <v>97.5</v>
       </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="21" t="n"/>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L28" s="21" t="n"/>
       <c r="M28" s="22" t="inlineStr">
         <is>
@@ -32274,21 +32422,25 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="n">
         <v>93.2</v>
       </c>
-      <c r="H29" s="21" t="n">
+      <c r="I29" s="21" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="J29" s="21" t="n">
         <v>47.1</v>
       </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="n"/>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L29" s="21" t="n"/>
       <c r="M29" s="22" t="inlineStr">
         <is>
@@ -33461,19 +33613,23 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>92.5</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>44.1</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -33522,19 +33678,23 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>99.2</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>63.6</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
@@ -33583,19 +33743,23 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>98.8</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>37.8</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>94.7</v>
       </c>
-      <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -33644,19 +33808,23 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>86.2</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>37.5</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
@@ -33705,19 +33873,23 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>25.3</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>87.8</v>
       </c>
-      <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
@@ -33766,23 +33938,27 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="n"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -20485,14 +20485,28 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
+      <c r="H96" s="21" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="I96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
+          <t>✅ 已驗證 (IndusAgent arXiv2605 Table 1, zero-shot)：MLLM Agentic Tools 工業異常檢測；MVTec 83.6 分類分數 (paper 自家數字 — MLLM yes/no 分類，非標準 AUROC，較難跟非 MLLM 方法直接比) [基於 MLLM Agent]</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -22979,14 +22979,28 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
+      <c r="H14" s="12" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
+          <t>✅ 已驗證 (SuperADD CVPR2026 VAND 4.0 Workshop Table 1)：Training-free Class-agnostic；VAND 2025 Cat-1 第一名後續強化版；MVTec AD2 SegF1 priv 57.42 mix 54.35（注：metric 為 SegF1 不是 AUROC）[基於表徵]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -33579,14 +33593,24 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
+      <c r="H16" s="12" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>Auto-fetched (2026-04); 待人工核對指標 [基於表徵 (Representation)]</t>
+          <t>✅ 已驗證 (TGMUIAD arXiv2604 Average row)：Text-Guided Multimodal Unified IAD；MVTec 3D I=93.99 P=96.99 AP=44.87 [基於 VLM]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O172"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -13242,6 +13242,1830 @@
         </is>
       </c>
       <c r="O172" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B173" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>Anomaly-Related Residual Fields for Cross-domain Anomaly Det</t>
+        </is>
+      </c>
+      <c r="D173" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="n"/>
+      <c r="I173" s="18" t="n"/>
+      <c r="J173" s="18" t="n"/>
+      <c r="K173" s="18" t="n"/>
+      <c r="L173" s="18" t="n"/>
+      <c r="M173" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Anomaly-Related Residual Fields for Cross-domain Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N173" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Gao_Anomaly-Related_Residual_Fields_for_Cross-domain_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O173" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>ADSeeker</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="n"/>
+      <c r="I174" s="18" t="n"/>
+      <c r="J174" s="18" t="n"/>
+      <c r="K174" s="18" t="n"/>
+      <c r="L174" s="18" t="n"/>
+      <c r="M174" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ADSeeker: A Knowledge-Grounded Reasoning Framework for Industry Anomaly Detection and Reasoning</t>
+        </is>
+      </c>
+      <c r="N174" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_ADSeeker_A_Knowledge-Grounded_Reasoning_Framework_for_Industry_Anomaly_Detection_and_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O174" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>MoECLIP</t>
+        </is>
+      </c>
+      <c r="D175" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="n"/>
+      <c r="I175" s="18" t="n"/>
+      <c r="J175" s="18" t="n"/>
+      <c r="K175" s="18" t="n"/>
+      <c r="L175" s="18" t="n"/>
+      <c r="M175" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MoECLIP: Patch-Specialized Experts for Zero-shot Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N175" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Park_MoECLIP_Patch-Specialized_Experts_for_Zero-shot_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O175" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>MMR-AD</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="n"/>
+      <c r="I176" s="18" t="n"/>
+      <c r="J176" s="18" t="n"/>
+      <c r="K176" s="18" t="n"/>
+      <c r="L176" s="18" t="n"/>
+      <c r="M176" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MMR-AD: A Large-Scale Multimodal Dataset for Benchmarking General Anomaly Detection with Multimodal Large Language Models</t>
+        </is>
+      </c>
+      <c r="N176" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yao_MMR-AD_A_Large-Scale_Multimodal_Dataset_for_Benchmarking_General_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O176" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>Geometry-Aligned and Anomaly-Aware Reconstruction for 3D Ano</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="n"/>
+      <c r="I177" s="18" t="n"/>
+      <c r="J177" s="18" t="n"/>
+      <c r="K177" s="18" t="n"/>
+      <c r="L177" s="18" t="n"/>
+      <c r="M177" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Geometry-Aligned and Anomaly-Aware Reconstruction for 3D Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N177" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wu_Geometry-Aligned_and_Anomaly-Aware_Reconstruction_for_3D_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O177" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>SFR-Net</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F178" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H178" s="18" t="n"/>
+      <c r="I178" s="18" t="n"/>
+      <c r="J178" s="18" t="n"/>
+      <c r="K178" s="18" t="n"/>
+      <c r="L178" s="18" t="n"/>
+      <c r="M178" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SFR-Net: Steering-Fusion-Refining Network in Multi-label Zero-Shot Sewer Defect Detection</t>
+        </is>
+      </c>
+      <c r="N178" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Chen_SFR-Net_Steering-Fusion-Refining_Network_in_Multi-label_Zero-Shot_Sewer_Defect_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O178" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B179" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>A Semantically Disentangled Unified Model for Multi-category</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F179" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H179" s="18" t="n"/>
+      <c r="I179" s="18" t="n"/>
+      <c r="J179" s="18" t="n"/>
+      <c r="K179" s="18" t="n"/>
+      <c r="L179" s="18" t="n"/>
+      <c r="M179" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Semantically Disentangled Unified Model for Multi-category 3D Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N179" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Kim_A_Semantically_Disentangled_Unified_Model_for_Multi-category_3D_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O179" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B180" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>LayoutAD</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F180" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H180" s="18" t="n"/>
+      <c r="I180" s="18" t="n"/>
+      <c r="J180" s="18" t="n"/>
+      <c r="K180" s="18" t="n"/>
+      <c r="L180" s="18" t="n"/>
+      <c r="M180" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。LayoutAD: Exploring Semantic-Geometric Misalignment Reasoning for Scene Layout Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N180" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zeng_LayoutAD_Exploring_Semantic-Geometric_Misalignment_Reasoning_for_Scene_Layout_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O180" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
+        <is>
+          <t>Back to Point</t>
+        </is>
+      </c>
+      <c r="D181" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F181" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G181" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H181" s="18" t="n"/>
+      <c r="I181" s="18" t="n"/>
+      <c r="J181" s="18" t="n"/>
+      <c r="K181" s="18" t="n"/>
+      <c r="L181" s="18" t="n"/>
+      <c r="M181" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Back to Point: Exploring Point-Language Models for Zero-Shot 3D Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N181" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_Back_to_Point_Exploring_Point-Language_Models_for_Zero-Shot_3D_Anomaly_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O181" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="inlineStr">
+        <is>
+          <t>VisualAD</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F182" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H182" s="18" t="n"/>
+      <c r="I182" s="18" t="n"/>
+      <c r="J182" s="18" t="n"/>
+      <c r="K182" s="18" t="n"/>
+      <c r="L182" s="18" t="n"/>
+      <c r="M182" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。VisualAD: Language-Free Zero-Shot Anomaly Detection via Vision Transformer</t>
+        </is>
+      </c>
+      <c r="N182" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Hou_VisualAD_Language-Free_Zero-Shot_Anomaly_Detection_via_Vision_Transformer_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O182" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>Multi-Prototype Compactness and Boundary-Aware Synthesis for</t>
+        </is>
+      </c>
+      <c r="D183" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H183" s="18" t="n"/>
+      <c r="I183" s="18" t="n"/>
+      <c r="J183" s="18" t="n"/>
+      <c r="K183" s="18" t="n"/>
+      <c r="L183" s="18" t="n"/>
+      <c r="M183" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Multi-Prototype Compactness and Boundary-Aware Synthesis for Unsupervised Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N183" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liao_Multi-Prototype_Compactness_and_Boundary-Aware_Synthesis_for_Unsupervised_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O183" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B184" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
+        <is>
+          <t>GS-CLIP</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F184" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H184" s="18" t="n"/>
+      <c r="I184" s="18" t="n"/>
+      <c r="J184" s="18" t="n"/>
+      <c r="K184" s="18" t="n"/>
+      <c r="L184" s="18" t="n"/>
+      <c r="M184" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。GS-CLIP: Zero-shot 3D Anomaly Detection by Geometry-Aware Prompt and Synergistic View Representation Learning</t>
+        </is>
+      </c>
+      <c r="N184" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Deng_GS-CLIP_Zero-shot_3D_Anomaly_Detection_by_Geometry-Aware_Prompt_and_Synergistic_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O184" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B185" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>GPFlow</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F185" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H185" s="18" t="n"/>
+      <c r="I185" s="18" t="n"/>
+      <c r="J185" s="18" t="n"/>
+      <c r="K185" s="18" t="n"/>
+      <c r="L185" s="18" t="n"/>
+      <c r="M185" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。GPFlow: Gaussian Prototype Probability Flow for Unsupervised Multi-Modal Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N185" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_GPFlow_Gaussian_Prototype_Probability_Flow_for_Unsupervised_Multi-Modal_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O185" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B186" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
+        <is>
+          <t>Complementary Prototype Mapping for Efficient Multimodal Ano</t>
+        </is>
+      </c>
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E186" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F186" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H186" s="18" t="n"/>
+      <c r="I186" s="18" t="n"/>
+      <c r="J186" s="18" t="n"/>
+      <c r="K186" s="18" t="n"/>
+      <c r="L186" s="18" t="n"/>
+      <c r="M186" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Complementary Prototype Mapping for Efficient Multimodal Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N186" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhao_Complementary_Prototype_Mapping_for_Efficient_Multimodal_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O186" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B187" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>From Attraction to Equilibrium</t>
+        </is>
+      </c>
+      <c r="D187" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E187" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F187" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G187" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H187" s="18" t="n"/>
+      <c r="I187" s="18" t="n"/>
+      <c r="J187" s="18" t="n"/>
+      <c r="K187" s="18" t="n"/>
+      <c r="L187" s="18" t="n"/>
+      <c r="M187" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。From Attraction to Equilibrium: Physics-Inspired Semantic Gravitons for Zero-Shot Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N187" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Pan_From_Attraction_to_Equilibrium_Physics-Inspired_Semantic_Gravitons_for_Zero-Shot_Anomaly_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O187" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B188" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="inlineStr">
+        <is>
+          <t>Reasoning-Driven Anomaly Detection and Localization with Ima</t>
+        </is>
+      </c>
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F188" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H188" s="18" t="n"/>
+      <c r="I188" s="18" t="n"/>
+      <c r="J188" s="18" t="n"/>
+      <c r="K188" s="18" t="n"/>
+      <c r="L188" s="18" t="n"/>
+      <c r="M188" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Reasoning-Driven Anomaly Detection and Localization with Image-Level Supervision</t>
+        </is>
+      </c>
+      <c r="N188" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Jin_Reasoning-Driven_Anomaly_Detection_and_Localization_with_Image-Level_Supervision_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O188" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B189" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>Towards an Incremental Unified Multimodal Anomaly Detection:</t>
+        </is>
+      </c>
+      <c r="D189" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E189" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F189" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G189" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H189" s="18" t="n"/>
+      <c r="I189" s="18" t="n"/>
+      <c r="J189" s="18" t="n"/>
+      <c r="K189" s="18" t="n"/>
+      <c r="L189" s="18" t="n"/>
+      <c r="M189" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards an Incremental Unified Multimodal Anomaly Detection: Augmenting Multimodal Denoising From an Information Bottleneck Perspective</t>
+        </is>
+      </c>
+      <c r="N189" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Long_Towards_an_Incremental_Unified_Multimodal_Anomaly_Detection_Augmenting_Multimodal_Denoising_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O189" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B190" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="inlineStr">
+        <is>
+          <t>Dual-Prototype-Guided Multi-task Learning for Unsupervised A</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E190" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F190" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G190" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H190" s="18" t="n"/>
+      <c r="I190" s="18" t="n"/>
+      <c r="J190" s="18" t="n"/>
+      <c r="K190" s="18" t="n"/>
+      <c r="L190" s="18" t="n"/>
+      <c r="M190" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Dual-Prototype-Guided Multi-task Learning for Unsupervised Anomaly Detection and Classification</t>
+        </is>
+      </c>
+      <c r="N190" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Luo_Dual-Prototype-Guided_Multi-task_Learning_for_Unsupervised_Anomaly_Detection_and_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O190" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B191" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>Omni-AD</t>
+        </is>
+      </c>
+      <c r="D191" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E191" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F191" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G191" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H191" s="18" t="n"/>
+      <c r="I191" s="18" t="n"/>
+      <c r="J191" s="18" t="n"/>
+      <c r="K191" s="18" t="n"/>
+      <c r="L191" s="18" t="n"/>
+      <c r="M191" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Omni-AD: A Large-scale and Versatile Benchmark for Industrial Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N191" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Shi_Omni-AD_A_Large-scale_and_Versatile_Benchmark_for_Industrial_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O191" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B192" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
+        <is>
+          <t>ClimaOoD</t>
+        </is>
+      </c>
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E192" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F192" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G192" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H192" s="18" t="n"/>
+      <c r="I192" s="18" t="n"/>
+      <c r="J192" s="18" t="n"/>
+      <c r="K192" s="18" t="n"/>
+      <c r="L192" s="18" t="n"/>
+      <c r="M192" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ClimaOoD: Improving Anomaly Segmentation via Physically Realistic Synthetic Data</t>
+        </is>
+      </c>
+      <c r="N192" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liu_ClimaOoD_Improving_Anomaly_Segmentation_via_Physically_Realistic_Synthetic_Data_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O192" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B193" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>Bidirectional Multimodal Prompt Learning with Scale-Aware Tr</t>
+        </is>
+      </c>
+      <c r="D193" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F193" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G193" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H193" s="18" t="n"/>
+      <c r="I193" s="18" t="n"/>
+      <c r="J193" s="18" t="n"/>
+      <c r="K193" s="18" t="n"/>
+      <c r="L193" s="18" t="n"/>
+      <c r="M193" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Bidirectional Multimodal Prompt Learning with Scale-Aware Training for Few-Shot Multi-Class Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N193" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_Bidirectional_Multimodal_Prompt_Learning_with_Scale-Aware_Training_for_Few-Shot_Multi-Class_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O193" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B194" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>DLVP-CLIP</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F194" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H194" s="18" t="n"/>
+      <c r="I194" s="18" t="n"/>
+      <c r="J194" s="18" t="n"/>
+      <c r="K194" s="18" t="n"/>
+      <c r="L194" s="18" t="n"/>
+      <c r="M194" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DLVP-CLIP: Enhancing Fine-Grained Zero-Shot Anomaly Detection via Dynamic Local Visual Prompting</t>
+        </is>
+      </c>
+      <c r="N194" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_DLVP-CLIP_Enhancing_Fine-Grained_Zero-Shot_Anomaly_Detection_via_Dynamic_Local_Visual_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O194" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>RAID</t>
+        </is>
+      </c>
+      <c r="D195" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F195" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G195" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H195" s="18" t="n"/>
+      <c r="I195" s="18" t="n"/>
+      <c r="J195" s="18" t="n"/>
+      <c r="K195" s="18" t="n"/>
+      <c r="L195" s="18" t="n"/>
+      <c r="M195" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RAID: Retrieval-Augmented Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N195" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Cai_RAID_Retrieval-Augmented_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O195" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B196" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>FastRef</t>
+        </is>
+      </c>
+      <c r="D196" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E196" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F196" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G196" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H196" s="18" t="n"/>
+      <c r="I196" s="18" t="n"/>
+      <c r="J196" s="18" t="n"/>
+      <c r="K196" s="18" t="n"/>
+      <c r="L196" s="18" t="n"/>
+      <c r="M196" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FastRef: Fast Prototype Refinement for Few-shot Industrial Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N196" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_FastRef_Fast_Prototype_Refinement_for_Few-shot_Industrial_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O196" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B197" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>FB-CLIP</t>
+        </is>
+      </c>
+      <c r="D197" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F197" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G197" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H197" s="18" t="n"/>
+      <c r="I197" s="18" t="n"/>
+      <c r="J197" s="18" t="n"/>
+      <c r="K197" s="18" t="n"/>
+      <c r="L197" s="18" t="n"/>
+      <c r="M197" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FB-CLIP: Fine-Grained Zero-Shot Anomaly Detection with Foreground-Background Disentanglement</t>
+        </is>
+      </c>
+      <c r="N197" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Hu_FB-CLIP_Fine-Grained_Zero-Shot_Anomaly_Detection_with_Foreground-Background_Disentanglement_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O197" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B198" s="18" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
+        <is>
+          <t>RC-NF</t>
+        </is>
+      </c>
+      <c r="D198" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F198" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G198" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H198" s="18" t="n"/>
+      <c r="I198" s="18" t="n"/>
+      <c r="J198" s="18" t="n"/>
+      <c r="K198" s="18" t="n"/>
+      <c r="L198" s="18" t="n"/>
+      <c r="M198" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RC-NF: Robot-Conditioned Normalizing Flow for Real-Time Anomaly Detection in Robotic Manipulation</t>
+        </is>
+      </c>
+      <c r="N198" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhou_RC-NF_Robot-Conditioned_Normalizing_Flow_for_Real-Time_Anomaly_Detection_in_Robotic_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O198" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B199" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>Hierarchical Point-Patch Fusion with Adaptive Patch Codebook</t>
+        </is>
+      </c>
+      <c r="D199" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F199" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G199" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H199" s="18" t="n"/>
+      <c r="I199" s="18" t="n"/>
+      <c r="J199" s="18" t="n"/>
+      <c r="K199" s="18" t="n"/>
+      <c r="L199" s="18" t="n"/>
+      <c r="M199" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Hierarchical Point-Patch Fusion with Adaptive Patch Codebook for 3D Shape Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N199" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Kang_Hierarchical_Point-Patch_Fusion_with_Adaptive_Patch_Codebook_for_3D_Shape_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O199" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B200" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wavelet-Driven 3D Anomaly Detection under Pose-Agnostic and </t>
+        </is>
+      </c>
+      <c r="D200" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E200" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F200" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G200" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H200" s="18" t="n"/>
+      <c r="I200" s="18" t="n"/>
+      <c r="J200" s="18" t="n"/>
+      <c r="K200" s="18" t="n"/>
+      <c r="L200" s="18" t="n"/>
+      <c r="M200" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Wavelet-Driven 3D Anomaly Detection under Pose-Agnostic and Sparse-View</t>
+        </is>
+      </c>
+      <c r="N200" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Shao_Wavelet-Driven_3D_Anomaly_Detection_under_Pose-Agnostic_and_Sparse-View_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O200" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B201" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>AG-VAS</t>
+        </is>
+      </c>
+      <c r="D201" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E201" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F201" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G201" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H201" s="18" t="n"/>
+      <c r="I201" s="18" t="n"/>
+      <c r="J201" s="18" t="n"/>
+      <c r="K201" s="18" t="n"/>
+      <c r="L201" s="18" t="n"/>
+      <c r="M201" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。AG-VAS: Anchor-Guided Zero-Shot Visual Anomaly Segmentation with Large Multimodal Models</t>
+        </is>
+      </c>
+      <c r="N201" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Qu_AG-VAS_Anchor-Guided_Zero-Shot_Visual_Anomaly_Segmentation_with_Large_Multimodal_Models_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O201" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B202" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="inlineStr">
+        <is>
+          <t>Defect Cue-Preserved Structural Feature Refinement for Few-S</t>
+        </is>
+      </c>
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F202" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G202" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H202" s="18" t="n"/>
+      <c r="I202" s="18" t="n"/>
+      <c r="J202" s="18" t="n"/>
+      <c r="K202" s="18" t="n"/>
+      <c r="L202" s="18" t="n"/>
+      <c r="M202" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Defect Cue-Preserved Structural Feature Refinement for Few-Shot Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N202" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Jiang_Defect_Cue-Preserved_Structural_Feature_Refinement_for_Few-Shot_Anomaly_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O202" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B203" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>Hunting Normality from Query Sample via Residual Learning fo</t>
+        </is>
+      </c>
+      <c r="D203" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F203" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G203" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H203" s="18" t="n"/>
+      <c r="I203" s="18" t="n"/>
+      <c r="J203" s="18" t="n"/>
+      <c r="K203" s="18" t="n"/>
+      <c r="L203" s="18" t="n"/>
+      <c r="M203" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Hunting Normality from Query Sample via Residual Learning for Generalist Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="N203" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wang_Hunting_Normality_from_Query_Sample_via_Residual_Learning_for_Generalist_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O203" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B204" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>SubspaceAD</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E204" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G204" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="n"/>
+      <c r="I204" s="18" t="n"/>
+      <c r="J204" s="18" t="n"/>
+      <c r="K204" s="18" t="n"/>
+      <c r="L204" s="18" t="n"/>
+      <c r="M204" s="19" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SubspaceAD: Training-Free Few-Shot Anomaly Detection via Subspace Modeling</t>
+        </is>
+      </c>
+      <c r="N204" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Lendering_SubspaceAD_Training-Free_Few-Shot_Anomaly_Detection_via_Subspace_Modeling_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O204" s="20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15444,7 +15444,7 @@
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>Global+Local Anomaly Synthesis；梯度上升+截斷投影的近分布異常 [基於資料擴增]</t>
+          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): MVTec AD I-AUROC 99.9 / P-AUROC 99.3 (Global+Local Anomaly Synthesis) [基於資料擴增]</t>
         </is>
       </c>
       <c r="N4" s="11" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>S-T + bottleneck + 領域特徵選擇 + 對比學習；統一工業/醫療/影片 12 資料集 (industrial: MVTec AD/BTAD/MVTec 3D-AD) [基於表徵]</t>
+          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>Dinomaly 強化版：DINOv2 ViT-S/B/L Encoder + ViT decoder 重構；MVTec/VisA/MPDD 同時 SOTA；ViT-S 153.6 FPS [基於重構]</t>
+          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — MVTec AD I-AUROC 99.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N6" s="17" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Conditioned Denoising Diffusion；以 target image 條件化去噪 + 域適應 [基於擴散]</t>
+          <t>✅ verified (DDAD BMVC24/WACV24, arxiv 2305.15956): MVTec AD I-AUROC 99.8 (Denoising Diffusion AD with conditioning) [基於擴散]</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>Strength-controllable Diffusion Anomaly Synthesis (SDAS) + AFS + RRS [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): MVTec AD I-AUROC 99.7 (realistic synthetic anomaly + feature selection) [基於資料擴增]</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t>多尺度 normalizing flow；非對稱並行 flow + fusion flow，MVTec AD SOTA [基於 NF]</t>
+          <t>✅ verified (MSFlow IEEE TNNLS24, arxiv 2308.15300): MVTec AD I-AUROC 99.7 (multi-scale normalizing flow) [基於 NF]</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>雙學生 (Encoder-Decoder + Encoder-Encoder) + DINOv2 知識蒸餾；Noisy-OR 聯合學習 [基於重構]</t>
+          <t>⚠️ Generalist Multi-Class AD (Dual-Student) (arXiv preprint 2025) — MVTec AD I-AUROC 99.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>Intrinsic Normal Prototypes：以單張測試影像的內部正常 token 線性組合做 reconstruction guide [基於重構]</t>
+          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): MVTec AD I-AUROC 99.7 (intrinsic normal prototypes) [基於表徵]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>Norm-guided 單步去噪 + 重構+分割子網 [基於擴散]</t>
+          <t>✅ verified (DiffusionAD IEEE TPAMI25, arxiv 2303.08730): MVTec AD I-AUROC 99.7 (noise-to-norm one-step denoising) [基於擴散]</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>雙互關擴散 anomaly+mask 同步生成；下游 AD 大幅提升 [基於資料擴增]</t>
+          <t>⚠️ Dual-Interrelated Diffusion (DualAnoDiff) (CVPR 2025) — MVTec AD I-AUROC 99.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>兩階段訓練：大規模規則合成預訓 + 小規模生成式微調；DRAEM 風格 Perlin 加入 [基於資料擴增]</t>
+          <t>⚠️ Effective Synthetic Images (arXiv preprint 2025) — MVTec AD I-AUROC 99.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="M15" s="16" t="inlineStr">
         <is>
-          <t>DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
+          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): MVTec AD multi-class I-AUROC 99.6 (DINOv2 ViT + linear decoder, "less is more") [基於重構]</t>
         </is>
       </c>
       <c r="N15" s="17" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>Feature Adapter + 高斯噪聲特徵偽造 + 判別器；77 FPS [基於表徵]</t>
+          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): MVTec AD I-AUROC 99.6 / P-AUROC 98.1 (feature adaptor + simple discriminator) [基於表徵]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Segmentation-oriented 工業異常合成；分級擴散 + explicit mask 對齊 [基於資料擴增]</t>
+          <t>⚠️ STAGE (Graded Diffusion + Mask Alignment) (arXiv preprint 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>Agentic Reinforcement Learning 合成；多輪推理 + 工具使用 + 環境回饋 [基於資料擴增]</t>
+          <t>⚠️ AnomalyAgent (Agentic RL Synthesis) (arXiv preprint 2026) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>Universal AD：以 Intrinsic Normal Prototypes 統一單類/多類/少樣本/zero-shot [基於表徵]</t>
+          <t>⚠️ INP-Former++ (arXiv preprint 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>Continual Diffusion + Gradient Projection；MVTec/VisA 17/18 設定第一 [基於擴散]</t>
+          <t>⚠️ One-for-More (Continual Diffusion) (CVPR 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>Coupled-Hypersphere Feature Adaptation；Patch descriptor + 可擴展 Memory Bank [基於表徵]</t>
+          <t>✅ verified (CFA IEEE Access22, arxiv 2206.04325): MVTec AD I-AUROC 99.5 (coupled-hypersphere feature adaptation) [基於記憶庫]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): MVTec AD I-AUROC 99.5 (contrastive reconstruction, domain-specific) [基於表徵]</t>
         </is>
       </c>
       <c r="N22" s="17" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="M25" s="19" t="inlineStr">
         <is>
-          <t>MIF 多模態融合 + DDF 動態擴散；多源 X-embedding 增強合成 [基於擴散]</t>
+          <t>⚠️ AnomalyXFusion (Multi-modal Diffusion) (arXiv preprint 2024) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Spatially-Grounded Diffusion；per-pixel 語意條件 + Gated Self-Attention 注入 [基於資料擴增]</t>
+          <t>⚠️ GroundingAnomaly (Spatial Diffusion) (arXiv preprint 2026) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>可微分特徵匹配；以可微 nearest-neighbor 直接優化匹配權重做 AD [基於表徵]</t>
+          <t>⚠️ DFM (Differentiable Feature Matching) (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Diffusion-based 少樣本異常驅動生成；分類+分割兩任務一致提升 [基於資料擴增]</t>
+          <t>⚠️ AnoGen (Few-Shot Anomaly-Driven Generation) (ECCV 2024 / arXiv 2025) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>2D 卷積 normalizing flow；相容 ResNet/ViT 任意 backbone [基於 NF]</t>
+          <t>✅ verified (FastFlow arxiv 2111.07677): MVTec AD I-AUROC 99.4 (2D normalizing flow, fast inference) [基於 NF]</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>MoE Feature Decompression；統一 9 個資料集 / 12 模態 / 66 類別 [基於表徵]</t>
+          <t>⚠️ UniMMAD (MoE Multi-Modal AD) (arXiv preprint 2025) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+          <t>✅ verified (RD++ CVPR23, arxiv 2304.12433): MVTec AD I-AUROC 99.4 (reverse distillation + multi-projection) [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="M33" s="16" t="inlineStr">
         <is>
-          <t>Self-Navigated 殘差 Mamba：以 inter/intra-residual 自參考學習；MVTec AD/3D/VisA SOTA [基於重構]</t>
+          <t>⚠️ SNARM (Self-Navigated Residual Mamba) (arXiv preprint 2025) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N33" s="17" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>Model-agnostic 真實感異常生成；TrueSkill 與真實圖差距 &lt; 0.28 [基於資料擴增]</t>
+          <t>⚠️ MIRAGE (Realistic Anomaly Generation) (arXiv preprint 2026) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="M35" s="19" t="inlineStr">
         <is>
-          <t>Global+Local 自適應擴散；每樣本預測去噪步驟、空間自適應特徵融合 [基於擴散]</t>
+          <t>⚠️ GLAD (ECCV 2024) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>GAN+Diffusion 混合異常合成；參考圖+depth-edge 條件控制保留結構與真實感 [基於資料擴增]</t>
+          <t>⚠️ AnomalyHybrid (GAN-Hybrid Synthesis) (CVPR 2025 SyntaGen Workshop (CVF Open Access)) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>Reconstruction-Free：在 latent space 直接以 likelihood 評分；無需顯式重構 [基於擴散]</t>
+          <t>⚠️ InvAD-Diff (Inversion-based Diffusion) (arXiv preprint / CVPR 2026 投稿中) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>Few-shot 異常生成：空間異常嵌入 + 自適應注意力重加權 [基於擴散]</t>
+          <t>✅ verified (AnomalyDiffusion AAAI24, arxiv 2312.05767): MVTec AD I-AUROC 99.2 (few-shot anomaly generation via diffusion) [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>Inpainting Diffusion；視覺檢測導向的真實感缺陷生成 [基於資料擴增]</t>
+          <t>⚠️ DefectFill (Inpainting Diffusion) (arXiv preprint 2025) — MVTec AD I-AUROC 99.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>Transparency-based 擴散；異常區域透明度漸增重構 [基於擴散]</t>
+          <t>✅ verified (TransFusion ECCV24, arxiv 2311.09999): MVTec AD I-AUROC 99.2 (transparency-based diffusion) [基於擴散]</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>Schrödinger Bridge 擴散：在端點分布之間直接學習映射；無監督 AD 重構 [基於擴散]</t>
+          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>階層式向量量化 Transformer；多類別統一模型，以離散原型重構 [基於重構]</t>
+          <t>✅ verified (HVQ-Trans NeurIPS23, arxiv 2310.14228): MVTec AD multi-class I-AUROC 99.2 (hierarchical vector-quantized transformer) [基於重構]</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec AD I-AUROC 99.1 / P-AUROC 98.1 (coreset memory bank + local patch features) [基於記憶庫]</t>
         </is>
       </c>
       <c r="N43" s="14" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
+          <t>⚠️ AMI-Net (IEEE TASE 2024) — MVTec AD I-AUROC 99.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N44" s="17" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="M45" s="22" t="inlineStr">
         <is>
-          <t>統一 NF；多類別異常檢測；MVTec AD I=99.1% / P=98.0%，含 VisA/BTAD [基於 NF]</t>
+          <t>⚠️ UniFlow (Unified NF) (MDPI Information 2024) — MVTec AD I-AUROC 99.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>Patch Description Network + S-T + AE；2ms 低延遲、614 FPS [基於表徵]</t>
+          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): MVTec AD I-AUROC 99.1 (PDN student-teacher + autoencoder, ms-level latency) [基於學生-教師]</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="M47" s="19" t="inlineStr">
         <is>
-          <t>完全 training-free 工業缺陷生成；擴散去除訓練成本 [基於擴散]</t>
+          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV 2025) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>未見類異常生成：以 SD + attention guidance 對任何類別生成新型異常 [基於資料擴增]</t>
+          <t>⚠️ AnomalyAny (Unseen Visual Anomaly Generation) (CVPR 2025 (CVF Open Access) / arXiv 2406.01078) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N48" s="11" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>⚠️ InvAD (Feature Inversion) (arXiv preprint 2024) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N49" s="17" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>Pyramid Mamba 多類異常；以 SSM 結合 NF 思想做密度估計 [基於 NF]</t>
+          <t>⚠️ Pyramid-based Mamba NF (arXiv preprint 2025) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N50" s="23" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>結構化原型聚合 + 邏輯異常檢測；MVTec LOCO 96.1% / MVTec AD 98.9% / VisA 97.9% [基於重構]</t>
+          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — MVTec AD I-AUROC 98.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
+          <t>⚠️ Adversarially Robust Diffusion AD (arXiv preprint 2024) — MVTec AD I-AUROC 98.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="M53" s="22" t="inlineStr">
         <is>
-          <t>U-shape NF + 無監督閾值估計；NFA 自動門檻 [基於 NF]</t>
+          <t>✅ verified (U-Flow JMIV24, arxiv 2211.12353): MVTec AD I-AUROC 98.7 (U-shaped normalizing flow + unsupervised threshold) [基於 NF]</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>模板特徵聚合網路；以多模板做特徵級重構，I-AUROC 98.7%、P-AUROC 98.3% [基於重構]</t>
+          <t>⚠️ TFA-Net (Template-based Feature Aggregation) (arXiv preprint 2026) — MVTec AD I-AUROC 98.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="M55" s="22" t="inlineStr">
         <is>
-          <t>跨尺度全卷積 normalizing flow；多 scale 特徵聯合建模 [基於 NF]</t>
+          <t>✅ verified (CS-Flow WACV22, arxiv 2110.02855): MVTec AD I-AUROC 98.7 (cross-scale normalizing flow) [基於 NF]</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>去噪學生-教師 + 分割網路；整合合成異常 [基於資料擴增]</t>
+          <t>✅ verified (DeSTSeg CVPR23, arxiv 2211.11317): MVTec AD I-AUROC 98.6 (denoising student-teacher segmentation) [基於學生-教師]</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M57" s="16" t="inlineStr">
         <is>
-          <t>首個將 Mamba State Space Model 應用於多類異常檢測；LSS 模組+HSS block 八向掃描 [基於重構]</t>
+          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): MVTec AD multi-class I-AUROC 98.6 (state-space Mamba + pyramid decoder) [基於重構]</t>
         </is>
       </c>
       <c r="N57" s="17" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>⚠️ Triad (LMM-Aided AD) (ICCV 2025 (CVF Open Access) / arXiv 2503.13184) — MVTec AD I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="M59" s="16" t="inlineStr">
         <is>
-          <t>Reverse Distillation 反向知識蒸餾；T-S encoder-decoder 重構特徵 [基於重構]</t>
+          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MVTec AD I-AUROC 98.5 (reverse distillation one-class bottleneck) [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N59" s="17" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>條件式 normalizing flow，以位置編碼為條件；即時檢測 [基於 NF]</t>
+          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): MVTec AD I-AUROC 98.3 (conditional normalizing flow) [基於 NF]</t>
         </is>
       </c>
       <c r="N60" s="23" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="M61" s="16" t="inlineStr">
         <is>
-          <t>Omni-frequency Channel-selection Reconstruction；GAN 頻域重構 [基於重構]</t>
+          <t>✅ verified (OCR-GAN IEEE TIP23, arxiv 2203.00259): MVTec AD I-AUROC 98.3 (omni-frequency channel-selection reconstruction GAN) [基於重構]</t>
         </is>
       </c>
       <c r="N61" s="17" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="M62" s="16" t="inlineStr">
         <is>
-          <t>記憶檢索 Transformer：學習式記憶 + 檢索；MVTec AD I-AUROC 98.2% [基於重構]</t>
+          <t>⚠️ USAGI (Memory-Retrieval Transformer) (Pattern Recognition 2025 / 預印) — MVTec AD I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N62" s="17" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>CLIP few-shot AD：以 rare class prompting；MVTec 98.2% / VisA 94.4%；latency ≈ 59.4ms [基於表徵]</t>
+          <t>⚠️ RareCLIP (ICCV 2025 (CVF Open Access)) — MVTec AD I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N63" s="14" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>Perlin 噪聲 + DTD 紋理合成缺陷 + 重構 + 判別網路 [基於資料擴增]</t>
+          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): MVTec AD I-AUROC 98.0 (discriminatively trained reconstruction + synthetic anomaly) [基於資料擴增]</t>
         </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>Pretrained CNN feature + Mahalanobis distance；經典 baseline，記憶體式 patch embedding [基於表徵]</t>
+          <t>✅ verified (PaDiM ICPR21 workshop, arxiv 2011.08785): MVTec AD I-AUROC 97.9 (patch distribution modeling, multivariate Gaussian) [基於表徵]</t>
         </is>
       </c>
       <c r="N65" s="14" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>Zero-shot 互評分機制；未標註測試集內相互打分 [基於表徵]</t>
+          <t>✅ verified (MuSc ICLR24, arxiv 2401.16753): MVTec AD I-AUROC 97.8 (training-free mutual scoring, zero-shot) [基於零樣本]</t>
         </is>
       </c>
       <c r="N66" s="14" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>Training-free Universal Visual AD：跨域不訓練即可推論；MVTec 97.8% / VisA 93.5% / MVTec LOCO 71.0% [基於表徵]</t>
+          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — MVTec AD I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N67" s="14" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="M68" s="13" t="inlineStr">
         <is>
-          <t>視覺基礎模型最近鄰搜尋；1-shot SOTA：MVTec 97.4% / VisA 94.8% [基於表徵]</t>
+          <t>⚠️ VisionAD (Search Is All You Need) (arXiv preprint 2025) — MVTec AD I-AUROC 97.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N68" s="14" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="M69" s="19" t="inlineStr">
         <is>
-          <t>Difference-Aware Diffusion；Pixel-AE + Latent Semantic-Guided Network 連接 Stable Diffusion；多類別 I=97.2 P=96.8 [基於擴散]</t>
+          <t>✅ verified (DiAD AAAI24, arxiv 2312.06607): MVTec AD multi-class I-AUROC 97.2 (denoising diffusion multi-class, semantic-guided) [基於擴散]</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="M70" s="13" t="inlineStr">
         <is>
-          <t>DINOv2 patch-based few-shot；無需訓練 / fine-tune，1-shot SOTA 96.6% [基於表徵]</t>
+          <t>✅ verified (AnomalyDINO WACV25, arxiv 2405.14529): MVTec AD I-AUROC 96.6 (training-free few-shot via DINOv2 patch features) [基於基礎模型]</t>
         </is>
       </c>
       <c r="N70" s="14" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>Few-shot prompt learning；MVTec/VisA 12 個少樣本中 11 項第一；4-shot MVTec 96.6 / 96.5 [基於表徵]</t>
+          <t>✅ verified (PromptAD CVPR24, arxiv 2404.05231): MVTec AD few-shot I-AUROC 96.6 (prompt learning for few-shot AD) [基於提示學習]</t>
         </is>
       </c>
       <c r="N71" s="14" t="inlineStr">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>Self-supervised CutPaste 增強：剪下貼上模擬缺陷；早期合成異常代表作 [基於資料擴增]</t>
+          <t>⚠️ CutPaste (CVPR 2021) — MVTec AD I-AUROC 96.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="M73" s="16" t="inlineStr">
         <is>
-          <t>首個多類別統一模型；Layer-wise Query Decoder + Neighbor-masked Attention 防 identical shortcut [基於重構]</t>
+          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): MVTec AD multi-class I-AUROC 96.5 (unified one-model-for-all transformer reconstruction) [基於重構]</t>
         </is>
       </c>
       <c r="N73" s="17" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+          <t>⚠️ PatchEAD (arXiv preprint 2025) — MVTec AD I-AUROC 96.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="M75" s="22" t="inlineStr">
         <is>
-          <t>首個將 normalizing flow 應用於異常檢測；feature density estimation [基於 NF]</t>
+          <t>✅ verified (DifferNet WACV21, arxiv 2008.12577): MVTec AD I-AUROC 94.9 (normalizing-flow density estimation on features) [基於 NF]</t>
         </is>
       </c>
       <c r="N75" s="23" t="inlineStr">
@@ -20960,7 +20960,7 @@
       </c>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+          <t>⚠️ AA-CLIP (Anomaly-Aware CLIP) (CVPR 2025 (CVF Open Access) / arXiv 2503.06661) — MVTec AD I-AUROC 92.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
@@ -21037,7 +21037,7 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>Bosch Research；多類型 zero-shot AD：依異常類型分支 prompt + 多任務分割 [基於表徵]</t>
+          <t>⚠️ MultiADS (Multi-Type Zero-Shot AD) (ICCV 2025 (CVF Open Access) / arXiv 2504.06740) — MVTec AD I-AUROC 92.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>Window-based CLIP zero-shot/few-shot；compositional language prompts；零樣本 91.8 / 85.1 [基於表徵]</t>
+          <t>✅ verified (WinCLIP CVPR23, arxiv 2303.14814): MVTec AD zero-shot I-AUROC 91.8 (window-based CLIP zero-/few-shot) [基於 VLM/CLIP]</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>Object-agnostic prompt learning；學習通用異常 prompts；零樣本 MVTec I=91.5 P=91.1 [基於表徵]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24, arxiv 2310.18961): MVTec AD zero-shot I-AUROC 91.5 (object-agnostic prompt learning) [基於 VLM/CLIP]</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
@@ -21268,7 +21268,7 @@
       </c>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>CLIP + 額外線性層映射到聯合嵌入空間；VAND 2023 zero-shot 第一名 [基於表徵]</t>
+          <t>✅ verified (April-GAN CVPR23 VAND challenge, arxiv 2305.17382): MVTec AD zero-shot I-AUROC 86.1 (CLIP + linear adapters) [基於 VLM/CLIP]</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="M81" s="22" t="inlineStr">
         <is>
-          <t>金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
+          <t>⚠️ PyramidFlow (CVPR23, arxiv 2303.02595) 主要報告 pixel-level 定位指標 (P-AUROC/AUPRO)，image-level I-AUROC 在原 paper 非主要指標，故此處 N/A。若需 I-AUROC 數值需查 paper 補充表或第三方 benchmark。 | 金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
         </is>
       </c>
       <c r="N81" s="23" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>結構化原型聚合 + 邏輯異常檢測；MVTec LOCO 96.1% / MVTec AD 98.9% / VisA 97.9% [基於重構]</t>
+          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — MVTec LOCO I-AUROC 96.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>MVTec LOCO 為主：I-AUROC 95.3 (logical 96.7 / structural 94.0)；latency 8.9ms / 321.8 FPS；Foundation model 自動標註 + Patch Histogram + LGST [基於表徵]</t>
+          <t>✅ verified (CSAD arxiv 2408.15628): MVTec LOCO avg I-AUROC 95.3 (component segmentation) [基於組件分割]</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -22807,7 +22807,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>Few-shot 部件分割揭示組合邏輯；3 個記憶體 (類別直方圖 / 組成嵌入 / patch-level)；MVTec LOCO logical 大幅提升 +8.5 avg [基於表徵]</t>
+          <t>✅ verified (PSAD AAAI24, arxiv 2312.13783): MVTec LOCO avg I-AUROC 91.4 (few-shot part segmentation) [基於組件分割]</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>Patch Description Network + S-T + AE；2ms 低延遲、614 FPS [基於表徵]</t>
+          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): MVTec LOCO avg I-AUROC 90.7 [基於學生-教師]</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -22961,7 +22961,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>Component-aware AD：以無監督分割將影像拆解為組件，分組件做特徵記憶；MVTec LOCO 邏輯 88.8 [基於表徵]</t>
+          <t>✅ verified (ComAD arxiv 2303.08730 — component-aware): MVTec LOCO avg I-AUROC 88.8 [基於組件分割]</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>Vision-Language Model 生成問題進行邏輯判斷；MVTec LOCO 邏輯 I=87.6 / F1-max=87.0 [基於表徵]</t>
+          <t>⚠️ LogicQA (VLM Logical AD) (ACL 2025 Industry Track / arXiv 2503.20252) — MVTec LOCO I-AUROC 87.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>Set Features：將每張影像視為 patch 集合做密度估計；MVTec LOCO 邏輯 86.8 [基於重構]</t>
+          <t>✅ verified (SINBAD ICML23, arxiv 2302.12245): MVTec LOCO logical I-AUROC 86.8 (set features) [基於全域上下文]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>非對稱 S-T：NF teacher + FFN student；強迫異常下兩者輸出發散；MVTec LOCO 邏輯 86.0 [基於重構]</t>
+          <t>✅ verified (AST WACV23, arxiv 2210.07829): MVTec LOCO avg I-AUROC 86.0 [基於學生-教師]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>原始 MVTec LOCO benchmark：Global Context AE + Local AE；structural+logical 雙分支 [基於重構]</t>
+          <t>✅ verified (GCAD IJCV22 — MVTec LOCO 原始 benchmark paper, Bergmann et al.): LOCO avg I-AUROC 80.2 (global-local) [基於全域上下文]</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>Reverse Distillation 反向知識蒸餾；T-S encoder-decoder 重構特徵 [基於重構]</t>
+          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MVTec LOCO avg I-AUROC 77.6 [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>Training-free Universal Visual AD：跨域不訓練即可推論；MVTec 97.8% / VisA 93.5% / MVTec LOCO 71.0% [基於表徵]</t>
+          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — MVTec LOCO I-AUROC 71.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec LOCO avg I-AUROC 69.0 (struggles on logical anomalies) [基於記憶庫]</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>VAND 3.0 Track 1 第一名；MVTec AD 2 (P-AP=SegF1 priv 53.81 / mix 51.43)；其他方法 AU-PRO &lt;60% [基於表徵]</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N4" s="29" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>VAND 3.0 Track 1 第二名；Swin-Cropping + INP-Former + SAM；MVTec AD 2 ClassF1=79.62 / SegF1=51.00 / AucPro=67.25 (priv)；mix 79.86/46.52/59.65 [基於表徵]</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>完全訓練-free DINOv2 特徵匹配；MVTec AD 2 ClassF1=70.2 / SegF1=47.18 / AucPro=60.51 (priv)；mix 74.4/42.51/58.37 [基於表徵]</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -24291,7 +24291,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>INP-Former 在 MVTec AD 2 SegF1 priv 21.8 (RoBiS baseline 起點，後續被 RoBiS+SAM 拉到 51.0) [基於表徵]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 EfficientAD SegF1 priv ≈16.9；速度仍維持 614 FPS [基於表徵]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 DDAD SegF1 priv ≈15.6；條件式擴散 baseline [基於擴散]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 RD4AD SegF1 priv ≈14.2；經典反向蒸餾 baseline [基於重構]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 PatchCore SegF1 priv ≈13.4；舊基準在 AD2 表現大幅下降 [基於表徵]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 DRAEM SegF1 priv ≈12.5；資料擴增類在 AD2 表現受限 [基於資料擴增]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>MVTec AD 2 paper 報告 SimpleNet SegF1 priv ≈11.8 [基於表徵]（近似值來自 AD 2 paper baseline 表）</t>
+          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>Dinomaly 強化版：DINOv2 ViT-S/B/L Encoder + ViT decoder 重構；MVTec/VisA/MPDD 同時 SOTA；ViT-S 153.6 FPS [基於重構]</t>
+          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — VisA I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>Global+Local 自適應擴散；每樣本預測去噪步驟、空間自適應特徵融合 [基於擴散]</t>
+          <t>✅ verified (GLAD ECCV24, arxiv 2406.07487): VisA I-AUROC 99.2 (global-local diffusion) [基於擴散]</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Conditioned Denoising Diffusion；以 target image 條件化去噪 + 域適應 [基於擴散]</t>
+          <t>✅ verified (DDAD BMVC24, arxiv 2305.15956): VisA I-AUROC 98.9 [基於擴散]</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -25265,7 +25265,7 @@
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Global+Local Anomaly Synthesis；梯度上升+截斷投影的近分布異常 [基於資料擴增]</t>
+          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): VisA I-AUROC 98.8 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>Norm-guided 單步去噪 + 重構+分割子網 [基於擴散]</t>
+          <t>✅ verified (DiffusionAD TPAMI25, arxiv 2303.08730): VisA I-AUROC 98.8 [基於擴散]</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>Universal AD：以 Intrinsic Normal Prototypes 統一單類/多類/少樣本/zero-shot [基於表徵]</t>
+          <t>⚠️ INP-Former++ (arXiv preprint 2025) — VisA I-AUROC 98.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
+          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): VisA multi-class I-AUROC 98.7 [基於重構]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="M11" s="19" t="inlineStr">
         <is>
-          <t>Continual Diffusion + Gradient Projection；MVTec/VisA 17/18 設定第一 [基於擴散]</t>
+          <t>⚠️ One-for-More (Continual Diffusion) (CVPR 2025) — VisA I-AUROC 98.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>Intrinsic Normal Prototypes：以單張測試影像的內部正常 token 線性組合做 reconstruction guide [基於重構]</t>
+          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): VisA I-AUROC 98.5 [基於表徵]</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>可微分特徵匹配；以可微 nearest-neighbor 直接優化匹配權重做 AD [基於表徵]</t>
+          <t>⚠️ DFM (Differentiable Feature Matching) (CVPR 2025 (CVF Open Access)) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Diffusion-based 少樣本異常驅動生成；分類+分割兩任務一致提升 [基於資料擴增]</t>
+          <t>⚠️ AnoGen (Few-Shot Anomaly-Driven Generation) (ECCV 2024 / arXiv 2025) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>Reconstruction-Free：在 latent space 直接以 likelihood 評分；無需顯式重構 [基於擴散]</t>
+          <t>⚠️ InvAD-Diff (Inversion-based Diffusion) (arXiv preprint / CVPR 2026 投稿中) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Agentic Reinforcement Learning 合成；多輪推理 + 工具使用 + 環境回饋 [基於資料擴增]</t>
+          <t>⚠️ AnomalyAgent (Agentic RL Synthesis) (arXiv preprint 2026) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>MIF 多模態融合 + DDF 動態擴散；多源 X-embedding 增強合成 [基於擴散]</t>
+          <t>⚠️ AnomalyXFusion (Multi-modal Diffusion) (arXiv preprint 2024) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="M19" s="19" t="inlineStr">
         <is>
-          <t>Transparency-based 擴散；異常區域透明度漸增重構 [基於擴散]</t>
+          <t>✅ verified (TransFusion ECCV24, arxiv 2311.09999): VisA I-AUROC 98.5 [基於擴散]</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>雙互關擴散 anomaly+mask 同步生成；下游 AD 大幅提升 [基於資料擴增]</t>
+          <t>⚠️ Dual-Interrelated Diffusion (DualAnoDiff) (CVPR 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
-          <t>雙學生 (Encoder-Decoder + Encoder-Encoder) + DINOv2 知識蒸餾；Noisy-OR 聯合學習 [基於重構]</t>
+          <t>⚠️ Generalist Multi-Class AD (Dual-Student) (arXiv preprint 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr">
@@ -26410,7 +26410,7 @@
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>MoE Feature Decompression；統一 9 個資料集 / 12 模態 / 66 類別 [基於表徵]</t>
+          <t>⚠️ UniMMAD (MoE Multi-Modal AD) (arXiv preprint 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="M23" s="19" t="inlineStr">
         <is>
-          <t>Schrödinger Bridge 擴散：在端點分布之間直接學習映射；無監督 AD 重構 [基於擴散]</t>
+          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR 2025 (CVF Open Access)) — VisA I-AUROC 98.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Spatially-Grounded Diffusion；per-pixel 語意條件 + Gated Self-Attention 注入 [基於資料擴增]</t>
+          <t>⚠️ GroundingAnomaly (Spatial Diffusion) (arXiv preprint 2026) — VisA I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>GAN+Diffusion 混合異常合成；參考圖+depth-edge 條件控制保留結構與真實感 [基於資料擴增]</t>
+          <t>⚠️ AnomalyHybrid (GAN-Hybrid Synthesis) (CVPR 2025 SyntaGen Workshop (CVF Open Access)) — VisA I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>Patch Description Network + S-T + AE；2ms 低延遲、614 FPS [基於表徵]</t>
+          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): VisA I-AUROC 98.1 [基於學生-教師]</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>Self-Navigated 殘差 Mamba：以 inter/intra-residual 自參考學習；MVTec AD/3D/VisA SOTA [基於重構]</t>
+          <t>⚠️ SNARM (Self-Navigated Residual Mamba) (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr">
@@ -26872,7 +26872,7 @@
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>兩階段訓練：大規模規則合成預訓 + 小規模生成式微調；DRAEM 風格 Perlin 加入 [基於資料擴增]</t>
+          <t>⚠️ Effective Synthetic Images (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Segmentation-oriented 工業異常合成；分級擴散 + explicit mask 對齊 [基於資料擴增]</t>
+          <t>⚠️ STAGE (Graded Diffusion + Mask Alignment) (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>結構化原型聚合 + 邏輯異常檢測；MVTec LOCO 96.1% / MVTec AD 98.9% / VisA 97.9% [基於重構]</t>
+          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — VisA I-AUROC 97.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr">
@@ -27103,7 +27103,7 @@
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>Adaptive Mask Inpainting；自適應遮罩重構正常區域、近 100% AUROC 多類 [基於重構]</t>
+          <t>⚠️ AMI-Net (IEEE TASE 2024) — VisA I-AUROC 97.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>Strength-controllable Diffusion Anomaly Synthesis (SDAS) + AFS + RRS [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): VisA I-AUROC 97.8 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
@@ -27257,7 +27257,7 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>Model-agnostic 真實感異常生成；TrueSkill 與真實圖差距 &lt; 0.28 [基於資料擴增]</t>
+          <t>⚠️ MIRAGE (Realistic Anomaly Generation) (arXiv preprint 2026) — VisA I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -27334,7 +27334,7 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>Inpainting Diffusion；視覺檢測導向的真實感缺陷生成 [基於資料擴增]</t>
+          <t>⚠️ DefectFill (Inpainting Diffusion) (arXiv preprint 2025) — VisA I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="M35" s="22" t="inlineStr">
         <is>
-          <t>Pyramid Mamba 多類異常；以 SSM 結合 NF 思想做密度估計 [基於 NF]</t>
+          <t>⚠️ Pyramid-based Mamba NF (arXiv preprint 2025) — VisA I-AUROC 97.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): VisA I-AUROC 97.5 [基於表徵]</t>
         </is>
       </c>
       <c r="N36" s="17" t="inlineStr">
@@ -27565,7 +27565,7 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>完全 training-free 工業缺陷生成；擴散去除訓練成本 [基於擴散]</t>
+          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV 2025) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>未見類異常生成：以 SD + attention guidance 對任何類別生成新型異常 [基於資料擴增]</t>
+          <t>⚠️ AnomalyAny (Unseen Visual Anomaly Generation) (CVPR 2025 (CVF Open Access) / arXiv 2406.01078) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
@@ -27719,7 +27719,7 @@
       </c>
       <c r="M39" s="22" t="inlineStr">
         <is>
-          <t>統一 NF；多類別異常檢測；MVTec AD I=99.1% / P=98.0%，含 VisA/BTAD [基於 NF]</t>
+          <t>⚠️ UniFlow (Unified NF) (MDPI Information 2024) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
@@ -27796,7 +27796,7 @@
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>LMM 視覺語言三角推理；以多模態大模型輔助工業異常推理判斷 [基於表徵]</t>
+          <t>⚠️ Triad (LMM-Aided AD) (ICCV 2025 (CVF Open Access) / arXiv 2503.13184) — VisA I-AUROC 97.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>對抗強健工業異常擴散；對抗性樣本下仍保持 SOTA 偵測能力 [基於擴散]</t>
+          <t>⚠️ Adversarially Robust Diffusion AD (arXiv preprint 2024) — VisA I-AUROC 97.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -27950,7 +27950,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>Reverse Distillation 反向知識蒸餾；T-S encoder-decoder 重構特徵 [基於重構]</t>
+          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): VisA I-AUROC 96.0 [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -28027,7 +28027,7 @@
       </c>
       <c r="M43" s="16" t="inlineStr">
         <is>
-          <t>GAN inversion 啟發的特徵反演重構；多類別統一模型 + COCO-AD benchmark [基於重構]</t>
+          <t>⚠️ InvAD (Feature Inversion) (arXiv preprint 2024) — VisA I-AUROC 95.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N43" s="17" t="inlineStr">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): VisA I-AUROC 95.1 [基於記憶庫]</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
@@ -28181,7 +28181,7 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>視覺基礎模型最近鄰搜尋；1-shot SOTA：MVTec 97.4% / VisA 94.8% [基於表徵]</t>
+          <t>⚠️ VisionAD (Search Is All You Need) (arXiv preprint 2025) — VisA I-AUROC 94.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N45" s="14" t="inlineStr">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>CLIP few-shot AD：以 rare class prompting；MVTec 98.2% / VisA 94.4%；latency ≈ 59.4ms [基於表徵]</t>
+          <t>⚠️ RareCLIP (ICCV 2025 (CVF Open Access)) — VisA I-AUROC 94.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -28335,7 +28335,7 @@
       </c>
       <c r="M47" s="16" t="inlineStr">
         <is>
-          <t>首個將 Mamba State Space Model 應用於多類異常檢測；LSS 模組+HSS block 八向掃描 [基於重構]</t>
+          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): VisA multi-class I-AUROC 94.3 [基於重構]</t>
         </is>
       </c>
       <c r="N47" s="17" t="inlineStr">
@@ -28412,7 +28412,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>DINOv2 patch-based few-shot；無需訓練 / fine-tune，1-shot SOTA 96.6% [基於表徵]</t>
+          <t>✅ verified (AnomalyDINO WACV25, arxiv 2405.14529): VisA I-AUROC 94.0 [基於基礎模型]</t>
         </is>
       </c>
       <c r="N48" s="14" t="inlineStr">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>Training-free Universal Visual AD：跨域不訓練即可推論；MVTec 97.8% / VisA 93.5% / MVTec LOCO 71.0% [基於表徵]</t>
+          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — VisA I-AUROC 93.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N49" s="14" t="inlineStr">
@@ -28566,7 +28566,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>Zero-shot 互評分機制；未標註測試集內相互打分 [基於表徵]</t>
+          <t>✅ verified (MuSc ICLR24, arxiv 2401.16753): VisA training-free I-AUROC 92.8 [基於零樣本]</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>階層式向量量化 Transformer；多類別統一模型，以離散原型重構 [基於重構]</t>
+          <t>✅ verified (HVQ-Trans NeurIPS23, arxiv 2310.14228): VisA multi-class I-AUROC 91.3 [基於重構]</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>Patch-Exclusive AD：統一視覺 prompting；few-shot 96% I-AUROC [基於表徵]</t>
+          <t>⚠️ PatchEAD (arXiv preprint 2025) — VisA I-AUROC 89.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N52" s="14" t="inlineStr">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>Memory-bank baseline；VisA 多類 I=89.1 / P=98.1 [基於表徵]</t>
+          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): VisA I-AUROC 89.1 [基於表徵]</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>Few-shot prompt learning；VisA 4-shot 89.1/97.4 (1-shot 86.9/96.7) [基於表徵]</t>
+          <t>✅ verified (PromptAD CVPR24, arxiv 2404.05231): VisA few-shot I-AUROC 89.1 [基於提示學習]</t>
         </is>
       </c>
       <c r="N54" s="14" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>去噪學生-教師 + 分割網路；整合合成異常 [基於資料擴增]</t>
+          <t>✅ verified (DeSTSeg CVPR23, arxiv 2211.11317): VisA I-AUROC 88.9 [基於學生-教師]</t>
         </is>
       </c>
       <c r="N55" s="17" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>多類別統一模型；VisA 多類設定 I=88.8 / P=98.3 [基於重構]</t>
+          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): VisA multi-class I-AUROC 88.8 [基於重構]</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
-          <t>Perlin 噪聲 + DTD 紋理合成缺陷 + 重構 + 判別網路 [基於資料擴增]</t>
+          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): VisA I-AUROC 88.7 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -29182,7 +29182,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>Feature Adapter + 高斯噪聲特徵偽造 + 判別器；77 FPS [基於表徵]</t>
+          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): VisA I-AUROC 87.2 [基於表徵]</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="M59" s="19" t="inlineStr">
         <is>
-          <t>Difference-Aware Diffusion；VisA 多類 I=86.8 / P=96.0 [基於擴散]</t>
+          <t>✅ verified (DiAD AAAI24, arxiv 2312.06607): VisA multi-class I-AUROC 86.8 [基於擴散]</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>Bosch Research；多類型 zero-shot AD：依異常類型分支 prompt + 多任務分割 [基於表徵]</t>
+          <t>⚠️ MultiADS (Multi-Type Zero-Shot AD) (ICCV 2025 (CVF Open Access) / arXiv 2504.06740) — VisA I-AUROC 86.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N60" s="14" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AA-CLIP：兩階段 anomaly-aware adapter；zero-shot pixel-AUROC 93.4% [基於表徵]</t>
+          <t>⚠️ AA-CLIP (Anomaly-Aware CLIP) (CVPR 2025 (CVF Open Access) / arXiv 2503.06661) — VisA I-AUROC 85.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>Object-agnostic prompt learning；VisA zero-shot 82.1/95.5；AP=85.4 [基於表徵]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24, arxiv 2310.18961): VisA zero-shot I-AUROC 82.1 [基於 VLM/CLIP]</t>
         </is>
       </c>
       <c r="N62" s="14" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>Window-based CLIP zero-shot；VisA zero-shot 78.1/79.6；few-shot WinCLIP+ 1-shot 83.8/96.4 [基於表徵]</t>
+          <t>✅ verified (WinCLIP CVPR23, arxiv 2303.14814): VisA zero-shot I-AUROC 78.1 [基於 VLM/CLIP]</t>
         </is>
       </c>
       <c r="N63" s="14" t="inlineStr">
@@ -30770,7 +30770,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>Dinomaly 強化版：DINOv2 ViT-S/B/L Encoder + ViT decoder 重構；MVTec/VisA/MPDD 同時 SOTA；ViT-S 153.6 FPS [基於重構]</t>
+          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — MPDD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -30847,7 +30847,7 @@
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Global+Local Anomaly Synthesis；梯度上升+截斷投影的近分布異常 [基於資料擴增]</t>
+          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): MPDD I-AUROC 99.0 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -30924,7 +30924,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Strength-controllable Diffusion Anomaly Synthesis (SDAS) + AFS + RRS [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): MPDD I-AUROC 96.3 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Norm-guided 單步去噪 + 重構+分割子網 [基於擴散]</t>
+          <t>✅ verified (DiffusionAD TPAMI25, arxiv 2303.08730): MPDD I-AUROC 95.9 [基於擴散]</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MPDD I-AUROC 94.5 [基於記憶庫]</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Perlin 噪聲 + DTD 紋理合成缺陷 + 重構 + 判別網路 [基於資料擴增]</t>
+          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): MPDD I-AUROC 94.1 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>Reverse Distillation 反向知識蒸餾；T-S encoder-decoder 重構特徵 [基於重構]</t>
+          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MPDD I-AUROC 92.7 [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>Feature Adapter + 高斯噪聲特徵偽造 + 判別器；77 FPS [基於表徵]</t>
+          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): MPDD I-AUROC 90.6 [基於表徵]</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>條件式 normalizing flow，以位置編碼為條件；即時檢測 [基於 NF]</t>
+          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): MPDD I-AUROC 86.1 [基於 NF]</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>Memory bank baseline；MPDD I-AUROC 74.8% [基於表徵]</t>
+          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): MPDD I-AUROC 74.8 [基於表徵]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -32481,7 +32481,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>S-T + bottleneck + 領域特徵選擇 + 對比學習；統一工業/醫療/影片 12 資料集 (industrial: MVTec AD/BTAD/MVTec 3D-AD) [基於表徵]</t>
+          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — BTAD I-AUROC 97.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -32558,7 +32558,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>DINOv2 ViT encoder-decoder 重構；BTAD 多類 I=96.7 [基於重構]</t>
+          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): BTAD I-AUROC 96.7 [基於重構]</t>
         </is>
       </c>
       <c r="N5" s="17" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Strength-controllable Diffusion Anomaly Synthesis (SDAS) + AFS + RRS [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): BTAD I-AUROC 96.1 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t>金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
+          <t>✅ verified (PyramidFlow CVPR23, arxiv 2303.02595): BTAD I-AUROC 95.8 [基於 NF]</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -32789,7 +32789,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>RD4AD 加入 pseudo-anomalies + projection layers；6× PatchCore 速度 [基於表徵]</t>
+          <t>✅ verified (RD++ CVPR23, arxiv 2304.12433): BTAD I-AUROC 95.6 [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N8" s="17" t="inlineStr">
@@ -32866,7 +32866,7 @@
       </c>
       <c r="M9" s="16" t="inlineStr">
         <is>
-          <t>Mamba SSM 多類異常；BTAD 多類設定 I=95.6 [基於重構]</t>
+          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): BTAD I-AUROC 95.6 [基於重構]</t>
         </is>
       </c>
       <c r="N9" s="17" t="inlineStr">
@@ -32943,7 +32943,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): BTAD I-AUROC 95.1 [基於表徵]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -33020,7 +33020,7 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>2D 卷積 NF；ResNet/ViT 任意 backbone；BTAD I=95.0 / P=97.5 [基於 NF]</t>
+          <t>✅ verified (FastFlow arxiv 2111.07677): BTAD I-AUROC 95.0 [基於 NF]</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
@@ -33097,7 +33097,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>多類別統一模型；BTAD 3 類別平均 I=94.5 / P=97.6 [基於重構]</t>
+          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): BTAD multi-class I-AUROC 94.5 [基於重構]</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -33174,7 +33174,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>BTAD 原始 benchmark 論文；ViT + GMM density network；BTAD PRO=90.0 [基於重構]</t>
+          <t>✅ verified (VT-ADL ISIE21 — BTAD 原始 benchmark paper): BTAD I-AUROC 94.5 [基於重構]</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -33251,7 +33251,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>Feature Adapter + 高斯噪聲特徵偽造 + 判別器；BTAD I=94.1 [基於表徵]</t>
+          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): BTAD I-AUROC 94.1 [基於表徵]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -33328,7 +33328,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>Memory bank baseline；BTAD I=94.0 / P=97.0 [基於表徵]</t>
+          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): BTAD I-AUROC 94.0 [基於表徵]</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): BTAD I-AUROC 93.1 [基於記憶庫]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Perlin 噪聲 + DTD 紋理合成 + 重構 + 判別網路；BTAD I=93.1 [基於資料擴增]</t>
+          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): BTAD I-AUROC 93.1 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>Conditional NF + 位置編碼為條件；BTAD I=92.9 [基於 NF]</t>
+          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): BTAD I-AUROC 92.9 [基於 NF]</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -34520,7 +34520,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>RGB-3D 跨模態特徵映射；以 RGB→3D 與 3D→RGB 雙向蒸餾學異常；MVTec 3D-AD SOTA I=98.5 [基於表徵]</t>
+          <t>✅ verified (CFM CVPR24, arxiv 2312.04521): MVTec 3D-AD I-AUROC 98.5 (RGB+3D crossmodal mapping) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -34597,7 +34597,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>Dinomaly 強化版於 RGB-3D 也達 SOTA；統一框架 industrial/biological/multi-modal [基於重構]</t>
+          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 / 2510.17611) — MVTec 3D I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N5" s="17" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>S-T + bottleneck + 領域特徵選擇 + 對比學習；統一工業/醫療/影片 12 資料集 (industrial: MVTec AD/BTAD/MVTec 3D-AD) [基於表徵]</t>
+          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — MVTec 3D I-AUROC 95.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -34751,7 +34751,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>互補偽多模態特徵；結合手工 PCD 描述子與預訓 2D NN；多視角 RGB 投影融合 [基於表徵]</t>
+          <t>✅ verified (CPMF PR24, arxiv 2303.13194): MVTec 3D-AD I-AUROC 95.2 (pseudo-multimodal) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>Shape-Guided 雙專家 + 雙記憶體 (color expert + shape expert)；ICML 2023 3D-AD [基於表徵]</t>
+          <t>✅ verified (Shape-Guided ICML23, arxiv 2306.07789): MVTec 3D-AD I-AUROC 94.7 (dual-memory expert) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>M3DM 雜訊穩健版：以多模態去雜訊處理 noisy 訓練集 [基於表徵]</t>
+          <t>✅ verified (M3DM-NR arxiv 2406.02263): MVTec 3D-AD I-AUROC 94.6 (noise-resistant multimodal) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>Multi-modal Memory Bank + 點雲對齊 + Patch-wise 對比學習；RGB-3D 異常檢測 [基於表徵]</t>
+          <t>✅ verified (M3DM CVPR23, arxiv 2303.00601): MVTec 3D-AD I-AUROC 94.5 (multimodal hybrid fusion) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>非對稱 S-T (NF teacher + FFN student)；MVTec 3D-AD RGB-only 設定 SOTA [基於重構]</t>
+          <t>✅ verified (AST WACV23, arxiv 2210.07829): MVTec 3D-AD I-AUROC 93.7 (RGB+depth asymmetric S-T) [基於學生-教師]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>輕量易部署網路：無需 pretrained / memory bank；多模態異常分割；快速推論 [基於重構]</t>
+          <t>✅ verified (EasyNet ACM MM23, arxiv 2307.13925): MVTec 3D-AD I-AUROC 92.4 (no pretrain, multimodal) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -35213,7 +35213,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>領域特定對比式重構；緩解pretrained feature bias [基於重構]</t>
+          <t>⚠️ ReContrast (NeurIPS23, arxiv 2306.02602) 原 paper 在 2D MVTec AD/VisA 評估；MVTec 3D-AD 88.6 為 RGB-only 設定（非原 paper 主要結果，可能來自第三方/後續評估）。需確認來源後才能標 ✅ [基於表徵]</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>Back to the Feature：經典 3D 手工特徵 + Color；強調 rotation invariance；MVTec 3D-AD 早期 SOTA [基於表徵]</t>
+          <t>✅ verified (BTF CVPRW23, arxiv 2203.05550): MVTec 3D-AD I-AUROC 86.5 (handcrafted FPFH+color) [基於多模態融合]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -35367,7 +35367,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>Memory Bank coreset + 最近鄰匹配；產業標準 baseline [基於表徵]</t>
+          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec 3D-AD RGB-only I-AUROC 81.1 (RGB baseline) [基於記憶庫]</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15280,7 +15280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -15966,10 +15966,8 @@
           <t>98.5</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J11" s="15" t="n">
+        <v>71</v>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
@@ -15983,7 +15981,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): MVTec AD I-AUROC 99.7 (intrinsic normal prototypes) [基於表徵]</t>
+          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): MVTec AD I-AUROC 99.7 (intrinsic normal prototypes) [基於表徵] （P-AP 已併自 CVF 重複條目「Exploring Intrinsic Normal Prototypes…」；該重複條目已刪除）</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -21951,7 +21949,7 @@
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
@@ -21975,26 +21973,28 @@
         </is>
       </c>
       <c r="H91" s="21" t="n">
-        <v>99.7</v>
+        <v>92.3</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>98.5</v>
+        <v>91.8</v>
       </c>
       <c r="J91" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="K91" s="21" t="n">
-        <v>94.90000000000001</v>
+        <v>48.3</v>
+      </c>
+      <c r="K91" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：Intrinsic Normal Prototypes 單張影像內提取；ViT-B/14 DINOv2 [基於重構]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
@@ -22011,12 +22011,12 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -22040,13 +22040,17 @@
         </is>
       </c>
       <c r="H92" s="21" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="I92" s="21" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="J92" s="21" t="n">
-        <v>48.3</v>
+        <v>99.17</v>
+      </c>
+      <c r="I92" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K92" s="21" t="inlineStr">
         <is>
@@ -22056,12 +22060,12 @@
       <c r="L92" s="21" t="n"/>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：Bayesian Prompt Flow Learning；多模態 prompt distribution [基於 VLM]</t>
+          <t>✅ 已驗證 (SSASDM WACV25 Table 2)：DTU-Net 自監督擴散+動態 Transformer UNet；MVTec AD 15-class avg AUROC 99.17 [基於擴散自監督]</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
@@ -22078,12 +22082,12 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
@@ -22107,7 +22111,7 @@
         </is>
       </c>
       <c r="H93" s="21" t="n">
-        <v>99.17</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -22127,12 +22131,12 @@
       <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (SSASDM WACV25 Table 2)：DTU-Net 自監督擴散+動態 Transformer UNet；MVTec AD 15-class avg AUROC 99.17 [基於擴散自監督]</t>
+          <t>✅ 已驗證 (ADL WACV25 Table 1, 10% contamination)：Adaptive Deviation Learning under contaminated data；MVTec AD avg AUROC 0.924 [基於監督式 + Noisy normal]</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
@@ -22149,17 +22153,17 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
@@ -22174,36 +22178,26 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H94" s="21" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I94" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J94" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K94" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>98.83</v>
+      </c>
+      <c r="I94" s="21" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="J94" s="21" t="n"/>
+      <c r="K94" s="21" t="n"/>
       <c r="L94" s="21" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ADL WACV25 Table 1, 10% contamination)：Adaptive Deviation Learning under contaminated data；MVTec AD avg AUROC 0.924 [基於監督式 + Noisy normal]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
@@ -22220,27 +22214,27 @@
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>ROADS</t>
+          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Hossein Kashiani, et al.</t>
+          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>arXiv preprint</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
@@ -22249,96 +22243,35 @@
         </is>
       </c>
       <c r="H95" s="21" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I95" s="21" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J95" s="21" t="n"/>
-      <c r="K95" s="21" t="n"/>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K95" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
+          <t>✅ 已驗證 (IndusAgent arXiv2605 Table 1, zero-shot)：MLLM Agentic Tools 工業異常檢測；MVTec 83.6 分類分數 (paper 自家數字 — MLLM yes/no 分類，非標準 AUROC，較難跟非 MLLM 方法直接比) [基於 MLLM Agent]</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O95" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="21" t="inlineStr">
-        <is>
-          <t>MVTec AD</t>
-        </is>
-      </c>
-      <c r="B96" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C96" s="21" t="inlineStr">
-        <is>
-          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
-        </is>
-      </c>
-      <c r="D96" s="21" t="inlineStr">
-        <is>
-          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
-        </is>
-      </c>
-      <c r="E96" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="G96" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L96" s="21" t="n"/>
-      <c r="M96" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (IndusAgent arXiv2605 Table 1, zero-shot)：MLLM Agentic Tools 工業異常檢測；MVTec 83.6 分類分數 (paper 自家數字 — MLLM yes/no 分類，非標準 AUROC，較難跟非 MLLM 方法直接比) [基於 MLLM Agent]</t>
-        </is>
-      </c>
-      <c r="N96" s="23" t="inlineStr">
-        <is>
           <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
-      <c r="O96" s="23" t="n"/>
+      <c r="O95" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -24870,7 +24803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25700,10 +25633,8 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J13" s="15" t="n">
+        <v>51.2</v>
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
@@ -25717,7 +25648,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): VisA I-AUROC 98.5 [基於表徵]</t>
+          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): VisA I-AUROC 98.5 [基於表徵] （P-AP 已併自 CVF 重複條目「Exploring Intrinsic Normal Prototypes…」，該條目多類別設定報 I=98.9；重複條目已刪除）</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -30240,7 +30171,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Exploring Intrinsic Normal Prototypes within a Single Image</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -30264,26 +30195,28 @@
         </is>
       </c>
       <c r="H74" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>29.8</v>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L74" s="12" t="n"/>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (INP-Former CVPR25 Table 2 multi-class)：[基於重構]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Luo_Exploring_Intrinsic_Normal_Prototypes_within_a_Single_Image_for_Universal_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
@@ -30305,7 +30238,7 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -30315,12 +30248,12 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -30329,13 +30262,17 @@
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>29.8</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
         <is>
@@ -30345,12 +30282,12 @@
       <c r="L75" s="12" t="n"/>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>✅ 已驗證 (ADL WACV25 Table 1 VisA, 10% contamination)：Adaptive Deviation Learning under contaminated data；VisA avg AUROC 0.844 [基於監督式 + Noisy normal]</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
@@ -30367,17 +30304,17 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -30392,100 +30329,29 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J76" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>95.42</v>
+      </c>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n">
+        <v>92.27</v>
       </c>
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ADL WACV25 Table 1 VisA, 10% contamination)：Adaptive Deviation Learning under contaminated data；VisA avg AUROC 0.844 [基於監督式 + Noisy normal]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>ROADS</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>Hossein Kashiani, et al.</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I77" s="12" t="n"/>
-      <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="L77" s="12" t="n"/>
-      <c r="M77" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
-        </is>
-      </c>
-      <c r="N77" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O77" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15280,7 +15280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22272,6 +22272,59 @@
         </is>
       </c>
       <c r="O95" s="23" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>Memory-Distilled Selection for Noise-Robust Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D96" s="21" t="inlineStr">
+        <is>
+          <t>Sirojbek Safarov, Jaewoo Park, Yoon Gyo Jung, Kuan-Chuan Peng, Wonchul Kim, Seongdeok Bang, Octavia Camps</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+      <c r="J96" s="21" t="n"/>
+      <c r="K96" s="21" t="n"/>
+      <c r="L96" s="21" t="n"/>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於重構 (Reconstruction)]</t>
+        </is>
+      </c>
+      <c r="N96" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.26676</t>
+        </is>
+      </c>
+      <c r="O96" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15598,7 +15598,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — MVTec AD I-AUROC 99.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (Dinomaly2 arxiv 2510.17611 abstract+Table): MVTec AD multi-class I-AUROC 99.9 [基於重構]</t>
         </is>
       </c>
       <c r="N6" s="17" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Generalist Multi-Class AD (Dual-Student) (arXiv preprint 2025) — MVTec AD I-AUROC 99.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (Generalist Multi-Class AD arxiv 2509.24448 Table 1): MVTec AD multi-class I-AUROC 99.7 (dual-student KD) [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -16108,10 +16108,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>99.6</t>
-        </is>
+      <c r="H13" s="9" t="n">
+        <v>99.8</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -16135,7 +16133,7 @@
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Dual-Interrelated Diffusion (DualAnoDiff) (CVPR 2025) — MVTec AD I-AUROC 99.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (DualAnoDiff CVPR25 arxiv 2408.13509 Table 7): MVTec AD downstream I-AUROC 99.8 (anomaly-synthesis method; sheet had 99.6) [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
@@ -16568,10 +16566,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
+      <c r="H19" s="12" t="n">
+        <v>99.8</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
@@ -16595,7 +16591,7 @@
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>⚠️ INP-Former++ (arXiv preprint 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (INP-Former++ arxiv 2506.03660 Table III): MVTec AD multi-class I-AUROC 99.8 (sheet had 99.5 — corrected) [基於表徵]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -16672,7 +16668,7 @@
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>⚠️ One-for-More (Continual Diffusion) (CVPR 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ One-for-More (Continual Diffusion, CVPR25 arxiv 2502.19848) is a CONTINUAL-learning AD method. Paper Table 2 reports continual-setting MVTec AD I-AUROC 89.1–96.4 depending on protocol (14-1/10-5/3×5/10-1×5). Sheet value 99.5 does NOT appear in paper — likely mis-entered. Continual-setting results are NOT comparable to standard multi-class ranking. Needs reconciliation.</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -17018,10 +17014,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
+      <c r="H25" s="18" t="n">
+        <v>99.2</v>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
@@ -17045,7 +17039,7 @@
       </c>
       <c r="M25" s="19" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyXFusion (Multi-modal Diffusion) (arXiv preprint 2024) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AnomalyXFusion arxiv 2404.19444 Table 3): MVTec AD downstream AUC-I 99.2 (sheet had 99.4) [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -17316,10 +17310,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
+      <c r="H29" s="9" t="n">
+        <v>98.8</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -17343,7 +17335,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnoGen (Few-Shot Anomaly-Driven Generation) (ECCV 2024 / arXiv 2025) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AnoGen ECCV24 arxiv 2505.09263 Table 1): MVTec AD best downstream I-AUROC 98.8 (DeSTSeg+AnoGen; sheet had 99.4). Anomaly-synthesis method [基於異常生成]</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -17805,7 +17797,7 @@
       </c>
       <c r="M35" s="19" t="inlineStr">
         <is>
-          <t>⚠️ GLAD (ECCV 2024) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (GLAD ECCV24 arxiv 2406.07487 Table 1): MVTec AD I-AUROC 99.3 [基於擴散]</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -18854,10 +18846,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+      <c r="H49" s="15" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -18881,7 +18871,7 @@
       </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>⚠️ InvAD (Feature Inversion) (arXiv preprint 2024) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (InvAD arxiv 2404.10760 Table 5): MVTec AD multi-class mAU-ROC 98.9 (sheet had 99.0) [基於重構]</t>
         </is>
       </c>
       <c r="N49" s="17" t="inlineStr">
@@ -19008,10 +18998,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
+      <c r="H51" s="15" t="n">
+        <v>98.8</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -19035,7 +19023,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — MVTec AD I-AUROC 98.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (SALAD ICCV25 arxiv 2509.02101): MVTec AD I-AUROC 98.8 (sheet had 98.9) [邏輯異常]</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -19574,7 +19562,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>⚠️ Triad (LMM-Aided AD) (ICCV 2025 (CVF Open Access) / arXiv 2503.13184) — MVTec AD I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Triad (LMM-Aided AD, arxiv 2503.13184) reports ACCURACY (0-shot/1-shot), NOT I-AUROC, on MVTec-AD/WFDD/PCB-Bank. Sheet I-AUROC 98.5 is a metric mismatch — not from paper. Needs reconciliation (paper metric is accuracy, not AUROC).</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
@@ -22639,7 +22627,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — MVTec LOCO I-AUROC 96.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (SALAD ICCV25 arxiv 2509.02101): MVTec LOCO I-AUROC 96.1 (new SOTA, +3.0pp) [邏輯異常]</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -25020,7 +25008,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — VisA I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (Dinomaly2 arxiv 2510.17611 abstract): VisA multi-class I-AUROC 99.3 [基於重構]</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -25070,10 +25058,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
+      <c r="H5" s="18" t="n">
+        <v>99.5</v>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
@@ -25097,7 +25083,7 @@
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (GLAD ECCV24, arxiv 2406.07487): VisA I-AUROC 99.2 (global-local diffusion) [基於擴散]</t>
+          <t>✅ verified+corrected (GLAD ECCV24 arxiv 2406.07487 Table 3): VisA I-AUROC 99.5 (sheet had 99.2 — corrected) [基於擴散]</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -25378,10 +25364,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
+      <c r="H9" s="12" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
@@ -25405,7 +25389,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>⚠️ INP-Former++ (arXiv preprint 2025) — VisA I-AUROC 98.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (INP-Former++ arxiv 2506.03660 Table III): VisA multi-class I-AUROC 98.9 (sheet had 98.7 — corrected) [基於表徵]</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -25559,7 +25543,7 @@
       </c>
       <c r="M11" s="19" t="inlineStr">
         <is>
-          <t>⚠️ One-for-More (Continual Diffusion) (CVPR 2025) — VisA I-AUROC 98.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ One-for-More (Continual Diffusion, CVPR25 arxiv 2502.19848): paper Table 3 reports continual-setting VisA I-AUROC 83.4–88.3 (11-1/8-4/8-1×4). Sheet value 98.6 does NOT appear in paper — likely mis-entered. Continual-setting not comparable to standard ranking.</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -25855,7 +25839,7 @@
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnoGen (Few-Shot Anomaly-Driven Generation) (ECCV 2024 / arXiv 2025) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AnoGen (ECCV24 arxiv 2505.09263) evaluates ONLY on MVTec AD; does NOT report VisA. Sheet VisA 98.5 not from this paper — needs source confirmation.</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
@@ -26086,7 +26070,7 @@
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyXFusion (Multi-modal Diffusion) (arXiv preprint 2024) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AnomalyXFusion (arxiv 2404.19444) evaluates on MVTec AD + MVTec LOCO only; does NOT report VisA. Sheet VisA 98.5 not from this paper — needs source confirmation.</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -26240,7 +26224,7 @@
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Dual-Interrelated Diffusion (DualAnoDiff) (CVPR 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ DualAnoDiff (CVPR25 arxiv 2408.13509) evaluates ONLY on MVTec AD in its paper (follows AnomalyDiffusion setup); does NOT report VisA. Sheet VisA value 98.4 not from this paper — likely third-party/citing source. Needs source confirmation.</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -26290,10 +26274,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
+      <c r="H21" s="15" t="n">
+        <v>98.8</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
@@ -26317,7 +26299,7 @@
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Generalist Multi-Class AD (Dual-Student) (arXiv preprint 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (Generalist Multi-Class AD arxiv 2509.24448 Table 1): VisA multi-class I-AUROC 98.8 (sheet had 98.4) [基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr">
@@ -27010,7 +26992,7 @@
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>⚠️ SALAD (Logical AD) (ICCV 2025 (CVF Open Access) / arXiv 2509.02101) — VisA I-AUROC 97.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (SALAD ICCV25 arxiv 2509.02101): VisA I-AUROC 97.9 [邏輯異常]</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr">
@@ -27780,7 +27762,7 @@
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>⚠️ Triad (LMM-Aided AD) (ICCV 2025 (CVF Open Access) / arXiv 2503.13184) — VisA I-AUROC 97.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Triad (arxiv 2503.13184) does NOT evaluate VisA and reports accuracy (not AUROC). Sheet VisA I-AUROC 97.2 not from paper — metric/dataset mismatch.</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
@@ -28011,7 +27993,7 @@
       </c>
       <c r="M43" s="16" t="inlineStr">
         <is>
-          <t>⚠️ InvAD (Feature Inversion) (arXiv preprint 2024) — VisA I-AUROC 95.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (InvAD arxiv 2404.10760 Table 5): VisA multi-class mAU-ROC 95.5 [基於重構]</t>
         </is>
       </c>
       <c r="N43" s="17" t="inlineStr">
@@ -30689,7 +30671,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 (CVPR 2025 Dinomaly 擴展版)) — MPDD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (Dinomaly2 arxiv 2510.17611 Table II): MPDD multi-class I-AUROC 99.0 [基於重構]</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -34489,10 +34471,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+      <c r="H5" s="15" t="n">
+        <v>95</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -34516,7 +34496,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Dinomaly2 (Dinomaly Extended) (arXiv preprint 2025 / 2510.17611) — MVTec 3D I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (Dinomaly2 arxiv 2510.17611 Table IV): MVTec 3D RGB-only multi-class I-AUROC 95.0 (sheet had 97.5 — corrected) [基於重構]</t>
         </is>
       </c>
       <c r="N5" s="17" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -17489,7 +17489,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniMMAD (MoE Multi-Modal AD) (arXiv preprint 2025) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): MVTec AD AUC_I 99.4 [基於多模態/MoE]</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
@@ -17616,10 +17616,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>99.3</t>
-        </is>
+      <c r="H33" s="15" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -17643,7 +17641,7 @@
       </c>
       <c r="M33" s="16" t="inlineStr">
         <is>
-          <t>⚠️ SNARM (Self-Navigated Residual Mamba) (arXiv preprint 2025) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): MVTec AD I-AUROC 99.4 (sheet had 99.3) [基於 Mamba/NF]</t>
         </is>
       </c>
       <c r="N33" s="17" t="inlineStr">
@@ -18463,10 +18461,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>99.1</t>
-        </is>
+      <c r="H44" s="15" t="n">
+        <v>99</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -18490,7 +18486,7 @@
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>⚠️ AMI-Net (IEEE TASE 2024) — MVTec AD I-AUROC 99.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AMI-Net arxiv 2412.11802 Table I): MVTec AD multi-class I-AUROC 99.0 (AMI-Net‡ w/ feature jittering; sheet had 99.1) [基於重構]</t>
         </is>
       </c>
       <c r="N44" s="17" t="inlineStr">
@@ -24034,7 +24030,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 82.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N4" s="29" t="inlineStr">
@@ -24111,7 +24107,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 79.62 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -24188,7 +24184,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 70.2 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -24265,7 +24261,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 55.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -24342,7 +24338,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 63.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -24419,7 +24415,7 @@
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 53.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -24496,7 +24492,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 50.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -24573,7 +24569,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 52.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -24650,7 +24646,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 48.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -24727,7 +24723,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 (Heckler-Kram et al. 2025) 是 2025 新發布的高難度 benchmark；此值為 VAND 2025 challenge 排行榜或官方 baseline 數字，需對照官方 challenge leaderboard / AD2 paper 表格個別確認。</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 46.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -24798,7 +24794,7 @@
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (SuperADD CVPR2026 VAND 4.0 Workshop Table 1)：Training-free Class-agnostic；VAND 2025 Cat-1 第一名後續強化版；MVTec AD2 SegF1 priv 57.42 mix 54.35（注：metric 為 SegF1 不是 AUROC）[基於表徵]</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 57.42 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -26349,10 +26345,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
+      <c r="H22" s="12" t="n">
+        <v>95.5</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -26376,7 +26370,7 @@
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniMMAD (MoE Multi-Modal AD) (arXiv preprint 2025) — VisA I-AUROC 98.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): VisA AUC_I 95.5 (sheet had 98.4 — corrected; same table as MVTec AD 99.4) [基於多模態/MoE]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -26734,10 +26728,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
+      <c r="H27" s="15" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -26761,7 +26753,7 @@
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>⚠️ SNARM (Self-Navigated Residual Mamba) (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): VisA I-AUROC 98.1 (sheet had 98.0) [基於 Mamba/NF]</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr">
@@ -27069,7 +27061,7 @@
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>⚠️ AMI-Net (IEEE TASE 2024) — VisA I-AUROC 97.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AMI-Net (arxiv 2412.11802): VisA I-AUROC not located in fetched paper tables (paper headlines MVTec AD + BTAD). Sheet VisA 97.9 needs source confirmation.</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
@@ -33720,7 +33712,7 @@
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AMI-Net IEEE TASE24 Table II)：Adaptive Masked Inpainting；BTAD Average I=95.1 P=97.1 [基於重構]</t>
+          <t>⚠️ AMI-Net (arxiv 2412.11802 Table II) reports BTAD I-AUROC 99.9 for the AMI-Net‡ variant; sheet has 95.1 — large gap, likely base vs ‡ variant. Needs reconciliation of which variant.</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16439,7 +16439,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>⚠️ STAGE (Graded Diffusion + Mask Alignment) (arXiv preprint 2025) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ STAGE (arxiv 2509.06693) is segmentation-oriented: primary metrics mIoU / pixel-Acc, auxiliary metrics are PIXEL-level AUROC/PRO/AP. No IMAGE-level AUROC reported. Sheet I-AUROC 99.5 unverified (metric mismatch / likely pixel or downstream). Needs reconciliation.</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -17922,10 +17922,8 @@
           <t>在審</t>
         </is>
       </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>99.3</t>
-        </is>
+      <c r="H37" s="18" t="n">
+        <v>99</v>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
@@ -17949,7 +17947,7 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>⚠️ InvAD-Diff (Inversion-based Diffusion) (arXiv preprint / CVPR 2026 投稿中) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): MVTec AD multi-class I-AUROC 99.0 (sheet had 99.3). ⚠️ Note: overlaps with "InvAD (Feature Inversion)" entry (2404.10760, 98.9) — possible duplicate to review.</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
@@ -18103,7 +18101,7 @@
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>⚠️ DefectFill (Inpainting Diffusion) (arXiv preprint 2025) — MVTec AD I-AUROC 99.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (DefectFill arxiv 2503.13985 Table S2): MVTec AD downstream I-AUROC per-object 0.97-1.00 (UNet trained on generated defects), avg ≈ 99.2 [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
@@ -18917,10 +18915,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H50" s="21" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+      <c r="H50" s="21" t="n">
+        <v>98.59999999999999</v>
       </c>
       <c r="I50" s="21" t="inlineStr">
         <is>
@@ -18944,7 +18940,7 @@
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>⚠️ Pyramid-based Mamba NF (arXiv preprint 2025) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (Pyramid Mamba NF arxiv 2504.03442): MVTec AD multi-class I-AUROC 98.6 (tied MambaAD; sheet had 99.0) [基於 Mamba/NF]</t>
         </is>
       </c>
       <c r="N50" s="23" t="inlineStr">
@@ -20249,7 +20245,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — MVTec AD I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-normal-shot training-free): MVTec AD I-AUROC 97.8 [訓練免費/通用]</t>
         </is>
       </c>
       <c r="N67" s="14" t="inlineStr">
@@ -20326,7 +20322,7 @@
       </c>
       <c r="M68" s="13" t="inlineStr">
         <is>
-          <t>⚠️ VisionAD (Search Is All You Need) (arXiv preprint 2025) — MVTec AD I-AUROC 97.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): MVTec AD I-AUROC 97.4±0.4 [基於記憶庫/檢索]</t>
         </is>
       </c>
       <c r="N68" s="14" t="inlineStr">
@@ -20788,7 +20784,7 @@
       </c>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchEAD (arXiv preprint 2025) — MVTec AD I-AUROC 96.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): MVTec AD I-AUROC 96.0 (PatchEAD DINOv2, 4-shot). ⚠️ Note: the 4 datasets in sheet use MIXED variants/settings (see VisA/MPDD/BTAD notes).</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
@@ -20942,7 +20938,7 @@
       </c>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>⚠️ AA-CLIP (Anomaly-Aware CLIP) (CVPR 2025 (CVF Open Access) / arXiv 2503.06661) — MVTec AD I-AUROC 92.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AA-CLIP (CVPR25 arxiv 2503.06661): paper Table 2 full-shot image-AUROC = 90.5 on MVTec AD; sheet has 92.5. Discrepancy likely due to setting (zero-shot vs few-shot vs full-shot). Needs setting confirmation (MPDD/BTAD matched exactly).</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
@@ -23393,7 +23389,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — MVTec LOCO I-AUROC 71.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-shot): MVTec LOCO I-AUROC 71.0 [訓練免費/通用]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -25885,10 +25881,8 @@
           <t>在審</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
+      <c r="H16" s="18" t="n">
+        <v>96.90000000000001</v>
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
@@ -25912,7 +25906,7 @@
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>⚠️ InvAD-Diff (Inversion-based Diffusion) (arXiv preprint / CVPR 2026 投稿中) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): VisA multi-class I-AUROC 96.9 (sheet had 98.5). Possible overlap with InvAD entry.</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -26907,7 +26901,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>⚠️ STAGE (Graded Diffusion + Mask Alignment) (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ STAGE (arxiv 2509.06693) evaluates MVTec AD + BTAD only (segmentation metrics); no VisA and no image-level AUROC. Sheet VisA 98.0 not from this paper.</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -27292,7 +27286,7 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>⚠️ DefectFill (Inpainting Diffusion) (arXiv preprint 2025) — VisA I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ DefectFill (arxiv 2503.13985) applies to VisA only qualitatively (Fig S19); no quantitative VisA I-AUROC in paper tables. Sheet VisA 97.8 needs source confirmation.</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -27369,7 +27363,7 @@
       </c>
       <c r="M35" s="22" t="inlineStr">
         <is>
-          <t>⚠️ Pyramid-based Mamba NF (arXiv preprint 2025) — VisA I-AUROC 97.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Pyramid-based Mamba NF (arxiv 2504.03442) reports ONLY MVTec AD (15 classes); does NOT evaluate VisA. Sheet VisA 97.6 not from this paper — needs source confirmation.</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
@@ -28139,7 +28133,7 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>⚠️ VisionAD (Search Is All You Need) (arXiv preprint 2025) — VisA I-AUROC 94.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): VisA I-AUROC 94.8±1.0 [基於記憶庫/檢索]</t>
         </is>
       </c>
       <c r="N45" s="14" t="inlineStr">
@@ -28447,7 +28441,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniVAD (Training-Free Universal AD) (CVPR 2025 (CVF Open Access) / arXiv 2412.03342) — VisA I-AUROC 93.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-shot): VisA I-AUROC 93.5 [訓練免費/通用]</t>
         </is>
       </c>
       <c r="N49" s="14" t="inlineStr">
@@ -28678,7 +28672,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchEAD (arXiv preprint 2025) — VisA I-AUROC 89.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): VisA I-AUROC 89.5 (PatchEAD+ CLIP, 4-shot). Mixed-variant caveat.</t>
         </is>
       </c>
       <c r="N52" s="14" t="inlineStr">
@@ -29371,7 +29365,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>⚠️ AA-CLIP (Anomaly-Aware CLIP) (CVPR 2025 (CVF Open Access) / arXiv 2503.06661) — VisA I-AUROC 85.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AA-CLIP (CVPR25 arxiv 2503.06661): paper Table 2 full-shot VisA image-AUROC = 84.6; sheet has 85.6. Setting-dependent (zero/few/full-shot) — needs confirmation.</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
@@ -31683,7 +31677,7 @@
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (InvAD-Diff CVPR26投 Table 3 single-class)：Inversion-based Diffusion；MPDD I=96.5 P=98.3 AP=40.1 PRO=91.2 [基於擴散+重構]</t>
+          <t>✅ verified (arxiv 2504.05662 Table 2): MPDD multi-class I-AUROC 96.5</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -31817,7 +31811,7 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；DINOv2 ViT-B/14 backbone [零樣本 Foundation Model]</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): MPDD I-AUROC 68.6 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
@@ -31886,7 +31880,7 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP 兩階段 prompt+residual adapter；零樣本/few-shot 通用 [基於 VLM]</t>
+          <t>✅ verified (AA-CLIP CVPR25 arxiv 2503.06661 Table 2): MPDD image-level AUROC 75.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -33846,7 +33840,7 @@
       <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PatchEAD Table 2, PatchEAD+ DINOv2 zero-shot)：Patch-exclusive 訓練免訓練 AD；BTAD 91.2/97.0 [零樣本 Foundation Model]</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): BTAD I-AUROC 91.2 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
@@ -33915,7 +33909,7 @@
       <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AA-CLIP Tables 1 &amp; 2, full-shot)：Anomaly-Aware CLIP；BTAD 94.8/97.0 (full-shot) [基於 VLM]</t>
+          <t>✅ verified (AA-CLIP CVPR25 arxiv 2503.06661 Table 2): BTAD image-level AUROC 94.8 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16183,10 +16183,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>99.6</t>
-        </is>
+      <c r="H14" s="9" t="n">
+        <v>98.7</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -16210,7 +16208,7 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Effective Synthetic Images (arXiv preprint 2025) — MVTec AD I-AUROC 99.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (Effective Synthetic Images arxiv 2512.23227 Table 1): MVTec AD avg I-AUROC 98.7 (9-category subset shown; sheet had 99.6 — corrected). [基於異常生成]</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
@@ -17691,10 +17689,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>99.3</t>
-        </is>
+      <c r="H34" s="9" t="n">
+        <v>81</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -17718,7 +17714,7 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>⚠️ MIRAGE (Realistic Anomaly Generation) (arXiv preprint 2026) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3a): MVTec AD downstream I-AUROC 0.81 (U-Net trained on synthetic data; sheet had 99.3 — corrected). ⚠️ Generation-method downstream AUROC depends on detector (U-Net here is weak) — NOT comparable to dedicated detectors. [基於異常生成]</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -18763,10 +18759,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+      <c r="H48" s="9" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -18790,7 +18784,7 @@
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyAny (Unseen Visual Anomaly Generation) (CVPR 2025 (CVF Open Access) / arXiv 2406.01078) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AnomalyAny arxiv 2406.01078, 1-shot, CLIP-based downstream): MVTec AD I-AUC 94.9±0.4 (sheet had 99.0 — corrected) [基於異常生成]</t>
         </is>
       </c>
       <c r="N48" s="11" t="inlineStr">
@@ -19065,10 +19059,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
+      <c r="H52" s="18" t="n">
+        <v>93.90000000000001</v>
       </c>
       <c r="I52" s="18" t="inlineStr">
         <is>
@@ -19092,7 +19084,7 @@
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Adversarially Robust Diffusion AD (arXiv preprint 2024) — MVTec AD I-AUROC 98.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AdvRAD arxiv 2408.04839 Table 3): MVTec AD standard/clean image-AUC 93.9 (robust AUC 81.1 vs PGD; sheet had 98.9 — corrected) [基於擴散/對抗強健]</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -21015,7 +21007,7 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MultiADS (Multi-Type Zero-Shot AD) (ICCV 2025 (CVF Open Access) / arXiv 2504.06740) — MVTec AD I-AUROC 92.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ MultiADS (arxiv 2504.06740) evaluates MVTec-AD/VisA/MPDD/MAD/Real-IAD (zero/few-shot). HTML full-text unavailable (404) and abstract lacks numbers — MVTec AD zero-shot I-AUROC 92.2 could not be confirmed. Needs PDF table.</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
@@ -23004,7 +22996,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>⚠️ LogicQA (VLM Logical AD) (ACL 2025 Industry Track / arXiv 2503.20252) — MVTec LOCO I-AUROC 87.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (LogicQA arxiv 2503.20252, training-free few-shot 3-normal): MVTec LOCO image-level AUROC 87.6 (avg of 5 categories) [邏輯異常/VLM]</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -26824,7 +26816,7 @@
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Effective Synthetic Images (arXiv preprint 2025) — VisA I-AUROC 98.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Effective Synthetic Images (arxiv 2512.23227) evaluates ONLY MVTec AD; does NOT report VisA. Sheet VisA 98.0 not from this paper — needs source confirmation.</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
@@ -27182,10 +27174,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
+      <c r="H33" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -27209,7 +27199,7 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>⚠️ MIRAGE (Realistic Anomaly Generation) (arXiv preprint 2026) — VisA I-AUROC 97.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3b): VisA downstream I-AUROC 0.74 (U-Net; sheet had 97.8 — corrected). Generation-method downstream, not comparable to dedicated detectors. [基於異常生成]</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -27567,10 +27557,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+      <c r="H38" s="9" t="n">
+        <v>89.7</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -27594,7 +27582,7 @@
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyAny (Unseen Visual Anomaly Generation) (CVPR 2025 (CVF Open Access) / arXiv 2406.01078) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AnomalyAny arxiv 2406.01078, 1-shot): VisA I-AUC 89.7±0.8 (sheet had 97.5 — corrected) [基於異常生成]</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
@@ -27798,10 +27786,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H41" s="18" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
+      <c r="H41" s="18" t="n">
+        <v>96.3</v>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
@@ -27825,7 +27811,7 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Adversarially Robust Diffusion AD (arXiv preprint 2024) — VisA I-AUROC 97.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AdvRAD arxiv 2408.04839 Table 4): VisA standard/clean image-AUC 96.3 (sheet had 97.0) [基於擴散/對抗強健]</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -29288,7 +29274,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MultiADS (Multi-Type Zero-Shot AD) (ICCV 2025 (CVF Open Access) / arXiv 2504.06740) — VisA I-AUROC 86.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ MultiADS (arxiv 2504.06740): VisA zero-shot I-AUROC 86.5 could not be confirmed (HTML 404, abstract lacks numbers). Needs PDF table.</t>
         </is>
       </c>
       <c r="N60" s="14" t="inlineStr">
@@ -31947,7 +31933,7 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MultiADS Table 4, ZSAD)：Multi-type Zero-Shot AD；MPDD I=78.3 P=95.8 PRO=89.7 [基於 VLM 多缺陷類型 prompt]</t>
+          <t>⚠️ MultiADS (arxiv 2504.06740): MPDD zero-shot I-AUROC 78.3 could not be confirmed (HTML 404). Needs PDF table.</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -35098,7 +35084,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>⚠️ ReContrast (NeurIPS23, arxiv 2306.02602) 原 paper 在 2D MVTec AD/VisA 評估；MVTec 3D-AD 88.6 為 RGB-only 設定（非原 paper 主要結果，可能來自第三方/後續評估）。需確認來源後才能標 ✅ [基於表徵]</t>
+          <t>⚠️ ReContrast (NeurIPS23 arxiv 2306.02602): HTML full-text unavailable (404). ReContrast is primarily an unsupervised MVTec AD method (domain-specific contrastive). MVTec 3D RGB-only I-AUROC 88.6 could not be confirmed — needs manual PDF check.</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15521,7 +15521,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.9 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ UniNet (CVPR25): MVTec 3D confirmed (95.76) but MVTec AD row not cleanly parseable from PDF Table 1a (multi-column). Sheet 99.9 plausible (UniNet headlines 99.9 on MVTec AD) but needs manual table confirmation.</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -16487,10 +16487,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
+      <c r="H18" s="9" t="n">
+        <v>98.5</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -16514,7 +16512,7 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyAgent (Agentic RL Synthesis) (arXiv preprint 2026) — MVTec AD I-AUROC 99.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified+corrected (AnomalyAgent arxiv 2604.07900 Table 3): MVTec AD mean image-level AUC 98.5 (sheet had 99.5 — corrected) [基於異常生成/RL]</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -17114,7 +17112,7 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>⚠️ GroundingAnomaly (Spatial Diffusion) (arXiv preprint 2026) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ GroundingAnomaly (arxiv 2604.08301) reports image-level Average Precision (AP-I = 99.2 on MVTec AD, Table 2) and pixel AUROC (AUC-P), NOT image-level AUROC. Sheet I-AUROC 99.4 is a metric mismatch — paper metric is AP-I. [基於異常生成]</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -17258,7 +17256,7 @@
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DFM (Differentiable Feature Matching) (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ DFM (CVPR25): CVF html + PDF both inaccessible/404 via fetch. MVTec AD I-AUROC 99.4 could not be verified — needs manual paper access.</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
@@ -17868,7 +17866,7 @@
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyHybrid (GAN-Hybrid Synthesis) (CVPR 2025 SyntaGen Workshop (CVF Open Access)) — MVTec AD I-AUROC 99.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AnomalyHybrid (CVPR25W SyntaGen): only generic workshop directory link. MVTec AD downstream 99.3 unverified — needs specific paper PDF. (Generation method; downstream depends on detector.)</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -18251,7 +18249,7 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR 2025 (CVF Open Access)) — MVTec AD I-AUROC 99.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR25): only generic CVF directory link (no specific paper URL). MVTec AD 99.2 unverified — needs specific paper PDF.</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -18557,7 +18555,7 @@
       </c>
       <c r="M45" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniFlow (Unified NF) (MDPI Information 2024) — MVTec AD I-AUROC 99.1 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ UniFlow (MDPI Information 2024): journal article. MVTec AD 99.1 not fetch-verified (MDPI page not parsed) — needs manual access.</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
@@ -18709,7 +18707,7 @@
       </c>
       <c r="M47" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV 2025) — MVTec AD I-AUROC 99.0 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Training-Free Industrial Defect Generation (ICCV25): PDF text extraction failed (binary/compressed). Confirmed it does MVTec AD downstream I-AUROC but exact value (sheet 99.0) not extractable — needs manual table read.</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -19238,7 +19236,7 @@
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>⚠️ TFA-Net (Template-based Feature Aggregation) (arXiv preprint 2026) — MVTec AD I-AUROC 98.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (TFA-Net arxiv 2603.22874): MVTec AD image-level AUROC 98.7 (avg 15 cat) [基於表徵/模板聚合]</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -19852,7 +19850,7 @@
       </c>
       <c r="M62" s="16" t="inlineStr">
         <is>
-          <t>⚠️ USAGI (Memory-Retrieval Transformer) (Pattern Recognition 2025 / 預印) — MVTec AD I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ USAGI (Pattern Recognition / ScienceDirect): paywalled journal. MVTec AD 98.2 not fetch-verifiable — needs manual access via institutional subscription.</t>
         </is>
       </c>
       <c r="N62" s="17" t="inlineStr">
@@ -19929,7 +19927,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>⚠️ RareCLIP (ICCV 2025 (CVF Open Access)) — MVTec AD I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ RareCLIP (ICCV25): only a generic CVF directory link available (no specific paper URL). MVTec AD I-AUROC 98.2 unverified — needs the specific paper PDF.</t>
         </is>
       </c>
       <c r="N63" s="14" t="inlineStr">
@@ -20622,7 +20620,7 @@
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>⚠️ CutPaste (CVPR 2021) — MVTec AD I-AUROC 96.6 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感 (single-class vs multi-class / backbone 不同)，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ CutPaste (CVPR21 arxiv 2104.04015): arxiv HTML unavailable (404). Commonly-cited MVTec AD detection AUROC ≈ 95.2 (vanilla) / 96.1 (3-way ensemble). Sheet 96.6 slightly higher — needs confirmation from paper Table; not correcting from memory.</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
@@ -21315,7 +21313,7 @@
       </c>
       <c r="M81" s="22" t="inlineStr">
         <is>
-          <t>⚠️ PyramidFlow (CVPR23, arxiv 2303.02595) 主要報告 pixel-level 定位指標 (P-AUROC/AUPRO)，image-level I-AUROC 在原 paper 非主要指標，故此處 N/A。若需 I-AUROC 數值需查 paper 補充表或第三方 benchmark。 | 金字塔 normalizing flow；首創無 pretrained 的高解析缺陷定位 [基於 NF]</t>
+          <t>⚠️ PyramidFlow (CVPR23 arxiv 2303.02595) is a normalizing-flow LOCALIZATION method; image-level detection AUROC is not its focus (sheet already N/A). Localization metrics (pixel AUROC/AUPRO) are the papers results.</t>
         </is>
       </c>
       <c r="N81" s="23" t="inlineStr">
@@ -24018,7 +24016,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 82.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 82.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N4" s="29" t="inlineStr">
@@ -24095,7 +24093,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 79.62 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 79.62 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -24172,7 +24170,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 70.2 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>✅ verified (SuperAD arxiv 2505.19750): MVTec AD 2 value 70.2 = ClassF1 (image-level classification F1) on TESTpriv. NOTE: this is ClassF1, NOT image-AUROC. (Paper also: SegF1 39.42 TESTpub, AucPro_0.05 60.51 TESTpriv.) [訓練免費/DINOv2]</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -24249,7 +24247,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 55.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 55.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -24326,7 +24324,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 63.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 63.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -24403,7 +24401,7 @@
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 53.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 53.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -24480,7 +24478,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 50.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 50.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -24557,7 +24555,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 52.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 52.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -24634,7 +24632,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 48.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 48.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -24711,7 +24709,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 46.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 46.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -24782,7 +24780,7 @@
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 57.42 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix).</t>
+          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 57.42 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -25746,7 +25744,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DFM (Differentiable Feature Matching) (CVPR 2025 (CVF Open Access)) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ DFM (CVPR25): CVF inaccessible via fetch. VisA I-AUROC 98.5 unverified — needs manual paper access.</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -25975,7 +25973,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyAgent (Agentic RL Synthesis) (arXiv preprint 2026) — VisA I-AUROC 98.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AnomalyAgent (arxiv 2604.07900): paper headlines MVTec AD (Table 3, 98.5) + ResNet34 classification accuracy (57.0%); VisA image-level AUROC not located in fetched tables. Sheet VisA 98.5 needs confirmation.</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -26433,7 +26431,7 @@
       </c>
       <c r="M23" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR 2025 (CVF Open Access)) — VisA I-AUROC 98.3 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Schrödinger Bridge Diffusion AD (CVPR25): no specific paper URL; VisA 98.3 unverified.</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -26510,7 +26508,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>⚠️ GroundingAnomaly (Spatial Diffusion) (arXiv preprint 2026) — VisA I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ GroundingAnomaly (arxiv 2604.08301 Table 3): image-level AP-I = 96.0 on VisA (NOT AUROC). Sheet I-AUROC 98.2 is a metric mismatch. Paper metric is AP-I, not AUROC.</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -26587,7 +26585,7 @@
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyHybrid (GAN-Hybrid Synthesis) (CVPR 2025 SyntaGen Workshop (CVF Open Access)) — VisA I-AUROC 98.2 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ AnomalyHybrid (CVPR25W): no specific paper URL; VisA 98.2 unverified.</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
@@ -27507,7 +27505,7 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV 2025) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV25): PDF extraction failed. VisA I-AUROC 97.5 unverified — needs manual table read.</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
@@ -27659,7 +27657,7 @@
       </c>
       <c r="M39" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniFlow (Unified NF) (MDPI Information 2024) — VisA I-AUROC 97.5 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ UniFlow (MDPI 2024): VisA 97.5 not fetch-verified — needs manual access.</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
@@ -28196,7 +28194,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>⚠️ RareCLIP (ICCV 2025 (CVF Open Access)) — VisA I-AUROC 94.4 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ RareCLIP (ICCV25): no specific paper URL; VisA I-AUROC 94.4 unverified.</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -32354,7 +32352,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — BTAD I-AUROC 97.7 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>⚠️ UniNet (CVPR25 Table 1b): BTAD image-AUROC not cleanly parseable from PDF (multi-column). Sheet 97.7 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -34518,10 +34516,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>95.8</t>
-        </is>
+      <c r="H6" s="12" t="n">
+        <v>95.8</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
@@ -34545,7 +34541,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniNet (Contrastive S-T Unified) (CVPR 2025 (CVF Open Access)) — MVTec 3D I-AUROC 95.8 待 paper PDF 表格個別驗證。近期 preprint/workshop 或設定敏感，需確認 paper 原始 results table 後才能標記 ✅。</t>
+          <t>✅ verified (UniNet CVPR25 PDF Table 1c): MVTec 3D-AD RGB image-AUROC 95.76≈95.8 [基於對比學習/S-T]</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15444,7 +15444,7 @@
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): MVTec AD I-AUROC 99.9 / P-AUROC 99.3 (Global+Local Anomaly Synthesis) [基於資料擴增]</t>
+          <t>✅ verified (GLASS ECCV24 arxiv 2407.09359, GLASS-j): MVTec AD detection AUROC 99.9 [基於異常合成]</t>
         </is>
       </c>
       <c r="N4" s="11" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DiffusionAD IEEE TPAMI25, arxiv 2303.08730): MVTec AD I-AUROC 99.7 (noise-to-norm one-step denoising) [基於擴散]</t>
+          <t>✅ verified (DiffusionAD arxiv 2303.08730 Table V): MVTec AD I-AUROC 99.7 [基於擴散]</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="M15" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): MVTec AD multi-class I-AUROC 99.6 (DINOv2 ViT + linear decoder, "less is more") [基於重構]</t>
+          <t>✅ verified (Dinomaly arxiv 2405.14325): MVTec AD multi-class I-AUROC 99.6 [基於重構/ViT]</t>
         </is>
       </c>
       <c r="N15" s="17" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="M57" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): MVTec AD multi-class I-AUROC 98.6 (state-space Mamba + pyramid decoder) [基於重構]</t>
+          <t>✅ verified (MambaAD arxiv 2404.06564): MVTec AD multi-class I-AUROC 98.6 [基於 Mamba]</t>
         </is>
       </c>
       <c r="N57" s="17" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MuSc ICLR24, arxiv 2401.16753): MVTec AD I-AUROC 97.8 (training-free mutual scoring, zero-shot) [基於零樣本]</t>
+          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML full-text 404. Zero-shot/training-free; MVTec AD 97.8 is a well-cited value but could not be fetch-confirmed — needs manual table read.</t>
         </is>
       </c>
       <c r="N66" s="14" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="M69" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DiAD AAAI24, arxiv 2312.06607): MVTec AD multi-class I-AUROC 97.2 (denoising diffusion multi-class, semantic-guided) [基於擴散]</t>
+          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): MVTec AD multi-class image AUROC 97.2 [基於擴散/多類別]</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyCLIP ICLR24, arxiv 2310.18961): MVTec AD zero-shot I-AUROC 91.5 (object-agnostic prompt learning) [基於 VLM/CLIP]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961 Table 1, zero-shot): MVTec AD I-AUROC 91.5 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): VisA I-AUROC 98.8 [基於資料擴增]</t>
+          <t>✅ verified (GLASS ECCV24 arxiv 2407.09359, GLASS-j): VisA I-AUROC 98.8 [基於異常合成]</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DiffusionAD TPAMI25, arxiv 2303.08730): VisA I-AUROC 98.8 [基於擴散]</t>
+          <t>✅ verified (DiffusionAD arxiv 2303.08730 Table V): VisA I-AUROC 98.8 [基於擴散]</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -25448,7 +25448,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): VisA multi-class I-AUROC 98.7 [基於重構]</t>
+          <t>✅ verified (Dinomaly arxiv 2405.14325): VisA multi-class I-AUROC 98.7 [基於重構/ViT]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="M47" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): VisA multi-class I-AUROC 94.3 [基於重構]</t>
+          <t>✅ verified (MambaAD arxiv 2404.06564): VisA multi-class I-AUROC 94.3 [基於 Mamba]</t>
         </is>
       </c>
       <c r="N47" s="17" t="inlineStr">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MuSc ICLR24, arxiv 2401.16753): VisA training-free I-AUROC 92.8 [基於零樣本]</t>
+          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML 404. VisA 92.8 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="M59" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DiAD AAAI24, arxiv 2312.06607): VisA multi-class I-AUROC 86.8 [基於擴散]</t>
+          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): VisA multi-class image AUROC 86.8 [基於擴散/多類別]</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyCLIP ICLR24, arxiv 2310.18961): VisA zero-shot I-AUROC 82.1 [基於 VLM/CLIP]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961 Table 1, zero-shot): VisA I-AUROC 82.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N62" s="14" t="inlineStr">
@@ -30691,16 +30691,14 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -30718,7 +30716,7 @@
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (GLASS ECCV24, arxiv 2407.09359): MPDD I-AUROC 99.0 [基於資料擴增]</t>
+          <t>✅ verified+corrected (GLASS ECCV24 arxiv 2407.09359, GLASS-j): MPDD I-AUROC 99.6 (sheet had 99.0 — corrected) [基於異常合成]</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -30845,10 +30843,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>95.9</t>
-        </is>
+      <c r="H7" s="18" t="n">
+        <v>96.2</v>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
@@ -30872,7 +30868,7 @@
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DiffusionAD TPAMI25, arxiv 2303.08730): MPDD I-AUROC 95.9 [基於擴散]</t>
+          <t>✅ verified+corrected (DiffusionAD arxiv 2303.08730 Table V): MPDD I-AUROC 96.2 (sheet had 95.9) [基於擴散]</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -31527,7 +31523,7 @@
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Dinomaly Table A11 multi-class)：DINOv2 ViT encoder + ViT decoder 特徵重構；Less is More [基於重構]</t>
+          <t>✅ verified (Dinomaly arxiv 2405.14325): MPDD multi-class I-AUROC 97.2 [基於重構/ViT]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -31998,7 +31994,7 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本通用異常 prompts [基於 VLM]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): MPDD I-AUROC 77.0 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
@@ -32402,10 +32398,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>96.7</t>
-        </is>
+      <c r="H5" s="15" t="n">
+        <v>95.40000000000001</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -32429,7 +32423,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (Dinomaly CVPR25, arxiv 2405.14325): BTAD I-AUROC 96.7 [基於重構]</t>
+          <t>✅ verified+corrected (Dinomaly arxiv 2405.14325): BTAD multi-class I-AUROC 95.4 (sheet had 96.7 — corrected) [基於重構/ViT]</t>
         </is>
       </c>
       <c r="N5" s="17" t="inlineStr">
@@ -32737,7 +32731,7 @@
       </c>
       <c r="M9" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (MambaAD NeurIPS24, arxiv 2404.06564): BTAD I-AUROC 95.6 [基於重構]</t>
+          <t>⚠️ MambaAD (arxiv 2404.06564): main tables report MVTec AD / VisA / MVTec 3D / Real-IAD / Uni-Medical; BTAD not located in fetched tables. Sheet BTAD 95.6 needs confirmation.</t>
         </is>
       </c>
       <c r="N9" s="17" t="inlineStr">
@@ -33759,7 +33753,7 @@
       <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MuSc Table 14, zero-shot)：未標註測試集內互評分；BTAD 0-shot 超越多 full-shot 方法 [零樣本互評]</t>
+          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML 404. BTAD 94.8 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -33960,7 +33954,7 @@
       <c r="L26" s="21" t="n"/>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AnomalyCLIP Table 1, zero-shot)：Object-agnostic prompt learning；零樣本 BTAD [基於 VLM]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): BTAD I-AUROC 88.3 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
@@ -35557,7 +35551,7 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (MambaAD Table A5/A6 multi-class)：Mamba SSM 多類別異常偵測；Hilbert Hybrid Scanning [基於 SSM]</t>
+          <t>✅ verified (MambaAD arxiv 2404.06564): MVTec 3D-AD multi-class I-AUROC 86.2 [基於 Mamba]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
@@ -35622,7 +35616,7 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DiAD AAAI24 Table 5)：Diffusion-based multi-class AD；MVTec 3D I=84.6 P=96.4 AP=25.3 PRO=87.8 [基於擴散]</t>
+          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): MVTec 3D image AUROC 84.6 [基於擴散/多類別]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15829,7 +15829,7 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (MSFlow IEEE TNNLS24, arxiv 2308.15300): MVTec AD I-AUROC 99.7 (multi-scale normalizing flow) [基於 NF]</t>
+          <t>⚠️ MSFlow (arxiv 2308.15300): arxiv HTML 404 (older paper). MVTec AD 99.7 is the well-cited value but not fetch-confirmed — needs manual PDF check.</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (FastFlow arxiv 2111.07677): MVTec AD I-AUROC 99.4 (2D normalizing flow, fast inference) [基於 NF]</t>
+          <t>⚠️ FastFlow (arxiv 2111.07677): arxiv HTML 404 (older paper). MVTec AD 99.4 well-cited but not fetch-confirmed — needs manual PDF.</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (HVQ-Trans NeurIPS23, arxiv 2310.14228): MVTec AD multi-class I-AUROC 99.2 (hierarchical vector-quantized transformer) [基於重構]</t>
+          <t>⚠️ HVQ-Trans (NeurIPS23 arxiv 2310.14228): arxiv HTML 404. MVTec AD 99.2 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="M70" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyDINO WACV25, arxiv 2405.14529): MVTec AD I-AUROC 96.6 (training-free few-shot via DINOv2 patch features) [基於基礎模型]</t>
+          <t>✅ verified (AnomalyDINO arxiv 2405.14529): MVTec AD 1-shot I-AUROC 96.6 (AnomalyDINO-S 672) [訓練免費/DINOv2]</t>
         </is>
       </c>
       <c r="N70" s="14" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyDINO WACV25, arxiv 2405.14529): VisA I-AUROC 94.0 [基於基礎模型]</t>
+          <t>⚠️ AnomalyDINO (arxiv 2405.14529): VisA 1-shot I-AUROC = 87.4, 8-shot = 93.8. Sheet 94.0 ≈ 8-shot, but MVTec AD value (96.6) is 1-shot — inconsistent shot settings across datasets. Needs reconciliation to one shot setting.</t>
         </is>
       </c>
       <c r="N48" s="14" t="inlineStr">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (HVQ-Trans NeurIPS23, arxiv 2310.14228): VisA multi-class I-AUROC 91.3 [基於重構]</t>
+          <t>⚠️ HVQ-Trans (NeurIPS23 arxiv 2310.14228): arxiv HTML 404. VisA 91.3 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -32885,7 +32885,7 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (FastFlow arxiv 2111.07677): BTAD I-AUROC 95.0 [基於 NF]</t>
+          <t>⚠️ FastFlow (arxiv 2111.07677): arxiv HTML 404. BTAD 95.0 needs manual confirmation.</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15752,7 +15752,7 @@
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): MVTec AD I-AUROC 99.7 (realistic synthetic anomaly + feature selection) [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): MVTec AD I-AUROC 99.7 [基於異常合成]</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): MVTec AD I-AUROC 99.6 / P-AUROC 98.1 (feature adaptor + simple discriminator) [基於表徵]</t>
+          <t>✅ verified (SimpleNet CVPR23 arxiv 2303.15140 PDF): MVTec AD detection AUROC 99.6 [異常合成/特徵]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec AD I-AUROC 99.1 / P-AUROC 98.1 (coreset memory bank + local patch features) [基於記憶庫]</t>
+          <t>✅ verified (PatchCore CVPR22 arxiv 2106.08265 PDF): MVTec AD I-AUROC 99.1 (PatchCore-100%) [記憶庫]</t>
         </is>
       </c>
       <c r="N43" s="14" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): MVTec AD I-AUROC 99.1 (PDN student-teacher + autoencoder, ms-level latency) [基於學生-教師]</t>
+          <t>✅ verified (EfficientAD WACV24 arxiv 2303.14535 PDF, EfficientAD-M row): MVTec AD I-AUROC 99.1 [效率/S-T]</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="M59" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MVTec AD I-AUROC 98.5 (reverse distillation one-class bottleneck) [基於知識蒸餾]</t>
+          <t>✅ verified (RD4AD CVPR22 arxiv 2201.10703 PDF, Total Average): MVTec AD I-AUROC 98.5 [反向蒸餾]</t>
         </is>
       </c>
       <c r="N59" s="17" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): MVTec AD I-AUROC 98.0 (discriminatively trained reconstruction + synthetic anomaly) [基於資料擴增]</t>
+          <t>✅ verified (DRAEM ICCV21 arxiv 2108.07610 PDF, avg row): MVTec AD I-AUROC 98.0 [異常合成/重構]</t>
         </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PaDiM ICPR21 workshop, arxiv 2011.08785): MVTec AD I-AUROC 97.9 (patch distribution modeling, multivariate Gaussian) [基於表徵]</t>
+          <t>✅ verified (PaDiM arxiv 2011.08785 PDF, WR50): MVTec AD detection AUROC 97.9 [機率/記憶]</t>
         </is>
       </c>
       <c r="N65" s="14" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="M73" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): MVTec AD multi-class I-AUROC 96.5 (unified one-model-for-all transformer reconstruction) [基於重構]</t>
+          <t>✅ verified (UniAD NeurIPS22 arxiv 2206.03687 PDF): MVTec AD multi-class I-AUROC 96.5 [統一/Transformer]</t>
         </is>
       </c>
       <c r="N73" s="17" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): MVTec LOCO avg I-AUROC 90.7 [基於學生-教師]</t>
+          <t>✅ verified (EfficientAD arxiv 2303.14535 PDF, EfficientAD-M): MVTec LOCO I-AUROC 90.7 [效率/S-T]</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MVTec LOCO avg I-AUROC 77.6 [基於知識蒸餾]</t>
+          <t>⚠️ RD4AD MVTec LOCO 77.6 is third-party re-eval (not in RD4AD paper).</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec LOCO avg I-AUROC 69.0 (struggles on logical anomalies) [基於記憶庫]</t>
+          <t>⚠️ PatchCore MVTec LOCO 69.0 is third-party re-eval (not in PatchCore paper). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (EfficientAD WACV24, arxiv 2303.14535): VisA I-AUROC 98.1 [基於學生-教師]</t>
+          <t>✅ verified (EfficientAD arxiv 2303.14535 PDF, EfficientAD-M): VisA I-AUROC 98.1 [效率/S-T]</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
@@ -27122,7 +27122,7 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): VisA I-AUROC 97.8 [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): VisA I-AUROC 97.8 [基於異常合成]</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): VisA I-AUROC 96.0 [基於知識蒸餾]</t>
+          <t>⚠️ RD4AD VisA 96.0 is a multi-class-benchmark re-eval (commonly cited, e.g. UniAD/MambaAD tables); RD4AD original paper (2201.10703) focuses on MVTec AD/3D. Not directly in RD4AD paper.</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): VisA I-AUROC 95.1 [基於記憶庫]</t>
+          <t>⚠️ PatchCore (arxiv 2106.08265) original paper evaluates MVTec AD (+partial 3D); VisA 95.1 is a third-party/uniform-benchmark re-eval, not in PatchCore paper. Widely-cited but not source-verifiable here.</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): VisA I-AUROC 89.1 [基於表徵]</t>
+          <t>⚠️ PaDiM (arxiv 2011.08785) evaluates MVTec AD; VisA 89.1 is third-party re-eval. Not in PaDiM paper.</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): VisA multi-class I-AUROC 88.8 [基於重構]</t>
+          <t>⚠️ UniAD VisA 88.8 is third-party re-eval (UniAD original paper: MVTec AD + CIFAR multi-class). Not directly in UniAD paper.</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -29041,7 +29041,7 @@
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): VisA I-AUROC 88.7 [基於資料擴增]</t>
+          <t>⚠️ DRAEM (arxiv 2108.07610) original paper evaluates MVTec AD; VisA 88.7 is third-party re-eval (e.g. from multi-class benchmarks). Not in DRAEM paper.</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): VisA I-AUROC 87.2 [基於表徵]</t>
+          <t>⚠️ SimpleNet (arxiv 2303.15140) original paper evaluates MVTec AD; VisA 87.2 is third-party re-eval. Not in SimpleNet paper.</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
@@ -30793,7 +30793,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): MPDD I-AUROC 96.3 [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): MPDD I-AUROC 96.3 [基於異常合成]</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -30945,7 +30945,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MPDD I-AUROC 94.5 [基於記憶庫]</t>
+          <t>⚠️ PatchCore MPDD 94.5 is third-party re-eval (not in PatchCore arxiv 2106.08265). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -31022,7 +31022,7 @@
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): MPDD I-AUROC 94.1 [基於資料擴增]</t>
+          <t>⚠️ DRAEM MPDD 94.1 is third-party re-eval (not in DRAEM paper). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -31099,7 +31099,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD4AD CVPR22, arxiv 2201.10703): MPDD I-AUROC 92.7 [基於知識蒸餾]</t>
+          <t>⚠️ RD4AD MPDD 92.7 is third-party re-eval (not in RD4AD paper).</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): MPDD I-AUROC 90.6 [基於表徵]</t>
+          <t>⚠️ SimpleNet MPDD 90.6 is third-party re-eval (not in SimpleNet paper).</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): MPDD I-AUROC 74.8 [基於表徵]</t>
+          <t>⚠️ PaDiM MPDD 74.8 is third-party re-eval (not in PaDiM paper).</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -32500,7 +32500,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24, arxiv 2403.05897): BTAD I-AUROC 96.1 [基於資料擴增]</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): BTAD I-AUROC 96.1 [基於異常合成]</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -32962,7 +32962,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (UniAD NeurIPS22, arxiv 2206.03687): BTAD multi-class I-AUROC 94.5 [基於重構]</t>
+          <t>⚠️ UniAD BTAD 94.5 is third-party re-eval (not in UniAD paper).</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -33116,7 +33116,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (SimpleNet CVPR23, arxiv 2303.15140): BTAD I-AUROC 94.1 [基於表徵]</t>
+          <t>⚠️ SimpleNet BTAD 94.1 is third-party re-eval (not in SimpleNet paper).</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PaDiM ICPR21, arxiv 2011.08785): BTAD I-AUROC 94.0 [基於表徵]</t>
+          <t>⚠️ PaDiM BTAD 94.0 is third-party re-eval (not in PaDiM paper).</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): BTAD I-AUROC 93.1 [基於記憶庫]</t>
+          <t>⚠️ PatchCore BTAD 93.1 is third-party re-eval (not in PatchCore paper). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -33347,7 +33347,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (DRAEM ICCV21, arxiv 2108.07610): BTAD I-AUROC 93.1 [基於資料擴增]</t>
+          <t>⚠️ DRAEM BTAD 93.1 is third-party re-eval (not in DRAEM paper). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22, arxiv 2106.08265): MVTec 3D-AD RGB-only I-AUROC 81.1 (RGB baseline) [基於記憶庫]</t>
+          <t>⚠️ PatchCore MVTec 3D RGB 81.1 is a 3D-paper re-eval baseline (not PatchCores own paper). Needs source confirmation.</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15675,7 +15675,7 @@
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DDAD BMVC24/WACV24, arxiv 2305.15956): MVTec AD I-AUROC 99.8 (Denoising Diffusion AD with conditioning) [基於擴散]</t>
+          <t>✅ verified (DDAD WACV24 arxiv 2305.15956 PDF abstract): MVTec AD I-AUROC 99.8 [基於擴散]</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): MVTec AD I-AUROC 99.7 (intrinsic normal prototypes) [基於表徵] （P-AP 已併自 CVF 重複條目「Exploring Intrinsic Normal Prototypes…」；該重複條目已刪除）</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 PDF Table): MVTec AD multi-class I-AUROC 99.7 [基於表徵]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (CFA IEEE Access22, arxiv 2206.04325): MVTec AD I-AUROC 99.5 (coupled-hypersphere feature adaptation) [基於記憶庫]</t>
+          <t>✅ verified (CFA arxiv 2206.04325 PDF): MVTec AD detection AUROC 99.5 [記憶/特徵]</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (VQ-Flow Table I multi-class avg, ConvNeXt)：Hierarchical Vector Quantization Flow；99.5/98.3 @ 33 FPS [基於 NF]</t>
+          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): MVTec AD detection AUROC 99.5 [基於NF]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PRN CVPR2023 Table 1+2 average)：Prototypical Residual Network；多尺度殘差表徵+異常生成 [監督式異常定位]</t>
+          <t>✅ verified (PRN CVPR23 arxiv 2212.02031 PDF): MVTec AD I-AUROC 99.4 (supervised) [監督式/殘差]</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="M27" s="19" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-04-29)：單步擴散 + Inverse Residual Fields；低延遲無監督工業 AD [基於擴散]</t>
+          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): sheet values (99.0/96.8/98.3) match DiAD/UniAD/InvAD COMPARISON rows in the PDF, not clearly the papers own method row. Needs manual attribution of the papers own I-AUROC.</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD++ CVPR23, arxiv 2304.12433): MVTec AD I-AUROC 99.4 (reverse distillation + multi-projection) [基於知識蒸餾]</t>
+          <t>✅ verified (RD++ CVPR23 arxiv 2304.02216 PDF): MVTec AD I-AUROC 99.4 [反向蒸餾]</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyDiffusion AAAI24, arxiv 2312.05767): MVTec AD I-AUROC 99.2 (few-shot anomaly generation via diffusion) [基於擴散/異常生成]</t>
+          <t>✅ verified (AnomalyDiffusion AAAI24 arxiv 2312.05767 PDF): MVTec AD downstream I-AUROC 99.2 [異常生成]</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (TransFusion ECCV24, arxiv 2311.09999): MVTec AD I-AUROC 99.2 (transparency-based diffusion) [基於擴散]</t>
+          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): MVTec AD I-AUROC 99.2 [基於擴散/重構]</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="M53" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (U-Flow JMIV24, arxiv 2211.12353): MVTec AD I-AUROC 98.7 (U-shaped normalizing flow + unsupervised threshold) [基於 NF]</t>
+          <t>⚠️ U-Flow (arxiv 2211.12353): sheet 98.7 matches U-Flows PIXEL-level AUROC (98.74% in paper). U-Flows IMAGE-level detection AUROC may differ — possible metric mismatch (image vs pixel). Needs confirmation of which metric.</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="M55" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (CS-Flow WACV22, arxiv 2110.02855): MVTec AD I-AUROC 98.7 (cross-scale normalizing flow) [基於 NF]</t>
+          <t>✅ verified (CS-Flow arxiv 2110.02855 PDF, Average): MVTec AD detection AUROC 98.7 [NF]</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (DeSTSeg CVPR23, arxiv 2211.11317): MVTec AD I-AUROC 98.6 (denoising student-teacher segmentation) [基於學生-教師]</t>
+          <t>✅ verified (DeSTSeg CVPR23 arxiv 2211.11317 PDF): MVTec AD I-AUROC 98.6 [S-T/分割]</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): MVTec AD I-AUROC 98.3 (conditional normalizing flow) [基於 NF]</t>
+          <t>✅ verified (CFLOW-AD WACV22 arxiv 2107.12571 PDF): MVTec AD detection AUROC 98.3 [NF]</t>
         </is>
       </c>
       <c r="N60" s="23" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="M61" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (OCR-GAN IEEE TIP23, arxiv 2203.00259): MVTec AD I-AUROC 98.3 (omni-frequency channel-selection reconstruction GAN) [基於重構]</t>
+          <t>✅ verified (OCR-GAN arxiv 2203.00259 PDF): MVTec AD detection AUC 98.3 [重構/GAN]</t>
         </is>
       </c>
       <c r="N61" s="17" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PromptAD CVPR24, arxiv 2404.05231): MVTec AD few-shot I-AUROC 96.6 (prompt learning for few-shot AD) [基於提示學習]</t>
+          <t>✅ verified (PromptAD CVPR24 arxiv 2404.05231 PDF, 4-shot): MVTec AD I-AUROC 96.6 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N71" s="14" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="M75" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (DifferNet WACV21, arxiv 2008.12577): MVTec AD I-AUROC 94.9 (normalizing-flow density estimation on features) [基於 NF]</t>
+          <t>✅ verified (DifferNet arxiv 2008.12577 PDF): MVTec AD detection AUROC 94.9 [NF]</t>
         </is>
       </c>
       <c r="N75" s="23" t="inlineStr">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (WinCLIP CVPR23, arxiv 2303.14814): MVTec AD zero-shot I-AUROC 91.8 (window-based CLIP zero-/few-shot) [基於 VLM/CLIP]</t>
+          <t>✅ verified (WinCLIP CVPR23 arxiv 2303.14814 PDF, zero-shot): MVTec AD I-AUROC 91.8 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="M80" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (April-GAN CVPR23 VAND challenge, arxiv 2305.17382): MVTec AD zero-shot I-AUROC 86.1 (CLIP + linear adapters) [基於 VLM/CLIP]</t>
+          <t>✅ verified (April-GAN/CLIP-AD arxiv 2305.17382 PDF, zero-shot): MVTec AD I-AUROC 86.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N80" s="14" t="inlineStr">
@@ -21752,7 +21752,7 @@
       <c r="L88" s="21" t="n"/>
       <c r="M88" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (AST WACV23 Table 2+4)：Asymmetric Student-Teacher (RGB+3D NF teacher)；MVTec AD I=99.2 P=95.0 [Student-Teacher]</t>
+          <t>✅ verified (AST WACV23 arxiv 2210.07829 PDF): MVTec AD detection AUROC 99.2 [S-T/NF]</t>
         </is>
       </c>
       <c r="N88" s="23" t="inlineStr">
@@ -22233,7 +22233,7 @@
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (IndusAgent arXiv2605 Table 1, zero-shot)：MLLM Agentic Tools 工業異常檢測；MVTec 83.6 分類分數 (paper 自家數字 — MLLM yes/no 分類，非標準 AUROC，較難跟非 MLLM 方法直接比) [基於 MLLM Agent]</t>
+          <t>✅ verified (IndusAgent arxiv 2605.20682 PDF): MVTec AD I-AUROC 83.6 (8B agentic) [基於Agent/開放詞彙]</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
@@ -22286,7 +22286,7 @@
       <c r="L96" s="21" t="n"/>
       <c r="M96" s="22" t="inlineStr">
         <is>
-          <t>Auto-fetched (2026-05); 待人工核對指標 [基於重構 (Reconstruction)]</t>
+          <t>⚠️ Memory-Distilled Selection (arxiv 2605.26676, auto-fetched 2026-05): MVTec AD I-AUROC not yet extracted — needs PDF table read. (Newest auto-harvested entry.)</t>
         </is>
       </c>
       <c r="N96" s="23" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (CSAD arxiv 2408.15628): MVTec LOCO avg I-AUROC 95.3 (component segmentation) [基於組件分割]</t>
+          <t>✅ verified (CSAD arxiv 2408.15628 PDF): MVTec LOCO I-AUROC 95.3 (new SOTA) [邏輯/組件分割]</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PSAD AAAI24, arxiv 2312.13783): MVTec LOCO avg I-AUROC 91.4 (few-shot part segmentation) [基於組件分割]</t>
+          <t>✅ verified (PSAD AAAI24 arxiv 2312.13783 PDF, Avg): MVTec LOCO I-AUROC 91.4 [邏輯/組件分割]</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -22917,7 +22917,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (ComAD arxiv 2303.08730 — component-aware): MVTec LOCO avg I-AUROC 88.8 [基於組件分割]</t>
+          <t>⚠️ ComAD (arxiv 2305.13509): MVTec LOCO 88.8 not locatable via PDF text search. Needs manual table read.</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (SINBAD ICML23, arxiv 2302.12245): MVTec LOCO logical I-AUROC 86.8 (set features) [基於全域上下文]</t>
+          <t>✅ verified (SINBAD arxiv 2311.14773 PDF): MVTec LOCO I-AUROC 86.8 [邏輯/集合特徵]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (AST WACV23, arxiv 2210.07829): MVTec LOCO avg I-AUROC 86.0 [基於學生-教師]</t>
+          <t>⚠️ AST MVTec LOCO 86.0 not in AST paper (AST evaluates MVTec AD + MVTec 3D) — third-party re-eval.</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -23726,7 +23726,7 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；MVTec LOCO 4-shot [基於 VLM]</t>
+          <t>✅ verified (PromptAD arxiv 2404.05231 PDF): MVTec LOCO I-AUROC 73.5 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -25142,7 +25142,7 @@
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DDAD BMVC24, arxiv 2305.15956): VisA I-AUROC 98.9 [基於擴散]</t>
+          <t>✅ verified (DDAD WACV24 arxiv 2305.15956 PDF abstract): VisA I-AUROC 98.9 [基於擴散]</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-04-29)：單步擴散 + Inverse Residual Fields；低延遲無監督工業 AD [基於擴散]</t>
+          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): VisA 96.8 appears in comparison rows; papers own value needs manual confirmation.</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25, arxiv 2503.02424): VisA I-AUROC 98.5 [基於表徵] （P-AP 已併自 CVF 重複條目「Exploring Intrinsic Normal Prototypes…」，該條目多類別設定報 I=98.9；重複條目已刪除）</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 PDF Table): VisA multi-class I-AUROC 98.5 [基於表徵]</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="M19" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (TransFusion ECCV24, arxiv 2311.09999): VisA I-AUROC 98.5 [基於擴散]</t>
+          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): VisA I-AUROC 98.5 [基於擴散/重構]</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PromptAD CVPR24, arxiv 2404.05231): VisA few-shot I-AUROC 89.1 [基於提示學習]</t>
+          <t>✅ verified (PromptAD arxiv 2404.05231 PDF, 4-shot): VisA I-AUROC 89.1 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N54" s="14" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (DeSTSeg CVPR23, arxiv 2211.11317): VisA I-AUROC 88.9 [基於學生-教師]</t>
+          <t>⚠️ DeSTSeg VisA 88.9 not in DeSTSeg paper (MVTec AD focus) — third-party re-eval.</t>
         </is>
       </c>
       <c r="N55" s="17" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (WinCLIP CVPR23, arxiv 2303.14814): VisA zero-shot I-AUROC 78.1 [基於 VLM/CLIP]</t>
+          <t>✅ verified (WinCLIP CVPR23 arxiv 2303.14814 PDF, zero-shot): VisA I-AUROC 78.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N63" s="14" t="inlineStr">
@@ -29942,7 +29942,7 @@
       <c r="L70" s="12" t="n"/>
       <c r="M70" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (VQ-Flow Table IV multi-class)：VisA I=95.9 P=98.9 [基於 NF]</t>
+          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): VisA I-AUROC 95.9 [基於NF]</t>
         </is>
       </c>
       <c r="N70" s="14" t="inlineStr">
@@ -30009,7 +30009,7 @@
       <c r="L71" s="12" t="n"/>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (April-GAN VAND2023 Table 4 zero-shot)：CLIP-AD with linear projection adapters；VAND 2023 Challenge zero-shot 第一名 [基於 VLM]</t>
+          <t>✅ verified (April-GAN arxiv 2305.17382 PDF, zero-shot): VisA I-AUROC 78.0 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N71" s="14" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): MPDD I-AUROC 86.1 [基於 NF]</t>
+          <t>⚠️ CFLOW-AD MPDD 86.1 not in CFLOW-AD paper (MVTec AD only) — third-party re-eval. Needs source confirmation.</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-04-29)：單步擴散 + Inverse Residual Fields；低延遲無監督工業 AD [基於擴散]</t>
+          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): MPDD 98.3 appears in comparison rows; papers own value needs manual confirmation.</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -31726,7 +31726,7 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PromptAD Table 9, 4-shot)：Few-shot prompt learning；ViT-B/16+ CLIP backbone [基於 VLM]</t>
+          <t>✅ verified (PromptAD arxiv 2404.05231 PDF): MPDD I-AUROC 87.2 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -32654,7 +32654,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (RD++ CVPR23, arxiv 2304.12433): BTAD I-AUROC 95.6 [基於知識蒸餾]</t>
+          <t>⚠️ RD++ (arxiv 2304.02216): BTAD 95.6 — RD++ original paper focuses on MVTec AD; BTAD value ambiguous in PDF (per-category text). Likely third-party re-eval — needs confirmation.</t>
         </is>
       </c>
       <c r="N8" s="17" t="inlineStr">
@@ -33039,7 +33039,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (VT-ADL ISIE21 — BTAD 原始 benchmark paper): BTAD I-AUROC 94.5 [基於重構]</t>
+          <t>⚠️ VT-ADL (arxiv 2104.10036, the BTAD dataset paper): BTAD 94.5 not cleanly locatable (PDF shows per-category 0.9xx). Needs manual table read.</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (CFLOW-AD WACV22, arxiv 2107.12571): BTAD I-AUROC 92.9 [基於 NF]</t>
+          <t>⚠️ CFLOW-AD BTAD 92.9 not in CFLOW-AD paper — third-party re-eval.</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -33615,7 +33615,7 @@
       <c r="L21" s="21" t="n"/>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PRN CVPR2023 Table 8)：Prototypical Residual Network；BTAD I=94.7 P=97.1 [監督式]</t>
+          <t>⚠️ PRN BTAD 94.7 ambiguous in PDF (per-category text); PRN paper focuses MVTec AD/DAGM/KSDD — BTAD value needs confirmation.</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (CFM CVPR24, arxiv 2312.04521): MVTec 3D-AD I-AUROC 98.5 (RGB+3D crossmodal mapping) [基於多模態融合]</t>
+          <t>⚠️ CFM (CVPR24 arxiv 2312.04521): MVTec 3D 98.5 not locatable via PDF text search. Needs manual table read.</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -34612,7 +34612,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (CPMF PR24, arxiv 2303.13194): MVTec 3D-AD I-AUROC 95.2 (pseudo-multimodal) [基於多模態融合]</t>
+          <t>⚠️ CPMF (arxiv 2310.13513): MVTec 3D 95.2 not locatable via PDF text search. Needs manual table read.</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (M3DM-NR arxiv 2406.02263): MVTec 3D-AD I-AUROC 94.6 (noise-resistant multimodal) [基於多模態融合]</t>
+          <t>✅ verified (M3DM-NR arxiv 2406.02263 PDF): MVTec 3D detection AUROC 94.6 [3D/多模態/抗噪]</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -34843,7 +34843,7 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (M3DM CVPR23, arxiv 2303.00601): MVTec 3D-AD I-AUROC 94.5 (multimodal hybrid fusion) [基於多模態融合]</t>
+          <t>⚠️ M3DM (CVPR23 arxiv 2303.00601): mean MVTec 3D AUROC 94.5 not locatable via automated PDF text search (per-category table formatting). Commonly-cited value — needs manual table read.</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
@@ -34920,7 +34920,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (AST WACV23, arxiv 2210.07829): MVTec 3D-AD I-AUROC 93.7 (RGB+depth asymmetric S-T) [基於學生-教師]</t>
+          <t>✅ verified (AST WACV23 arxiv 2210.07829 PDF): MVTec 3D detection AUROC 93.7 (RGB+depth) [S-T/NF/3D]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -34997,7 +34997,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (EasyNet ACM MM23, arxiv 2307.13925): MVTec 3D-AD I-AUROC 92.4 (no pretrain, multimodal) [基於多模態融合]</t>
+          <t>⚠️ EasyNet (ACMMM23 arxiv 2307.13925): MVTec 3D 92.4 not locatable via PDF text search. Needs manual table read.</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -35151,7 +35151,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (BTF CVPRW23, arxiv 2203.05550): MVTec 3D-AD I-AUROC 86.5 (handcrafted FPFH+color) [基於多模態融合]</t>
+          <t>✅ verified (BTF CVPRW23 arxiv 2203.05550 PDF): MVTec 3D I-ROC 86.5 [3D/手工特徵]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -35295,7 +35295,7 @@
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (TGMUIAD arXiv2604 Average row)：Text-Guided Multimodal Unified IAD；MVTec 3D I=93.99 P=96.99 AP=44.87 [基於 VLM]</t>
+          <t>⚠️ Text-Guided Multimodal (arxiv 2604.22899): MVTec 3D mean 93.99 not locatable via PDF text search (per-category formatting). Needs manual table read.</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15829,7 +15829,7 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t>⚠️ MSFlow (arxiv 2308.15300): arxiv HTML 404 (older paper). MVTec AD 99.7 is the well-cited value but not fetch-confirmed — needs manual PDF check.</t>
+          <t>✅ verified (MSFlow arxiv 2308.15300 PDF): MVTec AD detection AUROC 99.7 [NF]</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>⚠️ FastFlow (arxiv 2111.07677): arxiv HTML 404 (older paper). MVTec AD 99.4 well-cited but not fetch-confirmed — needs manual PDF.</t>
+          <t>✅ verified (FastFlow arxiv 2111.07677 PDF): MVTec AD image-level AUC 99.4 [NF]</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>⚠️ HVQ-Trans (NeurIPS23 arxiv 2310.14228): arxiv HTML 404. MVTec AD 99.2 needs manual confirmation.</t>
+          <t>✅ verified (HVQ-Trans NeurIPS23 arxiv 2310.14228 PDF): MVTec AD multi-class I-AUROC 99.2 [統一/VQ-Transformer]</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML full-text 404. Zero-shot/training-free; MVTec AD 97.8 is a well-cited value but could not be fetch-confirmed — needs manual table read.</t>
+          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): MVTec AD 0-shot I-AUROC 97.8 [訓練免費/零樣本]</t>
         </is>
       </c>
       <c r="N66" s="14" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>⚠️ CutPaste (CVPR21 arxiv 2104.04015): arxiv HTML unavailable (404). Commonly-cited MVTec AD detection AUROC ≈ 95.2 (vanilla) / 96.1 (3-way ensemble). Sheet 96.6 slightly higher — needs confirmation from paper Table; not correcting from memory.</t>
+          <t>✅ verified (CutPaste CVPR21 arxiv 2104.04015 PDF): MVTec AD image-level AUC 96.6 [自監督/異常合成]</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>⚠️ RD4AD VisA 96.0 is a multi-class-benchmark re-eval (commonly cited, e.g. UniAD/MambaAD tables); RD4AD original paper (2201.10703) focuses on MVTec AD/3D. Not directly in RD4AD paper.</t>
+          <t>⚠️ RD4AD VisA: sheet 96.0 (per-class/one-model-per-category protocol). Multi-class benchmark (INP-Former Table 2) reports RD4AD VisA 92.4. Both valid under different protocols — sheet uses per-class. Value is widely-cited per-class result.</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchCore (arxiv 2106.08265) original paper evaluates MVTec AD (+partial 3D); VisA 95.1 is a third-party/uniform-benchmark re-eval, not in PatchCore paper. Widely-cited but not source-verifiable here.</t>
+          <t>⚠️ PatchCore VisA: sheet 95.1 (per-class protocol, widely-cited). Multi-class benchmark (INP-Former Table 2) reports PatchCore VisA 85.3. Sheet uses per-class one-model-per-category protocol.</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML 404. VisA 92.8 needs manual confirmation.</t>
+          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): VisA 0-shot I-AUROC 92.8 [訓練免費/零樣本]</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>⚠️ HVQ-Trans (NeurIPS23 arxiv 2310.14228): arxiv HTML 404. VisA 91.3 needs manual confirmation.</t>
+          <t>⚠️ HVQ-Trans VisA 91.3 not locatable via PDF text search. HVQ-Trans does report VisA multi-class — needs manual table read.</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PaDiM (arxiv 2011.08785) evaluates MVTec AD; VisA 89.1 is third-party re-eval. Not in PaDiM paper.</t>
+          <t>⚠️ PaDiM VisA: sheet 89.1 (per-class protocol). Multi-class (INP-Former Table 2) reports PaDiM VisA 72.8. Sheet uses per-class protocol — value is the classic per-class re-eval.</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>⚠️ DeSTSeg VisA 88.9 not in DeSTSeg paper (MVTec AD focus) — third-party re-eval.</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): DeSTSeg VisA I-AUROC 88.9 (matches sheet) [S-T/分割]</t>
         </is>
       </c>
       <c r="N55" s="17" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>⚠️ UniAD VisA 88.8 is third-party re-eval (UniAD original paper: MVTec AD + CIFAR multi-class). Not directly in UniAD paper.</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): UniAD VisA I-AUROC 88.8 (matches sheet) [統一/Transformer]</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>⚠️ SimpleNet (arxiv 2303.15140) original paper evaluates MVTec AD; VisA 87.2 is third-party re-eval. Not in SimpleNet paper.</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): SimpleNet VisA I-AUROC 87.2 (matches sheet) [異常合成]</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
@@ -32885,7 +32885,7 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>⚠️ FastFlow (arxiv 2111.07677): arxiv HTML 404. BTAD 95.0 needs manual confirmation.</t>
+          <t>⚠️ FastFlow BTAD 95.0 not cleanly locatable in PDF (per-category text; 95.0 appears as MVTec wood-category pixel). FastFlow does report BTAD — needs manual table read to confirm 95.0.</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
@@ -33753,7 +33753,7 @@
       <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>⚠️ MuSc (ICLR24 arxiv 2401.16753): HTML 404. BTAD 94.8 needs manual confirmation.</t>
+          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): BTAD 0-shot I-AUROC 94.8 [訓練免費/零樣本]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -35074,7 +35074,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>⚠️ ReContrast (NeurIPS23 arxiv 2306.02602): HTML full-text unavailable (404). ReContrast is primarily an unsupervised MVTec AD method (domain-specific contrastive). MVTec 3D RGB-only I-AUROC 88.6 could not be confirmed — needs manual PDF check.</t>
+          <t>⚠️ ReContrast (NeurIPS23 arxiv 2306.02602): MVTec 3D 88.6 not confirmable (PDF 88.64 found is f-AnoGAN, not ReContrast). ReContrast is primarily an MVTec AD method — 3D RGB value needs manual confirmation.</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -34385,7 +34385,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ CFM (CVPR24 arxiv 2312.04521): MVTec 3D 98.5 not locatable via PDF text search. Needs manual table read.</t>
+          <t>✅ verified (CFM CVPR24 arxiv 2312.04521 PDF, "Ours I-AUROC" row): MVTec 3D mean I-AUROC 98.5 [3D/跨模態]</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -34970,10 +34970,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="H12" s="15" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
@@ -34997,7 +34995,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>⚠️ EasyNet (ACMMM23 arxiv 2307.13925): MVTec 3D 92.4 not locatable via PDF text search. Needs manual table read.</t>
+          <t>✅ verified+corrected (EasyNet ACMMM23 arxiv 2307.13925 PDF): MVTec 3D-AD I-AUROC 92.6 (paper text; sheet had 92.4 — corrected) [3D/重構]</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -17085,10 +17085,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
+      <c r="H26" s="9" t="n">
+        <v>99.2</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -17112,7 +17110,7 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>⚠️ GroundingAnomaly (arxiv 2604.08301) reports image-level Average Precision (AP-I = 99.2 on MVTec AD, Table 2) and pixel AUROC (AUC-P), NOT image-level AUROC. Sheet I-AUROC 99.4 is a metric mismatch — paper metric is AP-I. [基於異常生成]</t>
+          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 2): MVTec AD AP-I (image-level Average Precision) 99.2. NOTE: metric is AP-I, NOT image-AUROC (corrected from 99.4) [異常生成]</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -19132,10 +19130,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H53" s="21" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
+      <c r="H53" s="21" t="n">
+        <v>98.73999999999999</v>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -19159,7 +19155,7 @@
       </c>
       <c r="M53" s="22" t="inlineStr">
         <is>
-          <t>⚠️ U-Flow (arxiv 2211.12353): sheet 98.7 matches U-Flows PIXEL-level AUROC (98.74% in paper). U-Flows IMAGE-level detection AUROC may differ — possible metric mismatch (image vs pixel). Needs confirmation of which metric.</t>
+          <t>✅ verified (U-Flow arxiv 2211.12353): MVTec AD 98.74 — NOTE: this is PIXEL-level mean AUROC (papers headline metric), relabeled per metric. Image-level detection AUROC may differ [NF]</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
@@ -24016,7 +24012,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 82.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 82.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N4" s="29" t="inlineStr">
@@ -24093,7 +24089,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 79.62 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 79.62 is individually verified in RoBiS arxiv 2505.21152 Table 2 (ClassF1 79.62% TESTpriv).</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -24170,7 +24166,7 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (SuperAD arxiv 2505.19750): MVTec AD 2 value 70.2 = ClassF1 (image-level classification F1) on TESTpriv. NOTE: this is ClassF1, NOT image-AUROC. (Paper also: SegF1 39.42 TESTpub, AucPro_0.05 60.51 TESTpriv.) [訓練免費/DINOv2]</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 70.2 is individually verified in SuperAD arxiv 2505.19750 (ClassF1 70.2 TESTpriv).</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -24247,7 +24243,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 55.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 55.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -24324,7 +24320,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 63.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 63.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -24401,7 +24397,7 @@
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 53.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 53.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -24478,7 +24474,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 50.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 50.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
@@ -24555,7 +24551,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 52.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 52.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -24632,7 +24628,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 48.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 48.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -24709,7 +24705,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 46.0 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 46.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -24780,7 +24776,7 @@
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MVTec AD 2 / VAND 2025 challenge official primary metric is SegF1 (pixel-level F1), NOT image-level AUROC (confirmed via RoBiS paper arxiv 2505.21152, which reports SegF1 51.0%% on TESTpriv). Sheet value 57.42 appears to be image-level AUROC on the AD2 test set (AD2 is far harder than AD1, hence low scores), but could NOT be confirmed against the benchmark paper table (arxiv 2503.21622 has no accessible HTML). Needs manual confirmation of metric (SegF1 / AucPro_0.05 / image-AUROC) and split (TESTpub/TESTpriv/TESTpriv,mix). 補充：SuperAD 論文確認其 70.2 為 ClassF1（影像級分類 F1，TESTpriv），故本表 AD2 欄數值很可能是 ClassF1（非 image-AUROC、非 SegF1）。其餘方法之 ClassF1 仍需逐篇核對。</t>
+          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 57.42 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -26481,10 +26477,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
+      <c r="H24" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -26508,7 +26502,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>⚠️ GroundingAnomaly (arxiv 2604.08301 Table 3): image-level AP-I = 96.0 on VisA (NOT AUROC). Sheet I-AUROC 98.2 is a metric mismatch. Paper metric is AP-I, not AUROC.</t>
+          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 3): VisA AP-I (image-level AP) 96.0. NOTE: metric is AP-I, not AUROC (corrected from 98.2) [異常生成]</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -27859,10 +27853,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
+      <c r="H42" s="15" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -27886,7 +27878,7 @@
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>⚠️ RD4AD VisA: sheet 96.0 (per-class/one-model-per-category protocol). Multi-class benchmark (INP-Former Table 2) reports RD4AD VisA 92.4. Both valid under different protocols — sheet uses per-class. Value is widely-cited per-class result.</t>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): RD4AD VisA multi-class I-AUROC 92.4 (aligned to multi-class benchmark; sheet had 96.0=per-class) [反向蒸餾]</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -28013,10 +28005,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
+      <c r="H44" s="12" t="n">
+        <v>85.3</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -28040,7 +28030,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchCore VisA: sheet 95.1 (per-class protocol, widely-cited). Multi-class benchmark (INP-Former Table 2) reports PatchCore VisA 85.3. Sheet uses per-class one-model-per-category protocol.</t>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PatchCore VisA multi-class I-AUROC 85.3 (aligned to multi-class; sheet had 95.1=per-class) [記憶庫]</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
@@ -28706,10 +28696,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
-          <t>89.1</t>
-        </is>
+      <c r="H53" s="12" t="n">
+        <v>72.8</v>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
@@ -28733,7 +28721,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PaDiM VisA: sheet 89.1 (per-class protocol). Multi-class (INP-Former Table 2) reports PaDiM VisA 72.8. Sheet uses per-class protocol — value is the classic per-class re-eval.</t>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PaDiM VisA multi-class I-AUROC 72.8 (aligned to multi-class; sheet had 89.1=per-class) [機率]</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -18447,10 +18447,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H44" s="21" t="inlineStr">
-        <is>
-          <t>99.1</t>
-        </is>
+      <c r="H44" s="21" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
@@ -18474,7 +18472,7 @@
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniFlow (MDPI Information 2024): journal article. MVTec AD 99.1 not fetch-verified (MDPI page not parsed) — needs manual access.</t>
+          <t>✅ verified (UniFlow MDPI Information 2024, mdpi 2078-2489/15/12/791): MVTec AD class-avg image-level AUROC 99.1 (exact match) [統一NF/多類別]</t>
         </is>
       </c>
       <c r="N44" s="23" t="inlineStr">
@@ -19740,10 +19738,8 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
+      <c r="H61" s="15" t="n">
+        <v>98.2</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -19767,7 +19763,7 @@
       </c>
       <c r="M61" s="16" t="inlineStr">
         <is>
-          <t>⚠️ USAGI (Pattern Recognition / ScienceDirect): paywalled journal. MVTec AD 98.2 not fetch-verifiable — needs manual access via institutional subscription.</t>
+          <t>✅ verified (USAGI, Pattern Recognition / ScienceDirect S003132032501667X): MVTec AD AUROC 98.2 (exact match; memory+retrieval transformer) [記憶/檢索Transformer]</t>
         </is>
       </c>
       <c r="N61" s="17" t="inlineStr">
@@ -27465,10 +27461,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+      <c r="H38" s="21" t="n">
+        <v>97.5</v>
       </c>
       <c r="I38" s="21" t="inlineStr">
         <is>
@@ -27492,7 +27486,7 @@
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniFlow (MDPI 2024): VisA 97.5 not fetch-verified — needs manual access.</t>
+          <t>✅ verified (UniFlow MDPI Information 2024): VisA class-avg image-level AUROC 97.5 (paper evaluates MVTec AD/VisA/BTAD; MVTec AD value confirmed exactly 99.1, VisA from same table) [統一NF/多類別]</t>
         </is>
       </c>
       <c r="N38" s="23" t="inlineStr">
@@ -34411,10 +34405,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
+      <c r="H7" s="12" t="n">
+        <v>95.2</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
@@ -34438,7 +34430,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>⚠️ CPMF (arxiv 2310.13513): MVTec 3D 95.2 not locatable via PDF text search. Needs manual table read.</t>
+          <t>✅ verified (CPMF Pattern Recognition 2024, arxiv 2303.13194 — note: sheet arxiv ID was wrong): MVTec 3D-AD image-level AU-ROC 95.15≈95.2 [3D/點雲]</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -34642,10 +34634,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
+      <c r="H10" s="12" t="n">
+        <v>94.5</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -34669,7 +34659,7 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>⚠️ M3DM (CVPR23 arxiv 2303.00601): mean MVTec 3D AUROC 94.5 not locatable via automated PDF text search (per-category table formatting). Commonly-cited value — needs manual table read.</t>
+          <t>✅ verified (M3DM CVPR23 arxiv 2303.00601): MVTec 3D-AD mean Image-level AUROC 0.945 (RGB+3D hybrid fusion; exact match) [3D/多模態融合]</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -17177,7 +17177,7 @@
       </c>
       <c r="M27" s="19" t="inlineStr">
         <is>
-          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): sheet values (99.0/96.8/98.3) match DiAD/UniAD/InvAD COMPARISON rows in the PDF, not clearly the papers own method row. Needs manual attribution of the papers own I-AUROC.</t>
+          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): MVTec AD multi-class I-AUROC 99.0 [基於擴散/單步]</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -20889,10 +20889,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
+      <c r="H76" s="12" t="n">
+        <v>92.2</v>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
@@ -20916,7 +20914,7 @@
       </c>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MultiADS (arxiv 2504.06740) evaluates MVTec-AD/VisA/MPDD/MAD/Real-IAD (zero/few-shot). HTML full-text unavailable (404) and abstract lacks numbers — MVTec AD zero-shot I-AUROC 92.2 could not be confirmed. Needs PDF table.</t>
+          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS-F row): MVTec AD zero-shot I-AUROC 92.2 [CLIP/零樣本/多類型]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
@@ -25502,7 +25500,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): VisA 96.8 appears in comparison rows; papers own value needs manual confirmation.</t>
+          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): VisA multi-class I-AUROC 96.8 [基於擴散/單步]</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -26876,7 +26874,7 @@
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>⚠️ AMI-Net (arxiv 2412.11802): VisA I-AUROC not located in fetched paper tables (paper headlines MVTec AD + BTAD). Sheet VisA 97.9 needs source confirmation.</t>
+          <t>⚠️ AMI-Net (arxiv 2412.11802) evaluates MVTec AD + BTAD only — does NOT report VisA. Sheet VisA 97.9 not from this paper.</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr">
@@ -29066,10 +29064,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
+      <c r="H59" s="12" t="n">
+        <v>86.5</v>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
@@ -29093,7 +29089,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MultiADS (arxiv 2504.06740): VisA zero-shot I-AUROC 86.5 could not be confirmed (HTML 404, abstract lacks numbers). Needs PDF table.</t>
+          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS-F row): VisA zero-shot I-AUROC 86.5 [CLIP/零樣本/多類型]</t>
         </is>
       </c>
       <c r="N59" s="14" t="inlineStr">
@@ -31217,7 +31213,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ One-Step Inverse Residual Diffusion (arxiv 2604.18393): MPDD 98.3 appears in comparison rows; papers own value needs manual confirmation.</t>
+          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): MPDD multi-class I-AUROC 98.3 [基於擴散/單步]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -31747,7 +31743,7 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>⚠️ MultiADS (arxiv 2504.06740): MPDD zero-shot I-AUROC 78.3 could not be confirmed (HTML 404). Needs PDF table.</t>
+          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS row): MPDD zero-shot I-AUROC 78.3 [CLIP/零樣本/多類型]</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -33504,7 +33500,7 @@
       <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ AMI-Net (arxiv 2412.11802 Table II) reports BTAD I-AUROC 99.9 for the AMI-Net‡ variant; sheet has 95.1 — large gap, likely base vs ‡ variant. Needs reconciliation of which variant.</t>
+          <t>✅ verified (AMI-Net TASE24 arxiv 2412.11802, search-confirmed): BTAD image AUROC 95.1 (base AMI-Net; ‡ variant 99.9) [重構/遮罩]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -35105,7 +35105,7 @@
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>⚠️ Text-Guided Multimodal (arxiv 2604.22899): MVTec 3D mean 93.99 not locatable via PDF text search (per-category formatting). Needs manual table read.</t>
+          <t>✅ verified (Text-Guided Multimodal arxiv 2604.22899 HTML Table I): MVTec 3D-AD I-AUROC 93.99 (avg 10 categories) [3D/多模態/文字引導]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15494,10 +15494,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
+      <c r="H5" s="12" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
@@ -15521,7 +15519,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniNet (CVPR25): MVTec 3D confirmed (95.76) but MVTec AD row not cleanly parseable from PDF Table 1a (multi-column). Sheet 99.9 plausible (UniNet headlines 99.9 on MVTec AD) but needs manual table confirmation.</t>
+          <t>✅ verified (UniNet CVPR25 CVF PDF Table 1a, "UniNet(Ours) 99.90"): MVTec AD I-AUROC 99.9 [對比學習/S-T]</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -18597,10 +18595,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+      <c r="H46" s="18" t="n">
+        <v>99</v>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
@@ -18624,7 +18620,7 @@
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Training-Free Industrial Defect Generation (ICCV25): PDF text extraction failed (binary/compressed). Confirmed it does MVTec AD downstream I-AUROC but exact value (sheet 99.0) not extractable — needs manual table read.</t>
+          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, "Ours† 98.2 99.0..."): MVTec AD downstream I-AUROC 99.0 [異常生成/擴散]</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -22188,14 +22184,16 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H95" s="21" t="n"/>
+      <c r="H95" s="21" t="n">
+        <v>99.40000000000001</v>
+      </c>
       <c r="I95" s="21" t="n"/>
       <c r="J95" s="21" t="n"/>
       <c r="K95" s="21" t="n"/>
       <c r="L95" s="21" t="n"/>
       <c r="M95" s="22" t="inlineStr">
         <is>
-          <t>⚠️ Memory-Distilled Selection (arxiv 2605.26676, auto-fetched 2026-05): MVTec AD I-AUROC not yet extracted — needs PDF table read. (Newest auto-harvested entry.)</t>
+          <t>✅ verified (MeDS arxiv 2605.26676 HTML Table 1, on Dinomaly baseline): MVTec AD I-AUROC 99.37 (0%% noise)≈99.4; robust to 99.16 @40%% noise [抗噪/記憶蒸餾]</t>
         </is>
       </c>
       <c r="N95" s="23" t="inlineStr">
@@ -22825,7 +22823,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ ComAD (arxiv 2305.13509): MVTec LOCO 88.8 not locatable via PDF text search. Needs manual table read.</t>
+          <t>⚠️ ComAD (Expert Systems w/ Appl 2023, CORRECT arxiv=2305.08509 — sheet had wrong 2305.13509). Paper Table 1 reports MVTec LOCO image-AUROC, but multi-column table prevents clean attribution of ComADs own 88.8 (value appears but ambiguous vs AST column). Needs manual table read.</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -27103,7 +27101,7 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>⚠️ DefectFill (arxiv 2503.13985) applies to VisA only qualitatively (Fig S19); no quantitative VisA I-AUROC in paper tables. Sheet VisA 97.8 needs source confirmation.</t>
+          <t>⚠️ DefectFill (CVPR25 arxiv 2503.13985) evaluates MVTec AD downstream only (classification/localization); does NOT report a VisA I-AUROC table. Sheet VisA 97.8 not from this paper.</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -27307,10 +27305,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+      <c r="H36" s="18" t="n">
+        <v>97.5</v>
       </c>
       <c r="I36" s="18" t="inlineStr">
         <is>
@@ -27334,7 +27330,7 @@
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>⚠️ Training-Free Diffusion Defect Generation (ICCV25): PDF extraction failed. VisA I-AUROC 97.5 unverified — needs manual table read.</t>
+          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, VisA "Ours" downstream row 97.4/97.5): VisA downstream I-AUROC ≈97.5 (generation method, downstream-detector dependent) [異常生成/擴散]</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
@@ -32137,16 +32133,14 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="12" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -32164,7 +32158,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>⚠️ UniNet (CVPR25 Table 1b): BTAD image-AUROC not cleanly parseable from PDF (multi-column). Sheet 97.7 needs manual confirmation.</t>
+          <t>✅ verified (UniNet CVPR25 CVF PDF Table 1b, "UniNet(Ours) 97.73"): BTAD I-AUROC 97.7 [對比學習/S-T]</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -20731,10 +20731,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t>92.5</t>
-        </is>
+      <c r="H74" s="12" t="n">
+        <v>90.5</v>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
@@ -20758,7 +20756,7 @@
       </c>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>⚠️ AA-CLIP (CVPR25 arxiv 2503.06661): paper Table 2 full-shot image-AUROC = 90.5 on MVTec AD; sheet has 92.5. Discrepancy likely due to setting (zero-shot vs few-shot vs full-shot). Needs setting confirmation (MPDD/BTAD matched exactly).</t>
+          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot image-AUROC): MVTec AD 90.5 (sheet had 92.5; 90.5 is paper full-shot) [CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
@@ -27287,10 +27285,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
+      <c r="H37" s="12" t="n">
+        <v>93.8</v>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
@@ -27314,7 +27310,7 @@
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>⚠️ AnomalyDINO (arxiv 2405.14529): VisA 1-shot I-AUROC = 87.4, 8-shot = 93.8. Sheet 94.0 ≈ 8-shot, but MVTec AD value (96.6) is 1-shot — inconsistent shot settings across datasets. Needs reconciliation to one shot setting.</t>
+          <t>✅ verified+corrected (AnomalyDINO arxiv 2405.14529, 8-shot): VisA image-AUROC 93.8 (sheet had 94.0; 8-shot=93.8, 1-shot=87.4) [訓練免費/DINOv2]</t>
         </is>
       </c>
       <c r="N37" s="14" t="inlineStr">
@@ -28282,10 +28278,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
+      <c r="H50" s="12" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -28309,7 +28303,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>⚠️ AA-CLIP (CVPR25 arxiv 2503.06661): paper Table 2 full-shot VisA image-AUROC = 84.6; sheet has 85.6. Setting-dependent (zero/few/full-shot) — needs confirmation.</t>
+          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot): VisA image-AUROC 84.6 (sheet had 85.6) [CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
@@ -29865,10 +29859,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
+      <c r="H8" s="12" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
@@ -29892,7 +29884,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchCore MPDD 94.5 is third-party re-eval (not in PatchCore arxiv 2106.08265). Needs source confirmation.</t>
+          <t>✅ verified+corrected (RealNet CVPR24 arxiv 2403.05897 Table 4, visual read): PatchCore MPDD image-AUROC 82.1 (sheet had 94.5 from a different protocol/source; RealNet uniform re-eval = 82.1) [記憶庫]</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -30173,10 +30165,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
+      <c r="H12" s="21" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
@@ -30200,7 +30190,7 @@
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>⚠️ CFLOW-AD MPDD 86.1 not in CFLOW-AD paper (MVTec AD only) — third-party re-eval. Needs source confirmation.</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 Table 4, visual read): CFLOW MPDD image-AUROC 86.1 (exact match) [NF]</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -30250,10 +30240,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
+      <c r="H13" s="12" t="n">
+        <v>74.8</v>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
@@ -30277,7 +30265,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PaDiM MPDD 74.8 is third-party re-eval (not in PaDiM paper).</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 Table 4, visual read): PaDiM MPDD image-AUROC 74.8 (exact match) [機率/記憶]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -34084,7 +34072,11 @@
           <t>https://arxiv.org/abs/2604.22899</t>
         </is>
       </c>
-      <c r="O15" s="14" t="n"/>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16380,32 +16380,32 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>STAGE (Graded Diffusion + Mask Alignment)</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.06693)</t>
+          <t>Sungwook Lee, Seunghyun Lee, Byung Cheol Song</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>IEEE Access 2022</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -16435,12 +16435,12 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>⚠️ STAGE (arxiv 2509.06693) is segmentation-oriented: primary metrics mIoU / pixel-Acc, auxiliary metrics are PIXEL-level AUROC/PRO/AP. No IMAGE-level AUROC reported. Sheet I-AUROC 99.5 unverified (metric mismatch / likely pixel or downstream). Needs reconciliation.</t>
+          <t>✅ verified (CFA arxiv 2206.04325 PDF): MVTec AD detection AUROC 99.5 [記憶/特徵]</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.06693</t>
+          <t>https://arxiv.org/abs/2206.04325</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
@@ -16457,27 +16457,27 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>ReContrast</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Sungwook Lee, Seunghyun Lee, Byung Cheol Song</t>
+          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>IEEE Access 2022</t>
+          <t>NeurIPS 2023</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -16512,12 +16512,12 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (CFA arxiv 2206.04325 PDF): MVTec AD detection AUROC 99.5 [記憶/特徵]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): MVTec AD I-AUROC 99.5 (contrastive reconstruction, domain-specific) [基於表徵]</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2206.04325</t>
+          <t>https://arxiv.org/abs/2306.02602</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -16534,43 +16534,39 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>ReContrast</t>
+          <t>VQ-Flow</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
+          <t>Yu Wang, Shiwei Chen</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2023</t>
+          <t>arXiv preprint 2024 / IEEE 投稿中</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>98.3</v>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
@@ -16579,7 +16575,7 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
@@ -16589,12 +16585,12 @@
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): MVTec AD I-AUROC 99.5 (contrastive reconstruction, domain-specific) [基於表徵]</t>
+          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): MVTec AD detection AUROC 99.5 [基於NF]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2306.02602</t>
+          <t>https://arxiv.org/abs/2409.00942</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -16611,49 +16607,45 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>VQ-Flow</t>
+          <t>PRN</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Yu Wang, Shiwei Chen</t>
+          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024 / IEEE 投稿中</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H20" s="12" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>99</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>96.09999999999999</v>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
@@ -16662,12 +16654,12 @@
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): MVTec AD detection AUROC 99.5 [基於NF]</t>
+          <t>✅ verified (PRN CVPR23 arxiv 2212.02031 PDF): MVTec AD I-AUROC 99.4 (supervised) [監督式/殘差]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.00942</t>
+          <t>https://arxiv.org/abs/2212.02031</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
@@ -16684,59 +16676,67 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>PRN</t>
+          <t>FastFlow</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
+          <t>Jiawei Yu, Ye Zheng, Xiang Wang, Wei Li, Yushuang Wu, Rui Zhao, Liwei Wu</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>arXiv 2021</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="K21" s="15" t="n">
-        <v>96.09999999999999</v>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>99.4</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (PRN CVPR23 arxiv 2212.02031 PDF): MVTec AD I-AUROC 99.4 (supervised) [監督式/殘差]</t>
+          <t>✅ verified (FastFlow arxiv 2111.07677 PDF): MVTec AD image-level AUC 99.4 [NF]</t>
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.02031</t>
+          <t>https://arxiv.org/abs/2111.07677</t>
         </is>
       </c>
       <c r="O21" s="17" t="inlineStr">
@@ -16758,27 +16758,27 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>DFM (Differentiable Feature Matching)</t>
+          <t>UniMMAD (MoE Multi-Modal AD)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>Sheng Wu, Wei Cheng, et al.</t>
+          <t>Yuanzhao team (GitHub: yuanzhao-CVLAB)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access)</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ DFM (CVPR25, CVF PDF Wu et al.) is a CONTINUAL anomaly detection method — Table 1 reports per-class Instance AUROC + Forgetting Measure across a continual class sequence, not a single joint-training value. Sheet 99.4 (per-class hazelnut=99.4 in PDF) does not represent the continual setting. Needs the papers reported continual average I-AUROC.</t>
+          <t>✅ verified (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): MVTec AD AUC_I 99.4 [基於多模態/MoE]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Differentiable_Feature_Matching_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2509.25934</t>
         </is>
       </c>
       <c r="O22" s="23" t="inlineStr">
@@ -16830,32 +16830,32 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>FastFlow</t>
+          <t>RD++</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Jiawei Yu, Ye Zheng, Xiang Wang, Wei Li, Yushuang Wu, Rui Zhao, Liwei Wu</t>
+          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>arXiv 2021</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -16875,22 +16875,22 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (FastFlow arxiv 2111.07677 PDF): MVTec AD image-level AUC 99.4 [NF]</t>
+          <t>✅ verified (RD++ CVPR23 arxiv 2304.02216 PDF): MVTec AD I-AUROC 99.4 [反向蒸餾]</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2111.07677</t>
+          <t>https://arxiv.org/abs/2304.02216</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
@@ -16907,17 +16907,17 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>UniMMAD (MoE Multi-Modal AD)</t>
+          <t>SNARM (Self-Navigated Residual Mamba)</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Yuanzhao team (GitHub: yuanzhao-CVLAB)</t>
+          <t>Anonymous (arXiv 2508.01591)</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -16935,24 +16935,22 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
+      <c r="H24" s="18" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="L24" s="18" t="inlineStr">
@@ -16962,12 +16960,12 @@
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): MVTec AD AUC_I 99.4 [基於多模態/MoE]</t>
+          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): MVTec AD I-AUROC 99.4 (sheet had 99.3) [基於 Mamba/NF]</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.25934</t>
+          <t>https://arxiv.org/abs/2508.01591</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -16989,62 +16987,44 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>RD++</t>
+          <t>Memory-Distilled Selection for Noise-Robust Anomaly Detection</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+          <t>Sirojbek Safarov, Jaewoo Park, Yoon Gyo Jung, Kuan-Chuan Peng, Wonchul Kim, Seongdeok Bang, Octavia Camps</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>arXiv preprint</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>99.4</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (RD++ CVPR23 arxiv 2304.02216 PDF): MVTec AD I-AUROC 99.4 [反向蒸餾]</t>
+          <t>✅ verified (MeDS arxiv 2605.26676 HTML Table 1, on Dinomaly baseline): MVTec AD I-AUROC 99.37 (0%% noise)≈99.4; robust to 99.16 @40%% noise [抗噪/記憶蒸餾]</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.02216</t>
+          <t>https://arxiv.org/abs/2605.26676</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
@@ -17061,17 +17041,17 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>SNARM (Self-Navigated Residual Mamba)</t>
+          <t>STAGE (Graded Diffusion + Mask Alignment)</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2508.01591)</t>
+          <t>Anonymous (arXiv 2509.06693)</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -17081,7 +17061,7 @@
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -17090,7 +17070,7 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
@@ -17099,12 +17079,12 @@
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="L26" s="18" t="inlineStr">
@@ -17114,12 +17094,12 @@
       </c>
       <c r="M26" s="19" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): MVTec AD I-AUROC 99.4 (sheet had 99.3) [基於 Mamba/NF]</t>
+          <t>✅ verified-metric (STAGE arxiv 2509.06693 Table VI, Average): MVTec AD downstream AUROC 99.34≈99.3 (anomaly-synthesis auxiliary metric via SegFormer maps; primary metric is seg mIoU; AP=87.02 Table VII). Sheet 99.5→99.3 [異常生成/擴散]</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.01591</t>
+          <t>https://arxiv.org/abs/2509.06693</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -17136,49 +17116,67 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Memory-Distilled Selection for Noise-Robust Anomaly Detection</t>
+          <t>GLAD</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Sirojbek Safarov, Jaewoo Park, Yoon Gyo Jung, Kuan-Chuan Peng, Wonchul Kim, Seongdeok Bang, Octavia Camps</t>
+          <t>Hang Yao, Ming Liu, Haolin Wang, Zhicun Yin, Zifei Yan, Xiaopeng Hong, Wangmeng Zuo</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint</t>
+          <t>ECCV 2024</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>99.3</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MeDS arxiv 2605.26676 HTML Table 1, on Dinomaly baseline): MVTec AD I-AUROC 99.37 (0%% noise)≈99.4; robust to 99.16 @40%% noise [抗噪/記憶蒸餾]</t>
+          <t>✅ verified (GLAD ECCV24 arxiv 2406.07487 Table 1): MVTec AD I-AUROC 99.3 [基於擴散]</t>
         </is>
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2605.26676</t>
+          <t>https://arxiv.org/abs/2406.07487</t>
         </is>
       </c>
       <c r="O27" s="13" t="inlineStr">
@@ -17200,22 +17198,22 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>GLAD</t>
+          <t>DeCo-Diff</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Hang Yao, Ming Liu, Haolin Wang, Zhicun Yin, Zifei Yan, Xiaopeng Hong, Wangmeng Zuo</t>
+          <t>Farzad Beizaee, et al.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>ECCV 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -17223,39 +17221,27 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>99.3</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>95.3</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H28" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L28" s="9" t="n"/>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (GLAD ECCV24 arxiv 2406.07487 Table 1): MVTec AD I-AUROC 99.3 [基於擴散]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2406.07487</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
@@ -17277,50 +17263,60 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>DeCo-Diff</t>
+          <t>AnomalyXFusion (Multi-modal Diffusion)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>Farzad Beizaee, et al.</t>
+          <t>Anonymous (arXiv 2404.19444)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv preprint 2024</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H29" s="21" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="I29" s="21" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="J29" s="21" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="K29" s="21" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="L29" s="21" t="n"/>
+        <v>99.2</v>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
+          <t>✅ verified+corrected (AnomalyXFusion arxiv 2404.19444 Table 3): MVTec AD downstream AUC-I 99.2 (sheet had 99.4) [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2404.19444</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -17337,27 +17333,27 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>AnomalyXFusion (Multi-modal Diffusion)</t>
+          <t>GroundingAnomaly (Spatial Diffusion)</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2404.19444)</t>
+          <t>Anonymous (arXiv 2604.08301)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -17370,7 +17366,7 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -17380,7 +17376,7 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
@@ -17390,12 +17386,12 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AnomalyXFusion arxiv 2404.19444 Table 3): MVTec AD downstream AUC-I 99.2 (sheet had 99.4) [基於擴散/異常生成]</t>
+          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 2): MVTec AD AP-I (image-level Average Precision) 99.2. NOTE: metric is AP-I, NOT image-AUROC (corrected from 99.4) [異常生成]</t>
         </is>
       </c>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.19444</t>
+          <t>https://arxiv.org/abs/2604.08301</t>
         </is>
       </c>
       <c r="O30" s="14" t="inlineStr">
@@ -17412,50 +17408,52 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>GroundingAnomaly (Spatial Diffusion)</t>
+          <t>AnomalyDiffusion</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2604.08301)</t>
+          <t>Teng Hu, Jiangning Zhang, Ran Yi, Yuzhen Du, Xu Chen, Liang Liu, Yabiao Wang, Chengjie Wang</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>AAAI 2024</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>99.2</v>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>99.2</t>
+        </is>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
@@ -17465,12 +17463,12 @@
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 2): MVTec AD AP-I (image-level Average Precision) 99.2. NOTE: metric is AP-I, NOT image-AUROC (corrected from 99.4) [異常生成]</t>
+          <t>✅ verified (AnomalyDiffusion AAAI24 arxiv 2312.05767 PDF): MVTec AD downstream I-AUROC 99.2 [異常生成]</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.08301</t>
+          <t>https://arxiv.org/abs/2312.05767</t>
         </is>
       </c>
       <c r="O31" s="17" t="inlineStr">
@@ -17487,32 +17485,32 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>AnomalyDiffusion</t>
+          <t>DefectFill (Inpainting Diffusion)</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Teng Hu, Jiangning Zhang, Ran Yi, Yuzhen Du, Xu Chen, Liang Liu, Yabiao Wang, Chengjie Wang</t>
+          <t>Anonymous (arXiv 2503.13985)</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>AAAI 2024</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -17522,17 +17520,17 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="L32" s="15" t="inlineStr">
@@ -17542,12 +17540,12 @@
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyDiffusion AAAI24 arxiv 2312.05767 PDF): MVTec AD downstream I-AUROC 99.2 [異常生成]</t>
+          <t>✅ verified (DefectFill arxiv 2503.13985 Table S2): MVTec AD downstream I-AUROC per-object 0.97-1.00 (UNet trained on generated defects), avg ≈ 99.2 [基於擴散/異常生成]</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.05767</t>
+          <t>https://arxiv.org/abs/2503.13985</t>
         </is>
       </c>
       <c r="O32" s="16" t="inlineStr">
@@ -17564,32 +17562,32 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>DefectFill (Inpainting Diffusion)</t>
+          <t>TransFusion</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2503.13985)</t>
+          <t>Matic Fučka, Vitjan Zavrtanik, Danijel Skočaj</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>ECCV 2024</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -17599,7 +17597,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -17609,7 +17607,7 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -17619,12 +17617,12 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (DefectFill arxiv 2503.13985 Table S2): MVTec AD downstream I-AUROC per-object 0.97-1.00 (UNet trained on generated defects), avg ≈ 99.2 [基於擴散/異常生成]</t>
+          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): MVTec AD I-AUROC 99.2 [基於擴散/重構]</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13985</t>
+          <t>https://arxiv.org/abs/2311.09999</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -17641,27 +17639,27 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>TransFusion</t>
+          <t>HVQ-Trans</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>Matic Fučka, Vitjan Zavrtanik, Danijel Skočaj</t>
+          <t>Ruiying Lu, YuJie Wu, Long Tian, Dongsheng Wang, Bo Chen, Xiyang Liu, Ruimin Hu</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>ECCV 2024</t>
+          <t>NeurIPS 2023</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
@@ -17676,7 +17674,7 @@
       </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="J34" s="18" t="inlineStr">
@@ -17686,7 +17684,7 @@
       </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="L34" s="18" t="inlineStr">
@@ -17696,12 +17694,12 @@
       </c>
       <c r="M34" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): MVTec AD I-AUROC 99.2 [基於擴散/重構]</t>
+          <t>✅ verified (HVQ-Trans NeurIPS23 arxiv 2310.14228 PDF): MVTec AD multi-class I-AUROC 99.2 [統一/VQ-Transformer]</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2311.09999</t>
+          <t>https://arxiv.org/abs/2310.14228</t>
         </is>
       </c>
       <c r="O34" s="20" t="inlineStr">
@@ -17718,27 +17716,27 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>HVQ-Trans</t>
+          <t>FUN-AD</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Ruiying Lu, YuJie Wu, Long Tian, Dongsheng Wang, Bo Chen, Xiyang Liu, Ruimin Hu</t>
+          <t>Jiin Im, et al.</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>NeurIPS 2023</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -17746,39 +17744,23 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H35" s="9" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (HVQ-Trans NeurIPS23 arxiv 2310.14228 PDF): MVTec AD multi-class I-AUROC 99.2 [統一/VQ-Transformer]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.14228</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O35" s="10" t="inlineStr">
@@ -17795,27 +17777,27 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>FUN-AD</t>
+          <t>LASB</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>Jiin Im, et al.</t>
+          <t>Akshay Kulkarni, et al.</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -17827,19 +17809,19 @@
         <v>99.2</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>98.59999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="J36" s="18" t="n"/>
       <c r="K36" s="18" t="n"/>
       <c r="L36" s="18" t="n"/>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
+          <t>✅ verified (LASB / "Unified Latent Schrödinger Bridge" CVPR25 CVF PDF, unified multi-class Table 2): MVTec AD image-level AUROC_cls 99.2 (sheet had 99.66 — corrected) [基於擴散/Schrödinger Bridge]</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -17856,27 +17838,27 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>LASB</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
         <is>
-          <t>Akshay Kulkarni, et al.</t>
+          <t>Daehwan Kim, et al.</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr">
@@ -17888,19 +17870,19 @@
         <v>99.2</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>99.15000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="J37" s="18" t="n"/>
       <c r="K37" s="18" t="n"/>
       <c r="L37" s="18" t="n"/>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (LASB / "Unified Latent Schrödinger Bridge" CVPR25 CVF PDF, unified multi-class Table 2): MVTec AD image-level AUROC_cls 99.2 (sheet had 99.66 — corrected) [基於擴散/Schrödinger Bridge]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr">
@@ -17917,27 +17899,27 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>AST (Asymmetric Student-Teacher)</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Daehwan Kim, et al.</t>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>WACV 2023</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -17949,19 +17931,27 @@
         <v>99.2</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+          <t>✅ verified (AST WACV23 arxiv 2210.07829 PDF): MVTec AD detection AUROC 99.2 [S-T/NF]</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2210.07829</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
@@ -17978,27 +17968,27 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>AST (Asymmetric Student-Teacher)</t>
+          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
         <is>
-          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>WACV 2023</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
@@ -18007,10 +17997,12 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>95</v>
+        <v>99.17</v>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="J39" s="18" t="inlineStr">
         <is>
@@ -18025,12 +18017,12 @@
       <c r="L39" s="18" t="n"/>
       <c r="M39" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (AST WACV23 arxiv 2210.07829 PDF): MVTec AD detection AUROC 99.2 [S-T/NF]</t>
+          <t>✅ 已驗證 (SSASDM WACV25 Table 2)：DTU-Net 自監督擴散+動態 Transformer UNet；MVTec AD 15-class avg AUROC 99.17 [基於擴散自監督]</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2210.07829</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O39" s="20" t="inlineStr">
@@ -18047,27 +18039,27 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Self-Supervised Anomaly Segmentation via Diffusion Models wi</t>
+          <t>PatchCore</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2022</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -18075,12 +18067,14 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n">
-        <v>99.17</v>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
@@ -18090,18 +18084,22 @@
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L40" s="15" t="n"/>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
       <c r="M40" s="16" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (SSASDM WACV25 Table 2)：DTU-Net 自監督擴散+動態 Transformer UNet；MVTec AD 15-class avg AUROC 99.17 [基於擴散自監督]</t>
+          <t>✅ verified (PatchCore CVPR22 arxiv 2106.08265 PDF): MVTec AD I-AUROC 99.1 (PatchCore-100%) [記憶庫]</t>
         </is>
       </c>
       <c r="N40" s="17" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kumar_Self-Supervised_Anomaly_Segmentation_via_Diffusion_Models_with_Dynamic_Transformer_UNet_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2106.08265</t>
         </is>
       </c>
       <c r="O40" s="17" t="inlineStr">
@@ -18118,27 +18116,27 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>PatchCore</t>
+          <t>UniFlow (Unified NF)</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>MDPI Information 2024</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>MDPI Information 2024</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -18146,14 +18144,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>99.1</t>
-        </is>
+      <c r="H41" s="12" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -18163,22 +18159,22 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchCore CVPR22 arxiv 2106.08265 PDF): MVTec AD I-AUROC 99.1 (PatchCore-100%) [記憶庫]</t>
+          <t>✅ verified (UniFlow MDPI Information 2024, mdpi 2078-2489/15/12/791): MVTec AD class-avg image-level AUROC 99.1 (exact match) [統一NF/多類別]</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.08265</t>
+          <t>https://www.mdpi.com/2078-2489/15/12/791</t>
         </is>
       </c>
       <c r="O41" s="14" t="inlineStr">
@@ -18195,27 +18191,27 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>UniFlow (Unified NF)</t>
+          <t>EfficientAD</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>MDPI Information 2024</t>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>MDPI Information 2024</t>
+          <t>WACV 2024</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -18223,12 +18219,14 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H42" s="15" t="n">
-        <v>99.09999999999999</v>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="J42" s="15" t="inlineStr">
@@ -18238,22 +18236,20 @@
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="n">
+        <v>614</v>
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (UniFlow MDPI Information 2024, mdpi 2078-2489/15/12/791): MVTec AD class-avg image-level AUROC 99.1 (exact match) [統一NF/多類別]</t>
+          <t>✅ verified (EfficientAD WACV24 arxiv 2303.14535 PDF, EfficientAD-M row): MVTec AD I-AUROC 99.1 [效率/S-T]</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2078-2489/15/12/791</t>
+          <t>https://arxiv.org/abs/2303.14535</t>
         </is>
       </c>
       <c r="O42" s="17" t="inlineStr">
@@ -18270,65 +18266,57 @@
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>EfficientAD</t>
+          <t>One-Step Inverse Residual Diffusion</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>Boan Zhang, Wen Li, Guanhua Yu, Xiyang Liu, Wenchao Chen, Long Tian</t>
         </is>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
-          <t>WACV 2024</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F43" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H43" s="21" t="inlineStr">
-        <is>
-          <t>99.1</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t>96.8</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="I43" s="21" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="J43" s="21" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="K43" s="21" t="n">
+        <v>93.5</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>614</v>
+        <v>133</v>
       </c>
       <c r="M43" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (EfficientAD WACV24 arxiv 2303.14535 PDF, EfficientAD-M row): MVTec AD I-AUROC 99.1 [效率/S-T]</t>
+          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): MVTec AD multi-class I-AUROC 99.0 [基於擴散/單步]</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.14535</t>
+          <t>https://arxiv.org/abs/2604.18393</t>
         </is>
       </c>
       <c r="O43" s="22" t="inlineStr">
@@ -18350,52 +18338,60 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>One-Step Inverse Residual Diffusion</t>
+          <t>InvAD-Diff (Inversion-based Diffusion)</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Boan Zhang, Wen Li, Guanhua Yu, Xiyang Liu, Wenchao Chen, Long Tian</t>
+          <t>Shunsuke Sakai, et al.</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>arXiv preprint / CVPR 2026 投稿中</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>在審</t>
         </is>
       </c>
       <c r="H44" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>133</v>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): MVTec AD multi-class I-AUROC 99.0 [基於擴散/單步]</t>
+          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): MVTec AD multi-class I-AUROC 99.0 (sheet had 99.3). ⚠️ Note: overlaps with "InvAD (Feature Inversion)" entry (2404.10760, 98.9) — possible duplicate to review.</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.18393</t>
+          <t>https://arxiv.org/abs/2504.05662</t>
         </is>
       </c>
       <c r="O44" s="14" t="inlineStr">
@@ -18412,32 +18408,32 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>InvAD-Diff (Inversion-based Diffusion)</t>
+          <t>AMI-Net</t>
         </is>
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>Shunsuke Sakai, et al.</t>
+          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>arXiv preprint / CVPR 2026 投稿中</t>
+          <t>IEEE TASE 2024</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr">
         <is>
-          <t>在審</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H45" s="18" t="n">
@@ -18445,7 +18441,7 @@
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="J45" s="18" t="inlineStr">
@@ -18455,7 +18451,7 @@
       </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L45" s="18" t="inlineStr">
@@ -18465,12 +18461,12 @@
       </c>
       <c r="M45" s="19" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): MVTec AD multi-class I-AUROC 99.0 (sheet had 99.3). ⚠️ Note: overlaps with "InvAD (Feature Inversion)" entry (2404.10760, 98.9) — possible duplicate to review.</t>
+          <t>✅ verified+corrected (AMI-Net arxiv 2412.11802 Table I): MVTec AD multi-class I-AUROC 99.0 (AMI-Net‡ w/ feature jittering; sheet had 99.1) [基於重構]</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.05662</t>
+          <t>https://arxiv.org/abs/2412.11802</t>
         </is>
       </c>
       <c r="O45" s="19" t="inlineStr">
@@ -18487,27 +18483,27 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>AMI-Net</t>
+          <t>Training-Free Diffusion Defect Generation</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>IEEE TASE 2024</t>
+          <t>ICCV 2025</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -18520,7 +18516,7 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
@@ -18530,7 +18526,7 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -18540,12 +18536,12 @@
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AMI-Net arxiv 2412.11802 Table I): MVTec AD multi-class I-AUROC 99.0 (AMI-Net‡ w/ feature jittering; sheet had 99.1) [基於重構]</t>
+          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, "Ours† 98.2 99.0..."): MVTec AD downstream I-AUROC 99.0 [異常生成/擴散]</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.11802</t>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/papers/Xu_Training-Free_Industrial_Defect_Generation_with_Diffusion_Models_ICCV_2025_paper.pdf</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">
@@ -18562,40 +18558,40 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Training-Free Diffusion Defect Generation</t>
+          <t>InvAD (Feature Inversion)</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>ICCV 2025</t>
+          <t>arXiv preprint 2024</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="J47" s="15" t="inlineStr">
@@ -18605,7 +18601,7 @@
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
@@ -18615,12 +18611,12 @@
       </c>
       <c r="M47" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, "Ours† 98.2 99.0..."): MVTec AD downstream I-AUROC 99.0 [異常生成/擴散]</t>
+          <t>✅ verified+corrected (InvAD arxiv 2404.10760 Table 5): MVTec AD multi-class mAU-ROC 98.9 (sheet had 99.0) [基於重構]</t>
         </is>
       </c>
       <c r="N47" s="17" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/ICCV2025/papers/Xu_Training-Free_Industrial_Defect_Generation_with_Diffusion_Models_ICCV_2025_paper.pdf</t>
+          <t>https://arxiv.org/abs/2404.10760</t>
         </is>
       </c>
       <c r="O47" s="17" t="inlineStr">
@@ -18642,22 +18638,22 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -18666,36 +18662,22 @@
         </is>
       </c>
       <c r="H48" s="21" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>98.83</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="J48" s="21" t="n"/>
+      <c r="K48" s="21" t="n"/>
+      <c r="L48" s="21" t="n"/>
       <c r="M48" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (InvAD arxiv 2404.10760 Table 5): MVTec AD multi-class mAU-ROC 98.9 (sheet had 99.0) [基於重構]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N48" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O48" s="22" t="inlineStr">
@@ -18712,27 +18694,27 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>ROADS</t>
+          <t>AnoGen (Few-Shot Anomaly-Driven Generation)</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Hossein Kashiani, et al.</t>
+          <t>Guan Gui, Bin-Bin Gao, Jun Liu, Chengjie Wang, Yunsheng Wu</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>ECCV 2024 / arXiv 2025</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
@@ -18741,22 +18723,36 @@
         </is>
       </c>
       <c r="H49" s="15" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="J49" s="15" t="n"/>
-      <c r="K49" s="15" t="n"/>
-      <c r="L49" s="15" t="n"/>
+        <v>98.8</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="J49" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="15" t="inlineStr">
+        <is>
+          <t>95.1</t>
+        </is>
+      </c>
+      <c r="L49" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
+          <t>✅ verified+corrected (AnoGen ECCV24 arxiv 2505.09263 Table 1): MVTec AD best downstream I-AUROC 98.8 (DeSTSeg+AnoGen; sheet had 99.4). Anomaly-synthesis method [基於異常生成]</t>
         </is>
       </c>
       <c r="N49" s="17" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2505.09263</t>
         </is>
       </c>
       <c r="O49" s="17" t="inlineStr">
@@ -18773,32 +18769,32 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>AnoGen (Few-Shot Anomaly-Driven Generation)</t>
+          <t>SALAD (Logical AD)</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>Guan Gui, Bin-Bin Gao, Jun Liu, Chengjie Wang, Yunsheng Wu</t>
+          <t>ICCV 2025 SALAD team</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>ECCV 2024 / arXiv 2025</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2509.02101</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H50" s="18" t="n">
@@ -18806,7 +18802,7 @@
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="J50" s="18" t="inlineStr">
@@ -18816,7 +18812,7 @@
       </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="L50" s="18" t="inlineStr">
@@ -18826,12 +18822,12 @@
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AnoGen ECCV24 arxiv 2505.09263 Table 1): MVTec AD best downstream I-AUROC 98.8 (DeSTSeg+AnoGen; sheet had 99.4). Anomaly-synthesis method [基於異常生成]</t>
+          <t>✅ verified+corrected (SALAD ICCV25 arxiv 2509.02101): MVTec AD I-AUROC 98.8 (sheet had 98.9) [邏輯異常]</t>
         </is>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.09263</t>
+          <t>https://arxiv.org/abs/2509.02101</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr">
@@ -18848,36 +18844,36 @@
       </c>
       <c r="B51" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>SALAD (Logical AD)</t>
+          <t>U-Flow</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>ICCV 2025 SALAD team</t>
+          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2509.02101</t>
+          <t>JMIV 2024 / arXiv 2211.12353</t>
         </is>
       </c>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H51" s="21" t="n">
-        <v>98.8</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -18901,12 +18897,12 @@
       </c>
       <c r="M51" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (SALAD ICCV25 arxiv 2509.02101): MVTec AD I-AUROC 98.8 (sheet had 98.9) [邏輯異常]</t>
+          <t>✅ verified (U-Flow arxiv 2211.12353): MVTec AD 98.74 — NOTE: this is PIXEL-level mean AUROC (papers headline metric), relabeled per metric. Image-level detection AUROC may differ [NF]</t>
         </is>
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.02101</t>
+          <t>https://arxiv.org/abs/2211.12353</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
@@ -18923,27 +18919,27 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>U-Flow</t>
+          <t>Effective Synthetic Images</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Matías Tailanian, Álvaro Pardo, Pablo Musé</t>
+          <t>Anonymous (arXiv 2512.23227)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>JMIV 2024 / arXiv 2211.12353</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -18952,11 +18948,11 @@
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>98.73999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="J52" s="15" t="inlineStr">
@@ -18966,7 +18962,7 @@
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="L52" s="15" t="inlineStr">
@@ -18976,12 +18972,12 @@
       </c>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (U-Flow arxiv 2211.12353): MVTec AD 98.74 — NOTE: this is PIXEL-level mean AUROC (papers headline metric), relabeled per metric. Image-level detection AUROC may differ [NF]</t>
+          <t>✅ verified+corrected (Effective Synthetic Images arxiv 2512.23227 Table 1): MVTec AD avg I-AUROC 98.7 (9-category subset shown; sheet had 99.6 — corrected). [基於異常生成]</t>
         </is>
       </c>
       <c r="N52" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12353</t>
+          <t>https://arxiv.org/abs/2512.23227</t>
         </is>
       </c>
       <c r="O52" s="16" t="inlineStr">
@@ -18998,27 +18994,27 @@
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>Effective Synthetic Images</t>
+          <t>TFA-Net (Template-based Feature Aggregation)</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2512.23227)</t>
+          <t>Anonymous (arXiv 2603.22874)</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G53" s="21" t="inlineStr">
@@ -19026,12 +19022,14 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H53" s="21" t="n">
-        <v>98.7</v>
+      <c r="H53" s="21" t="inlineStr">
+        <is>
+          <t>98.7</t>
+        </is>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="J53" s="21" t="inlineStr">
@@ -19041,7 +19039,7 @@
       </c>
       <c r="K53" s="21" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L53" s="21" t="inlineStr">
@@ -19051,12 +19049,12 @@
       </c>
       <c r="M53" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (Effective Synthetic Images arxiv 2512.23227 Table 1): MVTec AD avg I-AUROC 98.7 (9-category subset shown; sheet had 99.6 — corrected). [基於異常生成]</t>
+          <t>✅ verified (TFA-Net arxiv 2603.22874): MVTec AD image-level AUROC 98.7 (avg 15 cat) [基於表徵/模板聚合]</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2512.23227</t>
+          <t>https://arxiv.org/abs/2603.22874</t>
         </is>
       </c>
       <c r="O53" s="23" t="inlineStr">
@@ -19073,32 +19071,32 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>TFA-Net (Template-based Feature Aggregation)</t>
+          <t>CS-Flow</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2603.22874)</t>
+          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>WACV 2022</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H54" s="15" t="inlineStr">
@@ -19108,7 +19106,7 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J54" s="15" t="inlineStr">
@@ -19128,12 +19126,12 @@
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (TFA-Net arxiv 2603.22874): MVTec AD image-level AUROC 98.7 (avg 15 cat) [基於表徵/模板聚合]</t>
+          <t>✅ verified (CS-Flow arxiv 2110.02855 PDF, Average): MVTec AD detection AUROC 98.7 [NF]</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2603.22874</t>
+          <t>https://arxiv.org/abs/2110.02855</t>
         </is>
       </c>
       <c r="O54" s="17" t="inlineStr">
@@ -19155,37 +19153,35 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>CS-Flow</t>
+          <t>Pyramid-based Mamba NF</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>Marco Rudolph, Tom Wehrbein, Bodo Rosenhahn, Bastian Wandt</t>
+          <t>Anonymous (arXiv 2504.03442)</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>WACV 2022</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>98.59999999999999</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="J55" s="15" t="inlineStr">
@@ -19195,7 +19191,7 @@
       </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="L55" s="15" t="inlineStr">
@@ -19205,12 +19201,12 @@
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (CS-Flow arxiv 2110.02855 PDF, Average): MVTec AD detection AUROC 98.7 [NF]</t>
+          <t>✅ verified+corrected (Pyramid Mamba NF arxiv 2504.03442): MVTec AD multi-class I-AUROC 98.6 (tied MambaAD; sheet had 99.0) [基於 Mamba/NF]</t>
         </is>
       </c>
       <c r="N55" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2110.02855</t>
+          <t>https://arxiv.org/abs/2504.03442</t>
         </is>
       </c>
       <c r="O55" s="17" t="inlineStr">
@@ -19227,50 +19223,52 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Pyramid-based Mamba NF</t>
+          <t>DeSTSeg</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2504.03442)</t>
+          <t>Xuan Zhang, Shiyu Li, Xi Li, Ping Huang, Jiulong Shan, Ting Chen</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>98.59999999999999</v>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L56" s="12" t="inlineStr">
@@ -19280,12 +19278,12 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (Pyramid Mamba NF arxiv 2504.03442): MVTec AD multi-class I-AUROC 98.6 (tied MambaAD; sheet had 99.0) [基於 Mamba/NF]</t>
+          <t>✅ verified (DeSTSeg CVPR23 arxiv 2211.11317 PDF): MVTec AD I-AUROC 98.6 [S-T/分割]</t>
         </is>
       </c>
       <c r="N56" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.03442</t>
+          <t>https://arxiv.org/abs/2211.11317</t>
         </is>
       </c>
       <c r="O56" s="14" t="inlineStr">
@@ -19307,22 +19305,22 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>DeSTSeg</t>
+          <t>MambaAD</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>Xuan Zhang, Shiyu Li, Xi Li, Ping Huang, Jiulong Shan, Ting Chen</t>
+          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>NeurIPS 2024</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
@@ -19337,17 +19335,17 @@
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="J57" s="15" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="L57" s="15" t="inlineStr">
@@ -19357,12 +19355,12 @@
       </c>
       <c r="M57" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (DeSTSeg CVPR23 arxiv 2211.11317 PDF): MVTec AD I-AUROC 98.6 [S-T/分割]</t>
+          <t>✅ verified (MambaAD arxiv 2404.06564): MVTec AD multi-class I-AUROC 98.6 [基於 Mamba]</t>
         </is>
       </c>
       <c r="N57" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.11317</t>
+          <t>https://arxiv.org/abs/2404.06564</t>
         </is>
       </c>
       <c r="O57" s="17" t="inlineStr">
@@ -19379,52 +19377,50 @@
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>MambaAD</t>
+          <t>AnomalyAgent (Agentic RL Synthesis)</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
+          <t>Anonymous (arXiv 2604.07900)</t>
         </is>
       </c>
       <c r="E58" s="21" t="inlineStr">
         <is>
-          <t>NeurIPS 2024</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F58" s="21" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H58" s="21" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>98.5</v>
       </c>
       <c r="I58" s="21" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="J58" s="21" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K58" s="21" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="L58" s="21" t="inlineStr">
@@ -19434,12 +19430,12 @@
       </c>
       <c r="M58" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (MambaAD arxiv 2404.06564): MVTec AD multi-class I-AUROC 98.6 [基於 Mamba]</t>
+          <t>✅ verified+corrected (AnomalyAgent arxiv 2604.07900 Table 3): MVTec AD mean image-level AUC 98.5 (sheet had 99.5 — corrected) [基於異常生成/RL]</t>
         </is>
       </c>
       <c r="N58" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.06564</t>
+          <t>https://arxiv.org/abs/2604.07900</t>
         </is>
       </c>
       <c r="O58" s="23" t="inlineStr">
@@ -19456,40 +19452,42 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>AnomalyAgent (Agentic RL Synthesis)</t>
+          <t>RD4AD (Reverse Distillation)</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2604.07900)</t>
+          <t>Hanqiu Deng, Xingyu Li</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>CVPR 2022</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="n">
-        <v>98.5</v>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="J59" s="15" t="inlineStr">
@@ -19499,7 +19497,7 @@
       </c>
       <c r="K59" s="15" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="L59" s="15" t="inlineStr">
@@ -19509,12 +19507,12 @@
       </c>
       <c r="M59" s="16" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AnomalyAgent arxiv 2604.07900 Table 3): MVTec AD mean image-level AUC 98.5 (sheet had 99.5 — corrected) [基於異常生成/RL]</t>
+          <t>✅ verified (RD4AD CVPR22 arxiv 2201.10703 PDF, Total Average): MVTec AD I-AUROC 98.5 [反向蒸餾]</t>
         </is>
       </c>
       <c r="N59" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.07900</t>
+          <t>https://arxiv.org/abs/2201.10703</t>
         </is>
       </c>
       <c r="O59" s="17" t="inlineStr">
@@ -19531,27 +19529,27 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Triad (LMM-Aided AD)</t>
+          <t>CFLOW-AD</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
+          <t>Denis Gudovskiy, Shun Ishizaka, Kazuki Kozuka</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
+          <t>WACV 2022</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -19561,12 +19559,12 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="J60" s="15" t="inlineStr">
@@ -19576,22 +19574,20 @@
       </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
-          <t>94.2</t>
-        </is>
-      </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>94.6</t>
+        </is>
+      </c>
+      <c r="L60" s="15" t="n">
+        <v>27</v>
       </c>
       <c r="M60" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Triad (LMM-Aided AD, arxiv 2503.13184) reports ACCURACY (0-shot/1-shot), NOT I-AUROC, on MVTec-AD/WFDD/PCB-Bank. Sheet I-AUROC 98.5 is a metric mismatch — not from paper. Needs reconciliation (paper metric is accuracy, not AUROC).</t>
+          <t>✅ verified (CFLOW-AD WACV22 arxiv 2107.12571 PDF): MVTec AD detection AUROC 98.3 [NF]</t>
         </is>
       </c>
       <c r="N60" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.13184</t>
+          <t>https://arxiv.org/abs/2107.12571</t>
         </is>
       </c>
       <c r="O60" s="16" t="inlineStr">
@@ -19613,22 +19609,22 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>RD4AD (Reverse Distillation)</t>
+          <t>OCR-GAN</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
+          <t>Yufei Liang, Jiangning Zhang, Shiwei Zhao, Runze Wu, Yong Liu, Shuwen Pan</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>IEEE TIP 2023</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -19638,12 +19634,12 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -19653,7 +19649,7 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L61" s="12" t="inlineStr">
@@ -19663,12 +19659,12 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (RD4AD CVPR22 arxiv 2201.10703 PDF, Total Average): MVTec AD I-AUROC 98.5 [反向蒸餾]</t>
+          <t>✅ verified (OCR-GAN arxiv 2203.00259 PDF): MVTec AD detection AUC 98.3 [重構/GAN]</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.10703</t>
+          <t>https://arxiv.org/abs/2203.00259</t>
         </is>
       </c>
       <c r="O61" s="14" t="inlineStr">
@@ -19685,27 +19681,27 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>CFLOW-AD</t>
+          <t>UniAS</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Denis Gudovskiy, Shun Ishizaka, Kazuki Kozuka</t>
+          <t>Wenxuan Ma, et al.</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>WACV 2022</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -19713,37 +19709,25 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="L62" s="9" t="n">
-        <v>27</v>
-      </c>
+      <c r="H62" s="9" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="I62" s="9" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="n"/>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (CFLOW-AD WACV22 arxiv 2107.12571 PDF): MVTec AD detection AUROC 98.3 [NF]</t>
+          <t>✅ verified-metric (UniAS WACV25 arxiv 2501.12295 Table 1): MVTec AD PIXEL-AUROC 98.22 — paper reports pixel pAP/DSC + pixel-AUROC, NOT image-AUROC (segmentation-focused). Value is pixel-AUROC, not image-level. [統一/分割]</t>
         </is>
       </c>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.12571</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
@@ -19765,37 +19749,35 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>OCR-GAN</t>
+          <t>USAGI (Memory-Retrieval Transformer)</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yufei Liang, Jiangning Zhang, Shiwei Zhao, Runze Wu, Yong Liu, Shuwen Pan</t>
+          <t>ScienceDirect 2025 (S0031320325...)</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>IEEE TIP 2023</t>
+          <t>Pattern Recognition 2025 / 預印</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>98.2</v>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -19815,12 +19797,12 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (OCR-GAN arxiv 2203.00259 PDF): MVTec AD detection AUC 98.3 [重構/GAN]</t>
+          <t>✅ verified (USAGI, Pattern Recognition / ScienceDirect S003132032501667X): MVTec AD AUROC 98.2 (exact match; memory+retrieval transformer) [記憶/檢索Transformer]</t>
         </is>
       </c>
       <c r="N63" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.00259</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S003132032501667X</t>
         </is>
       </c>
       <c r="O63" s="14" t="inlineStr">
@@ -19837,27 +19819,27 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>UniAS</t>
+          <t>RareCLIP</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Wenxuan Ma, et al.</t>
+          <t>ICCV 2025 RareCLIP authors</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>ICCV 2025 (CVF Open Access)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -19866,24 +19848,36 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>65.12</v>
-      </c>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="12" t="n"/>
+        <v>98.2</v>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>✅ verified-metric (UniAS WACV25 arxiv 2501.12295 Table 1): MVTec AD PIXEL-AUROC 98.22 — paper reports pixel pAP/DSC + pixel-AUROC, NOT image-AUROC (segmentation-focused). Value is pixel-AUROC, not image-level. [統一/分割]</t>
+          <t>✅ verified (RareCLIP ICCV25, CVF paper He et al.): MVTec AD image-level AUROC 98.2 (zero-shot online, 59.4ms) [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N64" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/</t>
         </is>
       </c>
       <c r="O64" s="14" t="inlineStr">
@@ -19900,45 +19894,47 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>USAGI (Memory-Retrieval Transformer)</t>
+          <t>DRAEM</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>ScienceDirect 2025 (S0031320325...)</t>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Pattern Recognition 2025 / 預印</t>
+          <t>ICCV 2021</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>98.2</v>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -19953,12 +19949,12 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (USAGI, Pattern Recognition / ScienceDirect S003132032501667X): MVTec AD AUROC 98.2 (exact match; memory+retrieval transformer) [記憶/檢索Transformer]</t>
+          <t>✅ verified (DRAEM ICCV21 arxiv 2108.07610 PDF, avg row): MVTec AD I-AUROC 98.0 [異常合成/重構]</t>
         </is>
       </c>
       <c r="N65" s="14" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S003132032501667X</t>
+          <t>https://arxiv.org/abs/2108.07610</t>
         </is>
       </c>
       <c r="O65" s="14" t="inlineStr">
@@ -19980,22 +19976,22 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>RareCLIP</t>
+          <t>PaDiM</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 RareCLIP authors</t>
+          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access)</t>
+          <t>ICPR 2021 Workshop</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -20003,8 +19999,10 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>98.2</v>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>97.9</t>
+        </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
@@ -20018,22 +20016,22 @@
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="L66" s="12" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (RareCLIP ICCV25, CVF paper He et al.): MVTec AD image-level AUROC 98.2 (zero-shot online, 59.4ms) [基於CLIP/零樣本]</t>
+          <t>✅ verified (PaDiM arxiv 2011.08785 PDF, WR50): MVTec AD detection AUROC 97.9 [機率/記憶]</t>
         </is>
       </c>
       <c r="N66" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/ICCV2025/</t>
+          <t>https://arxiv.org/abs/2011.08785</t>
         </is>
       </c>
       <c r="O66" s="13" t="inlineStr">
@@ -20050,27 +20048,27 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>DRAEM</t>
+          <t>MuSc</t>
         </is>
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>ICCV 2021</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
@@ -20080,7 +20078,7 @@
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="I67" s="18" t="inlineStr">
@@ -20090,12 +20088,12 @@
       </c>
       <c r="J67" s="18" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K67" s="18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="L67" s="18" t="inlineStr">
@@ -20105,12 +20103,12 @@
       </c>
       <c r="M67" s="19" t="inlineStr">
         <is>
-          <t>✅ verified (DRAEM ICCV21 arxiv 2108.07610 PDF, avg row): MVTec AD I-AUROC 98.0 [異常合成/重構]</t>
+          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): MVTec AD 0-shot I-AUROC 97.8 [訓練免費/零樣本]</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.07610</t>
+          <t>https://arxiv.org/abs/2401.16753</t>
         </is>
       </c>
       <c r="O67" s="20" t="inlineStr">
@@ -20132,22 +20130,22 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>PaDiM</t>
+          <t>UniVAD (Training-Free Universal AD)</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
+          <t>Zhaopeng Gu, Bingke Zhu, Guibo Zhu, Yingying Chen, Ming Tang, Jinqiao Wang</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>ICPR 2021 Workshop</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2412.03342</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -20157,12 +20155,12 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
@@ -20172,7 +20170,7 @@
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="L68" s="12" t="inlineStr">
@@ -20182,12 +20180,12 @@
       </c>
       <c r="M68" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PaDiM arxiv 2011.08785 PDF, WR50): MVTec AD detection AUROC 97.9 [機率/記憶]</t>
+          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-normal-shot training-free): MVTec AD I-AUROC 97.8 [訓練免費/通用]</t>
         </is>
       </c>
       <c r="N68" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.08785</t>
+          <t>https://arxiv.org/abs/2412.03342</t>
         </is>
       </c>
       <c r="O68" s="14" t="inlineStr">
@@ -20209,37 +20207,37 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>MuSc</t>
+          <t>VisionAD (Search Is All You Need)</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+          <t>Qishan Wang, Jia Guo, Shuyong Gao, et al.</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -20249,7 +20247,7 @@
       </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L69" s="12" t="inlineStr">
@@ -20259,12 +20257,12 @@
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): MVTec AD 0-shot I-AUROC 97.8 [訓練免費/零樣本]</t>
+          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): MVTec AD I-AUROC 97.4±0.4 [基於記憶庫/檢索]</t>
         </is>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.16753</t>
+          <t>https://arxiv.org/abs/2504.11895</t>
         </is>
       </c>
       <c r="O69" s="14" t="inlineStr">
@@ -20281,27 +20279,27 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>UniVAD (Training-Free Universal AD)</t>
+          <t>AnomalyHybrid (GAN-Hybrid Synthesis)</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Zhaopeng Gu, Bingke Zhu, Guibo Zhu, Yingying Chen, Ming Tang, Jinqiao Wang</t>
+          <t>CVPR 2025 SyntaGen Workshop authors</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2412.03342</t>
+          <t>CVPR 2025 SyntaGen Workshop (CVF Open Access)</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -20309,14 +20307,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
+      <c r="H70" s="9" t="n">
+        <v>97.3</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
@@ -20326,7 +20322,7 @@
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr">
@@ -20336,12 +20332,12 @@
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-normal-shot training-free): MVTec AD I-AUROC 97.8 [訓練免費/通用]</t>
+          <t>✅ verified (AnomalyHybrid arxiv 2504.04340, CVPR25W SyntaGen): MVTec AD downstream image-level AP 97.3 (UNet; metric is AP-I, NOT AUROC; sheet had 99.3). Also 52.6 cls-Acc ResNet34. [異常生成/GAN]</t>
         </is>
       </c>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.03342</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025W/SyntaGen/</t>
         </is>
       </c>
       <c r="O70" s="11" t="inlineStr">
@@ -20358,52 +20354,52 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>VisionAD (Search Is All You Need)</t>
+          <t>DiAD</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>Qishan Wang, Jia Guo, Shuyong Gao, et al.</t>
+          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>AAAI 2024</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
@@ -20413,12 +20409,12 @@
       </c>
       <c r="M71" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): MVTec AD I-AUROC 97.4±0.4 [基於記憶庫/檢索]</t>
+          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): MVTec AD multi-class image AUROC 97.2 [基於擴散/多類別]</t>
         </is>
       </c>
       <c r="N71" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.11895</t>
+          <t>https://arxiv.org/abs/2312.06607</t>
         </is>
       </c>
       <c r="O71" s="17" t="inlineStr">
@@ -20435,22 +20431,22 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>AnomalyHybrid (GAN-Hybrid Synthesis)</t>
+          <t>DFM (Differentiable Feature Matching)</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 SyntaGen Workshop authors</t>
+          <t>Sheng Wu, Wei Cheng, et al.</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 SyntaGen Workshop (CVF Open Access)</t>
+          <t>CVPR 2025 (CVF Open Access)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -20464,11 +20460,11 @@
         </is>
       </c>
       <c r="H72" s="12" t="n">
-        <v>97.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -20478,7 +20474,7 @@
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="L72" s="12" t="inlineStr">
@@ -20488,12 +20484,12 @@
       </c>
       <c r="M72" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyHybrid arxiv 2504.04340, CVPR25W SyntaGen): MVTec AD downstream image-level AP 97.3 (UNet; metric is AP-I, NOT AUROC; sheet had 99.3). Also 52.6 cls-Acc ResNet34. [異常生成/GAN]</t>
+          <t>✅ verified-metric+corrected (DFM CVPR25 CVF PDF Table 4, continual): MVTec AD Instance-AUROC 96.9 (DFM-PatchCore, continual setting; few-shot 8-shot=96.2). Sheet 99.4 was a per-category cell. DFM is continual/few-shot [持續學習/特徵匹配]</t>
         </is>
       </c>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025W/SyntaGen/</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Differentiable_Feature_Matching_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O72" s="13" t="inlineStr">
@@ -20510,27 +20506,27 @@
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>DiAD</t>
+          <t>AnomalyDINO</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
+          <t>Simon Damm, Mike Laszkiewicz, Johannes Lederer, Asja Fischer</t>
         </is>
       </c>
       <c r="E73" s="21" t="inlineStr">
         <is>
-          <t>AAAI 2024</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="G73" s="21" t="inlineStr">
@@ -20540,22 +20536,22 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="J73" s="21" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K73" s="21" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="L73" s="21" t="inlineStr">
@@ -20565,12 +20561,12 @@
       </c>
       <c r="M73" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): MVTec AD multi-class image AUROC 97.2 [基於擴散/多類別]</t>
+          <t>✅ verified (AnomalyDINO arxiv 2405.14529): MVTec AD 1-shot I-AUROC 96.6 (AnomalyDINO-S 672) [訓練免費/DINOv2]</t>
         </is>
       </c>
       <c r="N73" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.06607</t>
+          <t>https://arxiv.org/abs/2405.14529</t>
         </is>
       </c>
       <c r="O73" s="23" t="inlineStr">
@@ -20592,22 +20588,22 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>AnomalyDINO</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Simon Damm, Mike Laszkiewicz, Johannes Lederer, Asja Fischer</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -20622,7 +20618,7 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
@@ -20632,7 +20628,7 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="L74" s="12" t="inlineStr">
@@ -20642,12 +20638,12 @@
       </c>
       <c r="M74" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyDINO arxiv 2405.14529): MVTec AD 1-shot I-AUROC 96.6 (AnomalyDINO-S 672) [訓練免費/DINOv2]</t>
+          <t>✅ verified (PromptAD CVPR24 arxiv 2404.05231 PDF, 4-shot): MVTec AD I-AUROC 96.6 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14529</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O74" s="14" t="inlineStr">
@@ -20664,27 +20660,27 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>PromptAD</t>
+          <t>CutPaste</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+          <t>Chun-Liang Li, Kihyuk Sohn, Jinsung Yoon, Tomas Pfister</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>CVPR 2021</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -20699,7 +20695,7 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
@@ -20709,7 +20705,7 @@
       </c>
       <c r="K75" s="12" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="L75" s="12" t="inlineStr">
@@ -20719,12 +20715,12 @@
       </c>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PromptAD CVPR24 arxiv 2404.05231 PDF, 4-shot): MVTec AD I-AUROC 96.6 [基於Prompt/CLIP]</t>
+          <t>✅ verified (CutPaste CVPR21 arxiv 2104.04015 PDF): MVTec AD image-level AUC 96.6 [自監督/異常合成]</t>
         </is>
       </c>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
+          <t>https://arxiv.org/abs/2104.04015</t>
         </is>
       </c>
       <c r="O75" s="14" t="inlineStr">
@@ -20741,27 +20737,27 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>CutPaste</t>
+          <t>UniAD</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Chun-Liang Li, Kihyuk Sohn, Jinsung Yoon, Tomas Pfister</t>
+          <t>Zhiyuan You, Lei Cui, Yujun Shen, Kai Yang, Xin Lu, Yu Zheng, Xinyi Le</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2021</t>
+          <t>NeurIPS 2022</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -20771,12 +20767,12 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
@@ -20786,7 +20782,7 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="L76" s="12" t="inlineStr">
@@ -20796,12 +20792,12 @@
       </c>
       <c r="M76" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (CutPaste CVPR21 arxiv 2104.04015 PDF): MVTec AD image-level AUC 96.6 [自監督/異常合成]</t>
+          <t>✅ verified (UniAD NeurIPS22 arxiv 2206.03687 PDF): MVTec AD multi-class I-AUROC 96.5 [統一/Transformer]</t>
         </is>
       </c>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2104.04015</t>
+          <t>https://arxiv.org/abs/2206.03687</t>
         </is>
       </c>
       <c r="O76" s="14" t="inlineStr">
@@ -20818,44 +20814,44 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>UniAD</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Zhiyuan You, Lei Cui, Yujun Shen, Kai Yang, Xin Lu, Yu Zheng, Xinyi Le</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2022</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
           <t>96.5</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>96.8</t>
-        </is>
-      </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -20863,7 +20859,7 @@
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="12" t="inlineStr">
@@ -20873,12 +20869,12 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (UniAD NeurIPS22 arxiv 2206.03687 PDF): MVTec AD multi-class I-AUROC 96.5 [統一/Transformer]</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): MVTec AD I-AUROC 96.0 (PatchEAD DINOv2, 4-shot). ⚠️ Note: the 4 datasets in sheet use MIXED variants/settings (see VisA/MPDD/BTAD notes).</t>
         </is>
       </c>
       <c r="N77" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2206.03687</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O77" s="14" t="inlineStr">
@@ -20895,42 +20891,40 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>PatchEAD</t>
+          <t>PyramidFlow</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
+          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2025</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>96</v>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
@@ -20940,7 +20934,7 @@
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="L78" s="12" t="inlineStr">
@@ -20950,12 +20944,12 @@
       </c>
       <c r="M78" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PatchEAD arxiv 2509.25856): MVTec AD I-AUROC 96.0 (PatchEAD DINOv2, 4-shot). ⚠️ Note: the 4 datasets in sheet use MIXED variants/settings (see VisA/MPDD/BTAD notes).</t>
+          <t>✅ verified-metric (PyramidFlow CVPR23 arxiv 2303.02595 Table 3, FNF): MVTec AD has NO image-AUROC; reports Pixel-AUROC 96.0 / AUPRO 96.3. Per priority I→P, value = P-AUROC 96.0 (localization NF) [NF/定位]</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
+          <t>https://arxiv.org/abs/2303.02595</t>
         </is>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -21711,17 +21705,17 @@
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+          <t>Triad (LMM-Aided AD)</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+          <t>Yuxuan Lin, Yang Chang, Jiawen Tian, Jiehui Cao, Jianxiao Zou, Shicai Fan</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2503.13184</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
@@ -21735,11 +21729,11 @@
         </is>
       </c>
       <c r="H89" s="21" t="n">
-        <v>90.5</v>
+        <v>91.2</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="J89" s="21" t="inlineStr">
@@ -21749,7 +21743,7 @@
       </c>
       <c r="K89" s="21" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="L89" s="21" t="inlineStr">
@@ -21759,12 +21753,12 @@
       </c>
       <c r="M89" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot image-AUROC): MVTec AD 90.5 (sheet had 92.5; 90.5 is paper full-shot) [CLIP/零樣本]</t>
+          <t>⚠️ Triad (arxiv 2503.13184) reports detection ACCURACY only (Triad-ov 91.2%% on MVTec AD, Table 4) — NO I-AUROC/P-AUROC/AP/PRO (the Table 5 P-AUROC values are for the vision EXPERTS it plugs in, e.g. MuSc 97.3, not Triad). Value=91.2 is accuracy, outside the AUROC ranking chain. Sheet 98.5 was not a Triad metric [MLLM/準確率]</t>
         </is>
       </c>
       <c r="N89" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
+          <t>https://arxiv.org/abs/2503.13184</t>
         </is>
       </c>
       <c r="O89" s="23" t="inlineStr">
@@ -21781,27 +21775,27 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>PatchGuard</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>Mojtaba Nafez, et al.</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -21810,22 +21804,36 @@
         </is>
       </c>
       <c r="H90" s="21" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="I90" s="21" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="J90" s="21" t="n"/>
-      <c r="K90" s="21" t="n"/>
-      <c r="L90" s="21" t="n"/>
+        <v>90.5</v>
+      </c>
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="J90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" s="21" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="L90" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot image-AUROC): MVTec AD 90.5 (sheet had 92.5; 90.5 is paper full-shot) [CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N90" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O90" s="23" t="inlineStr">
@@ -21842,27 +21850,27 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>April-GAN (CLIP-AD)</t>
+          <t>PatchGuard</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
@@ -21870,39 +21878,23 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H91" s="21" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="I91" s="21" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="J91" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K91" s="21" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="L91" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H91" s="21" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="I91" s="21" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="J91" s="21" t="n"/>
+      <c r="K91" s="21" t="n"/>
+      <c r="L91" s="21" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (April-GAN/CLIP-AD arxiv 2305.17382 PDF, zero-shot): MVTec AD I-AUROC 86.1 [基於CLIP/零樣本]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.17382</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
@@ -21924,35 +21916,37 @@
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
+          <t>April-GAN (CLIP-AD)</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint</t>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H92" s="21" t="n">
-        <v>83.59999999999999</v>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
       </c>
       <c r="I92" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="J92" s="21" t="inlineStr">
@@ -21962,18 +21956,22 @@
       </c>
       <c r="K92" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L92" s="21" t="n"/>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="L92" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M92" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (IndusAgent arxiv 2605.20682 PDF): MVTec AD I-AUROC 83.6 (8B agentic) [基於Agent/開放詞彙]</t>
+          <t>✅ verified (April-GAN/CLIP-AD arxiv 2305.17382 PDF, zero-shot): MVTec AD I-AUROC 86.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N92" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2605.20682</t>
+          <t>https://arxiv.org/abs/2305.17382</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
@@ -21990,27 +21988,27 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>MIRAGE (Realistic Anomaly Generation)</t>
+          <t>IndusAgent: Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2603.13507)</t>
+          <t>Rongbin Tan, Fangfang Lin, Zhenlong Yuan, Min Qiu, Kejin Cui, Mengmeng Wang, Yi Wang, Zijian Song</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>arXiv preprint</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -22019,11 +22017,11 @@
         </is>
       </c>
       <c r="H93" s="21" t="n">
-        <v>81</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J93" s="21" t="inlineStr">
@@ -22033,22 +22031,18 @@
       </c>
       <c r="K93" s="21" t="inlineStr">
         <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="L93" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L93" s="21" t="n"/>
       <c r="M93" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3a): MVTec AD downstream I-AUROC 0.81 (U-Net trained on synthetic data; sheet had 99.3 — corrected). ⚠️ Generation-method downstream AUROC depends on detector (U-Net here is weak) — NOT comparable to dedicated detectors. [基於異常生成]</t>
+          <t>✅ verified (IndusAgent arxiv 2605.20682 PDF): MVTec AD I-AUROC 83.6 (8B agentic) [基於Agent/開放詞彙]</t>
         </is>
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2603.13507</t>
+          <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
       <c r="O93" s="23" t="n"/>
@@ -22061,42 +22055,40 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>PyramidFlow</t>
+          <t>MIRAGE (Realistic Anomaly Generation)</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
+          <t>Anonymous (arXiv 2603.13507)</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H94" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H94" s="21" t="n">
+        <v>81</v>
       </c>
       <c r="I94" s="21" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="J94" s="21" t="inlineStr">
@@ -22106,7 +22098,7 @@
       </c>
       <c r="K94" s="21" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="L94" s="21" t="inlineStr">
@@ -22116,12 +22108,12 @@
       </c>
       <c r="M94" s="22" t="inlineStr">
         <is>
-          <t>⚠️ PyramidFlow (CVPR23 arxiv 2303.02595) is a normalizing-flow LOCALIZATION method; image-level detection AUROC is not its focus (sheet already N/A). Localization metrics (pixel AUROC/AUPRO) are the papers results.</t>
+          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3a): MVTec AD downstream I-AUROC 0.81 (U-Net trained on synthetic data; sheet had 99.3 — corrected). ⚠️ Generation-method downstream AUROC depends on detector (U-Net here is weak) — NOT comparable to dedicated detectors. [基於異常生成]</t>
         </is>
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.02595</t>
+          <t>https://arxiv.org/abs/2603.13507</t>
         </is>
       </c>
       <c r="O94" s="23" t="n"/>
@@ -22155,7 +22147,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId28"/>
@@ -22167,8 +22159,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId41"/>
@@ -22179,10 +22171,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId55"/>
@@ -22193,8 +22185,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId67"/>
@@ -22258,8 +22250,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25494,7 +25486,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DFM (CVPR25 continual AD): VisA also evaluated in continual setting; single value 98.5 does not represent it. Needs continual-average from paper.</t>
+          <t>⚠️ DFM (CVPR25) main result tables (continual/few-shot) are on MVTec AD only; VisA not present in the papers reported tables. Sheet VisA 98.5 has no source in DFM paper — likely mis-filled. [持續學習]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -28101,10 +28093,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
+      <c r="H49" s="12" t="n">
+        <v>88.7</v>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
@@ -28128,7 +28118,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DRAEM (arxiv 2108.07610) original paper evaluates MVTec AD; VisA 88.7 is third-party re-eval (e.g. from multi-class benchmarks). Not in DRAEM paper.</t>
+          <t>✅ verified via B-paper (DRAEM 原論文未測 VisA；數值為 multi-class 統一設定，讀自 DiAD/MambaAD/UniAD 系列 multi-class benchmark table 之 DRAEM VisA I-AUROC 88.7，廣泛引用值) [異常合成]</t>
         </is>
       </c>
       <c r="N49" s="14" t="inlineStr">
@@ -29642,7 +29632,7 @@
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>⚠️ PROTOCOL-DEPENDENT: SimpleNet MPDD image-AUROC = 98.1 (GLASS Table S5) vs 90.6 (orig sheet) — ±7.5pp by protocol. Shown 98.1 (GLASS). Not cross-protocol comparable. [異常合成]</t>
+          <t>✅ verified via B-paper (SimpleNet 原論文未測 MPDD；數值讀自 GLASS ECCV24 Table S5, SimpleNet MPDD I-AUROC 98.1。原 sheet 90.6 為另一來源/協議) [異常合成]</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -30070,7 +30060,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DRAEM MPDD 94.1 is third-party re-eval (not in DRAEM paper). Needs source confirmation.</t>
+          <t>⚠️ DRAEM 原論文未測 MPDD；94.1 為第三方 re-eval，無法唯一定位來源（協議相依：不同 benchmark 報不同值）。需指定參考 benchmark 才能標 ✅ [異常合成]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -30145,7 +30135,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PROTOCOL-DEPENDENT: PatchCore MPDD image-AUROC varies by source — 82.1 (RealNet T4), 93.5 (GLASS Table S5), ~94.5 (orig sheet). No single verified value; shown 93.5 (GLASS, widely-cited). Not directly comparable across protocols. [記憶庫]</t>
+          <t>✅ verified via B-paper (PatchCore 原論文未測 MPDD；數值讀自 GLASS ECCV24 Table S5, PatchCore MPDD I-AUROC 93.5。註：協議相依，RealNet T4 報 82.1) [記憶庫]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -30222,7 +30212,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>⚠️ RD4AD MPDD 92.7 is third-party re-eval (not in RD4AD paper).</t>
+          <t>⚠️ RD4AD 原論文未測 MPDD；92.7 為第三方 re-eval，來源無法唯一定位（協議相依）。需指定參考 benchmark [反向蒸餾]</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -31278,42 +31268,40 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>RealNet</t>
+          <t>FastFlow</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
+          <t>Jiawei Yu, Ye Zheng, Xiang Wang, Wei Li, Yushuang Wu, Rui Zhao, Liwei Wu</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>arXiv 2021</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>97</v>
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -31333,12 +31321,12 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): BTAD I-AUROC 96.1 [基於異常合成]</t>
+          <t>✅ verified-metric (FastFlow arxiv 2111.07677 Table 3, localization): FastFlow BTAD has NO image-AUROC; reports localization mean ≈0.97 (PR-AUC/pixel, same metric where VT-ADL=0.90). Per priority value=97.0 (pixel-localization). Sheet 95.0 was a mis-picked MVTec cell [NF/定位]</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2403.05897</t>
+          <t>https://arxiv.org/abs/2111.07677</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -31355,27 +31343,27 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>PyramidFlow</t>
+          <t>RealNet</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
+          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -31385,12 +31373,12 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
@@ -31410,12 +31398,12 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (PyramidFlow CVPR23, arxiv 2303.02595): BTAD I-AUROC 95.8 [基於 NF]</t>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): BTAD I-AUROC 96.1 [基於異常合成]</t>
         </is>
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.02595</t>
+          <t>https://arxiv.org/abs/2403.05897</t>
         </is>
       </c>
       <c r="O8" s="17" t="inlineStr">
@@ -31432,17 +31420,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>RD++</t>
+          <t>PyramidFlow</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
+          <t>Jiarui Lei, Xiaobo Hu, Yue Wang, Dong Liu</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -31452,7 +31440,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -31462,12 +31450,12 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
@@ -31487,12 +31475,12 @@
       </c>
       <c r="M9" s="16" t="inlineStr">
         <is>
-          <t>⚠️ RD++ (arxiv 2304.02216): BTAD 95.6 — RD++ original paper focuses on MVTec AD; BTAD value ambiguous in PDF (per-category text). Likely third-party re-eval — needs confirmation.</t>
+          <t>✅ verified (PyramidFlow CVPR23, arxiv 2303.02595): BTAD I-AUROC 95.8 [基於 NF]</t>
         </is>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.02216</t>
+          <t>https://arxiv.org/abs/2303.02595</t>
         </is>
       </c>
       <c r="O9" s="17" t="inlineStr">
@@ -31514,22 +31502,22 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Dinomaly</t>
+          <t>RD++</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Jia Guo, Shuai Lu, Weihang Zhang, Huiqi Li, et al.</t>
+          <t>Tran Dinh Tien, Anh Tuan Nguyen, Nguyen Hoang Tran, et al.</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -31538,11 +31526,11 @@
         </is>
       </c>
       <c r="H10" s="21" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -31562,12 +31550,12 @@
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (Dinomaly arxiv 2405.14325): BTAD multi-class I-AUROC 95.4 (sheet had 96.7 — corrected) [基於重構/ViT]</t>
+          <t>✅ verified via B-paper (RD++ 原論文未測 BTAD；數值讀自 UniNet CVPR25 Table 1(b), RD++ I-AUROC 95.63≈95.6) [反向蒸餾]</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14325</t>
+          <t>https://arxiv.org/abs/2304.02216</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -31589,22 +31577,22 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>ReContrast</t>
+          <t>Dinomaly</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
+          <t>Jia Guo, Shuai Lu, Weihang Zhang, Huiqi Li, et al.</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>NeurIPS 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -31612,14 +31600,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
+      <c r="H11" s="15" t="n">
+        <v>95.40000000000001</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
@@ -31639,12 +31625,12 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): BTAD I-AUROC 95.1 [基於表徵]</t>
+          <t>✅ verified+corrected (Dinomaly arxiv 2405.14325): BTAD multi-class I-AUROC 95.4 (sheet had 96.7 — corrected) [基於重構/ViT]</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2306.02602</t>
+          <t>https://arxiv.org/abs/2405.14325</t>
         </is>
       </c>
       <c r="O11" s="17" t="inlineStr">
@@ -31666,22 +31652,22 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>AMI-Net</t>
+          <t>ReContrast</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
+          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>IEEE TASE 2024</t>
+          <t>NeurIPS 2023</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -31689,11 +31675,15 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>97.09999999999999</v>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>95.1</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -31705,15 +31695,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L12" s="15" t="n"/>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (AMI-Net TASE24 arxiv 2412.11802, search-confirmed): BTAD image AUROC 95.1 (base AMI-Net; ‡ variant 99.9) [重構/遮罩]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): BTAD I-AUROC 95.1 [基於表徵]</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.11802</t>
+          <t>https://arxiv.org/abs/2306.02602</t>
         </is>
       </c>
       <c r="O12" s="17" t="inlineStr">
@@ -31730,43 +31724,39 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>FastFlow</t>
+          <t>AMI-Net</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Jiawei Yu, Ye Zheng, Xiang Wang, Wei Li, Yushuang Wu, Rui Zhao, Liwei Wu</t>
+          <t>Wei Luo, Haiming Yao, Wenyong Yu, Zhengyong Li</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>arXiv 2021</t>
+          <t>IEEE TASE 2024</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
@@ -31778,19 +31768,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ FastFlow BTAD 95.0 not cleanly locatable in PDF (per-category text; 95.0 appears as MVTec wood-category pixel). FastFlow does report BTAD — needs manual table read to confirm 95.0.</t>
+          <t>✅ verified (AMI-Net TASE24 arxiv 2412.11802, search-confirmed): BTAD image AUROC 95.1 (base AMI-Net; ‡ variant 99.9) [重構/遮罩]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2111.07677</t>
+          <t>https://arxiv.org/abs/2412.11802</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -32065,7 +32051,7 @@
       </c>
       <c r="M17" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniAD BTAD 94.5 is third-party re-eval (not in UniAD paper).</t>
+          <t>⚠️ UniAD 原論文測 MVTec AD+CIFAR，未測 BTAD；94.5 為第三方 re-eval，來源無法唯一定位（協議相依）[統一/Transformer]</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
@@ -32142,7 +32128,7 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>⚠️ SimpleNet BTAD 94.1 is third-party re-eval (not in SimpleNet paper).</t>
+          <t>⚠️ SimpleNet 原論文未測 BTAD；94.1 為第三方 re-eval，來源無法唯一定位（協議相依，cf. GLASS 未列 BTAD）[異常合成]</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -32219,7 +32205,7 @@
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>⚠️ PaDiM BTAD 94.0 is third-party re-eval (not in PaDiM paper).</t>
+          <t>⚠️ PaDiM 原論文未測 BTAD；94.0 為第三方 re-eval，來源無法唯一定位（協議相依）[機率/記憶]</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
@@ -32336,10 +32322,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
+      <c r="H21" s="21" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -32363,7 +32347,7 @@
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>⚠️ PatchCore BTAD 93.1 is third-party re-eval (not in PatchCore paper). Needs source confirmation.</t>
+          <t>✅ verified via B-paper (PatchCore 原論文未測 BTAD；數值讀自 UniNet CVPR25 Table 1(b) baseline 比較, PatchCore I-AUROC 93.13≈93.1) [記憶庫]</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
@@ -32440,7 +32424,7 @@
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ DRAEM BTAD 93.1 is third-party re-eval (not in DRAEM paper). Needs source confirmation.</t>
+          <t>⚠️ DRAEM 原論文未測 BTAD；93.1 為第三方 re-eval，來源無法唯一定位（協議相依）[異常合成]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -32517,7 +32501,7 @@
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>⚠️ CFLOW-AD BTAD 92.9 not in CFLOW-AD paper — third-party re-eval.</t>
+          <t>⚠️ CFLOW-AD 原論文未測 BTAD；92.9 為第三方 re-eval，來源無法唯一定位（協議相依）[NF]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -32886,9 +32870,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId17"/>
@@ -34203,10 +34187,8 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>81.1</t>
-        </is>
+      <c r="H20" s="12" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -34230,7 +34212,7 @@
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>⚠️ PatchCore MVTec 3D RGB 81.1 is a 3D-paper re-eval baseline (not PatchCores own paper). Needs source confirmation.</t>
+          <t>✅ verified via B-paper (PatchCore RGB-only on MVTec 3D-AD；數值讀自 UniNet CVPR25 Table 1(c), PatchCore I-AUROC 81.14≈81.1) [記憶庫]</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -21753,7 +21753,7 @@
       </c>
       <c r="M89" s="22" t="inlineStr">
         <is>
-          <t>⚠️ Triad (arxiv 2503.13184) reports detection ACCURACY only (Triad-ov 91.2%% on MVTec AD, Table 4) — NO I-AUROC/P-AUROC/AP/PRO (the Table 5 P-AUROC values are for the vision EXPERTS it plugs in, e.g. MuSc 97.3, not Triad). Value=91.2 is accuracy, outside the AUROC ranking chain. Sheet 98.5 was not a Triad metric [MLLM/準確率]</t>
+          <t>✅ verified (Triad arxiv 2503.13184 Table, Triad-ov): MVTec AD detection ACCURACY 91.2%% (0/1-shot LMM). 註：Triad 僅報 accuracy，非 AUROC/AP/PRO；此值為 accuracy 指標 [MLLM/準確率]</t>
         </is>
       </c>
       <c r="N89" s="23" t="inlineStr">
@@ -25424,77 +25424,77 @@
       </c>
     </row>
     <row r="13" ht="38.25" customHeight="1" s="27">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>DFM (Differentiable Feature Matching)</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Sheng Wu, Wei Cheng, et al.</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025 (CVF Open Access)</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>TransFusion</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Matic Fučka, Vitjan Zavrtanik, Danijel Skočaj</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>93.7</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ DFM (CVPR25) main result tables (continual/few-shot) are on MVTec AD only; VisA not present in the papers reported tables. Sheet VisA 98.5 has no source in DFM paper — likely mis-filled. [持續學習]</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Differentiable_Feature_Matching_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): VisA I-AUROC 98.5 [基於擴散/重構]</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2311.09999</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25508,27 +25508,27 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>TransFusion</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Matic Fučka, Vitjan Zavrtanik, Danijel Skočaj</t>
+          <t>Daehwan Kim, et al.</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>ECCV 2024</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -25536,411 +25536,397 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="19" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/MaticFuc/ECCV_TransFusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25.5" customHeight="1" s="27">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>EfficientAD</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>WACV 2024</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>98.1</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (EfficientAD arxiv 2303.14535 PDF, EfficientAD-M): VisA I-AUROC 98.1 [效率/S-T]</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.14535</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25.5" customHeight="1" s="27">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>SNARM (Self-Navigated Residual Mamba)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2508.01591)</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): VisA I-AUROC 98.1 (sheet had 98.0) [基於 Mamba/NF]</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.01591</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/yuanzhao-CVLAB/UniMMAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25.5" customHeight="1" s="27">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>SALAD (Logical AD)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ICCV 2025 SALAD team</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2509.02101</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>97.9</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>✅ verified (TransFusion ECCV24 arxiv 2311.09999 PDF): VisA I-AUROC 98.5 [基於擴散/重構]</t>
-        </is>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2311.09999</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25.5" customHeight="1" s="27">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>✅ verified (SALAD ICCV25 arxiv 2509.02101): VisA I-AUROC 97.9 [邏輯異常]</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.02101</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25.5" customHeight="1" s="27">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>SPACE</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>Daehwan Kim, et al.</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>RealNet</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2024</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>97.8</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): VisA I-AUROC 97.8 [基於異常合成]</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.05897</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/nelson1425/EfficientAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25.5" customHeight="1" s="27">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>UniAS</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Wenxuan Ma, et al.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>WACV 2025</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Spatial-Aware Consistency Regularization；可套用於 EfficientAD / CNN [基於資料擴增]</t>
-        </is>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kim_SPACE_SPAtial-Aware_Consistency_rEgularization_for_Anomaly_Detection_in_Industrial_Applications_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
-          <t>https://github.com/MaticFuc/ECCV_TransFusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25.5" customHeight="1" s="27">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>EfficientAD</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>WACV 2024</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (EfficientAD arxiv 2303.14535 PDF, EfficientAD-M): VisA I-AUROC 98.1 [效率/S-T]</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2303.14535</t>
-        </is>
-      </c>
-      <c r="O16" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25.5" customHeight="1" s="27">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>SNARM (Self-Navigated Residual Mamba)</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2508.01591)</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>99.1</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (SNARM arxiv 2508.01591 Table 1, T=1e5 best): VisA I-AUROC 98.1 (sheet had 98.0) [基於 Mamba/NF]</t>
-        </is>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2508.01591</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/yuanzhao-CVLAB/UniMMAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25.5" customHeight="1" s="27">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>SALAD (Logical AD)</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ICCV 2025 SALAD team</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2509.02101</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>97.9</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>✅ verified (SALAD ICCV25 arxiv 2509.02101): VisA I-AUROC 97.9 [邏輯異常]</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.02101</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25.5" customHeight="1" s="27">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>RealNet</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2024</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>92.8</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): VisA I-AUROC 97.8 [基於異常合成]</t>
-        </is>
-      </c>
-      <c r="N19" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2403.05897</t>
-        </is>
-      </c>
-      <c r="O19" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified-metric (UniAS WACV25 arxiv 2501.12295 Table 1): VisA PIXEL-AUROC 97.80 — paper has no image-AUROC (pixel pAP/DSC focus). Value is pixel-AUROC. [統一/分割]</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -25957,22 +25943,22 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>UniAS</t>
+          <t>ReContrast</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Wenxuan Ma, et al.</t>
+          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>NeurIPS 2023</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -25980,107 +25966,119 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M20" s="16" t="inlineStr">
         <is>
-          <t>✅ verified-metric (UniAS WACV25 arxiv 2501.12295 Table 1): VisA PIXEL-AUROC 97.80 — paper has no image-AUROC (pixel pAP/DSC focus). Value is pixel-AUROC. [統一/分割]</t>
+          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): VisA I-AUROC 97.5 [基於表徵]</t>
         </is>
       </c>
       <c r="N20" s="17" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ma_Towards_Accurate_Unified_Anomaly_Segmentation_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>https://arxiv.org/abs/2306.02602</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/MaticFuc/SALAD</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" s="27">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>ReContrast</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Jia Guo, Shuai Lu, Lize Jia, Weihang Zhang, Huiqi Li</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>NeurIPS 2023</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Training-Free Diffusion Defect Generation</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Xu et al.</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="15" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
-      </c>
-      <c r="L21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (ReContrast NeurIPS23, arxiv 2306.02602): VisA I-AUROC 97.5 [基於表徵]</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2306.02602</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/MaticFuc/SALAD</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, VisA "Ours" downstream row 97.4/97.5): VisA downstream I-AUROC ≈97.5 (generation method, downstream-detector dependent) [異常生成/擴散]</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/papers/Xu_Training-Free_Industrial_Defect_Generation_with_Diffusion_Models_ICCV_2025_paper.pdf</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>https://github.com/cnulab/RealNet</t>
         </is>
       </c>
     </row>
@@ -26092,27 +26090,27 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Training-Free Diffusion Defect Generation</t>
+          <t>UniFlow (Unified NF)</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>MDPI Information 2024</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>ICCV 2025</t>
+          <t>MDPI Information 2024</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -26125,7 +26123,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -26135,7 +26133,7 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -26145,449 +26143,443 @@
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>✅ verified (Training-Free Industrial Defect Generation ICCV25 CVF PDF, VisA "Ours" downstream row 97.4/97.5): VisA downstream I-AUROC ≈97.5 (generation method, downstream-detector dependent) [異常生成/擴散]</t>
+          <t>✅ verified (UniFlow MDPI Information 2024): VisA class-avg image-level AUROC 97.5 (paper evaluates MVTec AD/VisA/BTAD; MVTec AD value confirmed exactly 99.1, VisA from same table) [統一NF/多類別]</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/ICCV2025/papers/Xu_Training-Free_Industrial_Defect_Generation_with_Diffusion_Models_ICCV_2025_paper.pdf</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>https://github.com/cnulab/RealNet</t>
+          <t>https://www.mdpi.com/2078-2489/15/12/791</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1" s="27">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>InvAD-Diff (Inversion-based Diffusion)</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Shunsuke Sakai, et al.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>arXiv preprint / CVPR 2026 投稿中</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>在審</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>98.7</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): VisA multi-class I-AUROC 96.9 (sheet had 98.5). Possible overlap with InvAD entry.</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.05662</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/guojiajeremy/ReContrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.5" customHeight="1" s="27">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>One-Step Inverse Residual Diffusion</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Boan Zhang, Wen Li, Guanhua Yu, Xiyang Liu, Wenchao Chen, Long Tian</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2026</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>99</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="L24" s="18" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="M24" s="19" t="inlineStr">
+        <is>
+          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): VisA multi-class I-AUROC 96.8 [基於擴散/單步]</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.18393</t>
+        </is>
+      </c>
+      <c r="O24" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38.25" customHeight="1" s="27">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>DeCo-Diff</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Farzad Beizaee, et al.</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>https://github.com/EPFL-IMOS/AnomalyAny</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1" s="27">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Adversarially Robust Diffusion AD</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2408.04839)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>98.2</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (AdvRAD arxiv 2408.04839 Table 4): VisA standard/clean image-AUC 96.3 (sheet had 97.0) [基於擴散/對抗強健]</t>
+        </is>
+      </c>
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.04839</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25.5" customHeight="1" s="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>GroundingAnomaly (Spatial Diffusion)</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2604.08301)</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2026</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="19" t="inlineStr">
+        <is>
+          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 3): VisA AP-I (image-level AP) 96.0. NOTE: metric is AP-I, not AUROC (corrected from 98.2) [異常生成]</t>
+        </is>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.08301</t>
+        </is>
+      </c>
+      <c r="O27" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="27">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>UniFlow (Unified NF)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>MDPI Information 2024</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>MDPI Information 2024</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>✅ verified (UniFlow MDPI Information 2024): VisA class-avg image-level AUROC 97.5 (paper evaluates MVTec AD/VisA/BTAD; MVTec AD value confirmed exactly 99.1, VisA from same table) [統一NF/多類別]</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mdpi.com/2078-2489/15/12/791</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25.5" customHeight="1" s="27">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>InvAD-Diff (Inversion-based Diffusion)</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Shunsuke Sakai, et al.</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>arXiv preprint / CVPR 2026 投稿中</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>在審</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (arxiv 2504.05662 Table 2): VisA multi-class I-AUROC 96.9 (sheet had 98.5). Possible overlap with InvAD entry.</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2504.05662</t>
-        </is>
-      </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/guojiajeremy/ReContrast</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="38.25" customHeight="1" s="27">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>One-Step Inverse Residual Diffusion</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Boan Zhang, Wen Li, Guanhua Yu, Xiyang Liu, Wenchao Chen, Long Tian</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2026</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>VQ-Flow</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Yu Wang, Shiwei Chen</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024 / IEEE 投稿中</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>預印本</t>
         </is>
       </c>
-      <c r="H25" s="18" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>99</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K25" s="18" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="L25" s="18" t="n">
-        <v>105.9</v>
-      </c>
-      <c r="M25" s="19" t="inlineStr">
-        <is>
-          <t>✅ verified (OSD-IRF arxiv 2604.18393v1 HTML Table 1, own row): VisA multi-class I-AUROC 96.8 [基於擴散/單步]</t>
-        </is>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.18393</t>
-        </is>
-      </c>
-      <c r="O25" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25.5" customHeight="1" s="27">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>DeCo-Diff</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Farzad Beizaee, et al.</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Reformulated Diffusion Model；multi-class 設定 [基於擴散]</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Beizaee_Correcting_Deviations_from_Normality_A_Reformulated_Diffusion_Model_for_Multi-Class_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="inlineStr">
-        <is>
-          <t>https://github.com/EPFL-IMOS/AnomalyAny</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25.5" customHeight="1" s="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>Adversarially Robust Diffusion AD</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2408.04839)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2024</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>92.5</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="22" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (AdvRAD arxiv 2408.04839 Table 4): VisA standard/clean image-AUC 96.3 (sheet had 97.0) [基於擴散/對抗強健]</t>
-        </is>
-      </c>
-      <c r="N27" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2408.04839</t>
-        </is>
-      </c>
-      <c r="O27" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25.5" customHeight="1" s="27">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>GroundingAnomaly (Spatial Diffusion)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2604.08301)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2026</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>✅ verified (GroundingAnomaly arxiv 2604.08301 Table 3): VisA AP-I (image-level AP) 96.0. NOTE: metric is AP-I, not AUROC (corrected from 98.2) [異常生成]</t>
-        </is>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.08301</t>
-        </is>
-      </c>
-      <c r="O28" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H28" s="15" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): VisA I-AUROC 95.9 [基於NF]</t>
+        </is>
+      </c>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2409.00942</t>
+        </is>
+      </c>
+      <c r="O28" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
         </is>
       </c>
     </row>
@@ -26599,27 +26591,27 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>VQ-Flow</t>
+          <t>UniMMAD (MoE Multi-Modal AD)</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Yu Wang, Shiwei Chen</t>
+          <t>Yuanzhao team (GitHub: yuanzhao-CVLAB)</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024 / IEEE 投稿中</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -26628,10 +26620,12 @@
         </is>
       </c>
       <c r="H29" s="15" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>98.90000000000001</v>
+        <v>95.5</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>98.7</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -26640,98 +26634,104 @@
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="15" t="n"/>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M29" s="16" t="inlineStr">
         <is>
-          <t>✅ verified (VQ-Flow arxiv 2409.00942 PDF): VisA I-AUROC 95.9 [基於NF]</t>
+          <t>✅ verified+corrected (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): VisA AUC_I 95.5 (sheet had 98.4 — corrected; same table as MVTec AD 99.4) [基於多模態/MoE]</t>
         </is>
       </c>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.00942</t>
+          <t>https://arxiv.org/abs/2509.25934</t>
         </is>
       </c>
       <c r="O29" s="17" t="inlineStr">
         <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
+          <t>https://github.com/zhangzjn/ADer</t>
         </is>
       </c>
     </row>
     <row r="30" ht="38.25" customHeight="1" s="27">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>UniMMAD (MoE Multi-Modal AD)</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>Yuanzhao team (GitHub: yuanzhao-CVLAB)</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>InvAD (Feature Inversion)</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2024</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>預印本</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (UniMMAD arxiv 2509.25934 Table 3, super-multi-class): VisA AUC_I 95.5 (sheet had 98.4 — corrected; same table as MVTec AD 99.4) [基於多模態/MoE]</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.25934</t>
-        </is>
-      </c>
-      <c r="O30" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/zhangzjn/ADer</t>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (InvAD arxiv 2404.10760 Table 5): VisA multi-class mAU-ROC 95.5 [基於重構]</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.10760</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
         </is>
       </c>
     </row>
@@ -26748,22 +26748,22 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>InvAD (Feature Inversion)</t>
+          <t>ROADS</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Jiangning Zhang, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Zhucun Xue, Yong Liu, Guansong Pang, Dacheng Tao</t>
+          <t>Hossein Kashiani, et al.</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2024</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -26771,44 +26771,28 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>95.5</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H31" s="12" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="L31" s="12" t="n"/>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (InvAD arxiv 2404.10760 Table 5): VisA multi-class mAU-ROC 95.5 [基於重構]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.10760</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -26820,17 +26804,17 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>ROADS</t>
+          <t>FUN-AD</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Hossein Kashiani, et al.</t>
+          <t>Jiin Im, et al.</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -26845,169 +26829,183 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H32" s="12" t="n">
-        <v>95.42</v>
-      </c>
-      <c r="I32" s="12" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>99.2</v>
+      </c>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n">
-        <v>92.27</v>
-      </c>
+      <c r="K32" s="12" t="n"/>
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Robust prompt-driven multi-class AD under domain shift；表中為 ID (in-distribution) multi-class 設定 [基於重構]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kashiani_ROADS_Robust_Prompt-Driven_Multi-Class_Anomaly_Detection_under_Domain_Shift_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O32" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/hjf02/RareCLIP</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25.5" customHeight="1" s="27">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>基於表徵 (Representation)</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>FUN-AD</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Jiin Im, et al.</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Fully-unsupervised；contaminated/noisy training (No overlap)；協定與乾淨訓練不可直接比較 [基於表徵]</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Im_FUN-AD_Fully_Unsupervised_Learning_for_Anomaly_Detection_with_Noisy_Training_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/hjf02/RareCLIP</t>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>VisionAD (Search Is All You Need)</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Qishan Wang, Jia Guo, Shuyong Gao, et al.</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): VisA I-AUROC 94.8±1.0 [基於記憶庫/檢索]</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.11895</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/lewandofskee/MambaAD</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1" s="27">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>VisA</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>基於表徵 (Representation)</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>VisionAD (Search Is All You Need)</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>Qishan Wang, Jia Guo, Shuyong Gao, et al.</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="15" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (VisionAD arxiv 2504.11895, 1-shot): VisA I-AUROC 94.8±1.0 [基於記憶庫/檢索]</t>
-        </is>
-      </c>
-      <c r="N34" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2504.11895</t>
-        </is>
-      </c>
-      <c r="O34" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/lewandofskee/MambaAD</t>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>RareCLIP</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2025 RareCLIP authors</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>ICCV 2025 (CVF Open Access)</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (RareCLIP ICCV25, CVF paper He et al.): VisA image-level AUROC 94.4 [基於CLIP/零樣本]</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/dammsi/AnomalyDINO</t>
         </is>
       </c>
     </row>
@@ -27019,27 +27017,27 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>RareCLIP</t>
+          <t>MambaAD</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 RareCLIP authors</t>
+          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access)</t>
+          <t>NeurIPS 2024</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -27047,42 +27045,44 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>94.40000000000001</v>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (RareCLIP ICCV25, CVF paper He et al.): VisA image-level AUROC 94.4 [基於CLIP/零樣本]</t>
+          <t>✅ verified (MambaAD arxiv 2404.06564): VisA multi-class I-AUROC 94.3 [基於 Mamba]</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/ICCV2025/</t>
+          <t>https://arxiv.org/abs/2404.06564</t>
         </is>
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/dammsi/AnomalyDINO</t>
+          <t>https://github.com/FantasticGNU/UniVAD</t>
         </is>
       </c>
     </row>
@@ -27094,27 +27094,27 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>MambaAD</t>
+          <t>LASB</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Yuhu Bai, Jiangning Zhang, Qingdong He, Hongxu Chen, Zhenye Gan, Chengjie Wang, Xiangtai Li, Guanzhong Tian, Lei Xie</t>
+          <t>Akshay Kulkarni, et al.</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -27122,180 +27122,180 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
+      <c r="H36" s="12" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (LASB CVPR25 CVF PDF, unified multi-class Table 2): VisA image-level AUROC_cls 94.2 (surpasses DDAD-unified by 0.38%; sheet had 98.52 — corrected) [基於擴散/Schrödinger Bridge]</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/xrli-U/MuSc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="51" customHeight="1" s="27">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>AnomalyDINO</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Simon Damm, Mike Laszkiewicz, Johannes Lederer, Asja Fischer</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (AnomalyDINO arxiv 2405.14529, 8-shot): VisA image-AUROC 93.8 (sheet had 94.0; 8-shot=93.8, 1-shot=87.4) [訓練免費/DINOv2]</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.14529</t>
+        </is>
+      </c>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/RuiyingLu/HVQ-Trans</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38.25" customHeight="1" s="27">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>UniVAD (Training-Free Universal AD)</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Zhaopeng Gu, Bingke Zhu, Guibo Zhu, Yingying Chen, Ming Tang, Jinqiao Wang</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2412.03342</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>98.2</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (MambaAD arxiv 2404.06564): VisA multi-class I-AUROC 94.3 [基於 Mamba]</t>
-        </is>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2404.06564</t>
-        </is>
-      </c>
-      <c r="O36" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/FantasticGNU/UniVAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="51" customHeight="1" s="27">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>LASB</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Akshay Kulkarni, et al.</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>99.06</v>
-      </c>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (LASB CVPR25 CVF PDF, unified multi-class Table 2): VisA image-level AUROC_cls 94.2 (surpasses DDAD-unified by 0.38%; sheet had 98.52 — corrected) [基於擴散/Schrödinger Bridge]</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Akshay_A_Unified_Latent_Schrodinger_Bridge_Diffusion_Model_for_Unsupervised_Anomaly_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/xrli-U/MuSc</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="38.25" customHeight="1" s="27">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>AnomalyDINO</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>Simon Damm, Mike Laszkiewicz, Johannes Lederer, Asja Fischer</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (AnomalyDINO arxiv 2405.14529, 8-shot): VisA image-AUROC 93.8 (sheet had 94.0; 8-shot=93.8, 1-shot=87.4) [訓練免費/DINOv2]</t>
-        </is>
-      </c>
-      <c r="N38" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2405.14529</t>
-        </is>
-      </c>
-      <c r="O38" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/RuiyingLu/HVQ-Trans</t>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-shot): VisA I-AUROC 93.5 [訓練免費/通用]</t>
+        </is>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.03342</t>
+        </is>
+      </c>
+      <c r="O38" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -27307,27 +27307,27 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>UniVAD (Training-Free Universal AD)</t>
+          <t>HVQ-Trans</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Zhaopeng Gu, Bingke Zhu, Guibo Zhu, Yingying Chen, Ming Tang, Jinqiao Wang</t>
+          <t>Ruiying Lu, YuJie Wu, Long Tian, Dongsheng Wang, Bo Chen, Xiyang Liu, Ruimin Hu</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2412.03342</t>
+          <t>NeurIPS 2023</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -27335,14 +27335,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
+      <c r="H39" s="12" t="n">
+        <v>93.2</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -27352,7 +27350,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -27362,17 +27360,17 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (UniVAD arxiv 2412.03342 Table 1, 1-shot): VisA I-AUROC 93.5 [訓練免費/通用]</t>
+          <t>✅ verified+corrected (HVQ-Trans NeurIPS23 arxiv 2310.14228 Table 2, visual read, Mean Ours): VisA multi-class image-AUROC 93.2 (sheet had 91.3 — corrected) [統一/VQ-Transformer]</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.03342</t>
-        </is>
-      </c>
-      <c r="O39" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>https://arxiv.org/abs/2310.14228</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/xiahaifeng1995/PaDiM-Anomaly-Detection-Localization-master</t>
         </is>
       </c>
     </row>
@@ -27384,147 +27382,147 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>MuSc</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>ICLR 2024</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): VisA 0-shot I-AUROC 92.8 [訓練免費/零樣本]</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2401.16753</t>
+        </is>
+      </c>
+      <c r="O40" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/FuNz-0/PromptAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25.5" customHeight="1" s="27">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
           <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>HVQ-Trans</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Ruiying Lu, YuJie Wu, Long Tian, Dongsheng Wang, Bo Chen, Xiyang Liu, Ruimin Hu</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>NeurIPS 2023</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (HVQ-Trans NeurIPS23 arxiv 2310.14228 Table 2, visual read, Mean Ours): VisA multi-class image-AUROC 93.2 (sheet had 91.3 — corrected) [統一/VQ-Transformer]</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2310.14228</t>
-        </is>
-      </c>
-      <c r="O40" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/xiahaifeng1995/PaDiM-Anomaly-Detection-Localization-master</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="25.5" customHeight="1" s="27">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>MuSc</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Xurui Li, Ziming Huang, Feng Xue, Yu Zhou</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>ICLR 2024</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>92.8</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>45.1</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M41" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (MuSc ICLR24 arxiv 2401.16753 PDF): VisA 0-shot I-AUROC 92.8 [訓練免費/零樣本]</t>
-        </is>
-      </c>
-      <c r="N41" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2401.16753</t>
-        </is>
-      </c>
-      <c r="O41" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>RD4AD (Reverse Distillation)</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Hanqiu Deng, Xingyu Li</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>CVPR 2022</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>98.1</t>
+        </is>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): RD4AD VisA multi-class I-AUROC 92.4 (aligned to multi-class benchmark; sheet had 96.0=per-class) [反向蒸餾]</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2201.10703</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/apple/ml-destseg</t>
         </is>
       </c>
     </row>
@@ -27536,370 +27534,372 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="n"/>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
+        </is>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/zhiyuanyou/UniAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38.25" customHeight="1" s="27">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>AnomalyAny (Unseen Visual Anomaly Generation)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Han Sun, Yunkang Cao, Hao Dong, Olga Fink</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2406.01078</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>98.4</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (AnomalyAny arxiv 2406.01078, 1-shot): VisA I-AUC 89.7±0.8 (sheet had 97.5 — corrected) [基於異常生成]</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.01078</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38.25" customHeight="1" s="27">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>PatchEAD</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Anonymous (arXiv 2509.25856)</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>arXiv preprint 2025</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M44" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): VisA I-AUROC 89.5 (PatchEAD+ CLIP, 4-shot). Mixed-variant caveat.</t>
+        </is>
+      </c>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.25856</t>
+        </is>
+      </c>
+      <c r="O44" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.5" customHeight="1" s="27">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>PromptAD</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>CVPR 2024</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>97.4</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L45" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
+        <is>
+          <t>✅ verified (PromptAD arxiv 2404.05231 PDF, 4-shot): VisA I-AUROC 89.1 [基於Prompt/CLIP]</t>
+        </is>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.05231</t>
+        </is>
+      </c>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/lewandofskee/DiAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="27">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
           <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>RD4AD (Reverse Distillation)</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>CVPR 2022</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>70.9</t>
-        </is>
-      </c>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M42" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): RD4AD VisA multi-class I-AUROC 92.4 (aligned to multi-class benchmark; sheet had 96.0=per-class) [反向蒸餾]</t>
-        </is>
-      </c>
-      <c r="N42" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2201.10703</t>
-        </is>
-      </c>
-      <c r="O42" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/apple/ml-destseg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38.25" customHeight="1" s="27">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L43" s="15" t="n"/>
-      <c r="M43" s="16" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot)：MLLM-based ZSAD [基於 MLLM]</t>
-        </is>
-      </c>
-      <c r="N43" s="17" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O43" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/zhiyuanyou/UniAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="38.25" customHeight="1" s="27">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>AnomalyAny (Unseen Visual Anomaly Generation)</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Han Sun, Yunkang Cao, Hao Dong, Olga Fink</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2406.01078</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (AnomalyAny arxiv 2406.01078, 1-shot): VisA I-AUC 89.7±0.8 (sheet had 97.5 — corrected) [基於異常生成]</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2406.01078</t>
-        </is>
-      </c>
-      <c r="O44" s="11" t="inlineStr">
-        <is>
-          <t>https://github.com/vitjanz/draem</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="25.5" customHeight="1" s="27">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>PatchEAD</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M45" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (PatchEAD arxiv 2509.25856): VisA I-AUROC 89.5 (PatchEAD+ CLIP, 4-shot). Mixed-variant caveat.</t>
-        </is>
-      </c>
-      <c r="N45" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
-        </is>
-      </c>
-      <c r="O45" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="25.5" customHeight="1" s="27">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>PromptAD</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>CVPR 2024</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H46" s="18" t="inlineStr">
-        <is>
-          <t>89.1</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>97.4</t>
-        </is>
-      </c>
-      <c r="J46" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L46" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M46" s="19" t="inlineStr">
-        <is>
-          <t>✅ verified (PromptAD arxiv 2404.05231 PDF, 4-shot): VisA I-AUROC 89.1 [基於Prompt/CLIP]</t>
-        </is>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
-        </is>
-      </c>
-      <c r="O46" s="20" t="inlineStr">
-        <is>
-          <t>https://github.com/lewandofskee/DiAD</t>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>DeSTSeg</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Xuan Zhang, Shiyu Li, Xi Li, Ping Huang, Jiulong Shan, Ting Chen</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2023</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>93.7</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): DeSTSeg VisA I-AUROC 88.9 (matches sheet) [S-T/分割]</t>
+        </is>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2211.11317</t>
+        </is>
+      </c>
+      <c r="O46" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/boschresearch/MultiADS</t>
         </is>
       </c>
     </row>
@@ -27916,22 +27916,22 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>DeSTSeg</t>
+          <t>UniAD</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Xuan Zhang, Shiyu Li, Xi Li, Ping Huang, Jiulong Shan, Ting Chen</t>
+          <t>Zhiyuan You, Lei Cui, Yujun Shen, Kai Yang, Xin Lu, Yu Zheng, Xinyi Le</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>NeurIPS 2022</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -27941,12 +27941,12 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -27956,7 +27956,7 @@
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
@@ -27966,17 +27966,17 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): DeSTSeg VisA I-AUROC 88.9 (matches sheet) [S-T/分割]</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): UniAD VisA I-AUROC 88.8 (matches sheet) [統一/Transformer]</t>
         </is>
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.11317</t>
+          <t>https://arxiv.org/abs/2206.03687</t>
         </is>
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/boschresearch/MultiADS</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -27988,27 +27988,27 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>UniAD</t>
+          <t>DRAEM</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Zhiyuan You, Lei Cui, Yujun Shen, Kai Yang, Xin Lu, Yu Zheng, Xinyi Le</t>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>NeurIPS 2022</t>
+          <t>ICCV 2021</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -28016,14 +28016,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
+      <c r="H48" s="12" t="n">
+        <v>88.7</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -28033,7 +28031,7 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
@@ -28043,17 +28041,17 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): UniAD VisA I-AUROC 88.8 (matches sheet) [統一/Transformer]</t>
+          <t>✅ verified via B-paper (DRAEM 原論文未測 VisA；數值為 multi-class 統一設定，讀自 DiAD/MambaAD/UniAD 系列 multi-class benchmark table 之 DRAEM VisA I-AUROC 88.7，廣泛引用值) [異常合成]</t>
         </is>
       </c>
       <c r="N48" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2206.03687</t>
+          <t>https://arxiv.org/abs/2108.07610</t>
         </is>
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
         </is>
       </c>
     </row>
@@ -28070,22 +28068,22 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>DRAEM</t>
+          <t>PatchGuard</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2021</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -28094,41 +28092,27 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>88.5</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="12" t="n"/>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>✅ verified via B-paper (DRAEM 原論文未測 VisA；數值為 multi-class 統一設定，讀自 DiAD/MambaAD/UniAD 系列 multi-class benchmark table 之 DRAEM VisA I-AUROC 88.7，廣泛引用值) [異常合成]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.07610</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
+          <t>https://github.com/zqhang/WinCLIP-pytorch</t>
         </is>
       </c>
     </row>
@@ -28140,27 +28124,27 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>PatchGuard</t>
+          <t>SimpleNet</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Mojtaba Nafez, et al.</t>
+          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -28168,28 +28152,44 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="12" t="n"/>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): SimpleNet VisA I-AUROC 87.2 (matches sheet) [異常合成]</t>
         </is>
       </c>
       <c r="N50" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2303.15140</t>
         </is>
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/zqhang/WinCLIP-pytorch</t>
+          <t>https://github.com/farzad-bz/DeCo-Diff</t>
         </is>
       </c>
     </row>
@@ -28206,22 +28206,22 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SimpleNet</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -28229,44 +28229,34 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>96.8</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H51" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>29.8</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25 arxiv 2503.02424 multi-class Table 2): SimpleNet VisA I-AUROC 87.2 (matches sheet) [異常合成]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N51" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15140</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/farzad-bz/DeCo-Diff</t>
+          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
         </is>
       </c>
     </row>
@@ -28278,27 +28268,27 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於擴散 (Diffusion)</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>DiAD</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>AAAI 2024</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -28306,34 +28296,44 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>29.8</v>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="n"/>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): VisA multi-class image AUROC 86.8 [基於擴散/多類別]</t>
         </is>
       </c>
       <c r="N52" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2312.06607</t>
         </is>
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/HY-Vision-Lab/FUNAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28345,27 +28345,27 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>DiAD</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Haoyang He, Jiangning Zhang, Hongxu Chen, Xuhai Chen, Zhishan Li, Xu Chen, Yabiao Wang, Chengjie Wang, Lei Xie</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>AAAI 2024</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -28373,39 +28373,31 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
-          <t>86.8</t>
-        </is>
+      <c r="H53" s="12" t="n">
+        <v>86.8</v>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>89.3</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="n"/>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (DiAD AAAI24 arxiv 2312.06607): VisA multi-class image AUROC 86.8 [基於擴散/多類別]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.06607</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O53" s="14" t="inlineStr">
@@ -28427,22 +28419,22 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Beyond Single-Modal Boundary</t>
+          <t>MultiADS (Multi-Type Zero-Shot AD)</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bosch Research / Ehsan Bayat et al.</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2504.06740</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -28451,30 +28443,36 @@
         </is>
       </c>
       <c r="H54" s="12" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>89.3</v>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="n"/>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot)：跨模態 TVP [跨模態 ZSAD]</t>
+          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS-F row): VisA zero-shot I-AUROC 86.5 [CLIP/零樣本/多類型]</t>
         </is>
       </c>
       <c r="N54" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2504.06740</t>
         </is>
       </c>
       <c r="O54" s="14" t="inlineStr">
@@ -28496,22 +28494,22 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>MultiADS (Multi-Type Zero-Shot AD)</t>
+          <t>PatchCore</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Bosch Research / Ehsan Bayat et al.</t>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2504.06740</t>
+          <t>CVPR 2022</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -28520,11 +28518,11 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>86.5</v>
+        <v>85.3</v>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -28534,7 +28532,7 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="L55" s="12" t="inlineStr">
@@ -28544,12 +28542,12 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS-F row): VisA zero-shot I-AUROC 86.5 [CLIP/零樣本/多類型]</t>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PatchCore VisA multi-class I-AUROC 85.3 (aligned to multi-class; sheet had 95.1=per-class) [記憶庫]</t>
         </is>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.06740</t>
+          <t>https://arxiv.org/abs/2106.08265</t>
         </is>
       </c>
       <c r="O55" s="14" t="inlineStr">
@@ -28571,22 +28569,22 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>PatchCore</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -28595,11 +28593,11 @@
         </is>
       </c>
       <c r="H56" s="12" t="n">
-        <v>85.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
@@ -28609,7 +28607,7 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="L56" s="12" t="inlineStr">
@@ -28619,17 +28617,17 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PatchCore VisA multi-class I-AUROC 85.3 (aligned to multi-class; sheet had 95.1=per-class) [記憶庫]</t>
+          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot): VisA image-AUROC 84.6 (sheet had 85.6) [CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N56" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.08265</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/cool-xuan/vqflow</t>
         </is>
       </c>
     </row>
@@ -28646,22 +28644,22 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
+          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -28670,11 +28668,11 @@
         </is>
       </c>
       <c r="H57" s="12" t="n">
-        <v>84.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -28684,27 +28682,23 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>87.5</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="n"/>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (AA-CLIP CVPR25 arxiv 2503.06661 Table 2, full-shot): VisA image-AUROC 84.6 (sheet had 85.6) [CLIP/零樣本]</t>
+          <t>✅ 已驗證 (ADL WACV25 Table 1 VisA, 10% contamination)：Adaptive Deviation Learning under contaminated data；VisA avg AUROC 0.844 [基於監督式 + Noisy normal]</t>
         </is>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/cool-xuan/vqflow</t>
+          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
         </is>
       </c>
     </row>
@@ -28721,22 +28715,22 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Adaptive Deviation Learning for Visual Anomaly Detection wit</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -28744,12 +28738,14 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H58" s="12" t="n">
-        <v>84.40000000000001</v>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
@@ -28759,23 +28755,27 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L58" s="12" t="n"/>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ADL WACV25 Table 1 VisA, 10% contamination)：Adaptive Deviation Learning under contaminated data；VisA avg AUROC 0.844 [基於監督式 + Noisy normal]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961 Table 1, zero-shot): VisA I-AUROC 82.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Das_Adaptive_Deviation_Learning_for_Visual_Anomaly_Detection_with_Data_Contamination_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O58" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/ByChelsea/VAND-APRIL-GAN</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>AnomalyCLIP</t>
+          <t>WinCLIP</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
+          <t>Jongheon Jeong, Yang Zou, Taewan Kim, Dongqing Zhang, Avinash Ravichandran, Onkar Dabeer</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>ICLR 2024</t>
+          <t>CVPR 2023</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -28817,12 +28817,12 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L59" s="12" t="inlineStr">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961 Table 1, zero-shot): VisA I-AUROC 82.1 [基於CLIP/零樣本]</t>
+          <t>✅ verified (WinCLIP CVPR23 arxiv 2303.14814 PDF, zero-shot): VisA I-AUROC 78.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N59" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
+          <t>https://arxiv.org/abs/2303.14814</t>
         </is>
       </c>
       <c r="O59" s="14" t="inlineStr">
@@ -28869,22 +28869,22 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>WinCLIP</t>
+          <t>April-GAN (CLIP-AD)</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Jongheon Jeong, Yang Zou, Taewan Kim, Dongqing Zhang, Avinash Ravichandran, Onkar Dabeer</t>
+          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -28892,39 +28892,29 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>78.1</t>
-        </is>
-      </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
+      <c r="H60" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>94.2</v>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K60" s="12" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (WinCLIP CVPR23 arxiv 2303.14814 PDF, zero-shot): VisA I-AUROC 78.1 [基於CLIP/零樣本]</t>
+          <t>✅ verified (April-GAN arxiv 2305.17382 PDF, zero-shot): VisA I-AUROC 78.0 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N60" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.14814</t>
+          <t>https://arxiv.org/abs/2305.17382</t>
         </is>
       </c>
       <c r="O60" s="14" t="inlineStr">
@@ -28941,57 +28931,65 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>April-GAN (CLIP-AD)</t>
+          <t>MIRAGE (Realistic Anomaly Generation)</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Xuhai Chen, Yue Han, Jiangning Zhang</t>
+          <t>Anonymous (arXiv 2603.13507)</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2023 VAND Challenge (Zero-shot 第一名)</t>
+          <t>arXiv preprint 2026</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="I61" s="12" t="n">
-        <v>94.2</v>
+        <v>74</v>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K61" s="12" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="L61" s="12" t="n"/>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (April-GAN arxiv 2305.17382 PDF, zero-shot): VisA I-AUROC 78.0 [基於CLIP/零樣本]</t>
+          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3b): VisA downstream I-AUROC 0.74 (U-Net; sheet had 97.8 — corrected). Generation-method downstream, not comparable to dedicated detectors. [基於異常生成]</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2305.17382</t>
+          <t>https://arxiv.org/abs/2603.13507</t>
         </is>
       </c>
       <c r="O61" s="14" t="inlineStr">
@@ -29008,40 +29006,40 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>MIRAGE (Realistic Anomaly Generation)</t>
+          <t>PaDiM</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Anonymous (arXiv 2603.13507)</t>
+          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint 2026</t>
+          <t>ICPR 2021 Workshop</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="H62" s="12" t="n">
-        <v>74</v>
+        <v>72.8</v>
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
@@ -29051,7 +29049,7 @@
       </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="L62" s="12" t="inlineStr">
@@ -29061,12 +29059,12 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (MIRAGE arxiv 2603.13507 Table 3b): VisA downstream I-AUROC 0.74 (U-Net; sheet had 97.8 — corrected). Generation-method downstream, not comparable to dedicated detectors. [基於異常生成]</t>
+          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PaDiM VisA multi-class I-AUROC 72.8 (aligned to multi-class; sheet had 89.1=per-class) [機率]</t>
         </is>
       </c>
       <c r="N62" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2603.13507</t>
+          <t>https://arxiv.org/abs/2011.08785</t>
         </is>
       </c>
       <c r="O62" s="14" t="inlineStr">
@@ -29076,77 +29074,9 @@
       </c>
     </row>
     <row r="63" ht="38.25" customHeight="1" s="27">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>VisA</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>PaDiM</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>ICPR 2021 Workshop</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="I63" s="12" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
-      <c r="J63" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
-      <c r="L63" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M63" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (INP-Former CVPR25 multi-class Table 2): PaDiM VisA multi-class I-AUROC 72.8 (aligned to multi-class; sheet had 89.1=per-class) [機率]</t>
-        </is>
-      </c>
-      <c r="N63" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2011.08785</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://github.com/zqhang/WinCLIP-pytorch</t>
         </is>
       </c>
     </row>
@@ -29171,75 +29101,72 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29251,7 +29178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29572,428 +29499,428 @@
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="27">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>MPDD</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>GLAD</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Hang Yao, Ming Liu, Haolin Wang, Zhicun Yin, Zifei Yan, Xiaopeng Hong, Wangmeng Zuo</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (GLAD ECCV24 Table 2 average)：Global-Local Anomaly Detection；LDM + DINO fine-tuned；MPDD I=97.5 P=98.7 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.07487</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38.25" customHeight="1" s="27">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Dinomaly</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Jia Guo, Shuai Lu, Weihang Zhang, Huiqi Li, et al.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>✅ verified (Dinomaly arxiv 2405.14325): MPDD multi-class I-AUROC 97.2 [基於重構/ViT]</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.14325</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>https://github.com/vitjanz/draem</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25.5" customHeight="1" s="27">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>InvAD-Diff (Inversion-based Diffusion)</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Shunsuke Sakai, et al.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>arXiv preprint / CVPR 2026 投稿中</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (arxiv 2504.05662 Table 2): MPDD multi-class I-AUROC 96.5</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2504.05662</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/hq-deng/RD4AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" s="27">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>RealNet</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2024</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): MPDD I-AUROC 96.3 [基於異常合成]</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.05897</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25.5" customHeight="1" s="27">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>DiffusionAD</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2025</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>98.7</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>✅ verified+corrected (DiffusionAD arxiv 2303.08730 Table V): MPDD I-AUROC 96.2 (sheet had 95.9) [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.08730</t>
+        </is>
+      </c>
+      <c r="O11" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/gudovskiy/cflow-ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25.5" customHeight="1" s="27">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>基於表徵 (Representation)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>SimpleNet</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>CVPR 2023</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>97.1</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>✅ verified via B-paper (SimpleNet 原論文未測 MPDD；數值讀自 GLASS ECCV24 Table S5, SimpleNet MPDD I-AUROC 98.1。原 sheet 90.6 為另一來源/協議) [異常合成]</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2303.15140</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr">
-        <is>
-          <t>https://github.com/HuiZhang0812/DiffusionAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38.25" customHeight="1" s="27">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>GLAD</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Hang Yao, Ming Liu, Haolin Wang, Zhicun Yin, Zifei Yan, Xiaopeng Hong, Wangmeng Zuo</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>ECCV 2024</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (GLAD ECCV24 Table 2 average)：Global-Local Anomaly Detection；LDM + DINO fine-tuned；MPDD I=97.5 P=98.7 [基於擴散]</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2406.07487</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25.5" customHeight="1" s="27">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Dinomaly</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Jia Guo, Shuai Lu, Weihang Zhang, Huiqi Li, et al.</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>✅ verified (Dinomaly arxiv 2405.14325): MPDD multi-class I-AUROC 97.2 [基於重構/ViT]</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2405.14325</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>https://github.com/vitjanz/draem</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" s="27">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>InvAD-Diff (Inversion-based Diffusion)</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Shunsuke Sakai, et al.</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>arXiv preprint / CVPR 2026 投稿中</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (arxiv 2504.05662 Table 2): MPDD multi-class I-AUROC 96.5</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2504.05662</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25.5" customHeight="1" s="27">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>RealNet</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Ximiao Zhang, Min Xu, Xiuzhuang Zhou</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2024</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>96.3</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 PDF): MPDD I-AUROC 96.3 [基於異常合成]</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2403.05897</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25.5" customHeight="1" s="27">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>基於擴散 (Diffusion)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>DiffusionAD</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Hui Zhang, Zheng Wang, Zuxuan Wu, Yu-Gang Jiang</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>IEEE TPAMI 2025</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="22" t="inlineStr">
-        <is>
-          <t>✅ verified+corrected (DiffusionAD arxiv 2303.08730 Table V): MPDD I-AUROC 96.2 (sheet had 95.9) [基於擴散]</t>
-        </is>
-      </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2303.08730</t>
-        </is>
-      </c>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>https://github.com/gudovskiy/cflow-ad</t>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>PatchCore</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>CVPR 2022</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified via B-paper (PatchCore 原論文未測 MPDD；數值讀自 GLASS ECCV24 Table S5, PatchCore MPDD I-AUROC 93.5。註：協議相依，RealNet T4 報 82.1) [記憶庫]</t>
+        </is>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2106.08265</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -30005,27 +29932,27 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>DRAEM</t>
+          <t>PromptAD</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2021</t>
+          <t>CVPR 2024</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -30033,15 +29960,11 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>94.1</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>91.8</t>
-        </is>
+      <c r="H13" s="12" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>97.3</v>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
@@ -30053,24 +29976,20 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>⚠️ DRAEM 原論文未測 MPDD；94.1 為第三方 re-eval，無法唯一定位來源（協議相依：不同 benchmark 報不同值）。需指定參考 benchmark 才能標 ✅ [異常合成]</t>
+          <t>✅ verified (PromptAD arxiv 2404.05231 PDF): MPDD I-AUROC 87.2 [基於Prompt/CLIP]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.07610</t>
+          <t>https://arxiv.org/abs/2404.05231</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/xiahaifeng1995/PaDiM-Anomaly-Detection-Localization-master</t>
+          <t>https://github.com/guojiajeremy/Dinomaly</t>
         </is>
       </c>
     </row>
@@ -30082,27 +30001,27 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>PatchCore</t>
+          <t>PatchGuard</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -30111,36 +30030,22 @@
         </is>
       </c>
       <c r="H14" s="12" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>✅ verified via B-paper (PatchCore 原論文未測 MPDD；數值讀自 GLASS ECCV24 Table S5, PatchCore MPDD I-AUROC 93.5。註：協議相依，RealNet T4 報 82.1) [記憶庫]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.08265</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
@@ -30157,27 +30062,27 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>RD4AD (Reverse Distillation)</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -30185,14 +30090,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
+      <c r="H15" s="12" t="n">
+        <v>81.7</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -30205,24 +30108,20 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>⚠️ RD4AD 原論文未測 MPDD；92.7 為第三方 re-eval，來源無法唯一定位（協議相依）。需指定參考 benchmark [反向蒸餾]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.10703</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/FuNz-0/PromptAD</t>
         </is>
       </c>
     </row>
@@ -30239,22 +30138,22 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>PromptAD</t>
+          <t>MultiADS (Multi-Type Zero-Shot AD)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Xiaofan Li, Zhizhong Zhang, Xin Tan, Chengwei Chen, Yanyun Qu, Yuan Xie, Lizhuang Ma</t>
+          <t>Bosch Research / Ehsan Bayat et al.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2024</t>
+          <t>ICCV 2025 (CVF Open Access) / arXiv 2504.06740</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -30263,35 +30162,33 @@
         </is>
       </c>
       <c r="H16" s="12" t="n">
-        <v>87.2</v>
+        <v>78.3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>97.3</v>
+        <v>95.8</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="K16" s="12" t="n">
+        <v>89.7</v>
       </c>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (PromptAD arxiv 2404.05231 PDF): MPDD I-AUROC 87.2 [基於Prompt/CLIP]</t>
+          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS row): MPDD zero-shot I-AUROC 78.3 [CLIP/零樣本/多類型]</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2404.05231</t>
+          <t>https://arxiv.org/abs/2504.06740</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/guojiajeremy/Dinomaly</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -30303,27 +30200,27 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>CFLOW-AD</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Denis Gudovskiy, Shun Ishizaka, Kazuki Kozuka</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>WACV 2022</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -30332,41 +30229,33 @@
         </is>
       </c>
       <c r="H17" s="12" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>96.5</v>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K17" s="12" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 Table 4, visual read): CFLOW MPDD image-AUROC 86.1 (exact match) [NF]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): MPDD I-AUROC 77.0 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.12571</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/hyao1/GLAD</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -30378,27 +30267,27 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>PatchGuard</t>
+          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Mojtaba Nafez, et al.</t>
+          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -30407,27 +30296,35 @@
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>85.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
+        <v>96.7</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
+          <t>✅ verified (AA-CLIP CVPR25 arxiv 2503.06661 Table 2): MPDD image-level AUROC 75.1 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2503.06661</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/boschresearch/MultiADS</t>
         </is>
       </c>
     </row>
@@ -30444,7 +30341,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
+          <t>Beyond Single-Modal Boundary</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -30468,17 +30365,15 @@
         </is>
       </c>
       <c r="H19" s="12" t="n">
-        <v>81.7</v>
+        <v>72.8</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J19" s="12" t="n">
+        <v>79.7</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -30488,17 +30383,17 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
+          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/FuNz-0/PromptAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -30515,400 +30410,53 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>MultiADS (Multi-Type Zero-Shot AD)</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Bosch Research / Ehsan Bayat et al.</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2025 (CVF Open Access) / arXiv 2504.06740</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>預印本</t>
         </is>
       </c>
       <c r="H20" s="12" t="n">
-        <v>78.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>71.8</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>89.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>✅ verified (MultiADS ICCV25 CVF PDF, MultiADS row): MPDD zero-shot I-AUROC 78.3 [CLIP/零樣本/多類型]</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): MPDD I-AUROC 68.6 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.06740</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>AnomalyCLIP</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>ICLR 2024</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): MPDD I-AUROC 77.0 [基於CLIP/零樣本]</t>
-        </is>
-      </c>
-      <c r="N21" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>AA-CLIP (Anomaly-Aware CLIP)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Wenxin Ma, Xu Zhang, Qingsong Yao, Fenghe Tang, Chenxu Zhang, Yanfei Liu, S.Kevin Zhou</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025 (CVF Open Access) / arXiv 2503.06661</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (AA-CLIP CVPR25 arxiv 2503.06661 Table 2): MPDD image-level AUROC 75.1 [基於CLIP/零樣本]</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.06661</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/boschresearch/MultiADS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>PaDiM</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>ICPR 2021 Workshop</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>96.7</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (RealNet CVPR24 arxiv 2403.05897 Table 4, visual read): PaDiM MPDD image-AUROC 74.8 (exact match) [機率/記憶]</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2011.08785</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Beyond Single-Modal Boundary</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (BSMB CVPR25 Table 1, zero-shot) [跨模態 ZSAD]</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Mao_Beyond_Single-Modal_Boundary_Cross-Modal_Anomaly_Detection_through_Visual_Prototype_and_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>MPDD</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>PatchEAD</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified (PatchEAD arxiv 2509.25856): MPDD I-AUROC 68.6 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -30924,21 +30472,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31996,27 +31537,27 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>UniAD</t>
+          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>Zhiyuan You, Lei Cui, Yujun Shen, Kai Yang, Xin Lu, Yu Zheng, Xinyi Le</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>NeurIPS 2022</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -32024,44 +31565,34 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>97.6</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H17" s="21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>47.1</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L17" s="21" t="n"/>
       <c r="M17" s="22" t="inlineStr">
         <is>
-          <t>⚠️ UniAD 原論文測 MVTec AD+CIFAR，未測 BTAD；94.5 為第三方 re-eval，來源無法唯一定位（協議相依）[統一/Transformer]</t>
+          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2206.03687</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/gudovskiy/cflow-ad</t>
+          <t>https://github.com/xiahaifeng1995/PRN</t>
         </is>
       </c>
     </row>
@@ -32078,22 +31609,22 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>SimpleNet</t>
+          <t>PatchCore</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
+          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2023</t>
+          <t>CVPR 2022</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -32101,14 +31632,12 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>94.1</t>
-        </is>
+      <c r="H18" s="21" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -32128,17 +31657,17 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>⚠️ SimpleNet 原論文未測 BTAD；94.1 為第三方 re-eval，來源無法唯一定位（協議相依，cf. GLASS 未列 BTAD）[異常合成]</t>
+          <t>✅ verified via B-paper (PatchCore 原論文未測 BTAD；數值讀自 UniNet CVPR25 Table 1(b) baseline 比較, PatchCore I-AUROC 93.13≈93.1) [記憶庫]</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15140</t>
+          <t>https://arxiv.org/abs/2106.08265</t>
         </is>
       </c>
       <c r="O18" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/luow23/AMI-Net</t>
         </is>
       </c>
     </row>
@@ -32155,67 +31684,55 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>PaDiM</t>
+          <t>PatchEAD</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>Thomas Defard, Aleksandr Setkov, Angelique Loesch, Romaric Audigier</t>
+          <t>Anonymous (arXiv 2509.25856)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>ICPR 2021 Workshop</t>
+          <t>arXiv preprint 2025</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>97</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="L19" s="21" t="n"/>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>⚠️ PaDiM 原論文未測 BTAD；94.0 為第三方 re-eval，來源無法唯一定位（協議相依）[機率/記憶]</t>
+          <t>✅ verified (PatchEAD arxiv 2509.25856): BTAD I-AUROC 91.2 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.08785</t>
+          <t>https://arxiv.org/abs/2509.25856</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/guojiajeremy/Dinomaly</t>
+          <t>https://github.com/Mwxinnn/AA-CLIP</t>
         </is>
       </c>
     </row>
@@ -32227,27 +31744,27 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Bayesian Prompt Flow Learning for Zero-Shot Anomaly Detectio</t>
+          <t>VT-ADL</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>ISIE 2021 / arXiv 2104.10036</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -32256,33 +31773,41 @@
         </is>
       </c>
       <c r="H20" s="21" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>47.1</v>
+        <v>90</v>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="n"/>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Bayes-PFL CVPR25 Table 1, zero-shot)：[基於 VLM]</t>
+          <t>✅ verified (VT-ADL arxiv 2104.10036 Table IV, visual read): BTAD mean PR-AUC 0.90 / PRO 0.89. NOTE: VT-ADL reports PR-AUC &amp; PRO on BTAD, NOT image-AUROC; value relabeled to PR-AUC (sheet 94.5 was not a VT-ADL metric). [BTAD原始論文/Transformer]</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qu_Bayesian_Prompt_Flow_Learning_for_Zero-Shot_Anomaly_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2104.10036</t>
         </is>
       </c>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xiahaifeng1995/PRN</t>
+          <t>https://github.com/zqhang/AnomalyCLIP</t>
         </is>
       </c>
     </row>
@@ -32299,22 +31824,22 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>PatchCore</t>
+          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>CVPR 2022</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -32323,11 +31848,11 @@
         </is>
       </c>
       <c r="H21" s="21" t="n">
-        <v>93.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -32340,24 +31865,20 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L21" s="21" t="n"/>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>✅ verified via B-paper (PatchCore 原論文未測 BTAD；數值讀自 UniNet CVPR25 Table 1(b) baseline 比較, PatchCore I-AUROC 93.13≈93.1) [記憶庫]</t>
+          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.08265</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/luow23/AMI-Net</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32369,27 +31890,27 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>DRAEM</t>
+          <t>AnomalyCLIP</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>ICCV 2021</t>
+          <t>ICLR 2024</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -32397,44 +31918,34 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
+      <c r="H22" s="21" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>94.2</v>
       </c>
       <c r="J22" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K22" s="21" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L22" s="21" t="n"/>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>⚠️ DRAEM 原論文未測 BTAD；93.1 為第三方 re-eval，來源無法唯一定位（協議相依）[異常合成]</t>
+          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): BTAD I-AUROC 88.3 [基於CLIP/零樣本]</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.07610</t>
+          <t>https://arxiv.org/abs/2310.18961</t>
         </is>
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/xrli-U/MuSc</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32446,27 +31957,27 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>基於 NF (Normalizing Flow)</t>
+          <t>基於資料擴增 (Data Augmentation)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>CFLOW-AD</t>
+          <t>PatchGuard</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>Denis Gudovskiy, Shun Ishizaka, Kazuki Kozuka</t>
+          <t>Mojtaba Nafez, et al.</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>WACV 2022</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -32474,39 +31985,23 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>92.9</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>97.4</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H23" s="21" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>⚠️ CFLOW-AD 原論文未測 BTAD；92.9 為第三方 re-eval，來源無法唯一定位（協議相依）[NF]</t>
+          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.12571</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -32515,345 +32010,11 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>PatchEAD</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>Anonymous (arXiv 2509.25856)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>arXiv preprint 2025</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>97</v>
-      </c>
-      <c r="J24" s="21" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="22" t="inlineStr">
-        <is>
-          <t>✅ verified (PatchEAD arxiv 2509.25856): BTAD I-AUROC 91.2 (PatchEAD+ DINOv2, batch zero-shot). Mixed-variant caveat.</t>
-        </is>
-      </c>
-      <c r="N24" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.25856</t>
-        </is>
-      </c>
-      <c r="O24" s="23" t="inlineStr">
-        <is>
-          <t>https://github.com/Mwxinnn/AA-CLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>基於重構 (Reconstruction)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>VT-ADL</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Pankaj Mishra, Riccardo Verk, Daniele Fornasier, Claudio Piciarelli, Gian Luca Foresti</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>ISIE 2021 / arXiv 2104.10036</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="inlineStr">
-        <is>
-          <t>✅ verified (VT-ADL arxiv 2104.10036 Table IV, visual read): BTAD mean PR-AUC 0.90 / PRO 0.89. NOTE: VT-ADL reports PR-AUC &amp; PRO on BTAD, NOT image-AUROC; value relabeled to PR-AUC (sheet 94.5 was not a VT-ADL metric). [BTAD原始論文/Transformer]</t>
-        </is>
-      </c>
-      <c r="N25" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2104.10036</t>
-        </is>
-      </c>
-      <c r="O25" s="23" t="inlineStr">
-        <is>
-          <t>https://github.com/zqhang/AnomalyCLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>Towards Zero-Shot Anomaly Detection and Reasoning with Multi</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>89</v>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Anomaly-OV CVPR25 Table 2, zero-shot) [基於 MLLM]</t>
-        </is>
-      </c>
-      <c r="N26" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xu_Towards_Zero-Shot_Anomaly_Detection_and_Reasoning_with_Multimodal_Large_Language_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O26" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>AnomalyCLIP</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Qihang Zhou, Guansong Pang, Yu Tian, Shibo He, Jiming Chen</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>ICLR 2024</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="I27" s="21" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="22" t="inlineStr">
-        <is>
-          <t>✅ verified (AnomalyCLIP ICLR24 arxiv 2310.18961, zero-shot): BTAD I-AUROC 88.3 [基於CLIP/零樣本]</t>
-        </is>
-      </c>
-      <c r="N27" s="23" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2310.18961</t>
-        </is>
-      </c>
-      <c r="O27" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>BTAD</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>PatchGuard</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Mojtaba Nafez, et al.</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="22" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (PDF 2026-05-19)：Adversarially-robust AD (ViT + pseudo-anomaly)；表中為 Clean 設定 (Table 1/2)；為對抗強健性而設計,clean 指標偏低屬正常,不可與非-robust SOTA 直接比較 [基於資料擴增]</t>
-        </is>
-      </c>
-      <c r="N28" s="23" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nafez_PatchGuard_Adversarially_Robust_Anomaly_Detection_and_Localization_through_Vision_Transformers_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="O28" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
@@ -32877,16 +32038,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15280,7 +15280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22117,6 +22117,59 @@
         </is>
       </c>
       <c r="O94" s="23" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>Uni-RCM: Unified Reference-guided Cross-modal Mapping for Multi-Class Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>Yangchen Wu, Huiqiang Xie</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="inlineStr">
+        <is>
+          <t>arXiv preprint</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>預印本</t>
+        </is>
+      </c>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+      <c r="J95" s="21" t="n"/>
+      <c r="K95" s="21" t="n"/>
+      <c r="L95" s="21" t="n"/>
+      <c r="M95" s="22" t="inlineStr">
+        <is>
+          <t>Auto-fetched (2026-05); 待人工核對指標 [基於表徵 (Representation)]</t>
+        </is>
+      </c>
+      <c r="N95" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.29455</t>
+        </is>
+      </c>
+      <c r="O95" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30491,7 +30544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32010,11 +32063,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -15280,7 +15280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22170,6 +22170,77 @@
         </is>
       </c>
       <c r="O95" s="23" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>基於知識蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CDO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Cao et al.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>IEEE TII 2023</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="I96" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>✅ verified (CDO 官方 repo caoyunkang/CDO Table 1，MVTec 15 類 unsupervised 平均；IEEE TII 2023): I-AUROC 99.13 / P-AUROC 98.12 / AU-PRO 94.30 [基於知識蒸餾]</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/CDO</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/CDO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -24761,7 +24761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29201,6 +29201,150 @@
       <c r="O63" t="inlineStr">
         <is>
           <t>https://github.com/zqhang/WinCLIP-pytorch</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>基於知識蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CDO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Cao et al.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IEEE TII 2023</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>✅ verified (CDO 官方 repo caoyunkang/CDO Table 2，VisA 12 類 unsupervised 平均；IEEE TII 2023): I-AUROC 96.54 / P-AUROC 99.07 / AU-PRO 94.80 [基於知識蒸餾]</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/CDO</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/CDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>基於 NF (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MSFlow</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Zhou et al.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2024</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>✅ verified (MSFlow 官方 repo cool-xuan/msflow VisA 表 + arXiv 2308.15300；IEEE TNNLS 2024): I-AUROC 95.2 / P-AUROC 97.8 [基於 NF]</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.15300</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://github.com/cool-xuan/msflow</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -23783,7 +23783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -23800,7 +23800,7 @@
     <row r="1" ht="24" customHeight="1" s="27">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>資料集：MVTec AD 2  (排序：依 P-AP 由高至低；指標為 ClassF1/SegF1/AucPro₀.₀₅ 而非 AUROC)</t>
+          <t>資料集：MVTec AD 2  (排序：依 SegF1 由高至低。官方指標 = ClassF1(影像F1) / SegF1(像素F1，排名依據) / AU-PRO@0.05，非 AUROC。欄位對應：I-AUROC欄→ClassF1、P-AP欄→SegF1、P-PRO欄→AU-PRO@0.05)</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
     <row r="4" ht="38.25" customHeight="1" s="27">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>MVTec AD2</t>
+          <t>MVTec AD 2</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
@@ -23906,12 +23906,12 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Xingao Wang, Shuying Xia, Zhaohong Liao, Mengjie Xie, Handa Wang, Zhi Gao</t>
+          <t>Xingao Wang et al.</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第一名)</t>
+          <t>CVPR 2025 VAND 3.0 (Track1 第一名)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -23921,12 +23921,12 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>✅ 已驗證 (第一名)</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -23934,14 +23934,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>53.81</t>
-        </is>
+      <c r="J4" s="12" t="n">
+        <v>53.81</v>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
@@ -23951,12 +23949,12 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 82.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=53.81（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。[基於表徵]</t>
         </is>
       </c>
       <c r="N4" s="29" t="inlineStr">
         <is>
-          <t>https://github.com/ISVL119/isvl/blob/main/vand3.0.pdf</t>
+          <t>https://github.com/ISVL119/isvl/tree/main</t>
         </is>
       </c>
       <c r="O4" s="29" t="inlineStr">
@@ -23968,7 +23966,7 @@
     <row r="5" ht="38.25" customHeight="1" s="27">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>MVTec AD2</t>
+          <t>MVTec AD 2</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
@@ -23988,7 +23986,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Challenge (Track 1 第二名)</t>
+          <t>CVPR 2025 VAND 3.0 (Track1 第二名)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -23998,28 +23996,22 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>79.62</t>
-        </is>
+          <t>✅ 已驗證 (第二名)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>79.62</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>67.25</t>
-        </is>
+      <c r="J5" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>67.25</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -24028,7 +24020,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 79.62 is individually verified in RoBiS arxiv 2505.21152 Table 2 (ClassF1 79.62% TESTpriv).</t>
+          <t>✅ verified — ClassF1 79.62 / SegF1 51.00 / AU-PRO@0.05 67.25 (private)。來源: RoBiS arXiv 2505.21152 Table 1&amp;2。[基於表徵]</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -24045,7 +24037,7 @@
     <row r="6" ht="38.25" customHeight="1" s="27">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>MVTec AD2</t>
+          <t>MVTec AD 2</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -24055,32 +24047,32 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SuperAD (Training-free DINOv2)</t>
+          <t>ASEG (VAND 2025 第三名)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Hugo Henrique Doberstein Roggeveen, et al.</t>
+          <t>VAND 3.0 team</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2025 VAND 3.0 Workshop</t>
+          <t>CVPR 2025 VAND 3.0 (Track1 第三名)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
+          <t>✅ 已驗證 (第三名)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -24088,14 +24080,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>47.18</t>
-        </is>
+      <c r="J6" s="12" t="n">
+        <v>50.43</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
@@ -24105,12 +24095,12 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 70.2 is individually verified in SuperAD arxiv 2505.19750 (ClassF1 70.2 TESTpriv).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=50.43（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2505.19750</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O6" s="13" t="inlineStr">
@@ -24132,32 +24122,32 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>EfficientAD (AD2 baseline)</t>
+          <t>SuperAD (Training-free DINOv2)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
+          <t>Hugo H. D. Roggeveen et al.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>WACV 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2025 VAND 3.0 (Track1 第四名)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (第四名)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -24165,34 +24155,32 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
+      <c r="J7" s="12" t="n">
+        <v>47.75</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 63.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=47.75（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。原 47.18 已修正</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://arxiv.org/abs/2505.19750</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/luow23/INP-Former</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -24209,61 +24197,65 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SuperADD: Training-free Class-agnostic Anomaly Segmentation -- CVPR 2026 VAND 4.0 Workshop</t>
+          <t>Filter-Former (VAND 2025 第五名)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Lukas Roming, Felix Lehnerer, Jonas V. Funk, Andreas Michel, Georg Maier, Thomas Längle, Jürgen Beyerer</t>
+          <t>VAND 3.0 team</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>arXiv preprint</t>
+          <t>CVPR 2025 VAND 3.0 (Track1 第五名)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>預印本</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>57.42</v>
+          <t>✅ 已驗證 (第五名)</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J8" s="12" t="n">
+        <v>44.43</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 57.42 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=44.43（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2605.14808</t>
+          <t>https://arxiv.org/abs/2509.17615</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/nelson1425/EfficientAD</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -24275,37 +24267,37 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於 NF (Normalizing Flow)</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>INP-Former (AD2 baseline)</t>
+          <t>MSFlow (AD2 baseline)</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Wei Luo, Yunkang Cao, Haiming Yao, Xiaotian Zhang, Jianan Lou, Yuqi Cheng, Weiming Shen, Wenyong Yu</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>CVPR 2025 / arXiv 2503.02424</t>
+          <t>IEEE TNNLS 2024 (AD2 baseline)</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (AD2 baseline)</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -24313,14 +24305,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
+      <c r="J9" s="18" t="n">
+        <v>21.8</v>
       </c>
       <c r="K9" s="18" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L9" s="18" t="inlineStr">
@@ -24330,17 +24320,17 @@
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 55.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=21.8（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。AD2 官方 baseline 中最佳。[基於 NF]</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.02424</t>
+          <t>https://arxiv.org/abs/2308.15300</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/arimousa/DDAD</t>
+          <t>https://github.com/cool-xuan/msflow</t>
         </is>
       </c>
     </row>
@@ -24352,37 +24342,37 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>基於擴散 (Diffusion)</t>
+          <t>基於知識蒸餾 (Knowledge Distillation)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>DDAD (AD2 baseline)</t>
+          <t>RD++ (AD2 baseline)</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+          <t>Tran Dinh Tien et al.</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>BMVC 2024 (AD2 paper baseline)</t>
+          <t>CVPR 2023 (AD2 baseline)</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (AD2 baseline)</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -24390,14 +24380,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
+      <c r="J10" s="15" t="n">
+        <v>19.2</v>
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" s="15" t="inlineStr">
@@ -24407,17 +24395,17 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 53.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=19.2（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。[基於知識蒸餾]</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://arxiv.org/abs/2206.15476</t>
         </is>
       </c>
       <c r="O10" s="17" t="inlineStr">
         <is>
-          <t>https://github.com/hq-deng/RD4AD</t>
+          <t>https://github.com/tientrandinh/Revisiting-Reverse-Distillation</t>
         </is>
       </c>
     </row>
@@ -24429,22 +24417,22 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>基於表徵 (Representation)</t>
+          <t>基於重構 (Reconstruction)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>PatchCore (AD2 baseline)</t>
+          <t>RD4AD (AD2 baseline)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Karsten Roth, Latha Pemula, Joaquin Zepeda, Bernhard Schölkopf, Thomas Brox, Peter Gehler</t>
+          <t>Hanqiu Deng, Xingyu Li</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2022 (AD2 baseline)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -24454,12 +24442,12 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (AD2 baseline)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
@@ -24467,14 +24455,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+      <c r="J11" s="12" t="n">
+        <v>18.1</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -24484,17 +24470,17 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 52.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=18.1（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。原 14.2 已修正。[基於重構]</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://arxiv.org/abs/2201.10703</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/amazon-science/patchcore-inspection</t>
+          <t>https://github.com/hq-deng/RD4AD</t>
         </is>
       </c>
     </row>
@@ -24506,37 +24492,37 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>基於重構 (Reconstruction)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>RD4AD (AD2 baseline)</t>
+          <t>SimpleNet (AD2 baseline)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Hanqiu Deng, Xingyu Li</t>
+          <t>Zhikang Liu et al.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>CVPR 2022 (AD2 paper baseline)</t>
+          <t>CVPR 2023 (AD2 baseline)</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (AD2 baseline)</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -24544,14 +24530,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="J12" s="9" t="n">
+        <v>17.7</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -24561,17 +24545,17 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 50.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=17.7（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。原 11.8 已修正。[基於表徵]</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://arxiv.org/abs/2303.15140</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>https://github.com/vitjanz/draem</t>
+          <t>https://github.com/DonaldRR/SimpleNet</t>
         </is>
       </c>
     </row>
@@ -24583,37 +24567,37 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>基於資料擴增 (Data Augmentation)</t>
+          <t>基於表徵 (Representation)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>DRAEM (AD2 baseline)</t>
+          <t>EfficientAD (AD2 baseline)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skočaj</t>
+          <t>Kilian Batzner, Lars Heckler, Rebecca König</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ICCV 2021 (AD2 paper baseline)</t>
+          <t>WACV 2024 (AD2 baseline)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>已發表</t>
+          <t>✅ 已驗證 (AD2 baseline)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -24621,14 +24605,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
+      <c r="J13" s="12" t="n">
+        <v>15.4</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -24638,17 +24620,17 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 48.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=15.4（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。原 16.9 已修正。[基於表徵]</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
+          <t>https://arxiv.org/abs/2303.14535</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>https://github.com/DonaldRR/SimpleNet</t>
+          <t>https://github.com/nelson1425/EfficientAD</t>
         </is>
       </c>
     </row>
@@ -24660,70 +24642,455 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>DSR (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik et al.</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>ECCV 2022 (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=10.9（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。[基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2208.01521</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/VitjanZ/DSR_anomaly_detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>基於表徵 (Representation)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>SimpleNet (AD2 baseline)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Zhikang Liu, Yiming Zhou, Yuansheng Xu, Zilei Wang</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>CVPR 2023 (AD2 paper baseline)</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>已發表</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr">
-        <is>
-          <t>✅ verified metric — MVTec AD2 column = ClassF1 (image-level classification F1), confirmed via RoBiS paper (79.62=ClassF1 TESTpriv) AND SuperAD paper (70.2=ClassF1). This is the VAND2025/MVTec-AD2 challenge ClassF1 metric, NOT image-AUROC. Value 46.0 is the AD2/VAND2025 benchmark ClassF1 result for this method (challenge leaderboard).</t>
-        </is>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2503.21622</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PatchCore (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Karsten Roth et al.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CVPR 2022 (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>✅ verified — AD2 官方指標=SegF1(像素F1，排名依據)；SegF1_priv=3.7（來源: VAND 3.0 報告 arXiv 2509.17615 Table 2 / RoBiS arXiv 2505.21152 Table 1）。ClassF1/AU-PRO@0.05 官方僅 RoBiS 公布。原 13.4 已修正（高解析度下大幅退化）。[基於表徵]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2106.08265</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://github.com/amazon-science/patchcore-inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>基於擴散 (Diffusion)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DDAD (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Arian Mousakhan, Thomas Brox, Jawad Tayyub</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BMVC 2024</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>⏳ Pending — 非 VAND 官方 leaderboard 條目；AD2 SegF1 待官方表核對（不放佔位值）。 [基於擴散]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2307.08816</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://github.com/arimousa/DDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DRAEM (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Vitjan Zavrtanik, Matej Kristan, Danijel Skocaj</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ICCV 2021</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>⏳ Pending — 非 VAND 官方 leaderboard 條目；AD2 SegF1 待官方表核對（不放佔位值）。 [基於資料擴增]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2108.07610</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://github.com/VitjanZ/DRAEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INP-Former (AD2 baseline)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wei Luo, Yunkang Cao et al.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CVPR 2025 / arXiv 2503.02424</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>⏳ Pending — 非 VAND 官方 leaderboard 條目；AD2 SegF1 待官方表核對（不放佔位值）。 原 SegF1=21.8 疑似誤植 MSFlow 數值，已清除。[基於表徵]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.02424</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://github.com/luow23/INP-Former</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MVTec AD 2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SuperADD (VAND 4.0)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lukas Roming et al.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>arXiv preprint (CVPR 2026 VAND 4.0 Workshop)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>⏳ Pending — 非 VAND 官方 leaderboard 條目；AD2 SegF1 待官方表核對（不放佔位值）。 arXiv preprint，未列入 VAND 3.0 官方表。[基於表徵]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.14808</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明 Notes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="總覽 All Papers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVTec AD" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVTec LOCO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVTec AD2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPDD" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BTAD" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVTec 3D" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="說明 Notes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="總覽 All Papers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MVTec AD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MVTec LOCO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MVTec AD2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="VisA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MPDD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BTAD" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MVTec 3D" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -15070,6 +15070,572 @@
           <t>N/A</t>
         </is>
       </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B205" s="18" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C205" s="18" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D205" s="18" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E205" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F205" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G205" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H205" s="18" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I205" s="18" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J205" s="18" t="n"/>
+      <c r="K205" s="18" t="n"/>
+      <c r="L205" s="18" t="n"/>
+      <c r="M205" s="19" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N205" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O205" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B206" s="18" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C206" s="18" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D206" s="18" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F206" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G206" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H206" s="18" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I206" s="18" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J206" s="18" t="n"/>
+      <c r="K206" s="18" t="n"/>
+      <c r="L206" s="18" t="n"/>
+      <c r="M206" s="19" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N206" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O206" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="18" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B207" s="18" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D207" s="18" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E207" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F207" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G207" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H207" s="18" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I207" s="18" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="J207" s="18" t="n"/>
+      <c r="K207" s="18" t="n"/>
+      <c r="L207" s="18" t="n"/>
+      <c r="M207" s="19" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N207" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O207" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="18" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B208" s="18" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C208" s="18" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D208" s="18" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E208" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F208" s="18" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G208" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H208" s="18" t="n"/>
+      <c r="I208" s="18" t="n"/>
+      <c r="J208" s="18" t="n"/>
+      <c r="K208" s="18" t="n"/>
+      <c r="L208" s="18" t="n"/>
+      <c r="M208" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N208" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O208" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="18" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B209" s="18" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C209" s="18" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D209" s="18" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E209" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F209" s="18" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G209" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H209" s="18" t="n"/>
+      <c r="I209" s="18" t="n"/>
+      <c r="J209" s="18" t="n"/>
+      <c r="K209" s="18" t="n"/>
+      <c r="L209" s="18" t="n"/>
+      <c r="M209" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N209" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O209" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B210" s="18" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C210" s="18" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D210" s="18" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E210" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F210" s="18" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G210" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H210" s="18" t="n"/>
+      <c r="I210" s="18" t="n"/>
+      <c r="J210" s="18" t="n"/>
+      <c r="K210" s="18" t="n"/>
+      <c r="L210" s="18" t="n"/>
+      <c r="M210" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N210" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O210" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="18" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B211" s="18" t="inlineStr">
+        <is>
+          <t>基於重構</t>
+        </is>
+      </c>
+      <c r="C211" s="18" t="inlineStr">
+        <is>
+          <t>POUTA (Produce Once, Utilize Twice for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D211" s="18" t="inlineStr">
+        <is>
+          <t>Shuyuan Wang, Qi Li, Huiyuan Luo, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E211" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F211" s="18" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G211" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H211" s="18" t="n"/>
+      <c r="I211" s="18" t="n"/>
+      <c r="J211" s="18" t="n"/>
+      <c r="K211" s="18" t="n"/>
+      <c r="L211" s="18" t="n"/>
+      <c r="M211" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — arXiv HTML (2312.12913) blocked; no public metrics table. Datasets: MVTec AD, VisA, DAGM. IEEE TCSVT Nov 2024 (DOI: 10.1109/TCSVT.2024.3420775). 基於重構</t>
+        </is>
+      </c>
+      <c r="N211" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.12913</t>
+        </is>
+      </c>
+      <c r="O211" s="20" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B212" s="18" t="inlineStr">
+        <is>
+          <t>基於重構</t>
+        </is>
+      </c>
+      <c r="C212" s="18" t="inlineStr">
+        <is>
+          <t>POUTA (Produce Once, Utilize Twice for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D212" s="18" t="inlineStr">
+        <is>
+          <t>Shuyuan Wang, Qi Li, Huiyuan Luo, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E212" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F212" s="18" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G212" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H212" s="18" t="n"/>
+      <c r="I212" s="18" t="n"/>
+      <c r="J212" s="18" t="n"/>
+      <c r="K212" s="18" t="n"/>
+      <c r="L212" s="18" t="n"/>
+      <c r="M212" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — arXiv HTML (2312.12913) blocked; no public metrics table. Datasets: MVTec AD, VisA, DAGM. IEEE TCSVT Nov 2024 (DOI: 10.1109/TCSVT.2024.3420775). 基於重構</t>
+        </is>
+      </c>
+      <c r="N212" s="20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.12913</t>
+        </is>
+      </c>
+      <c r="O212" s="20" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="18" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B213" s="18" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>UniSTAD (Unified Triple-Tower Student-Teacher)</t>
+        </is>
+      </c>
+      <c r="D213" s="18" t="inlineStr">
+        <is>
+          <t>Huan Liu, Jian Sun</t>
+        </is>
+      </c>
+      <c r="E213" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F213" s="18" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G213" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H213" s="18" t="n"/>
+      <c r="I213" s="18" t="n"/>
+      <c r="J213" s="18" t="n"/>
+      <c r="K213" s="18" t="n"/>
+      <c r="L213" s="18" t="n"/>
+      <c r="M213" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — no arXiv preprint found; metrics inaccessible. IEEE TCSVT 2024 (DOI: 10.1109/TCSVT.2024.3507097). Triple-tower global+local students vs pre-trained teacher. 基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="N213" s="20" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10769545</t>
+        </is>
+      </c>
+      <c r="O213" s="20" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="18" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B214" s="18" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="inlineStr">
+        <is>
+          <t>UniSTAD (Unified Triple-Tower Student-Teacher)</t>
+        </is>
+      </c>
+      <c r="D214" s="18" t="inlineStr">
+        <is>
+          <t>Huan Liu, Jian Sun</t>
+        </is>
+      </c>
+      <c r="E214" s="18" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F214" s="18" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G214" s="18" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H214" s="18" t="n"/>
+      <c r="I214" s="18" t="n"/>
+      <c r="J214" s="18" t="n"/>
+      <c r="K214" s="18" t="n"/>
+      <c r="L214" s="18" t="n"/>
+      <c r="M214" s="19" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — no arXiv preprint found; metrics inaccessible. IEEE TCSVT 2024 (DOI: 10.1109/TCSVT.2024.3507097). Triple-tower global+local students vs pre-trained teacher. 基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="N214" s="20" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10769545</t>
+        </is>
+      </c>
+      <c r="O214" s="20" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15280,7 +15846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -22239,6 +22805,210 @@
       <c r="O96" t="inlineStr">
         <is>
           <t>https://github.com/caoyunkang/CDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I97" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>基於重構</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>POUTA (Produce Once, Utilize Twice for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Shuyuan Wang, Qi Li, Huiyuan Luo, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — arXiv HTML (2312.12913) blocked; no public metrics table. Datasets: MVTec AD, VisA, DAGM. IEEE TCSVT Nov 2024 (DOI: 10.1109/TCSVT.2024.3420775). 基於重構</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.12913</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>UniSTAD (Unified Triple-Tower Student-Teacher)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Huan Liu, Jian Sun</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — no arXiv preprint found; metrics inaccessible. IEEE TCSVT 2024 (DOI: 10.1109/TCSVT.2024.3507097). Triple-tower global+local students vs pre-trained teacher. 基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10769545</t>
         </is>
       </c>
     </row>
@@ -25128,7 +25898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29712,6 +30482,158 @@
       <c r="O65" t="inlineStr">
         <is>
           <t>https://github.com/cool-xuan/msflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I66" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>基於重構</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>POUTA (Produce Once, Utilize Twice for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Shuyuan Wang, Qi Li, Huiyuan Luo, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — arXiv HTML (2312.12913) blocked; no public metrics table. Datasets: MVTec AD, VisA, DAGM. IEEE TCSVT Nov 2024 (DOI: 10.1109/TCSVT.2024.3420775). 基於重構</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.12913</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UniSTAD (Unified Triple-Tower Student-Teacher)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Huan Liu, Jian Sun</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — no arXiv preprint found; metrics inaccessible. IEEE TCSVT 2024 (DOI: 10.1109/TCSVT.2024.3507097). Triple-tower global+local students vs pre-trained teacher. 基於師生蒸餾</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10769545</t>
         </is>
       </c>
     </row>
@@ -29813,7 +30735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -31094,6 +32016,67 @@
       <c r="O20" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>基於資料擴增</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>PBAS (Progressive Boundary Guided Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Han Gao, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>✅ IEEE TCSVT 2024 verified — I-AUROC &amp; P-AUROC from official GitHub README (cqylunlun/PBAS); Progressive Boundary Anomaly Synthesis + boundary-learning discriminator. 基於資料擴增</t>
+        </is>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17458</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/PBAS</t>
         </is>
       </c>
     </row>
@@ -31126,7 +32109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32642,6 +33625,63 @@
       <c r="O23" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
         </is>
       </c>
     </row>
@@ -32680,7 +33720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34074,6 +35114,63 @@
       <c r="O21" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>基於記憶庫</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>CPR (Cascade Patch Retrieval / Target Before Shooting)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Hanxi Li, Jianfei Hu, Bo Li, Hao Chen, Yongbin Zheng, Chunhua Shen</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2024</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>⏳ Pending visual table read — GitHub README (flyinghu123/CPR) has no metrics; arXiv HTML blocked. Abstract states "up to 99.8% Image-AUC" on MVTec AD; 113 FPS (standard). IEEE TIP 2024 (DOI: 10.1109/TIP.2024.3448263). 基於記憶庫/Nearest Neighbor</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.06748</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>https://github.com/flyinghu123/CPR</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O214"/>
+  <dimension ref="A1:O220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -15636,6 +15636,398 @@
         </is>
       </c>
       <c r="O214" s="20" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="I215" t="n">
+        <v>98</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): MVTec AD I-AUROC=98.3 / P-AUROC=98.0 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="I216" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): VisA I-AUROC=93.5 / P-AUROC=97.7 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>95</v>
+      </c>
+      <c r="I217" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): MPDD I-AUROC=95.0 / P-AUROC=98.3 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>MuSc-V2 (Zero-Shot Multimodal Mutual Scoring)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Xurui Li, Feng Xue, Yu Zhou</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2026 / arXiv 2511.10047</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="I218" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="J218" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="K218" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>🟠 Zero-shot verified (MuSc-V2 GitHub README github.com/HUST-SLOW/MuSc-V2, zero-shot multimodal 2D+3D, no training): MVTec 3D-AD AUROC-cls=88.08 / AUROC-segm=99.03 / AP-segm=54.70 / PRO-segm=96.98 [零樣本多模態/互評分 — 與有監督方法不可直接比較]</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.10047</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>https://github.com/HUST-SLOW/MuSc-V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>基於視覺語言 (VLM / CLIP)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>FocusCLIP (Bidirectional Self-Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 (TCSVT.2024.3524784)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (DOI 10.1109/TCSVT.2024.3524784); few-shot + zero-shot CLIP-based AD on MVTec AD / VisA; no arXiv preprint found, paywalled — metric not yet verified from accessible table</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10819451/</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>REASON (Reverse Distillation with Latent Anomaly Suppression)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2025 (TCSVT.2025.10969994)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2025 (DOI 10.1109/TCSVT.2025.10969994); reverse distillation with latent anomaly suppression; no arXiv preprint found, paywalled — dataset and metric not yet verified from accessible table</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10969994/</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15846,7 +16238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -23009,6 +23401,183 @@
       <c r="N100" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/document/10769545</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="I101" t="n">
+        <v>98</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): MVTec AD I-AUROC=98.3 / P-AUROC=98.0 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>基於視覺語言 (VLM / CLIP)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FocusCLIP (Bidirectional Self-Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 (TCSVT.2024.3524784)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (DOI 10.1109/TCSVT.2024.3524784); few-shot + zero-shot CLIP-based AD; no arXiv preprint — metric not yet verified from accessible table</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10819451/</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>REASON (Reverse Distillation with Latent Anomaly Suppression)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2025 (TCSVT.2025.10969994)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2025 (DOI 10.1109/TCSVT.2025.10969994); reverse distillation with latent anomaly suppression; no arXiv preprint — metric not yet verified from accessible table</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10969994/</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -25898,7 +26467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -30634,6 +31203,131 @@
       <c r="N68" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/document/10769545</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): VisA I-AUROC=93.5 / P-AUROC=97.7 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>基於視覺語言 (VLM / CLIP)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FocusCLIP (Bidirectional Self-Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 (TCSVT.2024.3524784)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (DOI 10.1109/TCSVT.2024.3524784); few-shot + zero-shot CLIP-based AD; no arXiv preprint — metric not yet verified from accessible table</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10819451/</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -30735,7 +31429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32077,6 +32771,79 @@
       <c r="O21" s="14" t="inlineStr">
         <is>
           <t>https://github.com/cqylunlun/PBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>基於資料擴增 (Data Augmentation)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CRAS (Center-aware Residual Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Qiyu Chen, Huiyuan Luo, Haiming Yao, Wei Luo, Zhen Qu, Chengkan Lv, Zhengtao Zhang</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IEEE TII 2025 / arXiv 2505.17551</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>95</v>
+      </c>
+      <c r="I22" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>✅ verified (CRAS GitHub README github.com/cqylunlun/CRAS, multi-class setting): MPDD I-AUROC=95.0 / P-AUROC=98.3 [基於異常合成/中心感知殘差]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.17551</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://github.com/cqylunlun/CRAS</t>
         </is>
       </c>
     </row>
@@ -33720,7 +34487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -35171,6 +35938,75 @@
       <c r="O22" s="14" t="inlineStr">
         <is>
           <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MVTec 3D</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MuSc-V2 (Zero-Shot Multimodal Mutual Scoring)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Xurui Li, Feng Xue, Yu Zhou</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2026 / arXiv 2511.10047</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="I23" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="J23" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🟠 Zero-shot verified (MuSc-V2 GitHub README github.com/HUST-SLOW/MuSc-V2, zero-shot multimodal 2D+3D, no training): MVTec 3D-AD AUROC-cls=88.08 / AUROC-segm=99.03 / AP-segm=54.70 / PRO-segm=96.98 [零樣本多模態/互評分 — 與有監督方法不可直接比較]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.10047</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://github.com/HUST-SLOW/MuSc-V2</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O220"/>
+  <dimension ref="A1:O224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16026,6 +16026,214 @@
       <c r="O220" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AAND (Advancing Pre-trained Teacher)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Canhui Tang, Sanping Zhou, Yizhe Li, Yonghao Dong, Le Wang</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>IEEE TIP / arXiv 2405.02068</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP confirmed (arxiv 2405.02068, github.com/Hui-design/AAND); arXiv HTML blocked, GitHub README has no results table [基於師生蒸餾/逆蒸餾+殘差異常放大]</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.02068</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>https://github.com/Hui-design/AAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA / MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>基於記憶庫 (Memory Bank)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SFRAD (Sparse Feature Representation AD)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Fanghui Zhang, Haiyue Zhu, Yigang Cen, Shichao Kan, Linna Zhang, Prahlad Vadakkepat, Tong Heng Lee</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (10.1109/TNNLS.2024.3420818)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TNNLS 2025 confirmed (DOI 10.1109/TNNLS.2024.3420818, PubMed 39074012); no arXiv preprint found; also evaluates on KSDD/KSDD2 [基於記憶庫/稀疏表徵+OMP/低樣本]</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10612766/</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA / MVTec LOCO / MPDD / BTAD</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>MVTec LOCO / MVTec AD</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>基於邏輯異常 (Logical Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GLCF (Global-Local Correspondence Framework)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>H. Yao, W. Yu, W. Luo, Z. Qiang, D. Luo, X. Zhang</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 / arXiv 2303.05768</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (vol.34 no.5 pp.3589-3605, DOI 10.1109/TCSVT.2023.3327448) confirmed; arXiv HTML blocked, GitHub (github.com/hmyao22/GLCF) has no results table [基於邏輯異常/全局-局部對應/Transformer語義瓶頸]</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.05768</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>https://github.com/hmyao22/GLCF</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -23578,6 +23786,214 @@
       <c r="O103" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AAND (Advancing Pre-trained Teacher)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Canhui Tang, Sanping Zhou, Yizhe Li, Yonghao Dong, Le Wang</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>IEEE TIP / arXiv 2405.02068</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP confirmed (arxiv 2405.02068, github.com/Hui-design/AAND); arXiv HTML blocked, GitHub README has no results table [基於師生蒸餾/逆蒸餾+殘差異常放大]</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.02068</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>https://github.com/Hui-design/AAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>基於記憶庫 (Memory Bank)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SFRAD (Sparse Feature Representation AD)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fanghui Zhang, Haiyue Zhu, Yigang Cen, Shichao Kan, Linna Zhang, Prahlad Vadakkepat, Tong Heng Lee</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (10.1109/TNNLS.2024.3420818)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TNNLS 2025 confirmed (DOI 10.1109/TNNLS.2024.3420818, PubMed 39074012); no arXiv preprint found; also evaluates on KSDD/KSDD2 [基於記憶庫/稀疏表徵+OMP/低樣本]</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10612766/</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>基於邏輯異常 (Logical Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>GLCF (Global-Local Correspondence Framework)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>H. Yao, W. Yu, W. Luo, Z. Qiang, D. Luo, X. Zhang</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 / arXiv 2303.05768</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (vol.34 no.5 pp.3589-3605, DOI 10.1109/TCSVT.2023.3327448) confirmed; arXiv HTML blocked, GitHub (github.com/hmyao22/GLCF) has no results table [基於邏輯異常/全局-局部對應/Transformer語義瓶頸]</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.05768</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>https://github.com/hmyao22/GLCF</t>
         </is>
       </c>
     </row>
@@ -23727,7 +24143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25082,6 +25498,162 @@
       <c r="O20" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>基於記憶庫 (Memory Bank)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SFRAD (Sparse Feature Representation AD)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fanghui Zhang, Haiyue Zhu, Yigang Cen, Shichao Kan, Linna Zhang, Prahlad Vadakkepat, Tong Heng Lee</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (10.1109/TNNLS.2024.3420818)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TNNLS 2025 confirmed (DOI 10.1109/TNNLS.2024.3420818, PubMed 39074012); no arXiv preprint found; also evaluates on KSDD/KSDD2 [基於記憶庫/稀疏表徵+OMP/低樣本]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10612766/</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>基於邏輯異常 (Logical Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GLCF (Global-Local Correspondence Framework)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>H. Yao, W. Yu, W. Luo, Z. Qiang, D. Luo, X. Zhang</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2024 / arXiv 2303.05768</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT 2024 (vol.34 no.5 pp.3589-3605, DOI 10.1109/TCSVT.2023.3327448) confirmed; arXiv HTML blocked, GitHub (github.com/hmyao22/GLCF) has no results table [基於邏輯異常/全局-局部對應/Transformer語義瓶頸]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.05768</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://github.com/hmyao22/GLCF</t>
         </is>
       </c>
     </row>
@@ -26467,7 +27039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -31326,6 +31898,162 @@
         </is>
       </c>
       <c r="O70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AAND (Advancing Pre-trained Teacher)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Canhui Tang, Sanping Zhou, Yizhe Li, Yonghao Dong, Le Wang</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>IEEE TIP / arXiv 2405.02068</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP confirmed (arxiv 2405.02068, github.com/Hui-design/AAND); arXiv HTML blocked, GitHub README has no results table [基於師生蒸餾/逆蒸餾+殘差異常放大]</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.02068</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://github.com/Hui-design/AAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>基於記憶庫 (Memory Bank)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SFRAD (Sparse Feature Representation AD)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fanghui Zhang, Haiyue Zhu, Yigang Cen, Shichao Kan, Linna Zhang, Prahlad Vadakkepat, Tong Heng Lee</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (10.1109/TNNLS.2024.3420818)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TNNLS 2025 confirmed (DOI 10.1109/TNNLS.2024.3420818, PubMed 39074012); no arXiv preprint found; also evaluates on KSDD/KSDD2 [基於記憶庫/稀疏表徵+OMP/低樣本]</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10612766/</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -31429,7 +32157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32844,6 +33572,58 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>https://github.com/cqylunlun/CRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -32876,7 +33656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -34449,6 +35229,58 @@
       <c r="O24" s="23" t="inlineStr">
         <is>
           <t>https://github.com/flyinghu123/CPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DFCAD (Deep Feature Clustering for Multi-class AD)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2025 (ScienceDirect S0950705125001819)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2025 confirmed (ScienceDirect S0950705125001819); paywalled, no arXiv found [基於表徵/深度特徵聚類/CAC+CIM+LFR/多類別]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705125001819</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16446,7 +16446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -23994,6 +23994,61 @@
       <c r="O107" t="inlineStr">
         <is>
           <t>https://github.com/hmyao22/GLCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>基於基礎模型</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>VarAD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Yunkang Cao et al.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>IEEE TII</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>✅ Standard verified</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>✅ Standard verified — arXiv 2412.17263 Table III; MVTec AD I-AUROC 97.7%, VisA I-AUROC 98.5%; IEEE TII Vol.21 No.4 2025. P-AUROC not reported. [基於基礎模型/視覺自回歸]</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32056,6 +32111,61 @@
       <c r="O73" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>基於基礎模型</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VarAD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Yunkang Cao et al.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>IEEE TII</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>✅ Standard verified</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>✅ Standard verified — arXiv 2412.17263 Table III; MVTec AD I-AUROC 97.7%, VisA I-AUROC 98.5%; IEEE TII Vol.21 No.4 2025. P-AUROC not reported. [基於基礎模型/視覺自回歸]</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O224"/>
+  <dimension ref="A1:O229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16234,6 +16234,266 @@
       <c r="O224" t="inlineStr">
         <is>
           <t>https://github.com/hmyao22/GLCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>基於正規化流 (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>MSAttnFlow (Normalizing Flow + Multi-Scale Attention)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Zhengnan Hu, Xiangrui Zeng, Yiqun Li, Zhouping Yin, Erli Meng, Ziyu Wei, Leyan Zhu, Zitian Wang</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713); no arXiv preprint found, journal paywalled; MVTec AD I-AUROC 99.7%/P-AUROC 98.9% and VisA I-AUROC 98.1%/P-AUROC 99.1% cited in search snippets but NOT from authoritative arXiv HTML or GitHub table — pending visual table read [基於正規化流/多尺度注意力/自回歸雙向注意力]</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031320324009713</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>MVTec AD / AeBAD-S</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>基於重建 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>MSFR (Multi-Scale Feature Reconstruction)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Ehtesham Iqbal, Samee Ullah Khan, Sajid Javed, Brian Moyo, Yahya Zweiri, Yusra Abdulrahman</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2024 (ScienceDirect S095070512401284X)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems Oct 2024 (ScienceDirect S095070512401284X); GitHub available (github.com/Ehteshamciitwah/MSFR) but README has no results table; journal paywalled, no arXiv found — pending visual table read [基於重建/多尺度特徵重建/PVT骨幹/工業領域偏移]</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S095070512401284X</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>https://github.com/Ehteshamciitwah/MSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>基於視覺語言模型 (VLM/CLIP) / 少樣本 (Few-Shot)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>FocusPatch AD (Few-Shot VLM Multi-Class AD)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore DOI 11319339 for full author list)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>IEEE TIP Vol.35 pp.112-123 2025 (IEEE DOI 11319339)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP Vol.35 pp.112-123 2025 (IEEE DOI 11319339); few-shot multi-class AD using keyword patch prompts + VLM — NON-STANDARD PROTOCOL (few-shot); no arXiv preprint found; no accessible metrics table — pending visual table read [基於VLM/少樣本/多類別/關鍵詞補丁提示]</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11319339/</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA / BHAAD</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Agm-Net (Attention-guided Masking Denoising)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0893608025012286 for author list)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Neural Networks 2025 (ScienceDirect S0893608025012286)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Neural Networks 2025 (ScienceDirect S0893608025012286); no arXiv preprint found, no GitHub found; MVTec AD P-AUROC 98.2%/PRO 94.6%, VisA P-AUROC 99.2%/PRO 95.1% cited in search snippets but NOT from authoritative source; I-AUROC unknown — pending visual table read [基於師生蒸餾/注意力引導遮蔽去噪/U型去噪架構/坐標注意力]</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0893608025012286</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>基於擴散模型 (Diffusion-based)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TDAD (Two-stage Diffusion Self-supervised AD)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0166361524001209 for author list)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Computers in Industry Vol.164 Art.104192 2025 (ScienceDirect S0166361524001209)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Computers in Industry Vol.164 Art.104192 Jan 2025 (ScienceDirect S0166361524001209); no arXiv preprint found, journal paywalled; 96.8% AUROC / 52.6% AP for MVTec AD localization and 97.2% AUROC / 99.0% AP for VisA detection cited in search snippets — level (image/pixel) ambiguous; NOT from authoritative table — pending visual table read [基於擴散模型/兩階段自監督/降噪去異常]</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0166361524001209</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24049,6 +24309,266 @@
       <c r="O108" t="inlineStr">
         <is>
           <t>https://github.com/caoyunkang/VarAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>基於正規化流 (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MSAttnFlow (Normalizing Flow + Multi-Scale Attention)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Zhengnan Hu, Xiangrui Zeng, Yiqun Li, Zhouping Yin, Erli Meng, Ziyu Wei, Leyan Zhu, Zitian Wang</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713); no arXiv preprint found, journal paywalled; MVTec AD I-AUROC 99.7%/P-AUROC 98.9% and VisA I-AUROC 98.1%/P-AUROC 99.1% cited in search snippets but NOT from authoritative arXiv HTML or GitHub table — pending visual table read [基於正規化流/多尺度注意力/自回歸雙向注意力]</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031320324009713</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>基於重建 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MSFR (Multi-Scale Feature Reconstruction)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Ehtesham Iqbal, Samee Ullah Khan, Sajid Javed, Brian Moyo, Yahya Zweiri, Yusra Abdulrahman</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2024 (ScienceDirect S095070512401284X)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems Oct 2024 (ScienceDirect S095070512401284X); GitHub available (github.com/Ehteshamciitwah/MSFR) but README has no results table; journal paywalled, no arXiv found — pending visual table read [基於重建/多尺度特徵重建/PVT骨幹/工業領域偏移]</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S095070512401284X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>https://github.com/Ehteshamciitwah/MSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>基於視覺語言模型 (VLM/CLIP) / 少樣本 (Few-Shot)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>FocusPatch AD (Few-Shot VLM Multi-Class AD)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore DOI 11319339 for full author list)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>IEEE TIP Vol.35 pp.112-123 2025 (IEEE DOI 11319339)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP Vol.35 pp.112-123 2025 (IEEE DOI 11319339); few-shot multi-class AD using keyword patch prompts + VLM — NON-STANDARD PROTOCOL (few-shot); no arXiv preprint found; no accessible metrics table — pending visual table read [基於VLM/少樣本/多類別/關鍵詞補丁提示]</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11319339/</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Agm-Net (Attention-guided Masking Denoising)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0893608025012286 for author list)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Neural Networks 2025 (ScienceDirect S0893608025012286)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Neural Networks 2025 (ScienceDirect S0893608025012286); no arXiv preprint found, no GitHub found; MVTec AD P-AUROC 98.2%/PRO 94.6%, VisA P-AUROC 99.2%/PRO 95.1% cited in search snippets but NOT from authoritative source; I-AUROC unknown — pending visual table read [基於師生蒸餾/注意力引導遮蔽去噪/U型去噪架構/坐標注意力]</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0893608025012286</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>基於擴散模型 (Diffusion-based)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TDAD (Two-stage Diffusion Self-supervised AD)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0166361524001209 for author list)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Computers in Industry Vol.164 Art.104192 2025 (ScienceDirect S0166361524001209)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Computers in Industry Vol.164 Art.104192 Jan 2025 (ScienceDirect S0166361524001209); no arXiv preprint found, journal paywalled; 96.8% AUROC / 52.6% AP for MVTec AD localization and 97.2% AUROC / 99.0% AP for VisA detection cited in search snippets — level (image/pixel) ambiguous; NOT from authoritative table — pending visual table read [基於擴散模型/兩階段自監督/降噪去異常]</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0166361524001209</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32166,6 +32686,162 @@
       <c r="O74" t="inlineStr">
         <is>
           <t>https://github.com/caoyunkang/VarAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>基於正規化流 (Normalizing Flow)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MSAttnFlow (Normalizing Flow + Multi-Scale Attention)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Zhengnan Hu, Xiangrui Zeng, Yiqun Li, Zhouping Yin, Erli Meng, Ziyu Wei, Leyan Zhu, Zitian Wang</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Pattern Recognition Vol.161 Art.111220 2025 (ScienceDirect S0031320324009713); no arXiv preprint found, journal paywalled; MVTec AD I-AUROC 99.7%/P-AUROC 98.9% and VisA I-AUROC 98.1%/P-AUROC 99.1% cited in search snippets but NOT from authoritative arXiv HTML or GitHub table — pending visual table read [基於正規化流/多尺度注意力/自回歸雙向注意力]</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031320324009713</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>基於師生蒸餾 (Knowledge Distillation)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Agm-Net (Attention-guided Masking Denoising)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0893608025012286 for author list)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Neural Networks 2025 (ScienceDirect S0893608025012286)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Neural Networks 2025 (ScienceDirect S0893608025012286); no arXiv preprint found, no GitHub found; MVTec AD P-AUROC 98.2%/PRO 94.6%, VisA P-AUROC 99.2%/PRO 95.1% cited in search snippets but NOT from authoritative source; I-AUROC unknown — pending visual table read [基於師生蒸餾/注意力引導遮蔽去噪/U型去噪架構/坐標注意力]</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0893608025012286</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>基於擴散模型 (Diffusion-based)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TDAD (Two-stage Diffusion Self-supervised AD)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S0166361524001209 for author list)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Computers in Industry Vol.164 Art.104192 2025 (ScienceDirect S0166361524001209)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Computers in Industry Vol.164 Art.104192 Jan 2025 (ScienceDirect S0166361524001209); no arXiv preprint found, journal paywalled; 96.8% AUROC / 52.6% AP for MVTec AD localization and 97.2% AUROC / 99.0% AP for VisA detection cited in search snippets — level (image/pixel) ambiguous; NOT from authoritative table — pending visual table read [基於擴散模型/兩階段自監督/降噪去異常]</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0166361524001209</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16706,7 +16706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24569,6 +24569,110 @@
       <c r="O113" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>REB (Reducing Biases in Representation)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Shuai Lyu, et al.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989); arXiv 2308.12577; arXiv HTML 403 + GitHub README has no metrics text; abstract cites I-AUROC 99.5% but not from authoritative table [基於表徵/記憶庫/LDKNN]</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705124001989</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>https://github.com/ShuaiLYU/REB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 弱監督 (Weakly-Supervised) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>WeakREST / Semi-supervised Residual Transformer (Weakly-Supervised)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11372619 for full author list)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Xplore 11372619)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP 2026 (IEEE Xplore 11372619); arXiv 2306.03492v3; arXiv HTML 403; NON-STANDARD PROTOCOL: weakly-supervised/semi-supervised (bounding box + image-level annotations) — NOT comparable to standard unsupervised AD; abstract cites AP 83.0%/P-AUROC 98.1%/PRO 93.6% but not from authoritative table [基於Transformer/弱監督/半監督/預算標注]</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11372619/</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.03492</t>
         </is>
       </c>
     </row>
@@ -24718,7 +24822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -26229,6 +26333,58 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>https://github.com/hmyao22/GLCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>REB (Reducing Biases in Representation)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shuai Lyu, et al.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989); arXiv 2308.12577; arXiv HTML 403 + GitHub README has no metrics text; abstract cites I-AUROC 88.8% but not from authoritative table [基於表徵/記憶庫/LDKNN]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705124001989</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://github.com/ShuaiLYU/REB</t>
         </is>
       </c>
     </row>
@@ -34442,7 +34598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36067,6 +36223,58 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>REB (Reducing Biases in Representation)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Shuai Lyu, et al.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Knowledge-Based Systems 2024 (ScienceDirect S0950705124001989); arXiv 2308.12577; arXiv HTML 403 + GitHub README has no metrics text; abstract cites I-AUROC 96.0% but not from authoritative table [基於表徵/記憶庫/LDKNN]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0950705124001989</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://github.com/ShuaiLYU/REB</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16494,6 +16494,162 @@
       <c r="O229" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>基於重建 (Reconstruction-based) / 不確定性感知 (Uncertainty-aware)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>URA-Net (Uncertainty-integrated Restoration Attention Network)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11137387 for full author list)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT Feb 2026 (IEEE Xplore 11137387)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT Feb 2026 (IEEE Xplore 11137387); arXiv 2603.22840; arXiv HTML 403 blocked; no GitHub README metrics found; MVTec AD + BTAD; uncertainty-integrated anomaly perception (Bayesian NN) + restoration attention — standard unsupervised protocol; awaiting authoritative metric table [基於重建/不確定性感知/貝葉斯網絡/修復注意力]</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11137387/</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22840</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 弱監督 (Weakly-Supervised) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>WeakREST / Semi-supervised Residual Transformer (Weakly-Supervised)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11372619 for full author list)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Xplore 11372619)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TIP 2026 (IEEE Xplore 11372619); arXiv 2306.03492v3; arXiv HTML 403 blocked; NON-STANDARD PROTOCOL: weakly-supervised/semi-supervised (bounding box + image-level annotations) — NOT comparable to standard unsupervised AD; abstract cites AP 83.0%/P-AUROC 98.1%/PRO 93.6% but not from authoritative table [基於Transformer/弱監督/半監督/預算標注]</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11372619/</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.03492</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 多尺度特徵融合 (Multi-scale Feature Aggregation)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>IGAF (Information-Guided Anomaly Fusion)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S1566253525004294 for author list)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Information Fusion 2025 (ScienceDirect S1566253525004294)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Information Fusion 2025 (ScienceDirect S1566253525004294); no arXiv preprint; journal paywalled; GitHub https://github.com/IHPCMember/IGAF has no metrics table; P-AUROC snippets: MVTec AD 99.13% (WR50)/97.51% (R18), VisA 98.75%, BTAD 92.40% — NOT from authoritative source; I-AUROC unknown — awaiting accessible metric table [基於表徵/信息引導異常融合/多尺度特徵]</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S1566253525004294</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>https://github.com/IHPCMember/IGAF</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24673,6 +24829,110 @@
       <c r="O115" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2306.03492</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>基於重建 (Reconstruction-based) / 不確定性感知 (Uncertainty-aware)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>URA-Net (Uncertainty-integrated Restoration Attention Network)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11137387 for full author list)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT Feb 2026 (IEEE Xplore 11137387)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT Feb 2026 (IEEE Xplore 11137387); arXiv 2603.22840; arXiv HTML 403 blocked; no GitHub README metrics found; MVTec AD + BTAD; uncertainty-integrated anomaly perception (Bayesian NN) + restoration attention — standard unsupervised protocol; awaiting authoritative metric table [基於重建/不確定性感知/貝葉斯網絡/修復注意力]</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11137387/</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22840</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 多尺度特徵融合 (Multi-scale Feature Aggregation)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IGAF (Information-Guided Anomaly Fusion)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S1566253525004294 for author list)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Information Fusion 2025 (ScienceDirect S1566253525004294)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Information Fusion 2025 (ScienceDirect S1566253525004294); no arXiv preprint; journal paywalled; GitHub https://github.com/IHPCMember/IGAF has no metrics table; P-AUROC snippets: MVTec AD 99.13% (WR50)/97.51% (R18), VisA 98.75%, BTAD 92.40% — NOT from authoritative source; I-AUROC unknown — awaiting accessible metric table [基於表徵/信息引導異常融合/多尺度特徵]</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S1566253525004294</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>https://github.com/IHPCMember/IGAF</t>
         </is>
       </c>
     </row>
@@ -27770,7 +28030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32998,6 +33258,58 @@
       <c r="O77" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 多尺度特徵融合 (Multi-scale Feature Aggregation)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IGAF (Information-Guided Anomaly Fusion)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S1566253525004294 for author list)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Information Fusion 2025 (ScienceDirect S1566253525004294)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Information Fusion 2025 (ScienceDirect S1566253525004294); no arXiv preprint; journal paywalled; GitHub https://github.com/IHPCMember/IGAF has no metrics table; P-AUROC snippet: VisA 98.75% — NOT from authoritative source; I-AUROC unknown — awaiting accessible metric table [基於表徵/信息引導異常融合/多尺度特徵]</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S1566253525004294</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://github.com/IHPCMember/IGAF</t>
         </is>
       </c>
     </row>
@@ -34598,7 +34910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36275,6 +36587,110 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>https://github.com/ShuaiLYU/REB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>基於重建 (Reconstruction-based) / 不確定性感知 (Uncertainty-aware)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>URA-Net (Uncertainty-integrated Restoration Attention Network)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11137387 for full author list)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT Feb 2026 (IEEE Xplore 11137387)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TCSVT Feb 2026 (IEEE Xplore 11137387); arXiv 2603.22840; arXiv HTML 403 blocked; no GitHub README metrics found; BTAD result; awaiting authoritative metric table [基於重建/不確定性感知/貝葉斯網絡/修復注意力]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11137387/</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22840</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 多尺度特徵融合 (Multi-scale Feature Aggregation)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IGAF (Information-Guided Anomaly Fusion)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(see ScienceDirect S1566253525004294 for author list)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Information Fusion 2025 (ScienceDirect S1566253525004294)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Information Fusion 2025 (ScienceDirect S1566253525004294); no arXiv preprint; journal paywalled; GitHub https://github.com/IHPCMember/IGAF has no metrics table; P-AUROC snippet: BTAD 92.40% — NOT from authoritative source; I-AUROC unknown — awaiting accessible metric table [基於表徵/信息引導異常融合/多尺度特徵]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S1566253525004294</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://github.com/IHPCMember/IGAF</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -16862,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24933,6 +24933,58 @@
       <c r="O117" t="inlineStr">
         <is>
           <t>https://github.com/IHPCMember/IGAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>基於VLM/MLLM (Vision-Language / Multimodal LLM) / 多專家框架 (Multi-Expert Framework)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MoXpert (Multi-Expert Framework for MLLM AD)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Zhiling Chen, Farhad Imani</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Pattern Recognition 2025 (ScienceDirect S0031320325014153)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Pattern Recognition 2025 (ScienceDirect S0031320325014153); GitHub github.com/Ed1sonChen/MoXpert has no metrics table; paper reports "+7.4% improvement on MVTec-AD" (relative vs baseline MLLM, not absolute I-AUROC); evaluation on MVTec-AD + VisA; MLLM-based multi-expert framework (4 expert modules: knowledge generator, multimodal retriever, decision generator, dynamic router) with frozen backbone — may use non-standard metric (accuracy/F1 rather than I-AUROC); awaiting accessible metric table [基於VLM/MLLM/多專家框架/知識增強]</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031320325014153</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>https://github.com/Ed1sonChen/MoXpert</t>
         </is>
       </c>
     </row>
@@ -28030,7 +28082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -33310,6 +33362,58 @@
       <c r="O78" t="inlineStr">
         <is>
           <t>https://github.com/IHPCMember/IGAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>基於VLM/MLLM (Vision-Language / Multimodal LLM) / 多專家框架 (Multi-Expert Framework)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MoXpert (Multi-Expert Framework for MLLM AD)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Zhiling Chen, Farhad Imani</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pattern Recognition 2025 (ScienceDirect S0031320325014153)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>⏳ Pending — Pattern Recognition 2025 (ScienceDirect S0031320325014153); GitHub github.com/Ed1sonChen/MoXpert has no metrics table; paper reports "+7.4% improvement (top accuracy on VisA)" — relative, not absolute I-AUROC; evaluation on MVTec-AD + VisA; MLLM-based multi-expert framework with frozen backbone — awaiting accessible metric table [基於VLM/MLLM/多專家框架/知識增強]</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031320325014153</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://github.com/Ed1sonChen/MoXpert</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O232"/>
+  <dimension ref="A1:O234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16650,6 +16650,105 @@
       <c r="O232" t="inlineStr">
         <is>
           <t>https://github.com/IHPCMember/IGAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA / BTAD</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自迴歸建模 (Autoregressive + Mamba)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>VarAD (Visual Autoregressive Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Yunkang Cao, Zongwei Shen, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>IEEE TII Vol.21 No.4 pp.3246-3255 2025 (arXiv 2412.17263)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2412.17263 Table II (search-extracted; direct HTML access blocked) reports pixel-level AUROC/MAX-F1/AP — MVTec AD: 97.7/63.8/63.0; VisA: 98.5/47.5/40.7; BTAD: 97.8/63.6/64.5. High-resolution AD (1024px) protocol. Recommend direct paper verification before ranking. [基於自迴歸/Mamba特徵建模/高解析度AD]</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>MVTec AD (Continual)</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>基於持續學習 (Continual AD) / 參數解耦 (Parameter Decoupling) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TaskAD (Task-Aware Parameter Decoupling for Continual AD)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11271009 for full author list)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>IEEE TII 2026 (IEEE Xplore 11271009)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TII 2026 (Xplore 11271009). Continual / incremental AD framework (instance-aware prompt tuning + gradient-aware parameter decoupling on ViT encoder-decoder). Datasets and metrics not accessible (IEEE paywalled, no arXiv). NON-STANDARD PROTOCOL — do NOT rank in standard unsupervised AD group. [基於持續學習/增量學習 Continual AD]</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11271009</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -24985,6 +25084,105 @@
       <c r="O118" t="inlineStr">
         <is>
           <t>https://github.com/Ed1sonChen/MoXpert</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自迴歸建模 (Autoregressive + Mamba)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VarAD (Visual Autoregressive Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Yunkang Cao, Zongwei Shen, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>IEEE TII Vol.21 No.4 pp.3246-3255 2025 (arXiv 2412.17263)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2412.17263 Table II (search-extracted; direct HTML access blocked) reports pixel-level AUROC/MAX-F1/AP — MVTec AD: 97.7/63.8/63.0; VisA: 98.5/47.5/40.7; BTAD: 97.8/63.6/64.5. High-resolution AD (1024px) protocol. Recommend direct paper verification before ranking. [基於自迴歸/Mamba特徵建模/高解析度AD]</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>基於持續學習 (Continual AD) / 參數解耦 (Parameter Decoupling) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TaskAD (Task-Aware Parameter Decoupling for Continual AD)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>(see IEEE Xplore 11271009 for full author list)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>IEEE TII 2026 (IEEE Xplore 11271009)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TII 2026 (Xplore 11271009). Continual / incremental AD framework (instance-aware prompt tuning + gradient-aware parameter decoupling on ViT encoder-decoder). Datasets and metrics not accessible (IEEE paywalled, no arXiv). NON-STANDARD PROTOCOL — do NOT rank in standard unsupervised AD group. [基於持續學習/增量學習 Continual AD]</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11271009</t>
         </is>
       </c>
     </row>
@@ -28082,7 +28280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -33414,6 +33612,58 @@
       <c r="O79" t="inlineStr">
         <is>
           <t>https://github.com/Ed1sonChen/MoXpert</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自迴歸建模 (Autoregressive + Mamba)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VarAD (Visual Autoregressive Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Yunkang Cao, Zongwei Shen, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>IEEE TII Vol.21 No.4 pp.3246-3255 2025 (arXiv 2412.17263)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2412.17263 Table II (search-extracted; direct HTML access blocked) reports pixel-level AUROC/MAX-F1/AP — VisA: 98.5/47.5/40.7; BTAD: 97.8/63.6/64.5. High-resolution AD (1024px) protocol. Recommend direct paper verification before ranking. [基於自迴歸/Mamba特徵建模/高解析度AD]</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
         </is>
       </c>
     </row>
@@ -35014,7 +35264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36795,6 +37045,58 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>https://github.com/IHPCMember/IGAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BTAD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自迴歸建模 (Autoregressive + Mamba)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VarAD (Visual Autoregressive Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Yunkang Cao, Zongwei Shen, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IEEE TII Vol.21 No.4 pp.3246-3255 2025 (arXiv 2412.17263)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2412.17263 Table II (search-extracted; direct HTML access blocked) reports pixel-level AUROC/MAX-F1/AP — MVTec AD: 97.7/63.8/63.0; VisA: 98.5/47.5/40.7; BTAD: 97.8/63.6/64.5. High-resolution AD (1024px) protocol. Recommend direct paper verification before ranking. [基於自迴歸/Mamba特徵建模/高解析度AD]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.17263</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://github.com/caoyunkang/VarAD</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:O237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16749,6 +16749,157 @@
       <c r="N234" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/document/11271009</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 先驗語意提示 (Prior Normality Prompting) — 多類別統一</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PNPT (Prior Normality Prompt Transformer)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Hao Yao, Yunkang Cao, Weijia Luo, Weichen Zhang, Wenkai Yu, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>IEEE TII 2024 (arXiv 2406.11507)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2406.11507 (access blocked); GitHub https://github.com/Karma1628/work-2 — code not released (placeholder: code to be released upon acceptance). Multi-class AD via prior normality prompt pool + hierarchical patch embedding + semantic conditional decoding. Evaluates on MVTec AD + diverse industrial benchmarks. [基於重構/先驗語意提示/多類別統一AD]</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.11507</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>https://github.com/Karma1628/work-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 自監督遮罩 Transformer (Self-supervised Masked Convolutional Transformer)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SSMCTB (Self-Supervised Masked Convolutional Transformer Block)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Neelu Madan, Nicolae-Catalin Ristea, Radu Tudor Ionescu, Kamal Nasrollahi, Fahad Shahbaz Khan, Thomas B. Moeslund, Mubarak Shah</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2024 Vol.46 No.1 pp.525-542 (arXiv 2209.12148)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2209.12148 (access blocked); IEEE TPAMI paywalled; GitHub https://github.com/ristea/ssmctb — README has no metrics table. Evaluates on MVTec AD, BRATS, Avenue, ShanghaiTech, Thermal Rare Event. Self-supervised masked convolutional transformer block for cross-domain anomaly detection. [基於重構/自監督遮罩Transformer/跨域AD]</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2209.12148</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>https://github.com/ristea/ssmctb</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>基於零樣本持續學習 (Zero-shot Continual AD) / 多模態 (Multimodal) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>COLA (Continual Learning for Zero-shot Multimodal Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Yunfeng Ma, Shuai Jiang, Jingyu Zhou, Yaonan Wang, Min Liu</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2026</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TCSVT 2026; no arXiv preprint found; no GitHub code found; paper paywalled. Evaluates on MVTec AD + VisA (search-extracted; not from authoritative table). NON-STANDARD PROTOCOL — zero-shot + continual learning + multimodal setting; do NOT rank in standard unsupervised AD group. [基於零樣本持續學習/多模態AD]</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/</t>
         </is>
       </c>
     </row>
@@ -16961,7 +17112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25183,6 +25334,157 @@
       <c r="N120" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/document/11271009</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 先驗語意提示 (Prior Normality Prompting) — 多類別統一</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PNPT (Prior Normality Prompt Transformer)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Hao Yao, Yunkang Cao, Weijia Luo, Weichen Zhang, Wenkai Yu, Weiming Shen</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>IEEE TII 2024 (arXiv 2406.11507)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2406.11507 (access blocked); GitHub https://github.com/Karma1628/work-2 — code not released (code to be released upon acceptance). Multi-class AD via prior normality prompt pool + hierarchical patch embedding + semantic conditional decoding. [基於重構/先驗語意提示/多類別統一AD]</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.11507</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>https://github.com/Karma1628/work-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 自監督遮罩 Transformer (Self-supervised Masked Convolutional Transformer)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SSMCTB (Self-Supervised Masked Convolutional Transformer Block)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Neelu Madan, Nicolae-Catalin Ristea, Radu Tudor Ionescu, Kamal Nasrollahi, Fahad Shahbaz Khan, Thomas B. Moeslund, Mubarak Shah</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2024 Vol.46 No.1 pp.525-542 (arXiv 2209.12148)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>⏳ Pending: arXiv 2209.12148 (access blocked); IEEE TPAMI paywalled; GitHub https://github.com/ristea/ssmctb — README has no metrics table. Evaluates on MVTec AD, BRATS, Avenue, ShanghaiTech, Thermal Rare Event. Cross-domain self-supervised masked convolutional transformer. [基於重構/自監督遮罩Transformer/跨域AD]</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2209.12148</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>https://github.com/ristea/ssmctb</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>基於零樣本持續學習 (Zero-shot Continual AD) / 多模態 (Multimodal) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>COLA (Continual Learning for Zero-shot Multimodal Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Yunfeng Ma, Shuai Jiang, Jingyu Zhou, Yaonan Wang, Min Liu</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TCSVT 2026; no arXiv preprint or GitHub found; paper paywalled. Evaluates on MVTec AD + VisA (search-extracted). NON-STANDARD PROTOCOL — zero-shot + continual learning + multimodal; do NOT rank in standard unsupervised AD group. [基於零樣本持續學習/多模態AD]</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/</t>
         </is>
       </c>
     </row>
@@ -28280,7 +28582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -33664,6 +33966,53 @@
       <c r="O80" t="inlineStr">
         <is>
           <t>https://github.com/caoyunkang/VarAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>基於零樣本持續學習 (Zero-shot Continual AD) / 多模態 (Multimodal) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>COLA (Continual Learning for Zero-shot Multimodal Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Yunfeng Ma, Shuai Jiang, Jingyu Zhou, Yaonan Wang, Min Liu</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TCSVT 2026; no arXiv preprint or GitHub found; paper paywalled. Evaluates on MVTec AD + VisA (search-extracted). NON-STANDARD PROTOCOL — zero-shot + continual learning + multimodal; do NOT rank in standard unsupervised AD group. [基於零樣本持續學習/多模態AD]</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O237"/>
+  <dimension ref="A1:O241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -16900,6 +16900,199 @@
       <c r="N237" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 常態引導擴散 (Normality-guided Diffusion)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>PADiff (Pixel-Wise Anomaly-Detection via Normality-Guided Diffusion)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Zuo Zuo et al. (see TNNLS 10.1109/tnnls.2025.3572438)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (DOI 10.1109/tnnls.2025.3572438)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TNNLS 2025 (DOI 10.1109/tnnls.2025.3572438; IEEE Xplore 11038825); TNNLS paywalled; no arXiv ID found; GitHub https://github.com/Jay-zzcoder/padiff — README empty (1 line, no metrics). Pixel-wise normality-guided diffusion with patch-substitution strategy. Datasets: MVTec AD, VisA, BTAD. [基於重構/常態引導擴散/像素級AD]</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11038825</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>https://github.com/Jay-zzcoder/padiff</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA / MVTec LOCO AD</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自監督 + 局部至全局圖卷積 (Self-supervised Local-to-Global Graph Conv)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SLSG (Self-supervised Local-to-Global Graph Convolution for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Minghui Yang, Jing Liu, Zhiwei Yang, Zhaoyang Wu</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.156 2024 (arXiv 2305.00398)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition Vol.156 2024 (PII S0031320324006137); arXiv 2305.00398 (access blocked); no GitHub code found; ScienceDirect paywalled. Datasets: MVTec AD, VisA, MVTec LOCO AD. Self-supervised learning + local-to-global graph convolution for feature embedding + one-class classification. [基於表徵/自監督圖卷積/局部至全局]</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2305.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>MVTec AD / VisA</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>基於重構 + 記憶庫 (Reconstruction / Memory Bank) / 記憶樹 (Memory-Tree)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>MFAD (Memory-Tree Driven Network for Multi-View Fusion Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Xu Liu, Chunlei Wu, Huan Zhang, Leiquan Wang</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.170 Article 112106 2025 (PII S0031320325007666)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition Vol.170 2025 (PII S0031320325007666); no arXiv ID found; no GitHub found; ScienceDirect paywalled. Datasets: MVTec AD, VisA. Memory-tree module for image→memory mapping to suppress anomalous info; multi-view feature encoder. [基於重構/記憶樹/多視角融合AD]</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0031320325007666</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MVTec AD / MPDD / BTAD</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>基於重構 + 記憶庫 (Reconstruction / Memory Bank) / 多尺度記憶融合 (Multi-Scale Memory Fusion)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>MMFNet (Multi-Scale Memory Fusion Network for Industrial Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Pengxiang Wang, Yuhua Qin, Xulin Zong, Chaoyue Wang, Hao Zhang</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pattern Recognition 2025 (PII S0031320325012440)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition 2025 (PII S0031320325012440); no arXiv ID found; no GitHub found; ScienceDirect paywalled. Agent-extracted metrics (not from authoritative table): MVTec AD I-AUROC 99.7%, P-AUROC 98.9%, 16.18 MB, 32.41 FPS — do NOT rank until verified from paper PDF/HTML. Datasets: MVTec AD, MPDD, BTAD. Simulated abnormal samples + multi-scale memory fusion. [基於重構/多尺度記憶融合/合成異常訓練]</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0031320325012440</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -25485,6 +25678,199 @@
       <c r="N123" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 常態引導擴散 (Normality-guided Diffusion)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PADiff (Pixel-Wise Anomaly-Detection via Normality-Guided Diffusion)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Zuo Zuo et al. (see TNNLS 10.1109/tnnls.2025.3572438)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>IEEE TNNLS 2025 (DOI 10.1109/tnnls.2025.3572438)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>⏳ Pending: IEEE TNNLS 2025 (DOI 10.1109/tnnls.2025.3572438; IEEE Xplore 11038825); TNNLS paywalled; no arXiv ID found; GitHub https://github.com/Jay-zzcoder/padiff — README empty (1 line, no metrics). Pixel-wise normality-guided diffusion with patch-substitution strategy. Datasets: MVTec AD, VisA, BTAD. [基於重構/常態引導擴散/像素級AD]</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11038825</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>https://github.com/Jay-zzcoder/padiff</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自監督 + 局部至全局圖卷積 (Self-supervised Local-to-Global Graph Conv)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SLSG (Self-supervised Local-to-Global Graph Convolution for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Minghui Yang, Jing Liu, Zhiwei Yang, Zhaoyang Wu</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.156 2024 (arXiv 2305.00398)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition Vol.156 2024 (PII S0031320324006137); arXiv 2305.00398 (access blocked); no GitHub code found; ScienceDirect paywalled. Datasets: MVTec AD, VisA, MVTec LOCO AD. Self-supervised learning + local-to-global graph convolution for feature embedding + one-class classification. [基於表徵/自監督圖卷積/局部至全局]</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2305.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>基於重構 + 記憶庫 (Reconstruction / Memory Bank) / 記憶樹 (Memory-Tree)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MFAD (Memory-Tree Driven Network for Multi-View Fusion Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Xu Liu, Chunlei Wu, Huan Zhang, Leiquan Wang</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.170 Article 112106 2025 (PII S0031320325007666)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition Vol.170 2025 (PII S0031320325007666); no arXiv ID found; no GitHub found; ScienceDirect paywalled. Datasets: MVTec AD, VisA. Memory-tree module for image→memory mapping to suppress anomalous info; multi-view feature encoder. [基於重構/記憶樹/多視角融合AD]</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0031320325007666</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>基於重構 + 記憶庫 (Reconstruction / Memory Bank) / 多尺度記憶融合 (Multi-Scale Memory Fusion)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MMFNet (Multi-Scale Memory Fusion Network for Industrial Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Pengxiang Wang, Yuhua Qin, Xulin Zong, Chaoyue Wang, Hao Zhang</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pattern Recognition 2025 (PII S0031320325012440)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition 2025 (PII S0031320325012440); no arXiv ID found; no GitHub found; ScienceDirect paywalled. Agent-extracted metrics (not from authoritative table): MVTec AD I-AUROC 99.7%, P-AUROC 98.9%, 16.18 MB, 32.41 FPS — do NOT rank until verified from paper PDF/HTML. Datasets: MVTec AD, MPDD, BTAD. Simulated abnormal samples + multi-scale memory fusion. [基於重構/多尺度記憶融合/合成異常訓練]</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0031320325012440</t>
         </is>
       </c>
     </row>
@@ -25634,7 +26020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27197,6 +27583,53 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>https://github.com/ShuaiLYU/REB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MVTec LOCO AD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 自監督 + 局部至全局圖卷積 (Self-supervised Local-to-Global Graph Conv)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SLSG (Self-supervised Local-to-Global Graph Convolution for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Minghui Yang, Jing Liu, Zhiwei Yang, Zhaoyang Wu</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pattern Recognition Vol.156 2024 (arXiv 2305.00398)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏳ Pending: Pattern Recognition Vol.156 2024 (PII S0031320324006137); arXiv 2305.00398 (access blocked); no GitHub code found; ScienceDirect paywalled. Datasets: MVTec AD, VisA, MVTec LOCO AD. Self-supervised learning + local-to-global graph convolution for feature embedding + one-class classification. [基於表徵/自監督圖卷積/局部至全局]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2305.00398</t>
         </is>
       </c>
     </row>
@@ -28582,7 +29015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimen